--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="329">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -664,10 +664,10 @@
     <t>['47']</t>
   </si>
   <si>
-    <t>['36', '56']</t>
+    <t>['8']</t>
   </si>
   <si>
-    <t>['8']</t>
+    <t>['36', '56']</t>
   </si>
   <si>
     <t>['10', '23']</t>
@@ -676,13 +676,13 @@
     <t>['22', '87']</t>
   </si>
   <si>
-    <t>['76', '90+10']</t>
-  </si>
-  <si>
     <t>['23', '85', '90+3']</t>
   </si>
   <si>
     <t>['42']</t>
+  </si>
+  <si>
+    <t>['76', '90+10']</t>
   </si>
   <si>
     <t>['1', '41']</t>
@@ -967,10 +967,10 @@
     <t>['31', '62']</t>
   </si>
   <si>
-    <t>['62']</t>
+    <t>['34', '52']</t>
   </si>
   <si>
-    <t>['34', '52']</t>
+    <t>['62']</t>
   </si>
   <si>
     <t>['30', '65']</t>
@@ -998,6 +998,9 @@
   </si>
   <si>
     <t>['25', '42']</t>
+  </si>
+  <si>
+    <t>['13', '26']</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP231"/>
+  <dimension ref="A1:BP232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2439,7 +2442,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -6353,7 +6356,7 @@
         <v>110</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>3.24</v>
@@ -6434,7 +6437,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ25">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -9315,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>0.91</v>
@@ -11790,7 +11793,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -12405,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>0.73</v>
@@ -15086,7 +15089,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ67">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -17967,7 +17970,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81">
         <v>0.55</v>
@@ -18382,7 +18385,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ83">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -21057,7 +21060,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96">
         <v>1.09</v>
@@ -21884,7 +21887,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ100">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -25592,7 +25595,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ118">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -25795,7 +25798,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ119">
         <v>1.33</v>
@@ -29094,7 +29097,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ135">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -30327,7 +30330,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -31769,7 +31772,7 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ148">
         <v>1.5</v>
@@ -33214,7 +33217,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ155">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -35889,7 +35892,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168">
         <v>1.27</v>
@@ -37746,7 +37749,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ177">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -40421,7 +40424,7 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ190">
         <v>1.09</v>
@@ -42690,7 +42693,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ201">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -43185,7 +43188,7 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>7509785</v>
+        <v>7509786</v>
       </c>
       <c r="C204" t="s">
         <v>68</v>
@@ -43200,19 +43203,19 @@
         <v>21</v>
       </c>
       <c r="G204" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H204" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I204">
         <v>1</v>
       </c>
       <c r="J204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L204">
         <v>1</v>
@@ -43224,31 +43227,31 @@
         <v>2</v>
       </c>
       <c r="O204" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="Q204">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R204">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S204">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="T204">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U204">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V204">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="W204">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X204">
         <v>11</v>
@@ -43257,85 +43260,85 @@
         <v>1.05</v>
       </c>
       <c r="Z204">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AA204">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="AB204">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="AC204">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AD204">
+        <v>6.5</v>
+      </c>
+      <c r="AE204">
+        <v>1.45</v>
+      </c>
+      <c r="AF204">
+        <v>2.6</v>
+      </c>
+      <c r="AG204">
+        <v>2.35</v>
+      </c>
+      <c r="AH204">
+        <v>1.53</v>
+      </c>
+      <c r="AI204">
+        <v>2.05</v>
+      </c>
+      <c r="AJ204">
+        <v>1.7</v>
+      </c>
+      <c r="AK204">
+        <v>1.38</v>
+      </c>
+      <c r="AL204">
+        <v>1.36</v>
+      </c>
+      <c r="AM204">
+        <v>1.5</v>
+      </c>
+      <c r="AN204">
+        <v>0.8</v>
+      </c>
+      <c r="AO204">
+        <v>1.11</v>
+      </c>
+      <c r="AP204">
+        <v>0.82</v>
+      </c>
+      <c r="AQ204">
+        <v>1.27</v>
+      </c>
+      <c r="AR204">
+        <v>1.39</v>
+      </c>
+      <c r="AS204">
+        <v>1.2</v>
+      </c>
+      <c r="AT204">
+        <v>2.59</v>
+      </c>
+      <c r="AU204">
+        <v>8</v>
+      </c>
+      <c r="AV204">
+        <v>4</v>
+      </c>
+      <c r="AW204">
+        <v>5</v>
+      </c>
+      <c r="AX204">
         <v>7</v>
       </c>
-      <c r="AE204">
-        <v>1.44</v>
-      </c>
-      <c r="AF204">
-        <v>2.7</v>
-      </c>
-      <c r="AG204">
-        <v>2.3</v>
-      </c>
-      <c r="AH204">
-        <v>1.55</v>
-      </c>
-      <c r="AI204">
-        <v>2.1</v>
-      </c>
-      <c r="AJ204">
-        <v>1.67</v>
-      </c>
-      <c r="AK204">
-        <v>1.19</v>
-      </c>
-      <c r="AL204">
-        <v>1.31</v>
-      </c>
-      <c r="AM204">
-        <v>1.93</v>
-      </c>
-      <c r="AN204">
-        <v>2.56</v>
-      </c>
-      <c r="AO204">
-        <v>1.4</v>
-      </c>
-      <c r="AP204">
-        <v>2.45</v>
-      </c>
-      <c r="AQ204">
-        <v>1.25</v>
-      </c>
-      <c r="AR204">
-        <v>1.74</v>
-      </c>
-      <c r="AS204">
-        <v>1.09</v>
-      </c>
-      <c r="AT204">
-        <v>2.83</v>
-      </c>
-      <c r="AU204">
-        <v>6</v>
-      </c>
-      <c r="AV204">
-        <v>3</v>
-      </c>
-      <c r="AW204">
-        <v>6</v>
-      </c>
-      <c r="AX204">
-        <v>1</v>
-      </c>
       <c r="AY204">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AZ204">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BA204">
         <v>7</v>
@@ -43347,43 +43350,43 @@
         <v>9</v>
       </c>
       <c r="BD204">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="BE204">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="BF204">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="BG204">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BH204">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="BI204">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="BJ204">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="BK204">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="BL204">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="BM204">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="BN204">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BO204">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="BP204">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="205" spans="1:68">
@@ -43430,7 +43433,7 @@
         <v>2</v>
       </c>
       <c r="O205" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P205" t="s">
         <v>102</v>
@@ -43511,7 +43514,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ205">
         <v>0.83</v>
@@ -43597,7 +43600,7 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>7509786</v>
+        <v>7509785</v>
       </c>
       <c r="C206" t="s">
         <v>68</v>
@@ -43612,19 +43615,19 @@
         <v>21</v>
       </c>
       <c r="G206" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H206" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I206">
         <v>1</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L206">
         <v>1</v>
@@ -43636,31 +43639,31 @@
         <v>2</v>
       </c>
       <c r="O206" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="Q206">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="R206">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S206">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="T206">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U206">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V206">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="W206">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X206">
         <v>11</v>
@@ -43669,85 +43672,85 @@
         <v>1.05</v>
       </c>
       <c r="Z206">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AA206">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="AB206">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="AC206">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AD206">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE206">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF206">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AG206">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH206">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI206">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AJ206">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK206">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AL206">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AM206">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AN206">
-        <v>0.8</v>
+        <v>2.56</v>
       </c>
       <c r="AO206">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>0.82</v>
+        <v>2.45</v>
       </c>
       <c r="AQ206">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR206">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="AS206">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT206">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AU206">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW206">
+        <v>6</v>
+      </c>
+      <c r="AX206">
+        <v>1</v>
+      </c>
+      <c r="AY206">
+        <v>16</v>
+      </c>
+      <c r="AZ206">
         <v>5</v>
-      </c>
-      <c r="AX206">
-        <v>7</v>
-      </c>
-      <c r="AY206">
-        <v>21</v>
-      </c>
-      <c r="AZ206">
-        <v>12</v>
       </c>
       <c r="BA206">
         <v>7</v>
@@ -43759,43 +43762,43 @@
         <v>9</v>
       </c>
       <c r="BD206">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="BE206">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="BF206">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="BG206">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="BH206">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="BI206">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="BJ206">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="BK206">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="BL206">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="BM206">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="BN206">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="BO206">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="BP206">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="207" spans="1:68">
@@ -44872,7 +44875,7 @@
         <v>3</v>
       </c>
       <c r="O212" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P212" t="s">
         <v>316</v>
@@ -45039,7 +45042,7 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>7509794</v>
+        <v>7509790</v>
       </c>
       <c r="C213" t="s">
         <v>68</v>
@@ -45054,70 +45057,70 @@
         <v>22</v>
       </c>
       <c r="G213" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H213" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I213">
         <v>0</v>
       </c>
       <c r="J213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N213">
         <v>3</v>
       </c>
       <c r="O213" t="s">
-        <v>220</v>
+        <v>112</v>
       </c>
       <c r="P213" t="s">
         <v>317</v>
       </c>
       <c r="Q213">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="R213">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S213">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T213">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U213">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V213">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="W213">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X213">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Y213">
         <v>1.06</v>
       </c>
       <c r="Z213">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA213">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AB213">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="AC213">
         <v>1.08</v>
@@ -45126,118 +45129,118 @@
         <v>7.5</v>
       </c>
       <c r="AE213">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF213">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG213">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AH213">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AI213">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AJ213">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AK213">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL213">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AM213">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AN213">
+        <v>1.2</v>
+      </c>
+      <c r="AO213">
+        <v>0.55</v>
+      </c>
+      <c r="AP213">
         <v>1.09</v>
       </c>
-      <c r="AO213">
-        <v>1.2</v>
-      </c>
-      <c r="AP213">
-        <v>1.25</v>
-      </c>
       <c r="AQ213">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AR213">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AS213">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT213">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AU213">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV213">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW213">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX213">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY213">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ213">
         <v>13</v>
       </c>
       <c r="BA213">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC213">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BD213">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BE213">
         <v>6.25</v>
       </c>
       <c r="BF213">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BG213">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="BH213">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BI213">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BJ213">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="BK213">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BL213">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BM213">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BN213">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="BO213">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BP213">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="214" spans="1:68">
@@ -45245,7 +45248,7 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>7509790</v>
+        <v>7509791</v>
       </c>
       <c r="C214" t="s">
         <v>68</v>
@@ -45260,172 +45263,172 @@
         <v>22</v>
       </c>
       <c r="G214" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H214" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J214">
         <v>1</v>
       </c>
       <c r="K214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N214">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O214" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="P214" t="s">
-        <v>318</v>
+        <v>110</v>
       </c>
       <c r="Q214">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R214">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S214">
+        <v>5</v>
+      </c>
+      <c r="T214">
+        <v>1.43</v>
+      </c>
+      <c r="U214">
+        <v>2.6</v>
+      </c>
+      <c r="V214">
+        <v>2.95</v>
+      </c>
+      <c r="W214">
+        <v>1.34</v>
+      </c>
+      <c r="X214">
+        <v>7.75</v>
+      </c>
+      <c r="Y214">
+        <v>1.07</v>
+      </c>
+      <c r="Z214">
+        <v>1.68</v>
+      </c>
+      <c r="AA214">
+        <v>3.28</v>
+      </c>
+      <c r="AB214">
+        <v>4.41</v>
+      </c>
+      <c r="AC214">
+        <v>1.07</v>
+      </c>
+      <c r="AD214">
+        <v>8</v>
+      </c>
+      <c r="AE214">
+        <v>1.36</v>
+      </c>
+      <c r="AF214">
+        <v>3.1</v>
+      </c>
+      <c r="AG214">
+        <v>1.96</v>
+      </c>
+      <c r="AH214">
+        <v>1.75</v>
+      </c>
+      <c r="AI214">
+        <v>1.98</v>
+      </c>
+      <c r="AJ214">
+        <v>1.72</v>
+      </c>
+      <c r="AK214">
+        <v>1.18</v>
+      </c>
+      <c r="AL214">
+        <v>1.27</v>
+      </c>
+      <c r="AM214">
+        <v>2.05</v>
+      </c>
+      <c r="AN214">
+        <v>1.3</v>
+      </c>
+      <c r="AO214">
+        <v>1</v>
+      </c>
+      <c r="AP214">
+        <v>1.42</v>
+      </c>
+      <c r="AQ214">
+        <v>0.91</v>
+      </c>
+      <c r="AR214">
+        <v>1.56</v>
+      </c>
+      <c r="AS214">
+        <v>1.29</v>
+      </c>
+      <c r="AT214">
+        <v>2.85</v>
+      </c>
+      <c r="AU214">
+        <v>11</v>
+      </c>
+      <c r="AV214">
         <v>4</v>
       </c>
-      <c r="T214">
-        <v>1.46</v>
-      </c>
-      <c r="U214">
-        <v>2.5</v>
-      </c>
-      <c r="V214">
-        <v>3.1</v>
-      </c>
-      <c r="W214">
-        <v>1.32</v>
-      </c>
-      <c r="X214">
-        <v>8.5</v>
-      </c>
-      <c r="Y214">
-        <v>1.06</v>
-      </c>
-      <c r="Z214">
-        <v>2.08</v>
-      </c>
-      <c r="AA214">
-        <v>3.04</v>
-      </c>
-      <c r="AB214">
-        <v>3.11</v>
-      </c>
-      <c r="AC214">
-        <v>1.08</v>
-      </c>
-      <c r="AD214">
-        <v>7.5</v>
-      </c>
-      <c r="AE214">
-        <v>1.4</v>
-      </c>
-      <c r="AF214">
-        <v>2.9</v>
-      </c>
-      <c r="AG214">
-        <v>2.11</v>
-      </c>
-      <c r="AH214">
-        <v>1.65</v>
-      </c>
-      <c r="AI214">
-        <v>1.9</v>
-      </c>
-      <c r="AJ214">
-        <v>1.77</v>
-      </c>
-      <c r="AK214">
-        <v>1.29</v>
-      </c>
-      <c r="AL214">
-        <v>1.32</v>
-      </c>
-      <c r="AM214">
-        <v>1.7</v>
-      </c>
-      <c r="AN214">
-        <v>1.2</v>
-      </c>
-      <c r="AO214">
-        <v>0.55</v>
-      </c>
-      <c r="AP214">
-        <v>1.09</v>
-      </c>
-      <c r="AQ214">
-        <v>0.75</v>
-      </c>
-      <c r="AR214">
-        <v>1.3</v>
-      </c>
-      <c r="AS214">
-        <v>1.1</v>
-      </c>
-      <c r="AT214">
-        <v>2.4</v>
-      </c>
-      <c r="AU214">
-        <v>7</v>
-      </c>
-      <c r="AV214">
-        <v>6</v>
-      </c>
       <c r="AW214">
+        <v>18</v>
+      </c>
+      <c r="AX214">
+        <v>5</v>
+      </c>
+      <c r="AY214">
+        <v>37</v>
+      </c>
+      <c r="AZ214">
+        <v>11</v>
+      </c>
+      <c r="BA214">
         <v>14</v>
       </c>
-      <c r="AX214">
-        <v>6</v>
-      </c>
-      <c r="AY214">
-        <v>24</v>
-      </c>
-      <c r="AZ214">
-        <v>13</v>
-      </c>
-      <c r="BA214">
-        <v>6</v>
-      </c>
       <c r="BB214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC214">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BD214">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="BE214">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF214">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="BG214">
         <v>1.46</v>
       </c>
       <c r="BH214">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BI214">
         <v>1.77</v>
       </c>
       <c r="BJ214">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BK214">
         <v>2.23</v>
@@ -45437,7 +45440,7 @@
         <v>2.9</v>
       </c>
       <c r="BN214">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BO214">
         <v>3.9</v>
@@ -45451,7 +45454,7 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>7509791</v>
+        <v>7509792</v>
       </c>
       <c r="C215" t="s">
         <v>68</v>
@@ -45466,190 +45469,190 @@
         <v>22</v>
       </c>
       <c r="G215" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H215" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I215">
         <v>1</v>
       </c>
       <c r="J215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M215">
         <v>1</v>
       </c>
       <c r="N215">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O215" t="s">
         <v>221</v>
       </c>
       <c r="P215" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="Q215">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R215">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S215">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="T215">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="U215">
+        <v>2.37</v>
+      </c>
+      <c r="V215">
+        <v>3.4</v>
+      </c>
+      <c r="W215">
+        <v>1.27</v>
+      </c>
+      <c r="X215">
+        <v>9.75</v>
+      </c>
+      <c r="Y215">
+        <v>1.04</v>
+      </c>
+      <c r="Z215">
+        <v>2</v>
+      </c>
+      <c r="AA215">
+        <v>2.96</v>
+      </c>
+      <c r="AB215">
+        <v>3.44</v>
+      </c>
+      <c r="AC215">
+        <v>1.1</v>
+      </c>
+      <c r="AD215">
+        <v>6.5</v>
+      </c>
+      <c r="AE215">
+        <v>1.48</v>
+      </c>
+      <c r="AF215">
         <v>2.6</v>
       </c>
-      <c r="V215">
-        <v>2.95</v>
-      </c>
-      <c r="W215">
-        <v>1.34</v>
-      </c>
-      <c r="X215">
-        <v>7.75</v>
-      </c>
-      <c r="Y215">
-        <v>1.07</v>
-      </c>
-      <c r="Z215">
-        <v>1.68</v>
-      </c>
-      <c r="AA215">
-        <v>3.28</v>
-      </c>
-      <c r="AB215">
-        <v>4.41</v>
-      </c>
-      <c r="AC215">
-        <v>1.07</v>
-      </c>
-      <c r="AD215">
-        <v>8</v>
-      </c>
-      <c r="AE215">
-        <v>1.36</v>
-      </c>
-      <c r="AF215">
-        <v>3.1</v>
-      </c>
       <c r="AG215">
-        <v>1.96</v>
+        <v>2.41</v>
       </c>
       <c r="AH215">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI215">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AJ215">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AK215">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AL215">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AM215">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AN215">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AO215">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP215">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AQ215">
         <v>0.91</v>
       </c>
       <c r="AR215">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AS215">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT215">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="AU215">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AV215">
         <v>4</v>
       </c>
       <c r="AW215">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX215">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY215">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AZ215">
+        <v>9</v>
+      </c>
+      <c r="BA215">
         <v>11</v>
       </c>
-      <c r="BA215">
-        <v>14</v>
-      </c>
       <c r="BB215">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC215">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD215">
+        <v>1.67</v>
+      </c>
+      <c r="BE215">
+        <v>6.25</v>
+      </c>
+      <c r="BF215">
+        <v>2.48</v>
+      </c>
+      <c r="BG215">
         <v>1.53</v>
       </c>
-      <c r="BE215">
-        <v>6.4</v>
-      </c>
-      <c r="BF215">
-        <v>2.8</v>
-      </c>
-      <c r="BG215">
-        <v>1.46</v>
-      </c>
       <c r="BH215">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BI215">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="BJ215">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BK215">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="BL215">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="BM215">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BN215">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="BO215">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP215">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="216" spans="1:68">
@@ -45657,7 +45660,7 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>7509792</v>
+        <v>7509794</v>
       </c>
       <c r="C216" t="s">
         <v>68</v>
@@ -45672,124 +45675,124 @@
         <v>22</v>
       </c>
       <c r="G216" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H216" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J216">
         <v>0</v>
       </c>
       <c r="K216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M216">
         <v>1</v>
       </c>
       <c r="N216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O216" t="s">
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="Q216">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="R216">
+        <v>1.98</v>
+      </c>
+      <c r="S216">
+        <v>3.75</v>
+      </c>
+      <c r="T216">
+        <v>1.47</v>
+      </c>
+      <c r="U216">
+        <v>2.45</v>
+      </c>
+      <c r="V216">
+        <v>3.2</v>
+      </c>
+      <c r="W216">
+        <v>1.3</v>
+      </c>
+      <c r="X216">
+        <v>8.75</v>
+      </c>
+      <c r="Y216">
+        <v>1.06</v>
+      </c>
+      <c r="Z216">
+        <v>2.2</v>
+      </c>
+      <c r="AA216">
+        <v>2.97</v>
+      </c>
+      <c r="AB216">
+        <v>2.94</v>
+      </c>
+      <c r="AC216">
+        <v>1.08</v>
+      </c>
+      <c r="AD216">
+        <v>7.5</v>
+      </c>
+      <c r="AE216">
+        <v>1.42</v>
+      </c>
+      <c r="AF216">
+        <v>2.8</v>
+      </c>
+      <c r="AG216">
+        <v>2.19</v>
+      </c>
+      <c r="AH216">
+        <v>1.6</v>
+      </c>
+      <c r="AI216">
         <v>1.95</v>
       </c>
-      <c r="S216">
-        <v>4.1</v>
-      </c>
-      <c r="T216">
-        <v>1.51</v>
-      </c>
-      <c r="U216">
-        <v>2.37</v>
-      </c>
-      <c r="V216">
-        <v>3.4</v>
-      </c>
-      <c r="W216">
-        <v>1.27</v>
-      </c>
-      <c r="X216">
-        <v>9.75</v>
-      </c>
-      <c r="Y216">
-        <v>1.04</v>
-      </c>
-      <c r="Z216">
-        <v>2</v>
-      </c>
-      <c r="AA216">
-        <v>2.96</v>
-      </c>
-      <c r="AB216">
-        <v>3.44</v>
-      </c>
-      <c r="AC216">
-        <v>1.1</v>
-      </c>
-      <c r="AD216">
-        <v>6.5</v>
-      </c>
-      <c r="AE216">
-        <v>1.48</v>
-      </c>
-      <c r="AF216">
-        <v>2.6</v>
-      </c>
-      <c r="AG216">
-        <v>2.41</v>
-      </c>
-      <c r="AH216">
-        <v>1.5</v>
-      </c>
-      <c r="AI216">
-        <v>2.1</v>
-      </c>
       <c r="AJ216">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AK216">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL216">
         <v>1.33</v>
       </c>
       <c r="AM216">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AN216">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="AO216">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AQ216">
-        <v>0.91</v>
+        <v>1.09</v>
       </c>
       <c r="AR216">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AS216">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AT216">
-        <v>2.53</v>
+        <v>2.95</v>
       </c>
       <c r="AU216">
         <v>5</v>
@@ -45798,64 +45801,64 @@
         <v>4</v>
       </c>
       <c r="AW216">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX216">
+        <v>8</v>
+      </c>
+      <c r="AY216">
+        <v>26</v>
+      </c>
+      <c r="AZ216">
+        <v>13</v>
+      </c>
+      <c r="BA216">
         <v>3</v>
       </c>
-      <c r="AY216">
-        <v>25</v>
-      </c>
-      <c r="AZ216">
-        <v>9</v>
-      </c>
-      <c r="BA216">
-        <v>11</v>
-      </c>
       <c r="BB216">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC216">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BD216">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BE216">
         <v>6.25</v>
       </c>
       <c r="BF216">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="BG216">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="BH216">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BI216">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="BJ216">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="BK216">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BL216">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="BM216">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BN216">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BO216">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP216">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="217" spans="1:68">
@@ -46069,7 +46072,7 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>7509796</v>
+        <v>7509789</v>
       </c>
       <c r="C218" t="s">
         <v>68</v>
@@ -46084,190 +46087,190 @@
         <v>22</v>
       </c>
       <c r="G218" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H218" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K218">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L218">
+        <v>0</v>
+      </c>
+      <c r="M218">
+        <v>0</v>
+      </c>
+      <c r="N218">
+        <v>0</v>
+      </c>
+      <c r="O218" t="s">
+        <v>102</v>
+      </c>
+      <c r="P218" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q218">
+        <v>3.75</v>
+      </c>
+      <c r="R218">
+        <v>2</v>
+      </c>
+      <c r="S218">
+        <v>3.2</v>
+      </c>
+      <c r="T218">
+        <v>1.5</v>
+      </c>
+      <c r="U218">
+        <v>2.5</v>
+      </c>
+      <c r="V218">
+        <v>3.4</v>
+      </c>
+      <c r="W218">
+        <v>1.3</v>
+      </c>
+      <c r="X218">
+        <v>10</v>
+      </c>
+      <c r="Y218">
+        <v>1.06</v>
+      </c>
+      <c r="Z218">
+        <v>3.21</v>
+      </c>
+      <c r="AA218">
+        <v>2.8</v>
+      </c>
+      <c r="AB218">
+        <v>2.46</v>
+      </c>
+      <c r="AC218">
+        <v>1.09</v>
+      </c>
+      <c r="AD218">
+        <v>7</v>
+      </c>
+      <c r="AE218">
+        <v>1.42</v>
+      </c>
+      <c r="AF218">
+        <v>2.8</v>
+      </c>
+      <c r="AG218">
+        <v>2.19</v>
+      </c>
+      <c r="AH218">
+        <v>1.6</v>
+      </c>
+      <c r="AI218">
+        <v>1.91</v>
+      </c>
+      <c r="AJ218">
+        <v>1.91</v>
+      </c>
+      <c r="AK218">
+        <v>1.51</v>
+      </c>
+      <c r="AL218">
+        <v>1.36</v>
+      </c>
+      <c r="AM218">
+        <v>1.38</v>
+      </c>
+      <c r="AN218">
+        <v>1.55</v>
+      </c>
+      <c r="AO218">
+        <v>1.7</v>
+      </c>
+      <c r="AP218">
+        <v>1.5</v>
+      </c>
+      <c r="AQ218">
+        <v>1.75</v>
+      </c>
+      <c r="AR218">
+        <v>1.25</v>
+      </c>
+      <c r="AS218">
+        <v>1.11</v>
+      </c>
+      <c r="AT218">
+        <v>2.36</v>
+      </c>
+      <c r="AU218">
+        <v>7</v>
+      </c>
+      <c r="AV218">
+        <v>2</v>
+      </c>
+      <c r="AW218">
+        <v>9</v>
+      </c>
+      <c r="AX218">
+        <v>10</v>
+      </c>
+      <c r="AY218">
+        <v>18</v>
+      </c>
+      <c r="AZ218">
+        <v>14</v>
+      </c>
+      <c r="BA218">
         <v>5</v>
-      </c>
-      <c r="M218">
-        <v>3</v>
-      </c>
-      <c r="N218">
-        <v>8</v>
-      </c>
-      <c r="O218" t="s">
-        <v>224</v>
-      </c>
-      <c r="P218" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q218">
-        <v>2.05</v>
-      </c>
-      <c r="R218">
-        <v>2.2</v>
-      </c>
-      <c r="S218">
-        <v>5.5</v>
-      </c>
-      <c r="T218">
-        <v>1.37</v>
-      </c>
-      <c r="U218">
-        <v>2.85</v>
-      </c>
-      <c r="V218">
-        <v>2.7</v>
-      </c>
-      <c r="W218">
-        <v>1.41</v>
-      </c>
-      <c r="X218">
-        <v>6.75</v>
-      </c>
-      <c r="Y218">
-        <v>1.09</v>
-      </c>
-      <c r="Z218">
-        <v>1.5</v>
-      </c>
-      <c r="AA218">
-        <v>4.1</v>
-      </c>
-      <c r="AB218">
-        <v>6.08</v>
-      </c>
-      <c r="AC218">
-        <v>1.05</v>
-      </c>
-      <c r="AD218">
-        <v>9.5</v>
-      </c>
-      <c r="AE218">
-        <v>1.28</v>
-      </c>
-      <c r="AF218">
-        <v>3.55</v>
-      </c>
-      <c r="AG218">
-        <v>1.8</v>
-      </c>
-      <c r="AH218">
-        <v>1.9</v>
-      </c>
-      <c r="AI218">
-        <v>1.98</v>
-      </c>
-      <c r="AJ218">
-        <v>1.73</v>
-      </c>
-      <c r="AK218">
-        <v>1.12</v>
-      </c>
-      <c r="AL218">
-        <v>1.22</v>
-      </c>
-      <c r="AM218">
-        <v>2.45</v>
-      </c>
-      <c r="AN218">
-        <v>2.5</v>
-      </c>
-      <c r="AO218">
-        <v>1</v>
-      </c>
-      <c r="AP218">
-        <v>2.55</v>
-      </c>
-      <c r="AQ218">
-        <v>1.08</v>
-      </c>
-      <c r="AR218">
-        <v>1.73</v>
-      </c>
-      <c r="AS218">
-        <v>1.2</v>
-      </c>
-      <c r="AT218">
-        <v>2.93</v>
-      </c>
-      <c r="AU218">
-        <v>8</v>
-      </c>
-      <c r="AV218">
-        <v>6</v>
-      </c>
-      <c r="AW218">
-        <v>13</v>
-      </c>
-      <c r="AX218">
-        <v>5</v>
-      </c>
-      <c r="AY218">
-        <v>27</v>
-      </c>
-      <c r="AZ218">
-        <v>11</v>
-      </c>
-      <c r="BA218">
-        <v>4</v>
       </c>
       <c r="BB218">
         <v>5</v>
       </c>
       <c r="BC218">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD218">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="BE218">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF218">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="BG218">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BH218">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BI218">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BJ218">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="BK218">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="BL218">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BM218">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="BN218">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO218">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP218">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="219" spans="1:68">
@@ -46275,7 +46278,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>7509789</v>
+        <v>7509793</v>
       </c>
       <c r="C219" t="s">
         <v>68</v>
@@ -46290,10 +46293,10 @@
         <v>22</v>
       </c>
       <c r="G219" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H219" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -46305,124 +46308,124 @@
         <v>0</v>
       </c>
       <c r="L219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219">
         <v>0</v>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="P219" t="s">
         <v>102</v>
       </c>
       <c r="Q219">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="R219">
         <v>2</v>
       </c>
       <c r="S219">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="T219">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U219">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V219">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="W219">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X219">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="Y219">
         <v>1.06</v>
       </c>
       <c r="Z219">
-        <v>3.21</v>
+        <v>1.93</v>
       </c>
       <c r="AA219">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AB219">
-        <v>2.46</v>
+        <v>4.18</v>
       </c>
       <c r="AC219">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AD219">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE219">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF219">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AG219">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AH219">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI219">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AJ219">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AK219">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AL219">
+        <v>1.3</v>
+      </c>
+      <c r="AM219">
+        <v>1.82</v>
+      </c>
+      <c r="AN219">
+        <v>1.5</v>
+      </c>
+      <c r="AO219">
         <v>1.36</v>
-      </c>
-      <c r="AM219">
-        <v>1.38</v>
-      </c>
-      <c r="AN219">
-        <v>1.55</v>
-      </c>
-      <c r="AO219">
-        <v>1.7</v>
       </c>
       <c r="AP219">
         <v>1.5</v>
       </c>
       <c r="AQ219">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AR219">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AS219">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AT219">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="AU219">
+        <v>5</v>
+      </c>
+      <c r="AV219">
+        <v>4</v>
+      </c>
+      <c r="AW219">
+        <v>6</v>
+      </c>
+      <c r="AX219">
         <v>7</v>
       </c>
-      <c r="AV219">
-        <v>2</v>
-      </c>
-      <c r="AW219">
-        <v>9</v>
-      </c>
-      <c r="AX219">
-        <v>10</v>
-      </c>
       <c r="AY219">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ219">
         <v>14</v>
@@ -46431,49 +46434,49 @@
         <v>5</v>
       </c>
       <c r="BB219">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC219">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD219">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="BE219">
         <v>6.4</v>
       </c>
       <c r="BF219">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="BG219">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="BH219">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BI219">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="BJ219">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BK219">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="BL219">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BM219">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BN219">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO219">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BP219">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="220" spans="1:68">
@@ -46481,7 +46484,7 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>7509793</v>
+        <v>7509796</v>
       </c>
       <c r="C220" t="s">
         <v>68</v>
@@ -46496,190 +46499,190 @@
         <v>22</v>
       </c>
       <c r="G220" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H220" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K220">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L220">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M220">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N220">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O220" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>102</v>
+        <v>320</v>
       </c>
       <c r="Q220">
+        <v>2.05</v>
+      </c>
+      <c r="R220">
+        <v>2.2</v>
+      </c>
+      <c r="S220">
+        <v>5.5</v>
+      </c>
+      <c r="T220">
+        <v>1.37</v>
+      </c>
+      <c r="U220">
+        <v>2.85</v>
+      </c>
+      <c r="V220">
+        <v>2.7</v>
+      </c>
+      <c r="W220">
+        <v>1.41</v>
+      </c>
+      <c r="X220">
+        <v>6.75</v>
+      </c>
+      <c r="Y220">
+        <v>1.09</v>
+      </c>
+      <c r="Z220">
+        <v>1.5</v>
+      </c>
+      <c r="AA220">
+        <v>4.1</v>
+      </c>
+      <c r="AB220">
+        <v>6.08</v>
+      </c>
+      <c r="AC220">
+        <v>1.05</v>
+      </c>
+      <c r="AD220">
+        <v>9.5</v>
+      </c>
+      <c r="AE220">
+        <v>1.28</v>
+      </c>
+      <c r="AF220">
+        <v>3.55</v>
+      </c>
+      <c r="AG220">
+        <v>1.8</v>
+      </c>
+      <c r="AH220">
+        <v>1.9</v>
+      </c>
+      <c r="AI220">
+        <v>1.98</v>
+      </c>
+      <c r="AJ220">
+        <v>1.73</v>
+      </c>
+      <c r="AK220">
+        <v>1.12</v>
+      </c>
+      <c r="AL220">
+        <v>1.22</v>
+      </c>
+      <c r="AM220">
+        <v>2.45</v>
+      </c>
+      <c r="AN220">
+        <v>2.5</v>
+      </c>
+      <c r="AO220">
+        <v>1</v>
+      </c>
+      <c r="AP220">
         <v>2.55</v>
       </c>
-      <c r="R220">
-        <v>2</v>
-      </c>
-      <c r="S220">
-        <v>4.2</v>
-      </c>
-      <c r="T220">
+      <c r="AQ220">
+        <v>1.08</v>
+      </c>
+      <c r="AR220">
+        <v>1.73</v>
+      </c>
+      <c r="AS220">
+        <v>1.2</v>
+      </c>
+      <c r="AT220">
+        <v>2.93</v>
+      </c>
+      <c r="AU220">
+        <v>8</v>
+      </c>
+      <c r="AV220">
+        <v>6</v>
+      </c>
+      <c r="AW220">
+        <v>13</v>
+      </c>
+      <c r="AX220">
+        <v>5</v>
+      </c>
+      <c r="AY220">
+        <v>27</v>
+      </c>
+      <c r="AZ220">
+        <v>11</v>
+      </c>
+      <c r="BA220">
+        <v>4</v>
+      </c>
+      <c r="BB220">
+        <v>5</v>
+      </c>
+      <c r="BC220">
+        <v>9</v>
+      </c>
+      <c r="BD220">
         <v>1.44</v>
       </c>
-      <c r="U220">
+      <c r="BE220">
+        <v>6.75</v>
+      </c>
+      <c r="BF220">
+        <v>3.15</v>
+      </c>
+      <c r="BG220">
+        <v>1.44</v>
+      </c>
+      <c r="BH220">
         <v>2.55</v>
       </c>
-      <c r="V220">
-        <v>3</v>
-      </c>
-      <c r="W220">
-        <v>1.33</v>
-      </c>
-      <c r="X220">
-        <v>8.25</v>
-      </c>
-      <c r="Y220">
-        <v>1.06</v>
-      </c>
-      <c r="Z220">
-        <v>1.93</v>
-      </c>
-      <c r="AA220">
-        <v>3.15</v>
-      </c>
-      <c r="AB220">
-        <v>4.18</v>
-      </c>
-      <c r="AC220">
-        <v>1.07</v>
-      </c>
-      <c r="AD220">
-        <v>8</v>
-      </c>
-      <c r="AE220">
+      <c r="BI220">
+        <v>1.73</v>
+      </c>
+      <c r="BJ220">
+        <v>1.98</v>
+      </c>
+      <c r="BK220">
+        <v>2.17</v>
+      </c>
+      <c r="BL220">
+        <v>1.6</v>
+      </c>
+      <c r="BM220">
+        <v>2.8</v>
+      </c>
+      <c r="BN220">
         <v>1.38</v>
       </c>
-      <c r="AF220">
-        <v>3</v>
-      </c>
-      <c r="AG220">
-        <v>2.07</v>
-      </c>
-      <c r="AH220">
-        <v>1.67</v>
-      </c>
-      <c r="AI220">
-        <v>1.93</v>
-      </c>
-      <c r="AJ220">
-        <v>1.75</v>
-      </c>
-      <c r="AK220">
-        <v>1.24</v>
-      </c>
-      <c r="AL220">
-        <v>1.3</v>
-      </c>
-      <c r="AM220">
-        <v>1.82</v>
-      </c>
-      <c r="AN220">
-        <v>1.5</v>
-      </c>
-      <c r="AO220">
-        <v>1.36</v>
-      </c>
-      <c r="AP220">
-        <v>1.64</v>
-      </c>
-      <c r="AQ220">
-        <v>1.25</v>
-      </c>
-      <c r="AR220">
-        <v>1.84</v>
-      </c>
-      <c r="AS220">
-        <v>1.05</v>
-      </c>
-      <c r="AT220">
-        <v>2.89</v>
-      </c>
-      <c r="AU220">
-        <v>5</v>
-      </c>
-      <c r="AV220">
-        <v>4</v>
-      </c>
-      <c r="AW220">
-        <v>6</v>
-      </c>
-      <c r="AX220">
-        <v>7</v>
-      </c>
-      <c r="AY220">
-        <v>13</v>
-      </c>
-      <c r="AZ220">
-        <v>14</v>
-      </c>
-      <c r="BA220">
-        <v>5</v>
-      </c>
-      <c r="BB220">
-        <v>7</v>
-      </c>
-      <c r="BC220">
-        <v>12</v>
-      </c>
-      <c r="BD220">
-        <v>1.65</v>
-      </c>
-      <c r="BE220">
-        <v>6.4</v>
-      </c>
-      <c r="BF220">
-        <v>2.55</v>
-      </c>
-      <c r="BG220">
-        <v>1.46</v>
-      </c>
-      <c r="BH220">
-        <v>2.5</v>
-      </c>
-      <c r="BI220">
-        <v>1.76</v>
-      </c>
-      <c r="BJ220">
-        <v>1.94</v>
-      </c>
-      <c r="BK220">
-        <v>2.23</v>
-      </c>
-      <c r="BL220">
-        <v>1.57</v>
-      </c>
-      <c r="BM220">
-        <v>2.9</v>
-      </c>
-      <c r="BN220">
-        <v>1.35</v>
-      </c>
       <c r="BO220">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BP220">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="221" spans="1:68">
@@ -47099,7 +47102,7 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>7509806</v>
+        <v>7509810</v>
       </c>
       <c r="C223" t="s">
         <v>68</v>
@@ -47114,46 +47117,46 @@
         <v>23</v>
       </c>
       <c r="G223" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H223" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="I223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K223">
         <v>2</v>
       </c>
       <c r="L223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M223">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N223">
         <v>3</v>
       </c>
       <c r="O223" t="s">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="P223" t="s">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="Q223">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R223">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S223">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T223">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U223">
         <v>2.3</v>
@@ -47171,13 +47174,13 @@
         <v>1.04</v>
       </c>
       <c r="Z223">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AA223">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB223">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AC223">
         <v>1.1</v>
@@ -47186,118 +47189,118 @@
         <v>6.5</v>
       </c>
       <c r="AE223">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF223">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AG223">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH223">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI223">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AJ223">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AK223">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL223">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AM223">
+        <v>1.66</v>
+      </c>
+      <c r="AN223">
+        <v>1.5</v>
+      </c>
+      <c r="AO223">
+        <v>0.55</v>
+      </c>
+      <c r="AP223">
+        <v>1.64</v>
+      </c>
+      <c r="AQ223">
+        <v>0.5</v>
+      </c>
+      <c r="AR223">
+        <v>1.25</v>
+      </c>
+      <c r="AS223">
+        <v>1.15</v>
+      </c>
+      <c r="AT223">
+        <v>2.4</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>2</v>
+      </c>
+      <c r="AW223">
+        <v>1</v>
+      </c>
+      <c r="AX223">
+        <v>13</v>
+      </c>
+      <c r="AY223">
+        <v>6</v>
+      </c>
+      <c r="AZ223">
+        <v>17</v>
+      </c>
+      <c r="BA223">
+        <v>2</v>
+      </c>
+      <c r="BB223">
+        <v>7</v>
+      </c>
+      <c r="BC223">
+        <v>9</v>
+      </c>
+      <c r="BD223">
+        <v>1.7</v>
+      </c>
+      <c r="BE223">
+        <v>6.4</v>
+      </c>
+      <c r="BF223">
+        <v>2.43</v>
+      </c>
+      <c r="BG223">
+        <v>1.46</v>
+      </c>
+      <c r="BH223">
+        <v>2.5</v>
+      </c>
+      <c r="BI223">
+        <v>1.76</v>
+      </c>
+      <c r="BJ223">
+        <v>1.95</v>
+      </c>
+      <c r="BK223">
+        <v>2.23</v>
+      </c>
+      <c r="BL223">
         <v>1.57</v>
       </c>
-      <c r="AN223">
-        <v>1</v>
-      </c>
-      <c r="AO223">
-        <v>0.91</v>
-      </c>
-      <c r="AP223">
-        <v>0.92</v>
-      </c>
-      <c r="AQ223">
-        <v>1.08</v>
-      </c>
-      <c r="AR223">
-        <v>1.39</v>
-      </c>
-      <c r="AS223">
-        <v>1.22</v>
-      </c>
-      <c r="AT223">
-        <v>2.61</v>
-      </c>
-      <c r="AU223">
-        <v>3</v>
-      </c>
-      <c r="AV223">
-        <v>5</v>
-      </c>
-      <c r="AW223">
-        <v>12</v>
-      </c>
-      <c r="AX223">
-        <v>8</v>
-      </c>
-      <c r="AY223">
-        <v>17</v>
-      </c>
-      <c r="AZ223">
-        <v>13</v>
-      </c>
-      <c r="BA223">
-        <v>5</v>
-      </c>
-      <c r="BB223">
-        <v>6</v>
-      </c>
-      <c r="BC223">
-        <v>11</v>
-      </c>
-      <c r="BD223">
-        <v>1.82</v>
-      </c>
-      <c r="BE223">
-        <v>6.25</v>
-      </c>
-      <c r="BF223">
-        <v>2.2</v>
-      </c>
-      <c r="BG223">
-        <v>1.5</v>
-      </c>
-      <c r="BH223">
-        <v>2.35</v>
-      </c>
-      <c r="BI223">
-        <v>1.86</v>
-      </c>
-      <c r="BJ223">
-        <v>1.82</v>
-      </c>
-      <c r="BK223">
-        <v>2.38</v>
-      </c>
-      <c r="BL223">
-        <v>1.5</v>
-      </c>
       <c r="BM223">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BN223">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BO223">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP223">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="224" spans="1:68">
@@ -47305,7 +47308,7 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>7509810</v>
+        <v>7509806</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -47320,46 +47323,46 @@
         <v>23</v>
       </c>
       <c r="G224" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H224" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="I224">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K224">
         <v>2</v>
       </c>
       <c r="L224">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N224">
         <v>3</v>
       </c>
       <c r="O224" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>172</v>
+        <v>323</v>
       </c>
       <c r="Q224">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R224">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S224">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="T224">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U224">
         <v>2.3</v>
@@ -47377,13 +47380,13 @@
         <v>1.04</v>
       </c>
       <c r="Z224">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AA224">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB224">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AC224">
         <v>1.1</v>
@@ -47392,118 +47395,118 @@
         <v>6.5</v>
       </c>
       <c r="AE224">
+        <v>1.53</v>
+      </c>
+      <c r="AF224">
+        <v>2.37</v>
+      </c>
+      <c r="AG224">
+        <v>2.55</v>
+      </c>
+      <c r="AH224">
+        <v>1.45</v>
+      </c>
+      <c r="AI224">
+        <v>2.1</v>
+      </c>
+      <c r="AJ224">
+        <v>1.65</v>
+      </c>
+      <c r="AK224">
+        <v>1.33</v>
+      </c>
+      <c r="AL224">
+        <v>1.36</v>
+      </c>
+      <c r="AM224">
+        <v>1.57</v>
+      </c>
+      <c r="AN224">
+        <v>1</v>
+      </c>
+      <c r="AO224">
+        <v>0.91</v>
+      </c>
+      <c r="AP224">
+        <v>0.92</v>
+      </c>
+      <c r="AQ224">
+        <v>1.08</v>
+      </c>
+      <c r="AR224">
+        <v>1.39</v>
+      </c>
+      <c r="AS224">
+        <v>1.22</v>
+      </c>
+      <c r="AT224">
+        <v>2.61</v>
+      </c>
+      <c r="AU224">
+        <v>3</v>
+      </c>
+      <c r="AV224">
+        <v>5</v>
+      </c>
+      <c r="AW224">
+        <v>12</v>
+      </c>
+      <c r="AX224">
+        <v>8</v>
+      </c>
+      <c r="AY224">
+        <v>17</v>
+      </c>
+      <c r="AZ224">
+        <v>13</v>
+      </c>
+      <c r="BA224">
+        <v>5</v>
+      </c>
+      <c r="BB224">
+        <v>6</v>
+      </c>
+      <c r="BC224">
+        <v>11</v>
+      </c>
+      <c r="BD224">
+        <v>1.82</v>
+      </c>
+      <c r="BE224">
+        <v>6.25</v>
+      </c>
+      <c r="BF224">
+        <v>2.2</v>
+      </c>
+      <c r="BG224">
         <v>1.5</v>
       </c>
-      <c r="AF224">
-        <v>2.45</v>
-      </c>
-      <c r="AG224">
-        <v>2.4</v>
-      </c>
-      <c r="AH224">
+      <c r="BH224">
+        <v>2.35</v>
+      </c>
+      <c r="BI224">
+        <v>1.86</v>
+      </c>
+      <c r="BJ224">
+        <v>1.82</v>
+      </c>
+      <c r="BK224">
+        <v>2.38</v>
+      </c>
+      <c r="BL224">
         <v>1.5</v>
       </c>
-      <c r="AI224">
-        <v>2.15</v>
-      </c>
-      <c r="AJ224">
-        <v>1.62</v>
-      </c>
-      <c r="AK224">
-        <v>1.29</v>
-      </c>
-      <c r="AL224">
-        <v>1.34</v>
-      </c>
-      <c r="AM224">
-        <v>1.66</v>
-      </c>
-      <c r="AN224">
-        <v>1.5</v>
-      </c>
-      <c r="AO224">
-        <v>0.55</v>
-      </c>
-      <c r="AP224">
-        <v>1.64</v>
-      </c>
-      <c r="AQ224">
-        <v>0.5</v>
-      </c>
-      <c r="AR224">
-        <v>1.25</v>
-      </c>
-      <c r="AS224">
-        <v>1.15</v>
-      </c>
-      <c r="AT224">
-        <v>2.4</v>
-      </c>
-      <c r="AU224">
-        <v>5</v>
-      </c>
-      <c r="AV224">
-        <v>2</v>
-      </c>
-      <c r="AW224">
-        <v>1</v>
-      </c>
-      <c r="AX224">
-        <v>13</v>
-      </c>
-      <c r="AY224">
-        <v>6</v>
-      </c>
-      <c r="AZ224">
-        <v>17</v>
-      </c>
-      <c r="BA224">
-        <v>2</v>
-      </c>
-      <c r="BB224">
-        <v>7</v>
-      </c>
-      <c r="BC224">
-        <v>9</v>
-      </c>
-      <c r="BD224">
-        <v>1.7</v>
-      </c>
-      <c r="BE224">
-        <v>6.4</v>
-      </c>
-      <c r="BF224">
-        <v>2.43</v>
-      </c>
-      <c r="BG224">
-        <v>1.46</v>
-      </c>
-      <c r="BH224">
-        <v>2.5</v>
-      </c>
-      <c r="BI224">
-        <v>1.76</v>
-      </c>
-      <c r="BJ224">
-        <v>1.95</v>
-      </c>
-      <c r="BK224">
-        <v>2.23</v>
-      </c>
-      <c r="BL224">
-        <v>1.57</v>
-      </c>
       <c r="BM224">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BN224">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BO224">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP224">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="225" spans="1:68">
@@ -48946,6 +48949,212 @@
       </c>
       <c r="BP231">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7509822</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45688.6875</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>89</v>
+      </c>
+      <c r="H232" t="s">
+        <v>73</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>2</v>
+      </c>
+      <c r="K232">
+        <v>2</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>2</v>
+      </c>
+      <c r="N232">
+        <v>3</v>
+      </c>
+      <c r="O232" t="s">
+        <v>112</v>
+      </c>
+      <c r="P232" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q232">
+        <v>3.1</v>
+      </c>
+      <c r="R232">
+        <v>2.05</v>
+      </c>
+      <c r="S232">
+        <v>3.75</v>
+      </c>
+      <c r="T232">
+        <v>1.44</v>
+      </c>
+      <c r="U232">
+        <v>2.63</v>
+      </c>
+      <c r="V232">
+        <v>3.4</v>
+      </c>
+      <c r="W232">
+        <v>1.3</v>
+      </c>
+      <c r="X232">
+        <v>10</v>
+      </c>
+      <c r="Y232">
+        <v>1.06</v>
+      </c>
+      <c r="Z232">
+        <v>2.36</v>
+      </c>
+      <c r="AA232">
+        <v>3.09</v>
+      </c>
+      <c r="AB232">
+        <v>3.28</v>
+      </c>
+      <c r="AC232">
+        <v>1.07</v>
+      </c>
+      <c r="AD232">
+        <v>8</v>
+      </c>
+      <c r="AE232">
+        <v>1.38</v>
+      </c>
+      <c r="AF232">
+        <v>2.95</v>
+      </c>
+      <c r="AG232">
+        <v>2.15</v>
+      </c>
+      <c r="AH232">
+        <v>1.7</v>
+      </c>
+      <c r="AI232">
+        <v>1.91</v>
+      </c>
+      <c r="AJ232">
+        <v>1.91</v>
+      </c>
+      <c r="AK232">
+        <v>1.34</v>
+      </c>
+      <c r="AL232">
+        <v>1.34</v>
+      </c>
+      <c r="AM232">
+        <v>1.58</v>
+      </c>
+      <c r="AN232">
+        <v>1.64</v>
+      </c>
+      <c r="AO232">
+        <v>1.64</v>
+      </c>
+      <c r="AP232">
+        <v>1.5</v>
+      </c>
+      <c r="AQ232">
+        <v>1.75</v>
+      </c>
+      <c r="AR232">
+        <v>1.79</v>
+      </c>
+      <c r="AS232">
+        <v>1.12</v>
+      </c>
+      <c r="AT232">
+        <v>2.91</v>
+      </c>
+      <c r="AU232">
+        <v>4</v>
+      </c>
+      <c r="AV232">
+        <v>3</v>
+      </c>
+      <c r="AW232">
+        <v>8</v>
+      </c>
+      <c r="AX232">
+        <v>6</v>
+      </c>
+      <c r="AY232">
+        <v>14</v>
+      </c>
+      <c r="AZ232">
+        <v>11</v>
+      </c>
+      <c r="BA232">
+        <v>6</v>
+      </c>
+      <c r="BB232">
+        <v>0</v>
+      </c>
+      <c r="BC232">
+        <v>6</v>
+      </c>
+      <c r="BD232">
+        <v>1.83</v>
+      </c>
+      <c r="BE232">
+        <v>6.4</v>
+      </c>
+      <c r="BF232">
+        <v>2.18</v>
+      </c>
+      <c r="BG232">
+        <v>1.46</v>
+      </c>
+      <c r="BH232">
+        <v>2.5</v>
+      </c>
+      <c r="BI232">
+        <v>1.75</v>
+      </c>
+      <c r="BJ232">
+        <v>1.95</v>
+      </c>
+      <c r="BK232">
+        <v>2</v>
+      </c>
+      <c r="BL232">
+        <v>1.8</v>
+      </c>
+      <c r="BM232">
+        <v>2.9</v>
+      </c>
+      <c r="BN232">
+        <v>1.35</v>
+      </c>
+      <c r="BO232">
+        <v>3.9</v>
+      </c>
+      <c r="BP232">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -709,6 +709,24 @@
     <t>['17', '88']</t>
   </si>
   <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['45', '71']</t>
+  </si>
+  <si>
+    <t>['3', '10', '38', '66']</t>
+  </si>
+  <si>
+    <t>['18', '38', '90']</t>
+  </si>
+  <si>
+    <t>['75']</t>
+  </si>
+  <si>
+    <t>['14', '50']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1001,6 +1019,15 @@
   </si>
   <si>
     <t>['13', '26']</t>
+  </si>
+  <si>
+    <t>['20', '33']</t>
+  </si>
+  <si>
+    <t>['30', '70']</t>
+  </si>
+  <si>
+    <t>['41', '45+6']</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1824,7 +1851,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1905,7 +1932,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2030,7 +2057,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2108,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.83</v>
@@ -2236,7 +2263,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2317,7 +2344,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2520,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6">
         <v>1.33</v>
@@ -2648,7 +2675,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3060,7 +3087,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3141,7 +3168,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3266,7 +3293,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3344,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -3553,7 +3580,7 @@
         <v>1</v>
       </c>
       <c r="AQ11">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3678,7 +3705,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3756,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
         <v>1.09</v>
@@ -3884,7 +3911,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -3962,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>0.55</v>
@@ -4090,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4168,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ14">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4708,7 +4735,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5198,10 +5225,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ19">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5326,7 +5353,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5407,7 +5434,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ20">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5610,10 +5637,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ21">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR21">
         <v>1.33</v>
@@ -5738,7 +5765,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6022,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23">
         <v>1.08</v>
@@ -6150,7 +6177,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6228,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24">
         <v>1</v>
@@ -6434,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ25">
         <v>1.75</v>
@@ -6643,7 +6670,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -6768,7 +6795,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7467,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR30">
         <v>1.65</v>
@@ -7673,7 +7700,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -7876,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
         <v>1.09</v>
@@ -8004,7 +8031,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8082,7 +8109,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
         <v>1.33</v>
@@ -8291,7 +8318,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ34">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8416,7 +8443,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8494,10 +8521,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ35">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8622,7 +8649,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8700,10 +8727,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -8909,7 +8936,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR37">
         <v>1.58</v>
@@ -9240,7 +9267,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9321,7 +9348,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9446,7 +9473,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9527,7 +9554,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ40">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR40">
         <v>1.5</v>
@@ -9652,7 +9679,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9730,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9858,7 +9885,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10142,7 +10169,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ43">
         <v>1.27</v>
@@ -10351,7 +10378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10682,7 +10709,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10969,7 +10996,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR47">
         <v>1.62</v>
@@ -11094,7 +11121,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11300,7 +11327,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11378,7 +11405,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11506,7 +11533,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11712,7 +11739,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11790,7 +11817,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51">
         <v>1.75</v>
@@ -11918,7 +11945,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -11996,10 +12023,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ52">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12411,7 +12438,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR54">
         <v>2.1</v>
@@ -12536,7 +12563,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12617,7 +12644,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR55">
         <v>1.42</v>
@@ -13026,7 +13053,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ57">
         <v>1.08</v>
@@ -13232,10 +13259,10 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR58">
         <v>1.74</v>
@@ -13360,7 +13387,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13772,7 +13799,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13978,7 +14005,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14056,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ62">
         <v>0.91</v>
@@ -14262,10 +14289,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14390,7 +14417,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14471,7 +14498,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14674,10 +14701,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14802,7 +14829,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -14883,7 +14910,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ66">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15214,7 +15241,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15292,7 +15319,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15498,7 +15525,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69">
         <v>1.27</v>
@@ -15626,7 +15653,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15704,7 +15731,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15832,7 +15859,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15913,7 +15940,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ71">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -16038,7 +16065,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16116,10 +16143,10 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR72">
         <v>0.97</v>
@@ -16244,7 +16271,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16450,7 +16477,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16528,7 +16555,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ74">
         <v>1.33</v>
@@ -16737,7 +16764,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ75">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16862,7 +16889,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16943,7 +16970,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ76">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR76">
         <v>1.44</v>
@@ -17068,7 +17095,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17274,7 +17301,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17355,7 +17382,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17480,7 +17507,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17686,7 +17713,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17764,7 +17791,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ80">
         <v>0.83</v>
@@ -18304,7 +18331,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18382,7 +18409,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.75</v>
@@ -18510,7 +18537,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18588,10 +18615,10 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR84">
         <v>1.72</v>
@@ -18794,10 +18821,10 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -18922,7 +18949,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19000,7 +19027,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19128,7 +19155,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19334,7 +19361,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19415,7 +19442,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ88">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -19540,7 +19567,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19618,10 +19645,10 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ89">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -19952,7 +19979,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20445,7 +20472,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR93">
         <v>1.54</v>
@@ -20651,7 +20678,7 @@
         <v>1</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -21063,7 +21090,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ96">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21266,7 +21293,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ97">
         <v>0.83</v>
@@ -21472,7 +21499,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ98">
         <v>1.33</v>
@@ -21678,7 +21705,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ99">
         <v>1.08</v>
@@ -22090,10 +22117,10 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ101">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22505,7 +22532,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ103">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR103">
         <v>1.86</v>
@@ -22630,7 +22657,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22836,7 +22863,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -22914,10 +22941,10 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -23123,7 +23150,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ106">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -23326,10 +23353,10 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ107">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23532,7 +23559,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ108">
         <v>0.91</v>
@@ -23738,7 +23765,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -24484,7 +24511,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24565,7 +24592,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.36</v>
@@ -24768,10 +24795,10 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
         <v>1.23</v>
@@ -24974,7 +25001,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ115">
         <v>0.91</v>
@@ -25308,7 +25335,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25514,7 +25541,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25926,7 +25953,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26004,10 +26031,10 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR120">
         <v>1.28</v>
@@ -26210,10 +26237,10 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ121">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26338,7 +26365,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26622,7 +26649,7 @@
         <v>2</v>
       </c>
       <c r="AP123">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -27034,7 +27061,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ125">
         <v>0.5</v>
@@ -27162,7 +27189,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27243,7 +27270,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ126">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -27449,7 +27476,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ127">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27574,7 +27601,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27655,7 +27682,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR128">
         <v>1.36</v>
@@ -27780,7 +27807,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27858,10 +27885,10 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ129">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR129">
         <v>1.41</v>
@@ -27986,7 +28013,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28192,7 +28219,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28270,7 +28297,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ131">
         <v>1.09</v>
@@ -28398,7 +28425,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28682,7 +28709,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ133">
         <v>0.55</v>
@@ -28891,7 +28918,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29094,7 +29121,7 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ135">
         <v>1.75</v>
@@ -29222,7 +29249,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29300,10 +29327,10 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29509,7 +29536,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ137">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.49</v>
@@ -29634,7 +29661,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30252,7 +30279,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30458,7 +30485,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30664,7 +30691,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30742,7 +30769,7 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ143">
         <v>1.27</v>
@@ -30870,7 +30897,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -30948,10 +30975,10 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31282,7 +31309,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31360,10 +31387,10 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ146">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR146">
         <v>1.34</v>
@@ -31775,7 +31802,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR148">
         <v>1.81</v>
@@ -31900,7 +31927,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -31981,7 +32008,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ149">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32106,7 +32133,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32187,7 +32214,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR150">
         <v>1.37</v>
@@ -32390,7 +32417,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ151">
         <v>0.5</v>
@@ -32518,7 +32545,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32805,7 +32832,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33008,7 +33035,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ154">
         <v>1</v>
@@ -33136,7 +33163,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33420,7 +33447,7 @@
         <v>0.71</v>
       </c>
       <c r="AP156">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156">
         <v>0.55</v>
@@ -33548,7 +33575,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33832,10 +33859,10 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR158">
         <v>1.22</v>
@@ -33960,7 +33987,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34041,7 +34068,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ159">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.43</v>
@@ -34372,7 +34399,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34450,7 +34477,7 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34784,7 +34811,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34862,10 +34889,10 @@
         <v>0.38</v>
       </c>
       <c r="AP163">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ163">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35196,7 +35223,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35483,7 +35510,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ166">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35686,10 +35713,10 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ167">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR167">
         <v>1.43</v>
@@ -35814,7 +35841,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36304,10 +36331,10 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36432,7 +36459,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36510,10 +36537,10 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ171">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
         <v>1.73</v>
@@ -36716,10 +36743,10 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ172">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR172">
         <v>1.72</v>
@@ -36922,7 +36949,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37334,10 +37361,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ175">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37746,7 +37773,7 @@
         <v>1.75</v>
       </c>
       <c r="AP177">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ177">
         <v>1.75</v>
@@ -37874,7 +37901,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -37952,10 +37979,10 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR178">
         <v>1.29</v>
@@ -38080,7 +38107,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38158,10 +38185,10 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ179">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR179">
         <v>1.23</v>
@@ -38367,7 +38394,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ180">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38985,7 +39012,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ183">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39110,7 +39137,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39191,7 +39218,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ184">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39316,7 +39343,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39394,7 +39421,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -39809,7 +39836,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ187">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -39934,7 +39961,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40552,7 +40579,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40630,7 +40657,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ191">
         <v>0.5</v>
@@ -40758,7 +40785,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40839,7 +40866,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR192">
         <v>1.54</v>
@@ -41045,7 +41072,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ193">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41248,10 +41275,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ194">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41454,10 +41481,10 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ195">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41660,7 +41687,7 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196">
         <v>1.08</v>
@@ -41788,7 +41815,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -41869,7 +41896,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ197">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR197">
         <v>1.37</v>
@@ -42072,7 +42099,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42278,7 +42305,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ199">
         <v>0.55</v>
@@ -42406,7 +42433,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42690,7 +42717,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ201">
         <v>1.75</v>
@@ -42818,7 +42845,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -42896,7 +42923,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202">
         <v>2</v>
@@ -43230,7 +43257,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43308,7 +43335,7 @@
         <v>1.11</v>
       </c>
       <c r="AP204">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AQ204">
         <v>1.27</v>
@@ -43642,7 +43669,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43723,7 +43750,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ206">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR206">
         <v>1.74</v>
@@ -43848,7 +43875,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -43929,7 +43956,7 @@
         <v>1</v>
       </c>
       <c r="AQ207">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -44054,7 +44081,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44135,7 +44162,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ208">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR208">
         <v>1.42</v>
@@ -44878,7 +44905,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -44956,10 +44983,10 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AQ212">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR212">
         <v>1.48</v>
@@ -45084,7 +45111,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45162,10 +45189,10 @@
         <v>0.55</v>
       </c>
       <c r="AP213">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ213">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR213">
         <v>1.3</v>
@@ -45371,7 +45398,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ214">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR214">
         <v>1.56</v>
@@ -45574,7 +45601,7 @@
         <v>0.9</v>
       </c>
       <c r="AP215">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ215">
         <v>0.91</v>
@@ -45702,7 +45729,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45780,10 +45807,10 @@
         <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ216">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR216">
         <v>1.68</v>
@@ -45908,7 +45935,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -45989,7 +46016,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46192,7 +46219,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ218">
         <v>1.75</v>
@@ -46401,7 +46428,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ219">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR219">
         <v>1.84</v>
@@ -46526,7 +46553,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46604,7 +46631,7 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ220">
         <v>1.08</v>
@@ -46732,7 +46759,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46810,10 +46837,10 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ221">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR221">
         <v>1.33</v>
@@ -46938,7 +46965,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47350,7 +47377,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47556,7 +47583,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47762,7 +47789,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47968,7 +47995,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48174,7 +48201,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48792,7 +48819,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -48998,7 +49025,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49154,6 +49181,1654 @@
         <v>3.9</v>
       </c>
       <c r="BP232">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7509824</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>81</v>
+      </c>
+      <c r="H233" t="s">
+        <v>79</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>1</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>1</v>
+      </c>
+      <c r="O233" t="s">
+        <v>231</v>
+      </c>
+      <c r="P233" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q233">
+        <v>2.75</v>
+      </c>
+      <c r="R233">
+        <v>2.05</v>
+      </c>
+      <c r="S233">
+        <v>4.5</v>
+      </c>
+      <c r="T233">
+        <v>1.5</v>
+      </c>
+      <c r="U233">
+        <v>2.5</v>
+      </c>
+      <c r="V233">
+        <v>3.4</v>
+      </c>
+      <c r="W233">
+        <v>1.3</v>
+      </c>
+      <c r="X233">
+        <v>10</v>
+      </c>
+      <c r="Y233">
+        <v>1.06</v>
+      </c>
+      <c r="Z233">
+        <v>2.09</v>
+      </c>
+      <c r="AA233">
+        <v>3.26</v>
+      </c>
+      <c r="AB233">
+        <v>4</v>
+      </c>
+      <c r="AC233">
+        <v>1.08</v>
+      </c>
+      <c r="AD233">
+        <v>7.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.4</v>
+      </c>
+      <c r="AF233">
+        <v>2.88</v>
+      </c>
+      <c r="AG233">
+        <v>2.05</v>
+      </c>
+      <c r="AH233">
+        <v>1.65</v>
+      </c>
+      <c r="AI233">
+        <v>1.95</v>
+      </c>
+      <c r="AJ233">
+        <v>1.8</v>
+      </c>
+      <c r="AK233">
+        <v>1.25</v>
+      </c>
+      <c r="AL233">
+        <v>1.31</v>
+      </c>
+      <c r="AM233">
+        <v>1.77</v>
+      </c>
+      <c r="AN233">
+        <v>0.91</v>
+      </c>
+      <c r="AO233">
+        <v>0.91</v>
+      </c>
+      <c r="AP233">
+        <v>1.08</v>
+      </c>
+      <c r="AQ233">
+        <v>0.83</v>
+      </c>
+      <c r="AR233">
+        <v>1.42</v>
+      </c>
+      <c r="AS233">
+        <v>1.27</v>
+      </c>
+      <c r="AT233">
+        <v>2.69</v>
+      </c>
+      <c r="AU233">
+        <v>3</v>
+      </c>
+      <c r="AV233">
+        <v>5</v>
+      </c>
+      <c r="AW233">
+        <v>8</v>
+      </c>
+      <c r="AX233">
+        <v>17</v>
+      </c>
+      <c r="AY233">
+        <v>15</v>
+      </c>
+      <c r="AZ233">
+        <v>24</v>
+      </c>
+      <c r="BA233">
+        <v>4</v>
+      </c>
+      <c r="BB233">
+        <v>8</v>
+      </c>
+      <c r="BC233">
+        <v>12</v>
+      </c>
+      <c r="BD233">
+        <v>1.71</v>
+      </c>
+      <c r="BE233">
+        <v>6.4</v>
+      </c>
+      <c r="BF233">
+        <v>2.4</v>
+      </c>
+      <c r="BG233">
+        <v>1.46</v>
+      </c>
+      <c r="BH233">
+        <v>2.5</v>
+      </c>
+      <c r="BI233">
+        <v>1.76</v>
+      </c>
+      <c r="BJ233">
+        <v>1.93</v>
+      </c>
+      <c r="BK233">
+        <v>2.23</v>
+      </c>
+      <c r="BL233">
+        <v>1.56</v>
+      </c>
+      <c r="BM233">
+        <v>2.9</v>
+      </c>
+      <c r="BN233">
+        <v>1.34</v>
+      </c>
+      <c r="BO233">
+        <v>3.9</v>
+      </c>
+      <c r="BP233">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7509825</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>84</v>
+      </c>
+      <c r="H234" t="s">
+        <v>88</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>0</v>
+      </c>
+      <c r="N234">
+        <v>2</v>
+      </c>
+      <c r="O234" t="s">
+        <v>232</v>
+      </c>
+      <c r="P234" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q234">
+        <v>2.2</v>
+      </c>
+      <c r="R234">
+        <v>2.25</v>
+      </c>
+      <c r="S234">
+        <v>5.5</v>
+      </c>
+      <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.75</v>
+      </c>
+      <c r="W234">
+        <v>1.4</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.08</v>
+      </c>
+      <c r="Z234">
+        <v>1.62</v>
+      </c>
+      <c r="AA234">
+        <v>4.2</v>
+      </c>
+      <c r="AB234">
+        <v>5.7</v>
+      </c>
+      <c r="AC234">
+        <v>1.05</v>
+      </c>
+      <c r="AD234">
+        <v>9.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.28</v>
+      </c>
+      <c r="AF234">
+        <v>3.65</v>
+      </c>
+      <c r="AG234">
+        <v>1.86</v>
+      </c>
+      <c r="AH234">
+        <v>1.95</v>
+      </c>
+      <c r="AI234">
+        <v>1.95</v>
+      </c>
+      <c r="AJ234">
+        <v>1.8</v>
+      </c>
+      <c r="AK234">
+        <v>1.15</v>
+      </c>
+      <c r="AL234">
+        <v>1.24</v>
+      </c>
+      <c r="AM234">
+        <v>2.25</v>
+      </c>
+      <c r="AN234">
+        <v>2.55</v>
+      </c>
+      <c r="AO234">
+        <v>1.25</v>
+      </c>
+      <c r="AP234">
+        <v>2.58</v>
+      </c>
+      <c r="AQ234">
+        <v>1.15</v>
+      </c>
+      <c r="AR234">
+        <v>1.78</v>
+      </c>
+      <c r="AS234">
+        <v>1.08</v>
+      </c>
+      <c r="AT234">
+        <v>2.86</v>
+      </c>
+      <c r="AU234">
+        <v>4</v>
+      </c>
+      <c r="AV234">
+        <v>6</v>
+      </c>
+      <c r="AW234">
+        <v>6</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>10</v>
+      </c>
+      <c r="AZ234">
+        <v>13</v>
+      </c>
+      <c r="BA234">
+        <v>5</v>
+      </c>
+      <c r="BB234">
+        <v>3</v>
+      </c>
+      <c r="BC234">
+        <v>8</v>
+      </c>
+      <c r="BD234">
+        <v>1.46</v>
+      </c>
+      <c r="BE234">
+        <v>6.5</v>
+      </c>
+      <c r="BF234">
+        <v>3.05</v>
+      </c>
+      <c r="BG234">
+        <v>1.44</v>
+      </c>
+      <c r="BH234">
+        <v>2.55</v>
+      </c>
+      <c r="BI234">
+        <v>1.73</v>
+      </c>
+      <c r="BJ234">
+        <v>1.98</v>
+      </c>
+      <c r="BK234">
+        <v>2.15</v>
+      </c>
+      <c r="BL234">
+        <v>1.63</v>
+      </c>
+      <c r="BM234">
+        <v>2.75</v>
+      </c>
+      <c r="BN234">
+        <v>1.38</v>
+      </c>
+      <c r="BO234">
+        <v>3.65</v>
+      </c>
+      <c r="BP234">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7509820</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>87</v>
+      </c>
+      <c r="H235" t="s">
+        <v>83</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>2</v>
+      </c>
+      <c r="K235">
+        <v>2</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>2</v>
+      </c>
+      <c r="O235" t="s">
+        <v>102</v>
+      </c>
+      <c r="P235" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q235">
+        <v>4.75</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>2.63</v>
+      </c>
+      <c r="T235">
+        <v>1.5</v>
+      </c>
+      <c r="U235">
+        <v>2.5</v>
+      </c>
+      <c r="V235">
+        <v>3.4</v>
+      </c>
+      <c r="W235">
+        <v>1.3</v>
+      </c>
+      <c r="X235">
+        <v>10</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>3.77</v>
+      </c>
+      <c r="AA235">
+        <v>3.31</v>
+      </c>
+      <c r="AB235">
+        <v>2.14</v>
+      </c>
+      <c r="AC235">
+        <v>1.08</v>
+      </c>
+      <c r="AD235">
+        <v>7.5</v>
+      </c>
+      <c r="AE235">
+        <v>1.42</v>
+      </c>
+      <c r="AF235">
+        <v>2.85</v>
+      </c>
+      <c r="AG235">
+        <v>2.15</v>
+      </c>
+      <c r="AH235">
+        <v>1.57</v>
+      </c>
+      <c r="AI235">
+        <v>2</v>
+      </c>
+      <c r="AJ235">
+        <v>1.75</v>
+      </c>
+      <c r="AK235">
+        <v>1.71</v>
+      </c>
+      <c r="AL235">
+        <v>1.32</v>
+      </c>
+      <c r="AM235">
+        <v>1.28</v>
+      </c>
+      <c r="AN235">
+        <v>1.09</v>
+      </c>
+      <c r="AO235">
+        <v>1.5</v>
+      </c>
+      <c r="AP235">
+        <v>1</v>
+      </c>
+      <c r="AQ235">
+        <v>1.62</v>
+      </c>
+      <c r="AR235">
+        <v>1.39</v>
+      </c>
+      <c r="AS235">
+        <v>1.39</v>
+      </c>
+      <c r="AT235">
+        <v>2.78</v>
+      </c>
+      <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
+        <v>6</v>
+      </c>
+      <c r="AW235">
+        <v>9</v>
+      </c>
+      <c r="AX235">
+        <v>9</v>
+      </c>
+      <c r="AY235">
+        <v>15</v>
+      </c>
+      <c r="AZ235">
+        <v>15</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>1</v>
+      </c>
+      <c r="BC235">
+        <v>5</v>
+      </c>
+      <c r="BD235">
+        <v>2.4</v>
+      </c>
+      <c r="BE235">
+        <v>6.4</v>
+      </c>
+      <c r="BF235">
+        <v>1.7</v>
+      </c>
+      <c r="BG235">
+        <v>1.47</v>
+      </c>
+      <c r="BH235">
+        <v>2.48</v>
+      </c>
+      <c r="BI235">
+        <v>1.79</v>
+      </c>
+      <c r="BJ235">
+        <v>1.9</v>
+      </c>
+      <c r="BK235">
+        <v>2.23</v>
+      </c>
+      <c r="BL235">
+        <v>1.56</v>
+      </c>
+      <c r="BM235">
+        <v>2.95</v>
+      </c>
+      <c r="BN235">
+        <v>1.33</v>
+      </c>
+      <c r="BO235">
+        <v>4.1</v>
+      </c>
+      <c r="BP235">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7509819</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45689.45833333334</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>78</v>
+      </c>
+      <c r="H236" t="s">
+        <v>76</v>
+      </c>
+      <c r="I236">
+        <v>3</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>4</v>
+      </c>
+      <c r="L236">
+        <v>4</v>
+      </c>
+      <c r="M236">
+        <v>2</v>
+      </c>
+      <c r="N236">
+        <v>6</v>
+      </c>
+      <c r="O236" t="s">
+        <v>233</v>
+      </c>
+      <c r="P236" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q236">
+        <v>3.4</v>
+      </c>
+      <c r="R236">
+        <v>2.05</v>
+      </c>
+      <c r="S236">
+        <v>3.4</v>
+      </c>
+      <c r="T236">
+        <v>1.44</v>
+      </c>
+      <c r="U236">
+        <v>2.63</v>
+      </c>
+      <c r="V236">
+        <v>3.4</v>
+      </c>
+      <c r="W236">
+        <v>1.3</v>
+      </c>
+      <c r="X236">
+        <v>10</v>
+      </c>
+      <c r="Y236">
+        <v>1.06</v>
+      </c>
+      <c r="Z236">
+        <v>2.71</v>
+      </c>
+      <c r="AA236">
+        <v>3.23</v>
+      </c>
+      <c r="AB236">
+        <v>2.81</v>
+      </c>
+      <c r="AC236">
+        <v>1.08</v>
+      </c>
+      <c r="AD236">
+        <v>7.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.4</v>
+      </c>
+      <c r="AF236">
+        <v>2.9</v>
+      </c>
+      <c r="AG236">
+        <v>2.05</v>
+      </c>
+      <c r="AH236">
+        <v>1.61</v>
+      </c>
+      <c r="AI236">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236">
+        <v>1.91</v>
+      </c>
+      <c r="AK236">
+        <v>1.44</v>
+      </c>
+      <c r="AL236">
+        <v>1.33</v>
+      </c>
+      <c r="AM236">
+        <v>1.47</v>
+      </c>
+      <c r="AN236">
+        <v>1.5</v>
+      </c>
+      <c r="AO236">
+        <v>0.73</v>
+      </c>
+      <c r="AP236">
+        <v>1.62</v>
+      </c>
+      <c r="AQ236">
+        <v>0.67</v>
+      </c>
+      <c r="AR236">
+        <v>1.29</v>
+      </c>
+      <c r="AS236">
+        <v>1.31</v>
+      </c>
+      <c r="AT236">
+        <v>2.6</v>
+      </c>
+      <c r="AU236">
+        <v>8</v>
+      </c>
+      <c r="AV236">
+        <v>5</v>
+      </c>
+      <c r="AW236">
+        <v>2</v>
+      </c>
+      <c r="AX236">
+        <v>9</v>
+      </c>
+      <c r="AY236">
+        <v>11</v>
+      </c>
+      <c r="AZ236">
+        <v>17</v>
+      </c>
+      <c r="BA236">
+        <v>1</v>
+      </c>
+      <c r="BB236">
+        <v>4</v>
+      </c>
+      <c r="BC236">
+        <v>5</v>
+      </c>
+      <c r="BD236">
+        <v>2</v>
+      </c>
+      <c r="BE236">
+        <v>6.25</v>
+      </c>
+      <c r="BF236">
+        <v>1.98</v>
+      </c>
+      <c r="BG236">
+        <v>1.44</v>
+      </c>
+      <c r="BH236">
+        <v>2.55</v>
+      </c>
+      <c r="BI236">
+        <v>1.73</v>
+      </c>
+      <c r="BJ236">
+        <v>1.98</v>
+      </c>
+      <c r="BK236">
+        <v>2.17</v>
+      </c>
+      <c r="BL236">
+        <v>1.6</v>
+      </c>
+      <c r="BM236">
+        <v>2.8</v>
+      </c>
+      <c r="BN236">
+        <v>1.36</v>
+      </c>
+      <c r="BO236">
+        <v>3.8</v>
+      </c>
+      <c r="BP236">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7509821</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45689.55208333334</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>80</v>
+      </c>
+      <c r="H237" t="s">
+        <v>85</v>
+      </c>
+      <c r="I237">
+        <v>2</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>3</v>
+      </c>
+      <c r="L237">
+        <v>3</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>4</v>
+      </c>
+      <c r="O237" t="s">
+        <v>234</v>
+      </c>
+      <c r="P237" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q237">
+        <v>2.4</v>
+      </c>
+      <c r="R237">
+        <v>2.1</v>
+      </c>
+      <c r="S237">
+        <v>5</v>
+      </c>
+      <c r="T237">
+        <v>1.44</v>
+      </c>
+      <c r="U237">
+        <v>2.63</v>
+      </c>
+      <c r="V237">
+        <v>3.25</v>
+      </c>
+      <c r="W237">
+        <v>1.33</v>
+      </c>
+      <c r="X237">
+        <v>9</v>
+      </c>
+      <c r="Y237">
+        <v>1.07</v>
+      </c>
+      <c r="Z237">
+        <v>1.81</v>
+      </c>
+      <c r="AA237">
+        <v>3.64</v>
+      </c>
+      <c r="AB237">
+        <v>4.8</v>
+      </c>
+      <c r="AC237">
+        <v>1.07</v>
+      </c>
+      <c r="AD237">
+        <v>8</v>
+      </c>
+      <c r="AE237">
+        <v>1.38</v>
+      </c>
+      <c r="AF237">
+        <v>3</v>
+      </c>
+      <c r="AG237">
+        <v>2.05</v>
+      </c>
+      <c r="AH237">
+        <v>1.65</v>
+      </c>
+      <c r="AI237">
+        <v>1.95</v>
+      </c>
+      <c r="AJ237">
+        <v>1.8</v>
+      </c>
+      <c r="AK237">
+        <v>1.19</v>
+      </c>
+      <c r="AL237">
+        <v>1.29</v>
+      </c>
+      <c r="AM237">
+        <v>1.98</v>
+      </c>
+      <c r="AN237">
+        <v>1.55</v>
+      </c>
+      <c r="AO237">
+        <v>0.75</v>
+      </c>
+      <c r="AP237">
+        <v>1.67</v>
+      </c>
+      <c r="AQ237">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR237">
+        <v>1.46</v>
+      </c>
+      <c r="AS237">
+        <v>1.12</v>
+      </c>
+      <c r="AT237">
+        <v>2.58</v>
+      </c>
+      <c r="AU237">
+        <v>7</v>
+      </c>
+      <c r="AV237">
+        <v>8</v>
+      </c>
+      <c r="AW237">
+        <v>2</v>
+      </c>
+      <c r="AX237">
+        <v>18</v>
+      </c>
+      <c r="AY237">
+        <v>9</v>
+      </c>
+      <c r="AZ237">
+        <v>34</v>
+      </c>
+      <c r="BA237">
+        <v>1</v>
+      </c>
+      <c r="BB237">
+        <v>5</v>
+      </c>
+      <c r="BC237">
+        <v>6</v>
+      </c>
+      <c r="BD237">
+        <v>1.55</v>
+      </c>
+      <c r="BE237">
+        <v>6.4</v>
+      </c>
+      <c r="BF237">
+        <v>2.75</v>
+      </c>
+      <c r="BG237">
+        <v>1.47</v>
+      </c>
+      <c r="BH237">
+        <v>2.48</v>
+      </c>
+      <c r="BI237">
+        <v>1.77</v>
+      </c>
+      <c r="BJ237">
+        <v>1.93</v>
+      </c>
+      <c r="BK237">
+        <v>2.23</v>
+      </c>
+      <c r="BL237">
+        <v>1.57</v>
+      </c>
+      <c r="BM237">
+        <v>2.9</v>
+      </c>
+      <c r="BN237">
+        <v>1.35</v>
+      </c>
+      <c r="BO237">
+        <v>3.9</v>
+      </c>
+      <c r="BP237">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7509823</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>74</v>
+      </c>
+      <c r="H238" t="s">
+        <v>82</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>1</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>1</v>
+      </c>
+      <c r="O238" t="s">
+        <v>228</v>
+      </c>
+      <c r="P238" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q238">
+        <v>3.75</v>
+      </c>
+      <c r="R238">
+        <v>2.05</v>
+      </c>
+      <c r="S238">
+        <v>3.1</v>
+      </c>
+      <c r="T238">
+        <v>1.44</v>
+      </c>
+      <c r="U238">
+        <v>2.63</v>
+      </c>
+      <c r="V238">
+        <v>3.25</v>
+      </c>
+      <c r="W238">
+        <v>1.33</v>
+      </c>
+      <c r="X238">
+        <v>10</v>
+      </c>
+      <c r="Y238">
+        <v>1.06</v>
+      </c>
+      <c r="Z238">
+        <v>3.28</v>
+      </c>
+      <c r="AA238">
+        <v>3.3</v>
+      </c>
+      <c r="AB238">
+        <v>2.34</v>
+      </c>
+      <c r="AC238">
+        <v>1.07</v>
+      </c>
+      <c r="AD238">
+        <v>8</v>
+      </c>
+      <c r="AE238">
+        <v>1.38</v>
+      </c>
+      <c r="AF238">
+        <v>3</v>
+      </c>
+      <c r="AG238">
+        <v>2.05</v>
+      </c>
+      <c r="AH238">
+        <v>1.61</v>
+      </c>
+      <c r="AI238">
+        <v>1.91</v>
+      </c>
+      <c r="AJ238">
+        <v>1.91</v>
+      </c>
+      <c r="AK238">
+        <v>1.6</v>
+      </c>
+      <c r="AL238">
+        <v>1.32</v>
+      </c>
+      <c r="AM238">
+        <v>1.34</v>
+      </c>
+      <c r="AN238">
+        <v>1.25</v>
+      </c>
+      <c r="AO238">
+        <v>1.82</v>
+      </c>
+      <c r="AP238">
+        <v>1.38</v>
+      </c>
+      <c r="AQ238">
+        <v>1.67</v>
+      </c>
+      <c r="AR238">
+        <v>1.73</v>
+      </c>
+      <c r="AS238">
+        <v>1.38</v>
+      </c>
+      <c r="AT238">
+        <v>3.11</v>
+      </c>
+      <c r="AU238">
+        <v>6</v>
+      </c>
+      <c r="AV238">
+        <v>6</v>
+      </c>
+      <c r="AW238">
+        <v>8</v>
+      </c>
+      <c r="AX238">
+        <v>15</v>
+      </c>
+      <c r="AY238">
+        <v>15</v>
+      </c>
+      <c r="AZ238">
+        <v>27</v>
+      </c>
+      <c r="BA238">
+        <v>1</v>
+      </c>
+      <c r="BB238">
+        <v>11</v>
+      </c>
+      <c r="BC238">
+        <v>12</v>
+      </c>
+      <c r="BD238">
+        <v>2.35</v>
+      </c>
+      <c r="BE238">
+        <v>6.75</v>
+      </c>
+      <c r="BF238">
+        <v>1.72</v>
+      </c>
+      <c r="BG238">
+        <v>1.32</v>
+      </c>
+      <c r="BH238">
+        <v>3.22</v>
+      </c>
+      <c r="BI238">
+        <v>1.56</v>
+      </c>
+      <c r="BJ238">
+        <v>2.33</v>
+      </c>
+      <c r="BK238">
+        <v>1.93</v>
+      </c>
+      <c r="BL238">
+        <v>1.82</v>
+      </c>
+      <c r="BM238">
+        <v>2.47</v>
+      </c>
+      <c r="BN238">
+        <v>1.51</v>
+      </c>
+      <c r="BO238">
+        <v>3.35</v>
+      </c>
+      <c r="BP238">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7509818</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F239">
+        <v>24</v>
+      </c>
+      <c r="G239" t="s">
+        <v>86</v>
+      </c>
+      <c r="H239" t="s">
+        <v>70</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239">
+        <v>2</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>235</v>
+      </c>
+      <c r="P239" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q239">
+        <v>3</v>
+      </c>
+      <c r="R239">
+        <v>2</v>
+      </c>
+      <c r="S239">
+        <v>4</v>
+      </c>
+      <c r="T239">
+        <v>1.5</v>
+      </c>
+      <c r="U239">
+        <v>2.5</v>
+      </c>
+      <c r="V239">
+        <v>3.4</v>
+      </c>
+      <c r="W239">
+        <v>1.3</v>
+      </c>
+      <c r="X239">
+        <v>10</v>
+      </c>
+      <c r="Y239">
+        <v>1.06</v>
+      </c>
+      <c r="Z239">
+        <v>2.32</v>
+      </c>
+      <c r="AA239">
+        <v>3.17</v>
+      </c>
+      <c r="AB239">
+        <v>3.47</v>
+      </c>
+      <c r="AC239">
+        <v>1.09</v>
+      </c>
+      <c r="AD239">
+        <v>7</v>
+      </c>
+      <c r="AE239">
+        <v>1.42</v>
+      </c>
+      <c r="AF239">
+        <v>2.8</v>
+      </c>
+      <c r="AG239">
+        <v>2.2</v>
+      </c>
+      <c r="AH239">
+        <v>1.55</v>
+      </c>
+      <c r="AI239">
+        <v>1.95</v>
+      </c>
+      <c r="AJ239">
+        <v>1.8</v>
+      </c>
+      <c r="AK239">
+        <v>1.32</v>
+      </c>
+      <c r="AL239">
+        <v>1.34</v>
+      </c>
+      <c r="AM239">
+        <v>1.62</v>
+      </c>
+      <c r="AN239">
+        <v>1.91</v>
+      </c>
+      <c r="AO239">
+        <v>1</v>
+      </c>
+      <c r="AP239">
+        <v>1.75</v>
+      </c>
+      <c r="AQ239">
+        <v>1.17</v>
+      </c>
+      <c r="AR239">
+        <v>1.34</v>
+      </c>
+      <c r="AS239">
+        <v>1.19</v>
+      </c>
+      <c r="AT239">
+        <v>2.53</v>
+      </c>
+      <c r="AU239">
+        <v>7</v>
+      </c>
+      <c r="AV239">
+        <v>4</v>
+      </c>
+      <c r="AW239">
+        <v>9</v>
+      </c>
+      <c r="AX239">
+        <v>14</v>
+      </c>
+      <c r="AY239">
+        <v>20</v>
+      </c>
+      <c r="AZ239">
+        <v>20</v>
+      </c>
+      <c r="BA239">
+        <v>5</v>
+      </c>
+      <c r="BB239">
+        <v>2</v>
+      </c>
+      <c r="BC239">
+        <v>7</v>
+      </c>
+      <c r="BD239">
+        <v>1.78</v>
+      </c>
+      <c r="BE239">
+        <v>6.5</v>
+      </c>
+      <c r="BF239">
+        <v>2.23</v>
+      </c>
+      <c r="BG239">
+        <v>1.32</v>
+      </c>
+      <c r="BH239">
+        <v>3.22</v>
+      </c>
+      <c r="BI239">
+        <v>1.56</v>
+      </c>
+      <c r="BJ239">
+        <v>2.33</v>
+      </c>
+      <c r="BK239">
+        <v>1.93</v>
+      </c>
+      <c r="BL239">
+        <v>1.82</v>
+      </c>
+      <c r="BM239">
+        <v>2.47</v>
+      </c>
+      <c r="BN239">
+        <v>1.51</v>
+      </c>
+      <c r="BO239">
+        <v>3.35</v>
+      </c>
+      <c r="BP239">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7509826</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45690.45833333334</v>
+      </c>
+      <c r="F240">
+        <v>24</v>
+      </c>
+      <c r="G240" t="s">
+        <v>72</v>
+      </c>
+      <c r="H240" t="s">
+        <v>77</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>2</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>2</v>
+      </c>
+      <c r="O240" t="s">
+        <v>236</v>
+      </c>
+      <c r="P240" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q240">
+        <v>3.25</v>
+      </c>
+      <c r="R240">
+        <v>1.91</v>
+      </c>
+      <c r="S240">
+        <v>4</v>
+      </c>
+      <c r="T240">
+        <v>1.57</v>
+      </c>
+      <c r="U240">
+        <v>2.25</v>
+      </c>
+      <c r="V240">
+        <v>3.75</v>
+      </c>
+      <c r="W240">
+        <v>1.25</v>
+      </c>
+      <c r="X240">
+        <v>13</v>
+      </c>
+      <c r="Y240">
+        <v>1.04</v>
+      </c>
+      <c r="Z240">
+        <v>2.56</v>
+      </c>
+      <c r="AA240">
+        <v>3.01</v>
+      </c>
+      <c r="AB240">
+        <v>3.2</v>
+      </c>
+      <c r="AC240">
+        <v>1.11</v>
+      </c>
+      <c r="AD240">
+        <v>6.25</v>
+      </c>
+      <c r="AE240">
+        <v>1.5</v>
+      </c>
+      <c r="AF240">
+        <v>2.3</v>
+      </c>
+      <c r="AG240">
+        <v>2.62</v>
+      </c>
+      <c r="AH240">
+        <v>1.43</v>
+      </c>
+      <c r="AI240">
+        <v>2.05</v>
+      </c>
+      <c r="AJ240">
+        <v>1.7</v>
+      </c>
+      <c r="AK240">
+        <v>1.37</v>
+      </c>
+      <c r="AL240">
+        <v>1.36</v>
+      </c>
+      <c r="AM240">
+        <v>1.52</v>
+      </c>
+      <c r="AN240">
+        <v>0.82</v>
+      </c>
+      <c r="AO240">
+        <v>1.09</v>
+      </c>
+      <c r="AP240">
+        <v>1</v>
+      </c>
+      <c r="AQ240">
+        <v>1</v>
+      </c>
+      <c r="AR240">
+        <v>1.42</v>
+      </c>
+      <c r="AS240">
+        <v>1.26</v>
+      </c>
+      <c r="AT240">
+        <v>2.68</v>
+      </c>
+      <c r="AU240">
+        <v>4</v>
+      </c>
+      <c r="AV240">
+        <v>7</v>
+      </c>
+      <c r="AW240">
+        <v>6</v>
+      </c>
+      <c r="AX240">
+        <v>11</v>
+      </c>
+      <c r="AY240">
+        <v>14</v>
+      </c>
+      <c r="AZ240">
+        <v>21</v>
+      </c>
+      <c r="BA240">
+        <v>8</v>
+      </c>
+      <c r="BB240">
+        <v>6</v>
+      </c>
+      <c r="BC240">
+        <v>14</v>
+      </c>
+      <c r="BD240">
+        <v>1.82</v>
+      </c>
+      <c r="BE240">
+        <v>6.25</v>
+      </c>
+      <c r="BF240">
+        <v>2.23</v>
+      </c>
+      <c r="BG240">
+        <v>1.44</v>
+      </c>
+      <c r="BH240">
+        <v>2.67</v>
+      </c>
+      <c r="BI240">
+        <v>1.74</v>
+      </c>
+      <c r="BJ240">
+        <v>2.02</v>
+      </c>
+      <c r="BK240">
+        <v>2.22</v>
+      </c>
+      <c r="BL240">
+        <v>1.62</v>
+      </c>
+      <c r="BM240">
+        <v>2.92</v>
+      </c>
+      <c r="BN240">
+        <v>1.38</v>
+      </c>
+      <c r="BO240">
+        <v>4.1</v>
+      </c>
+      <c r="BP240">
         <v>1.21</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,9 @@
     <t>['14', '50']</t>
   </si>
   <si>
+    <t>['45+4', '73']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1028,6 +1031,9 @@
   </si>
   <si>
     <t>['41', '45+6']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1851,7 +1857,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1929,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -2057,7 +2063,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2263,7 +2269,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2675,7 +2681,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3087,7 +3093,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3293,7 +3299,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3705,7 +3711,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3911,7 +3917,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4117,7 +4123,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4735,7 +4741,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4816,7 +4822,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ17">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5353,7 +5359,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5765,7 +5771,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5843,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -6177,7 +6183,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6795,7 +6801,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -8031,7 +8037,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8443,7 +8449,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8649,7 +8655,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9267,7 +9273,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9473,7 +9479,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9679,7 +9685,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9885,7 +9891,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10375,7 +10381,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ44">
         <v>0.6899999999999999</v>
@@ -10584,7 +10590,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ45">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR45">
         <v>1.98</v>
@@ -10709,7 +10715,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11121,7 +11127,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11327,7 +11333,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11533,7 +11539,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11739,7 +11745,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11945,7 +11951,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12563,7 +12569,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13387,7 +13393,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13799,7 +13805,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14005,7 +14011,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14086,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="AQ62">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR62">
         <v>1.33</v>
@@ -14417,7 +14423,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14495,7 +14501,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -14829,7 +14835,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15241,7 +15247,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15653,7 +15659,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15859,7 +15865,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16065,7 +16071,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16271,7 +16277,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16477,7 +16483,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16889,7 +16895,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17095,7 +17101,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17301,7 +17307,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17507,7 +17513,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17713,7 +17719,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18203,7 +18209,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ82">
         <v>1.27</v>
@@ -18331,7 +18337,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18537,7 +18543,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18949,7 +18955,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19155,7 +19161,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19361,7 +19367,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19567,7 +19573,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -19854,7 +19860,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ90">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -19979,7 +19985,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -22323,7 +22329,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ102">
         <v>0.5</v>
@@ -22657,7 +22663,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22863,7 +22869,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23562,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR108">
         <v>1.52</v>
@@ -24511,7 +24517,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24589,7 +24595,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -25004,7 +25010,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ115">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR115">
         <v>1.26</v>
@@ -25335,7 +25341,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25541,7 +25547,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25953,7 +25959,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26365,7 +26371,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -27189,7 +27195,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27601,7 +27607,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27807,7 +27813,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28013,7 +28019,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28219,7 +28225,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28425,7 +28431,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29249,7 +29255,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29661,7 +29667,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29739,7 +29745,7 @@
         <v>1.29</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ138">
         <v>1.33</v>
@@ -30154,7 +30160,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ140">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30279,7 +30285,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30485,7 +30491,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30691,7 +30697,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30897,7 +30903,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31309,7 +31315,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31927,7 +31933,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32133,7 +32139,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32545,7 +32551,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32829,7 +32835,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ153">
         <v>0.67</v>
@@ -33163,7 +33169,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33575,7 +33581,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33656,7 +33662,7 @@
         <v>1</v>
       </c>
       <c r="AQ157">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR157">
         <v>1.58</v>
@@ -33987,7 +33993,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34399,7 +34405,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34811,7 +34817,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35223,7 +35229,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35841,7 +35847,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36459,7 +36465,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37155,7 +37161,7 @@
         <v>0.75</v>
       </c>
       <c r="AP174">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ174">
         <v>1.08</v>
@@ -37570,7 +37576,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ176">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR176">
         <v>1.34</v>
@@ -37901,7 +37907,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38107,7 +38113,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -39137,7 +39143,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39343,7 +39349,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39961,7 +39967,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40579,7 +40585,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40785,7 +40791,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41069,7 +41075,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ193">
         <v>1.62</v>
@@ -41815,7 +41821,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42433,7 +42439,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42514,7 +42520,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ200">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42845,7 +42851,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43257,7 +43263,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43669,7 +43675,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43875,7 +43881,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44081,7 +44087,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44905,7 +44911,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45111,7 +45117,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45604,7 +45610,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ215">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45729,7 +45735,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45935,7 +45941,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46013,7 +46019,7 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ217">
         <v>1.17</v>
@@ -46553,7 +46559,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46759,7 +46765,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46965,7 +46971,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47377,7 +47383,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47583,7 +47589,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47789,7 +47795,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47995,7 +48001,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48201,7 +48207,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48819,7 +48825,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49025,7 +49031,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49643,7 +49649,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49849,7 +49855,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50467,7 +50473,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50830,6 +50836,212 @@
       </c>
       <c r="BP240">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7509817</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45690.55208333334</v>
+      </c>
+      <c r="F241">
+        <v>24</v>
+      </c>
+      <c r="G241" t="s">
+        <v>71</v>
+      </c>
+      <c r="H241" t="s">
+        <v>75</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>2</v>
+      </c>
+      <c r="M241">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>237</v>
+      </c>
+      <c r="P241" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q241">
+        <v>2.75</v>
+      </c>
+      <c r="R241">
+        <v>2</v>
+      </c>
+      <c r="S241">
+        <v>4.5</v>
+      </c>
+      <c r="T241">
+        <v>1.5</v>
+      </c>
+      <c r="U241">
+        <v>2.5</v>
+      </c>
+      <c r="V241">
+        <v>3.5</v>
+      </c>
+      <c r="W241">
+        <v>1.29</v>
+      </c>
+      <c r="X241">
+        <v>11</v>
+      </c>
+      <c r="Y241">
+        <v>1.05</v>
+      </c>
+      <c r="Z241">
+        <v>2.08</v>
+      </c>
+      <c r="AA241">
+        <v>3.2</v>
+      </c>
+      <c r="AB241">
+        <v>4.1</v>
+      </c>
+      <c r="AC241">
+        <v>1.09</v>
+      </c>
+      <c r="AD241">
+        <v>7</v>
+      </c>
+      <c r="AE241">
+        <v>1.44</v>
+      </c>
+      <c r="AF241">
+        <v>2.7</v>
+      </c>
+      <c r="AG241">
+        <v>2.25</v>
+      </c>
+      <c r="AH241">
+        <v>1.53</v>
+      </c>
+      <c r="AI241">
+        <v>2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.75</v>
+      </c>
+      <c r="AK241">
+        <v>1.26</v>
+      </c>
+      <c r="AL241">
+        <v>1.33</v>
+      </c>
+      <c r="AM241">
+        <v>1.73</v>
+      </c>
+      <c r="AN241">
+        <v>1.5</v>
+      </c>
+      <c r="AO241">
+        <v>0.91</v>
+      </c>
+      <c r="AP241">
+        <v>1.62</v>
+      </c>
+      <c r="AQ241">
+        <v>0.83</v>
+      </c>
+      <c r="AR241">
+        <v>1.41</v>
+      </c>
+      <c r="AS241">
+        <v>1.14</v>
+      </c>
+      <c r="AT241">
+        <v>2.55</v>
+      </c>
+      <c r="AU241">
+        <v>4</v>
+      </c>
+      <c r="AV241">
+        <v>7</v>
+      </c>
+      <c r="AW241">
+        <v>4</v>
+      </c>
+      <c r="AX241">
+        <v>16</v>
+      </c>
+      <c r="AY241">
+        <v>10</v>
+      </c>
+      <c r="AZ241">
+        <v>27</v>
+      </c>
+      <c r="BA241">
+        <v>3</v>
+      </c>
+      <c r="BB241">
+        <v>6</v>
+      </c>
+      <c r="BC241">
+        <v>9</v>
+      </c>
+      <c r="BD241">
+        <v>1.61</v>
+      </c>
+      <c r="BE241">
+        <v>6.4</v>
+      </c>
+      <c r="BF241">
+        <v>2.55</v>
+      </c>
+      <c r="BG241">
+        <v>1.38</v>
+      </c>
+      <c r="BH241">
+        <v>2.8</v>
+      </c>
+      <c r="BI241">
+        <v>1.64</v>
+      </c>
+      <c r="BJ241">
+        <v>2.1</v>
+      </c>
+      <c r="BK241">
+        <v>2.02</v>
+      </c>
+      <c r="BL241">
+        <v>1.7</v>
+      </c>
+      <c r="BM241">
+        <v>2.55</v>
+      </c>
+      <c r="BN241">
+        <v>1.44</v>
+      </c>
+      <c r="BO241">
+        <v>3.3</v>
+      </c>
+      <c r="BP241">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1395,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -3998,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ15">
         <v>1.33</v>
@@ -9148,7 +9148,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ38">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR38">
         <v>1.18</v>
@@ -10587,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45">
         <v>0.83</v>
@@ -12856,7 +12856,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -15943,7 +15943,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ71">
         <v>1.67</v>
@@ -18006,7 +18006,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -19239,7 +19239,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ87">
         <v>2</v>
@@ -20890,7 +20890,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ95">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -22535,7 +22535,7 @@
         <v>1.4</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ103">
         <v>1.62</v>
@@ -25422,7 +25422,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -27273,7 +27273,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ126">
         <v>0.83</v>
@@ -28718,7 +28718,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ133">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR133">
         <v>1.46</v>
@@ -31187,7 +31187,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ145">
         <v>1.09</v>
@@ -33456,7 +33456,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -36131,7 +36131,7 @@
         <v>0.5</v>
       </c>
       <c r="AP169">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ169">
         <v>0.5</v>
@@ -40045,7 +40045,7 @@
         <v>0.89</v>
       </c>
       <c r="AP188">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ188">
         <v>0.83</v>
@@ -40254,7 +40254,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ189">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR189">
         <v>1.33</v>
@@ -42314,7 +42314,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ199">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR199">
         <v>1.22</v>
@@ -44577,7 +44577,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ210">
         <v>1</v>
@@ -48285,7 +48285,7 @@
         <v>1.1</v>
       </c>
       <c r="AP228">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ228">
         <v>1.27</v>
@@ -48494,7 +48494,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ229">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -51042,6 +51042,212 @@
       </c>
       <c r="BP241">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7509827</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45695.6875</v>
+      </c>
+      <c r="F242">
+        <v>25</v>
+      </c>
+      <c r="G242" t="s">
+        <v>70</v>
+      </c>
+      <c r="H242" t="s">
+        <v>74</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242" t="s">
+        <v>102</v>
+      </c>
+      <c r="P242" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q242">
+        <v>3.2</v>
+      </c>
+      <c r="R242">
+        <v>2.05</v>
+      </c>
+      <c r="S242">
+        <v>3.6</v>
+      </c>
+      <c r="T242">
+        <v>1.44</v>
+      </c>
+      <c r="U242">
+        <v>2.63</v>
+      </c>
+      <c r="V242">
+        <v>3.25</v>
+      </c>
+      <c r="W242">
+        <v>1.33</v>
+      </c>
+      <c r="X242">
+        <v>10</v>
+      </c>
+      <c r="Y242">
+        <v>1.06</v>
+      </c>
+      <c r="Z242">
+        <v>2.49</v>
+      </c>
+      <c r="AA242">
+        <v>3.25</v>
+      </c>
+      <c r="AB242">
+        <v>3.06</v>
+      </c>
+      <c r="AC242">
+        <v>1.07</v>
+      </c>
+      <c r="AD242">
+        <v>8</v>
+      </c>
+      <c r="AE242">
+        <v>1.36</v>
+      </c>
+      <c r="AF242">
+        <v>2.85</v>
+      </c>
+      <c r="AG242">
+        <v>2</v>
+      </c>
+      <c r="AH242">
+        <v>1.65</v>
+      </c>
+      <c r="AI242">
+        <v>1.91</v>
+      </c>
+      <c r="AJ242">
+        <v>1.91</v>
+      </c>
+      <c r="AK242">
+        <v>1.39</v>
+      </c>
+      <c r="AL242">
+        <v>1.33</v>
+      </c>
+      <c r="AM242">
+        <v>1.53</v>
+      </c>
+      <c r="AN242">
+        <v>1.17</v>
+      </c>
+      <c r="AO242">
+        <v>0.55</v>
+      </c>
+      <c r="AP242">
+        <v>1.15</v>
+      </c>
+      <c r="AQ242">
+        <v>0.58</v>
+      </c>
+      <c r="AR242">
+        <v>1.65</v>
+      </c>
+      <c r="AS242">
+        <v>1.09</v>
+      </c>
+      <c r="AT242">
+        <v>2.74</v>
+      </c>
+      <c r="AU242">
+        <v>2</v>
+      </c>
+      <c r="AV242">
+        <v>3</v>
+      </c>
+      <c r="AW242">
+        <v>9</v>
+      </c>
+      <c r="AX242">
+        <v>5</v>
+      </c>
+      <c r="AY242">
+        <v>12</v>
+      </c>
+      <c r="AZ242">
+        <v>8</v>
+      </c>
+      <c r="BA242">
+        <v>3</v>
+      </c>
+      <c r="BB242">
+        <v>2</v>
+      </c>
+      <c r="BC242">
+        <v>5</v>
+      </c>
+      <c r="BD242">
+        <v>1.88</v>
+      </c>
+      <c r="BE242">
+        <v>6.4</v>
+      </c>
+      <c r="BF242">
+        <v>2.15</v>
+      </c>
+      <c r="BG242">
+        <v>1.46</v>
+      </c>
+      <c r="BH242">
+        <v>2.5</v>
+      </c>
+      <c r="BI242">
+        <v>1.7</v>
+      </c>
+      <c r="BJ242">
+        <v>2.05</v>
+      </c>
+      <c r="BK242">
+        <v>2.2</v>
+      </c>
+      <c r="BL242">
+        <v>1.58</v>
+      </c>
+      <c r="BM242">
+        <v>2.88</v>
+      </c>
+      <c r="BN242">
+        <v>1.35</v>
+      </c>
+      <c r="BO242">
+        <v>3.8</v>
+      </c>
+      <c r="BP242">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="341">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['45+4', '73']</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -860,9 +863,6 @@
   </si>
   <si>
     <t>['3', '73']</t>
-  </si>
-  <si>
-    <t>['69']</t>
   </si>
   <si>
     <t>['14', '22', '55', '61', '88']</t>
@@ -1034,6 +1034,9 @@
   </si>
   <si>
     <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['19', '54', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1857,7 +1860,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2063,7 +2066,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2269,7 +2272,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2681,7 +2684,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2968,7 +2971,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3093,7 +3096,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3299,7 +3302,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3380,7 +3383,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3583,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ11">
         <v>1.67</v>
@@ -3711,7 +3714,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3917,7 +3920,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4123,7 +4126,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4616,7 +4619,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4741,7 +4744,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5359,7 +5362,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5437,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ20">
         <v>0.83</v>
@@ -5771,7 +5774,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5852,7 +5855,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -6183,7 +6186,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6801,7 +6804,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7294,7 +7297,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ29">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR29">
         <v>1.89</v>
@@ -7497,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ30">
         <v>1.62</v>
@@ -8037,7 +8040,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8449,7 +8452,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8655,7 +8658,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9145,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38">
         <v>0.58</v>
@@ -9273,7 +9276,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9479,7 +9482,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9685,7 +9688,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9766,7 +9769,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR41">
         <v>1.16</v>
@@ -9891,7 +9894,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10178,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="AQ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR43">
         <v>1.15</v>
@@ -10715,7 +10718,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11127,7 +11130,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11333,7 +11336,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11414,7 +11417,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -11539,7 +11542,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11617,7 +11620,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11745,7 +11748,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11951,7 +11954,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12235,10 +12238,10 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -12569,7 +12572,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13393,7 +13396,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13677,7 +13680,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ60">
         <v>1.33</v>
@@ -13805,7 +13808,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13886,7 +13889,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR61">
         <v>1.42</v>
@@ -14011,7 +14014,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14423,7 +14426,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14835,7 +14838,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15247,7 +15250,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15534,7 +15537,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR69">
         <v>1.8</v>
@@ -15659,7 +15662,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15865,7 +15868,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16071,7 +16074,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16277,7 +16280,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16358,7 +16361,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16483,7 +16486,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16895,7 +16898,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17101,7 +17104,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17179,7 +17182,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77">
         <v>1.08</v>
@@ -17307,7 +17310,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17385,7 +17388,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ78">
         <v>1.17</v>
@@ -17513,7 +17516,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17719,7 +17722,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18212,7 +18215,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ82">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR82">
         <v>1.28</v>
@@ -18337,7 +18340,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18543,7 +18546,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18955,7 +18958,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19161,7 +19164,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19242,7 +19245,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19367,7 +19370,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19573,7 +19576,7 @@
         <v>150</v>
       </c>
       <c r="P89" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="Q89">
         <v>2.88</v>
@@ -20681,7 +20684,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ94">
         <v>1.15</v>
@@ -22332,7 +22335,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22744,7 +22747,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23977,7 +23980,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24186,7 +24189,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ111">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR111">
         <v>1.35</v>
@@ -25341,7 +25344,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25419,7 +25422,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ117">
         <v>0.58</v>
@@ -25959,7 +25962,7 @@
         <v>102</v>
       </c>
       <c r="P120" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="Q120">
         <v>2.4</v>
@@ -26658,7 +26661,7 @@
         <v>1</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -27070,7 +27073,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ125">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR125">
         <v>1.55</v>
@@ -27479,7 +27482,7 @@
         <v>1.67</v>
       </c>
       <c r="AP127">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -28100,7 +28103,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ130">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR130">
         <v>1.24</v>
@@ -28509,7 +28512,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ132">
         <v>0.83</v>
@@ -30285,7 +30288,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30572,7 +30575,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ142">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30778,7 +30781,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ143">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR143">
         <v>1.37</v>
@@ -31599,7 +31602,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ147">
         <v>0.83</v>
@@ -32426,7 +32429,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ151">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR151">
         <v>1.67</v>
@@ -33247,7 +33250,7 @@
         <v>1.57</v>
       </c>
       <c r="AP155">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ155">
         <v>1.75</v>
@@ -33659,7 +33662,7 @@
         <v>0.71</v>
       </c>
       <c r="AP157">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ157">
         <v>0.83</v>
@@ -35310,7 +35313,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ165">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35928,7 +35931,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ168">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -36134,7 +36137,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ169">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -37573,7 +37576,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ176">
         <v>0.83</v>
@@ -37907,7 +37910,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38812,7 +38815,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ182">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39633,10 +39636,10 @@
         <v>1.13</v>
       </c>
       <c r="AP186">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ186">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR186">
         <v>1.56</v>
@@ -40666,7 +40669,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ191">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR191">
         <v>1.37</v>
@@ -41899,7 +41902,7 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ197">
         <v>1</v>
@@ -42932,7 +42935,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ202">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR202">
         <v>1.7</v>
@@ -43344,7 +43347,7 @@
         <v>1</v>
       </c>
       <c r="AQ204">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR204">
         <v>1.39</v>
@@ -43675,7 +43678,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43959,7 +43962,7 @@
         <v>0.5</v>
       </c>
       <c r="AP207">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ207">
         <v>0.6899999999999999</v>
@@ -44786,7 +44789,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR211">
         <v>1.37</v>
@@ -47052,7 +47055,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ222">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR222">
         <v>1.73</v>
@@ -47258,7 +47261,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ223">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR223">
         <v>1.25</v>
@@ -47795,7 +47798,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47873,7 +47876,7 @@
         <v>1.18</v>
       </c>
       <c r="AP226">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ226">
         <v>1.33</v>
@@ -48079,7 +48082,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ227">
         <v>1</v>
@@ -48288,7 +48291,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ228">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -51248,6 +51251,624 @@
       </c>
       <c r="BP242">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7509832</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>85</v>
+      </c>
+      <c r="H243" t="s">
+        <v>84</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>3</v>
+      </c>
+      <c r="N243">
+        <v>3</v>
+      </c>
+      <c r="O243" t="s">
+        <v>102</v>
+      </c>
+      <c r="P243" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q243">
+        <v>4.75</v>
+      </c>
+      <c r="R243">
+        <v>2.25</v>
+      </c>
+      <c r="S243">
+        <v>2.3</v>
+      </c>
+      <c r="T243">
+        <v>1.36</v>
+      </c>
+      <c r="U243">
+        <v>3</v>
+      </c>
+      <c r="V243">
+        <v>2.63</v>
+      </c>
+      <c r="W243">
+        <v>1.44</v>
+      </c>
+      <c r="X243">
+        <v>7</v>
+      </c>
+      <c r="Y243">
+        <v>1.1</v>
+      </c>
+      <c r="Z243">
+        <v>4.7</v>
+      </c>
+      <c r="AA243">
+        <v>3.92</v>
+      </c>
+      <c r="AB243">
+        <v>1.76</v>
+      </c>
+      <c r="AC243">
+        <v>1.05</v>
+      </c>
+      <c r="AD243">
+        <v>9.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.23</v>
+      </c>
+      <c r="AF243">
+        <v>3.8</v>
+      </c>
+      <c r="AG243">
+        <v>1.81</v>
+      </c>
+      <c r="AH243">
+        <v>2.01</v>
+      </c>
+      <c r="AI243">
+        <v>1.75</v>
+      </c>
+      <c r="AJ243">
+        <v>2</v>
+      </c>
+      <c r="AK243">
+        <v>1.98</v>
+      </c>
+      <c r="AL243">
+        <v>1.26</v>
+      </c>
+      <c r="AM243">
+        <v>1.21</v>
+      </c>
+      <c r="AN243">
+        <v>1.73</v>
+      </c>
+      <c r="AO243">
+        <v>2</v>
+      </c>
+      <c r="AP243">
+        <v>1.58</v>
+      </c>
+      <c r="AQ243">
+        <v>2.08</v>
+      </c>
+      <c r="AR243">
+        <v>1.33</v>
+      </c>
+      <c r="AS243">
+        <v>1.39</v>
+      </c>
+      <c r="AT243">
+        <v>2.72</v>
+      </c>
+      <c r="AU243">
+        <v>3</v>
+      </c>
+      <c r="AV243">
+        <v>9</v>
+      </c>
+      <c r="AW243">
+        <v>5</v>
+      </c>
+      <c r="AX243">
+        <v>3</v>
+      </c>
+      <c r="AY243">
+        <v>9</v>
+      </c>
+      <c r="AZ243">
+        <v>15</v>
+      </c>
+      <c r="BA243">
+        <v>3</v>
+      </c>
+      <c r="BB243">
+        <v>3</v>
+      </c>
+      <c r="BC243">
+        <v>6</v>
+      </c>
+      <c r="BD243">
+        <v>2.55</v>
+      </c>
+      <c r="BE243">
+        <v>6.75</v>
+      </c>
+      <c r="BF243">
+        <v>1.63</v>
+      </c>
+      <c r="BG243">
+        <v>1.38</v>
+      </c>
+      <c r="BH243">
+        <v>2.8</v>
+      </c>
+      <c r="BI243">
+        <v>1.7</v>
+      </c>
+      <c r="BJ243">
+        <v>2.05</v>
+      </c>
+      <c r="BK243">
+        <v>2</v>
+      </c>
+      <c r="BL243">
+        <v>1.71</v>
+      </c>
+      <c r="BM243">
+        <v>2.55</v>
+      </c>
+      <c r="BN243">
+        <v>1.45</v>
+      </c>
+      <c r="BO243">
+        <v>3.3</v>
+      </c>
+      <c r="BP243">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7509830</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>75</v>
+      </c>
+      <c r="H244" t="s">
+        <v>78</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>2</v>
+      </c>
+      <c r="O244" t="s">
+        <v>196</v>
+      </c>
+      <c r="P244" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q244">
+        <v>3.1</v>
+      </c>
+      <c r="R244">
+        <v>2.05</v>
+      </c>
+      <c r="S244">
+        <v>3.75</v>
+      </c>
+      <c r="T244">
+        <v>1.44</v>
+      </c>
+      <c r="U244">
+        <v>2.63</v>
+      </c>
+      <c r="V244">
+        <v>3.25</v>
+      </c>
+      <c r="W244">
+        <v>1.33</v>
+      </c>
+      <c r="X244">
+        <v>10</v>
+      </c>
+      <c r="Y244">
+        <v>1.06</v>
+      </c>
+      <c r="Z244">
+        <v>2.47</v>
+      </c>
+      <c r="AA244">
+        <v>3.19</v>
+      </c>
+      <c r="AB244">
+        <v>3.15</v>
+      </c>
+      <c r="AC244">
+        <v>1.07</v>
+      </c>
+      <c r="AD244">
+        <v>8</v>
+      </c>
+      <c r="AE244">
+        <v>1.35</v>
+      </c>
+      <c r="AF244">
+        <v>2.95</v>
+      </c>
+      <c r="AG244">
+        <v>2</v>
+      </c>
+      <c r="AH244">
+        <v>1.67</v>
+      </c>
+      <c r="AI244">
+        <v>1.8</v>
+      </c>
+      <c r="AJ244">
+        <v>1.95</v>
+      </c>
+      <c r="AK244">
+        <v>1.38</v>
+      </c>
+      <c r="AL244">
+        <v>1.33</v>
+      </c>
+      <c r="AM244">
+        <v>1.55</v>
+      </c>
+      <c r="AN244">
+        <v>0.92</v>
+      </c>
+      <c r="AO244">
+        <v>1.27</v>
+      </c>
+      <c r="AP244">
+        <v>0.92</v>
+      </c>
+      <c r="AQ244">
+        <v>1.25</v>
+      </c>
+      <c r="AR244">
+        <v>1.4</v>
+      </c>
+      <c r="AS244">
+        <v>1.2</v>
+      </c>
+      <c r="AT244">
+        <v>2.6</v>
+      </c>
+      <c r="AU244">
+        <v>3</v>
+      </c>
+      <c r="AV244">
+        <v>3</v>
+      </c>
+      <c r="AW244">
+        <v>14</v>
+      </c>
+      <c r="AX244">
+        <v>11</v>
+      </c>
+      <c r="AY244">
+        <v>20</v>
+      </c>
+      <c r="AZ244">
+        <v>14</v>
+      </c>
+      <c r="BA244">
+        <v>7</v>
+      </c>
+      <c r="BB244">
+        <v>4</v>
+      </c>
+      <c r="BC244">
+        <v>11</v>
+      </c>
+      <c r="BD244">
+        <v>1.89</v>
+      </c>
+      <c r="BE244">
+        <v>6.25</v>
+      </c>
+      <c r="BF244">
+        <v>2.15</v>
+      </c>
+      <c r="BG244">
+        <v>1.47</v>
+      </c>
+      <c r="BH244">
+        <v>2.48</v>
+      </c>
+      <c r="BI244">
+        <v>1.78</v>
+      </c>
+      <c r="BJ244">
+        <v>1.92</v>
+      </c>
+      <c r="BK244">
+        <v>2.23</v>
+      </c>
+      <c r="BL244">
+        <v>1.56</v>
+      </c>
+      <c r="BM244">
+        <v>2.9</v>
+      </c>
+      <c r="BN244">
+        <v>1.34</v>
+      </c>
+      <c r="BO244">
+        <v>3.9</v>
+      </c>
+      <c r="BP244">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7509828</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245" t="s">
+        <v>79</v>
+      </c>
+      <c r="H245" t="s">
+        <v>86</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>1</v>
+      </c>
+      <c r="O245" t="s">
+        <v>238</v>
+      </c>
+      <c r="P245" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q245">
+        <v>3</v>
+      </c>
+      <c r="R245">
+        <v>2</v>
+      </c>
+      <c r="S245">
+        <v>4</v>
+      </c>
+      <c r="T245">
+        <v>1.5</v>
+      </c>
+      <c r="U245">
+        <v>2.5</v>
+      </c>
+      <c r="V245">
+        <v>3.5</v>
+      </c>
+      <c r="W245">
+        <v>1.29</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>2.39</v>
+      </c>
+      <c r="AA245">
+        <v>3.04</v>
+      </c>
+      <c r="AB245">
+        <v>3.47</v>
+      </c>
+      <c r="AC245">
+        <v>1.09</v>
+      </c>
+      <c r="AD245">
+        <v>7</v>
+      </c>
+      <c r="AE245">
+        <v>1.4</v>
+      </c>
+      <c r="AF245">
+        <v>2.65</v>
+      </c>
+      <c r="AG245">
+        <v>2.3</v>
+      </c>
+      <c r="AH245">
+        <v>1.5</v>
+      </c>
+      <c r="AI245">
+        <v>1.95</v>
+      </c>
+      <c r="AJ245">
+        <v>1.8</v>
+      </c>
+      <c r="AK245">
+        <v>1.32</v>
+      </c>
+      <c r="AL245">
+        <v>1.35</v>
+      </c>
+      <c r="AM245">
+        <v>1.58</v>
+      </c>
+      <c r="AN245">
+        <v>1</v>
+      </c>
+      <c r="AO245">
+        <v>0.5</v>
+      </c>
+      <c r="AP245">
+        <v>1.15</v>
+      </c>
+      <c r="AQ245">
+        <v>0.46</v>
+      </c>
+      <c r="AR245">
+        <v>1.59</v>
+      </c>
+      <c r="AS245">
+        <v>1.18</v>
+      </c>
+      <c r="AT245">
+        <v>2.77</v>
+      </c>
+      <c r="AU245">
+        <v>4</v>
+      </c>
+      <c r="AV245">
+        <v>4</v>
+      </c>
+      <c r="AW245">
+        <v>5</v>
+      </c>
+      <c r="AX245">
+        <v>9</v>
+      </c>
+      <c r="AY245">
+        <v>11</v>
+      </c>
+      <c r="AZ245">
+        <v>18</v>
+      </c>
+      <c r="BA245">
+        <v>6</v>
+      </c>
+      <c r="BB245">
+        <v>6</v>
+      </c>
+      <c r="BC245">
+        <v>12</v>
+      </c>
+      <c r="BD245">
+        <v>1.76</v>
+      </c>
+      <c r="BE245">
+        <v>6.4</v>
+      </c>
+      <c r="BF245">
+        <v>2.3</v>
+      </c>
+      <c r="BG245">
+        <v>1.38</v>
+      </c>
+      <c r="BH245">
+        <v>2.75</v>
+      </c>
+      <c r="BI245">
+        <v>1.65</v>
+      </c>
+      <c r="BJ245">
+        <v>2.08</v>
+      </c>
+      <c r="BK245">
+        <v>2.05</v>
+      </c>
+      <c r="BL245">
+        <v>1.7</v>
+      </c>
+      <c r="BM245">
+        <v>2.55</v>
+      </c>
+      <c r="BN245">
+        <v>1.44</v>
+      </c>
+      <c r="BO245">
+        <v>3.4</v>
+      </c>
+      <c r="BP245">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="345">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,15 @@
     <t>['69']</t>
   </si>
   <si>
+    <t>['28', '76', '90+2']</t>
+  </si>
+  <si>
+    <t>['90+2', '90+5']</t>
+  </si>
+  <si>
+    <t>['21', '47', '90+5']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1037,6 +1046,9 @@
   </si>
   <si>
     <t>['19', '54', '90+5']</t>
+  </si>
+  <si>
+    <t>['1', '72']</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP245"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1860,7 +1872,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2066,7 +2078,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2147,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2272,7 +2284,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2350,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ5">
         <v>1.62</v>
@@ -2559,7 +2571,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2684,7 +2696,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3096,7 +3108,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3174,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9">
         <v>0.6899999999999999</v>
@@ -3302,7 +3314,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3714,7 +3726,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3795,7 +3807,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3920,7 +3932,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4126,7 +4138,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4204,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -4413,7 +4425,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ15">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR15">
         <v>1.84</v>
@@ -4616,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ16">
         <v>0.46</v>
@@ -4744,7 +4756,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4822,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -5028,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5237,7 +5249,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ19">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5362,7 +5374,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5774,7 +5786,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6061,7 +6073,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ23">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6186,7 +6198,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6676,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26">
         <v>1.17</v>
@@ -6804,7 +6816,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -6882,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7091,7 +7103,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ28">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7706,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>0.6899999999999999</v>
@@ -7912,10 +7924,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ32">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -8040,7 +8052,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8121,7 +8133,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR33">
         <v>1.54</v>
@@ -8324,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8452,7 +8464,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8658,7 +8670,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9276,7 +9288,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9482,7 +9494,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9560,10 +9572,10 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR40">
         <v>1.5</v>
@@ -9688,7 +9700,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9894,7 +9906,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9975,7 +9987,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ42">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10718,7 +10730,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10796,7 +10808,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11002,7 +11014,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ47">
         <v>1.62</v>
@@ -11130,7 +11142,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11208,10 +11220,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ48">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.25</v>
@@ -11336,7 +11348,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11542,7 +11554,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11748,7 +11760,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11954,7 +11966,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12447,7 +12459,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR54">
         <v>2.1</v>
@@ -12572,7 +12584,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12650,7 +12662,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ55">
         <v>1.17</v>
@@ -12856,7 +12868,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56">
         <v>0.58</v>
@@ -13062,10 +13074,10 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ57">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>0.86</v>
@@ -13396,7 +13408,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13477,7 +13489,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ59">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13683,7 +13695,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR60">
         <v>0.97</v>
@@ -13808,7 +13820,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13886,7 +13898,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ61">
         <v>0.46</v>
@@ -14014,7 +14026,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14426,7 +14438,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14838,7 +14850,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15122,7 +15134,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ67">
         <v>1.75</v>
@@ -15250,7 +15262,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15662,7 +15674,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15868,7 +15880,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16074,7 +16086,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16152,7 +16164,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -16280,7 +16292,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16486,7 +16498,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16567,7 +16579,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR74">
         <v>1.29</v>
@@ -16770,7 +16782,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -16898,7 +16910,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16976,10 +16988,10 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ76">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR76">
         <v>1.44</v>
@@ -17104,7 +17116,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17185,7 +17197,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ77">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17310,7 +17322,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17516,7 +17528,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17594,10 +17606,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ79">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17722,7 +17734,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17803,7 +17815,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ80">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18340,7 +18352,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18546,7 +18558,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18958,7 +18970,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19164,7 +19176,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19370,7 +19382,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19448,7 +19460,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ88">
         <v>1.67</v>
@@ -19860,7 +19872,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ90">
         <v>0.83</v>
@@ -19988,7 +20000,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20272,10 +20284,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ92">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -20890,7 +20902,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ95">
         <v>0.58</v>
@@ -21305,7 +21317,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ97">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -21511,7 +21523,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR98">
         <v>1.24</v>
@@ -21717,7 +21729,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ99">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.26</v>
@@ -22126,7 +22138,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ101">
         <v>0.6899999999999999</v>
@@ -22666,7 +22678,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22744,7 +22756,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104">
         <v>2.08</v>
@@ -22872,7 +22884,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23156,7 +23168,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ106">
         <v>0.83</v>
@@ -23365,7 +23377,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ107">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -24186,7 +24198,7 @@
         <v>0.75</v>
       </c>
       <c r="AP111">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ111">
         <v>1.25</v>
@@ -24392,10 +24404,10 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ112">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24520,7 +24532,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25219,7 +25231,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ116">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.53</v>
@@ -25344,7 +25356,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25550,7 +25562,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25628,7 +25640,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ118">
         <v>1.75</v>
@@ -25837,7 +25849,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR119">
         <v>1.61</v>
@@ -26040,7 +26052,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ120">
         <v>1.17</v>
@@ -26374,7 +26386,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26864,7 +26876,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -27198,7 +27210,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27610,7 +27622,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27688,7 +27700,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ128">
         <v>1.62</v>
@@ -27816,7 +27828,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27897,7 +27909,7 @@
         <v>1</v>
       </c>
       <c r="AQ129">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR129">
         <v>1.41</v>
@@ -28022,7 +28034,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28100,7 +28112,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ130">
         <v>1.25</v>
@@ -28228,7 +28240,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28309,7 +28321,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28434,7 +28446,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28515,7 +28527,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ132">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -28924,7 +28936,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ134">
         <v>1.17</v>
@@ -29258,7 +29270,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29670,7 +29682,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29751,7 +29763,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ138">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR138">
         <v>1.4</v>
@@ -29954,10 +29966,10 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ139">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.53</v>
@@ -30160,7 +30172,7 @@
         <v>0.83</v>
       </c>
       <c r="AP140">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ140">
         <v>0.83</v>
@@ -30288,7 +30300,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30494,7 +30506,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30572,7 +30584,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ142">
         <v>2.08</v>
@@ -30700,7 +30712,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30778,7 +30790,7 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ143">
         <v>1.25</v>
@@ -30906,7 +30918,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31193,7 +31205,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ145">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31318,7 +31330,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31605,7 +31617,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ147">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -31936,7 +31948,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32014,7 +32026,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ149">
         <v>0.83</v>
@@ -32142,7 +32154,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32223,7 +32235,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ150">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR150">
         <v>1.37</v>
@@ -32554,7 +32566,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32632,10 +32644,10 @@
         <v>0.86</v>
       </c>
       <c r="AP152">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ152">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR152">
         <v>1.26</v>
@@ -32841,7 +32853,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33172,7 +33184,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33584,7 +33596,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33996,7 +34008,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34074,7 +34086,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -34280,10 +34292,10 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ160">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR160">
         <v>1.62</v>
@@ -34408,7 +34420,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34692,10 +34704,10 @@
         <v>1.43</v>
       </c>
       <c r="AP162">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ162">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34820,7 +34832,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35104,10 +35116,10 @@
         <v>0.63</v>
       </c>
       <c r="AP164">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ164">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35232,7 +35244,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35722,7 +35734,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ167">
         <v>1.62</v>
@@ -35850,7 +35862,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36468,7 +36480,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37167,7 +37179,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ174">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37910,7 +37922,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38116,7 +38128,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38400,10 +38412,10 @@
         <v>0.63</v>
       </c>
       <c r="AP180">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ180">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38606,7 +38618,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -38812,7 +38824,7 @@
         <v>2.33</v>
       </c>
       <c r="AP182">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ182">
         <v>2.08</v>
@@ -39018,7 +39030,7 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ183">
         <v>1.15</v>
@@ -39146,7 +39158,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39224,7 +39236,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ184">
         <v>0.6899999999999999</v>
@@ -39352,7 +39364,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39433,7 +39445,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39970,7 +39982,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40051,7 +40063,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ188">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40463,7 +40475,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ190">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40588,7 +40600,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40666,7 +40678,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ191">
         <v>0.46</v>
@@ -40794,7 +40806,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40872,7 +40884,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192">
         <v>1.17</v>
@@ -41287,7 +41299,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ194">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41699,7 +41711,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ196">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR196">
         <v>1.41</v>
@@ -41824,7 +41836,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42442,7 +42454,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42520,7 +42532,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ200">
         <v>0.83</v>
@@ -42726,7 +42738,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ201">
         <v>1.75</v>
@@ -42854,7 +42866,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43138,10 +43150,10 @@
         <v>1.11</v>
       </c>
       <c r="AP203">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ203">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR203">
         <v>1.37</v>
@@ -43266,7 +43278,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43553,7 +43565,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ205">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR205">
         <v>1.88</v>
@@ -43678,7 +43690,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43756,7 +43768,7 @@
         <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ206">
         <v>1.15</v>
@@ -43884,7 +43896,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44090,7 +44102,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44377,7 +44389,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ209">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44786,7 +44798,7 @@
         <v>0.6</v>
       </c>
       <c r="AP211">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ211">
         <v>0.46</v>
@@ -44914,7 +44926,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -44992,10 +45004,10 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ212">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR212">
         <v>1.48</v>
@@ -45120,7 +45132,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45404,7 +45416,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ214">
         <v>0.83</v>
@@ -45738,7 +45750,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45944,7 +45956,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46562,7 +46574,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46643,7 +46655,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ220">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -46768,7 +46780,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46974,7 +46986,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47052,7 +47064,7 @@
         <v>2.18</v>
       </c>
       <c r="AP222">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AQ222">
         <v>2.08</v>
@@ -47258,7 +47270,7 @@
         <v>0.55</v>
       </c>
       <c r="AP223">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ223">
         <v>0.46</v>
@@ -47386,7 +47398,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47467,7 +47479,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ224">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR224">
         <v>1.39</v>
@@ -47592,7 +47604,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47673,7 +47685,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ225">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR225">
         <v>1.49</v>
@@ -47798,7 +47810,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47879,7 +47891,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ226">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR226">
         <v>1.51</v>
@@ -48004,7 +48016,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48210,7 +48222,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48494,7 +48506,7 @@
         <v>0.6</v>
       </c>
       <c r="AP229">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ229">
         <v>0.58</v>
@@ -48700,7 +48712,7 @@
         <v>1.09</v>
       </c>
       <c r="AP230">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ230">
         <v>1</v>
@@ -48828,7 +48840,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -48906,10 +48918,10 @@
         <v>0.82</v>
       </c>
       <c r="AP231">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ231">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49034,7 +49046,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49318,7 +49330,7 @@
         <v>0.91</v>
       </c>
       <c r="AP233">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ233">
         <v>0.83</v>
@@ -49652,7 +49664,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49858,7 +49870,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -49939,7 +49951,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ236">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR236">
         <v>1.29</v>
@@ -50476,7 +50488,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50888,7 +50900,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51258,7 +51270,7 @@
         <v>242</v>
       </c>
       <c r="B243">
-        <v>7509832</v>
+        <v>7509833</v>
       </c>
       <c r="C243" t="s">
         <v>68</v>
@@ -51273,166 +51285,166 @@
         <v>25</v>
       </c>
       <c r="G243" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H243" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I243">
         <v>0</v>
       </c>
       <c r="J243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L243">
         <v>0</v>
       </c>
       <c r="M243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O243" t="s">
         <v>102</v>
       </c>
       <c r="P243" t="s">
-        <v>340</v>
+        <v>138</v>
       </c>
       <c r="Q243">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="R243">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S243">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="T243">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U243">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V243">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="W243">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X243">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y243">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z243">
-        <v>4.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA243">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AB243">
-        <v>1.76</v>
+        <v>5.2</v>
       </c>
       <c r="AC243">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD243">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AE243">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AF243">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG243">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AH243">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AI243">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AJ243">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AK243">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="AL243">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AM243">
+        <v>2.15</v>
+      </c>
+      <c r="AN243">
+        <v>2.5</v>
+      </c>
+      <c r="AO243">
+        <v>1.33</v>
+      </c>
+      <c r="AP243">
+        <v>2.31</v>
+      </c>
+      <c r="AQ243">
+        <v>1.46</v>
+      </c>
+      <c r="AR243">
+        <v>1.47</v>
+      </c>
+      <c r="AS243">
         <v>1.21</v>
       </c>
-      <c r="AN243">
-        <v>1.73</v>
-      </c>
-      <c r="AO243">
-        <v>2</v>
-      </c>
-      <c r="AP243">
-        <v>1.58</v>
-      </c>
-      <c r="AQ243">
-        <v>2.08</v>
-      </c>
-      <c r="AR243">
-        <v>1.33</v>
-      </c>
-      <c r="AS243">
-        <v>1.39</v>
-      </c>
       <c r="AT243">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AU243">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV243">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW243">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY243">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ243">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="BA243">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="BB243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC243">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BD243">
-        <v>2.55</v>
+        <v>1.49</v>
       </c>
       <c r="BE243">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF243">
-        <v>1.63</v>
+        <v>2.95</v>
       </c>
       <c r="BG243">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="BH243">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="BI243">
         <v>1.7</v>
@@ -51441,22 +51453,22 @@
         <v>2.05</v>
       </c>
       <c r="BK243">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BL243">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="BM243">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="BN243">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="BO243">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BP243">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="244" spans="1:68">
@@ -51464,7 +51476,7 @@
         <v>243</v>
       </c>
       <c r="B244">
-        <v>7509830</v>
+        <v>7509832</v>
       </c>
       <c r="C244" t="s">
         <v>68</v>
@@ -51479,190 +51491,190 @@
         <v>25</v>
       </c>
       <c r="G244" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H244" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K244">
         <v>1</v>
       </c>
       <c r="L244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M244">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N244">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O244" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>112</v>
+        <v>343</v>
       </c>
       <c r="Q244">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R244">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S244">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="T244">
+        <v>1.36</v>
+      </c>
+      <c r="U244">
+        <v>3</v>
+      </c>
+      <c r="V244">
+        <v>2.63</v>
+      </c>
+      <c r="W244">
         <v>1.44</v>
       </c>
-      <c r="U244">
-        <v>2.63</v>
-      </c>
-      <c r="V244">
-        <v>3.25</v>
-      </c>
-      <c r="W244">
+      <c r="X244">
+        <v>7</v>
+      </c>
+      <c r="Y244">
+        <v>1.1</v>
+      </c>
+      <c r="Z244">
+        <v>4.7</v>
+      </c>
+      <c r="AA244">
+        <v>3.92</v>
+      </c>
+      <c r="AB244">
+        <v>1.76</v>
+      </c>
+      <c r="AC244">
+        <v>1.05</v>
+      </c>
+      <c r="AD244">
+        <v>9.5</v>
+      </c>
+      <c r="AE244">
+        <v>1.23</v>
+      </c>
+      <c r="AF244">
+        <v>3.8</v>
+      </c>
+      <c r="AG244">
+        <v>1.81</v>
+      </c>
+      <c r="AH244">
+        <v>2.01</v>
+      </c>
+      <c r="AI244">
+        <v>1.75</v>
+      </c>
+      <c r="AJ244">
+        <v>2</v>
+      </c>
+      <c r="AK244">
+        <v>1.98</v>
+      </c>
+      <c r="AL244">
+        <v>1.26</v>
+      </c>
+      <c r="AM244">
+        <v>1.21</v>
+      </c>
+      <c r="AN244">
+        <v>1.73</v>
+      </c>
+      <c r="AO244">
+        <v>2</v>
+      </c>
+      <c r="AP244">
+        <v>1.58</v>
+      </c>
+      <c r="AQ244">
+        <v>2.08</v>
+      </c>
+      <c r="AR244">
         <v>1.33</v>
       </c>
-      <c r="X244">
-        <v>10</v>
-      </c>
-      <c r="Y244">
-        <v>1.06</v>
-      </c>
-      <c r="Z244">
-        <v>2.47</v>
-      </c>
-      <c r="AA244">
-        <v>3.19</v>
-      </c>
-      <c r="AB244">
-        <v>3.15</v>
-      </c>
-      <c r="AC244">
-        <v>1.07</v>
-      </c>
-      <c r="AD244">
-        <v>8</v>
-      </c>
-      <c r="AE244">
-        <v>1.35</v>
-      </c>
-      <c r="AF244">
-        <v>2.95</v>
-      </c>
-      <c r="AG244">
-        <v>2</v>
-      </c>
-      <c r="AH244">
-        <v>1.67</v>
-      </c>
-      <c r="AI244">
-        <v>1.8</v>
-      </c>
-      <c r="AJ244">
-        <v>1.95</v>
-      </c>
-      <c r="AK244">
-        <v>1.38</v>
-      </c>
-      <c r="AL244">
-        <v>1.33</v>
-      </c>
-      <c r="AM244">
-        <v>1.55</v>
-      </c>
-      <c r="AN244">
-        <v>0.92</v>
-      </c>
-      <c r="AO244">
-        <v>1.27</v>
-      </c>
-      <c r="AP244">
-        <v>0.92</v>
-      </c>
-      <c r="AQ244">
-        <v>1.25</v>
-      </c>
-      <c r="AR244">
-        <v>1.4</v>
-      </c>
       <c r="AS244">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AT244">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AU244">
         <v>3</v>
       </c>
       <c r="AV244">
+        <v>9</v>
+      </c>
+      <c r="AW244">
+        <v>5</v>
+      </c>
+      <c r="AX244">
         <v>3</v>
       </c>
-      <c r="AW244">
-        <v>14</v>
-      </c>
-      <c r="AX244">
-        <v>11</v>
-      </c>
       <c r="AY244">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AZ244">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA244">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC244">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BD244">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="BE244">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="BF244">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="BG244">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BH244">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="BI244">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BJ244">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="BK244">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="BL244">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="BM244">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BN244">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="BO244">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="BP244">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="245" spans="1:68">
@@ -51670,7 +51682,7 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>7509828</v>
+        <v>7509830</v>
       </c>
       <c r="C245" t="s">
         <v>68</v>
@@ -51685,55 +51697,55 @@
         <v>25</v>
       </c>
       <c r="G245" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H245" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245">
         <v>0</v>
       </c>
       <c r="K245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L245">
         <v>1</v>
       </c>
       <c r="M245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N245">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O245" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="P245" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="Q245">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R245">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S245">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T245">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U245">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V245">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="W245">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X245">
         <v>10</v>
@@ -51742,133 +51754,1369 @@
         <v>1.06</v>
       </c>
       <c r="Z245">
+        <v>2.47</v>
+      </c>
+      <c r="AA245">
+        <v>3.19</v>
+      </c>
+      <c r="AB245">
+        <v>3.15</v>
+      </c>
+      <c r="AC245">
+        <v>1.07</v>
+      </c>
+      <c r="AD245">
+        <v>8</v>
+      </c>
+      <c r="AE245">
+        <v>1.35</v>
+      </c>
+      <c r="AF245">
+        <v>2.95</v>
+      </c>
+      <c r="AG245">
+        <v>2</v>
+      </c>
+      <c r="AH245">
+        <v>1.67</v>
+      </c>
+      <c r="AI245">
+        <v>1.8</v>
+      </c>
+      <c r="AJ245">
+        <v>1.95</v>
+      </c>
+      <c r="AK245">
+        <v>1.38</v>
+      </c>
+      <c r="AL245">
+        <v>1.33</v>
+      </c>
+      <c r="AM245">
+        <v>1.55</v>
+      </c>
+      <c r="AN245">
+        <v>0.92</v>
+      </c>
+      <c r="AO245">
+        <v>1.27</v>
+      </c>
+      <c r="AP245">
+        <v>0.92</v>
+      </c>
+      <c r="AQ245">
+        <v>1.25</v>
+      </c>
+      <c r="AR245">
+        <v>1.4</v>
+      </c>
+      <c r="AS245">
+        <v>1.2</v>
+      </c>
+      <c r="AT245">
+        <v>2.6</v>
+      </c>
+      <c r="AU245">
+        <v>3</v>
+      </c>
+      <c r="AV245">
+        <v>3</v>
+      </c>
+      <c r="AW245">
+        <v>14</v>
+      </c>
+      <c r="AX245">
+        <v>11</v>
+      </c>
+      <c r="AY245">
+        <v>20</v>
+      </c>
+      <c r="AZ245">
+        <v>14</v>
+      </c>
+      <c r="BA245">
+        <v>7</v>
+      </c>
+      <c r="BB245">
+        <v>4</v>
+      </c>
+      <c r="BC245">
+        <v>11</v>
+      </c>
+      <c r="BD245">
+        <v>1.89</v>
+      </c>
+      <c r="BE245">
+        <v>6.25</v>
+      </c>
+      <c r="BF245">
+        <v>2.15</v>
+      </c>
+      <c r="BG245">
+        <v>1.47</v>
+      </c>
+      <c r="BH245">
+        <v>2.48</v>
+      </c>
+      <c r="BI245">
+        <v>1.78</v>
+      </c>
+      <c r="BJ245">
+        <v>1.92</v>
+      </c>
+      <c r="BK245">
+        <v>2.23</v>
+      </c>
+      <c r="BL245">
+        <v>1.56</v>
+      </c>
+      <c r="BM245">
+        <v>2.9</v>
+      </c>
+      <c r="BN245">
+        <v>1.34</v>
+      </c>
+      <c r="BO245">
+        <v>3.9</v>
+      </c>
+      <c r="BP245">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7509828</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45696.45833333334</v>
+      </c>
+      <c r="F246">
+        <v>25</v>
+      </c>
+      <c r="G246" t="s">
+        <v>79</v>
+      </c>
+      <c r="H246" t="s">
+        <v>86</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>1</v>
+      </c>
+      <c r="O246" t="s">
+        <v>238</v>
+      </c>
+      <c r="P246" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q246">
+        <v>3</v>
+      </c>
+      <c r="R246">
+        <v>2</v>
+      </c>
+      <c r="S246">
+        <v>4</v>
+      </c>
+      <c r="T246">
+        <v>1.5</v>
+      </c>
+      <c r="U246">
+        <v>2.5</v>
+      </c>
+      <c r="V246">
+        <v>3.5</v>
+      </c>
+      <c r="W246">
+        <v>1.29</v>
+      </c>
+      <c r="X246">
+        <v>10</v>
+      </c>
+      <c r="Y246">
+        <v>1.06</v>
+      </c>
+      <c r="Z246">
         <v>2.39</v>
       </c>
-      <c r="AA245">
+      <c r="AA246">
         <v>3.04</v>
       </c>
-      <c r="AB245">
+      <c r="AB246">
         <v>3.47</v>
       </c>
-      <c r="AC245">
+      <c r="AC246">
         <v>1.09</v>
       </c>
-      <c r="AD245">
+      <c r="AD246">
         <v>7</v>
       </c>
-      <c r="AE245">
+      <c r="AE246">
         <v>1.4</v>
       </c>
-      <c r="AF245">
+      <c r="AF246">
         <v>2.65</v>
       </c>
-      <c r="AG245">
+      <c r="AG246">
         <v>2.3</v>
       </c>
-      <c r="AH245">
+      <c r="AH246">
         <v>1.5</v>
       </c>
-      <c r="AI245">
+      <c r="AI246">
         <v>1.95</v>
       </c>
-      <c r="AJ245">
+      <c r="AJ246">
         <v>1.8</v>
       </c>
-      <c r="AK245">
+      <c r="AK246">
         <v>1.32</v>
       </c>
-      <c r="AL245">
+      <c r="AL246">
         <v>1.35</v>
       </c>
-      <c r="AM245">
+      <c r="AM246">
         <v>1.58</v>
       </c>
-      <c r="AN245">
-        <v>1</v>
-      </c>
-      <c r="AO245">
+      <c r="AN246">
+        <v>1</v>
+      </c>
+      <c r="AO246">
         <v>0.5</v>
       </c>
-      <c r="AP245">
+      <c r="AP246">
         <v>1.15</v>
       </c>
-      <c r="AQ245">
+      <c r="AQ246">
         <v>0.46</v>
       </c>
-      <c r="AR245">
+      <c r="AR246">
         <v>1.59</v>
       </c>
-      <c r="AS245">
+      <c r="AS246">
         <v>1.18</v>
       </c>
-      <c r="AT245">
+      <c r="AT246">
         <v>2.77</v>
       </c>
-      <c r="AU245">
+      <c r="AU246">
         <v>4</v>
       </c>
-      <c r="AV245">
+      <c r="AV246">
         <v>4</v>
       </c>
-      <c r="AW245">
+      <c r="AW246">
         <v>5</v>
       </c>
-      <c r="AX245">
+      <c r="AX246">
         <v>9</v>
       </c>
-      <c r="AY245">
+      <c r="AY246">
         <v>11</v>
       </c>
-      <c r="AZ245">
+      <c r="AZ246">
         <v>18</v>
       </c>
-      <c r="BA245">
+      <c r="BA246">
         <v>6</v>
       </c>
-      <c r="BB245">
+      <c r="BB246">
         <v>6</v>
       </c>
-      <c r="BC245">
+      <c r="BC246">
         <v>12</v>
       </c>
-      <c r="BD245">
+      <c r="BD246">
         <v>1.76</v>
       </c>
-      <c r="BE245">
+      <c r="BE246">
         <v>6.4</v>
       </c>
-      <c r="BF245">
+      <c r="BF246">
         <v>2.3</v>
       </c>
-      <c r="BG245">
+      <c r="BG246">
         <v>1.38</v>
       </c>
-      <c r="BH245">
+      <c r="BH246">
         <v>2.75</v>
       </c>
-      <c r="BI245">
+      <c r="BI246">
         <v>1.65</v>
       </c>
-      <c r="BJ245">
+      <c r="BJ246">
         <v>2.08</v>
       </c>
-      <c r="BK245">
+      <c r="BK246">
         <v>2.05</v>
       </c>
-      <c r="BL245">
+      <c r="BL246">
         <v>1.7</v>
       </c>
-      <c r="BM245">
+      <c r="BM246">
         <v>2.55</v>
       </c>
-      <c r="BN245">
+      <c r="BN246">
         <v>1.44</v>
       </c>
-      <c r="BO245">
+      <c r="BO246">
         <v>3.4</v>
       </c>
-      <c r="BP245">
+      <c r="BP246">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7509835</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45696.55208333334</v>
+      </c>
+      <c r="F247">
+        <v>25</v>
+      </c>
+      <c r="G247" t="s">
+        <v>81</v>
+      </c>
+      <c r="H247" t="s">
+        <v>80</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>1</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
+      </c>
+      <c r="N247">
+        <v>1</v>
+      </c>
+      <c r="O247" t="s">
+        <v>166</v>
+      </c>
+      <c r="P247" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q247">
+        <v>3.25</v>
+      </c>
+      <c r="R247">
+        <v>2</v>
+      </c>
+      <c r="S247">
+        <v>3.6</v>
+      </c>
+      <c r="T247">
+        <v>1.5</v>
+      </c>
+      <c r="U247">
+        <v>2.5</v>
+      </c>
+      <c r="V247">
+        <v>3.5</v>
+      </c>
+      <c r="W247">
+        <v>1.29</v>
+      </c>
+      <c r="X247">
+        <v>11</v>
+      </c>
+      <c r="Y247">
+        <v>1.05</v>
+      </c>
+      <c r="Z247">
+        <v>2.62</v>
+      </c>
+      <c r="AA247">
+        <v>3.09</v>
+      </c>
+      <c r="AB247">
+        <v>3.03</v>
+      </c>
+      <c r="AC247">
+        <v>1.09</v>
+      </c>
+      <c r="AD247">
+        <v>7</v>
+      </c>
+      <c r="AE247">
+        <v>1.41</v>
+      </c>
+      <c r="AF247">
+        <v>2.65</v>
+      </c>
+      <c r="AG247">
+        <v>2.25</v>
+      </c>
+      <c r="AH247">
+        <v>1.53</v>
+      </c>
+      <c r="AI247">
+        <v>1.95</v>
+      </c>
+      <c r="AJ247">
+        <v>1.8</v>
+      </c>
+      <c r="AK247">
+        <v>1.39</v>
+      </c>
+      <c r="AL247">
+        <v>1.35</v>
+      </c>
+      <c r="AM247">
+        <v>1.5</v>
+      </c>
+      <c r="AN247">
+        <v>1.08</v>
+      </c>
+      <c r="AO247">
+        <v>0.83</v>
+      </c>
+      <c r="AP247">
+        <v>1.23</v>
+      </c>
+      <c r="AQ247">
+        <v>0.77</v>
+      </c>
+      <c r="AR247">
+        <v>1.4</v>
+      </c>
+      <c r="AS247">
+        <v>1.18</v>
+      </c>
+      <c r="AT247">
+        <v>2.58</v>
+      </c>
+      <c r="AU247">
+        <v>3</v>
+      </c>
+      <c r="AV247">
+        <v>2</v>
+      </c>
+      <c r="AW247">
+        <v>16</v>
+      </c>
+      <c r="AX247">
+        <v>11</v>
+      </c>
+      <c r="AY247">
+        <v>24</v>
+      </c>
+      <c r="AZ247">
+        <v>16</v>
+      </c>
+      <c r="BA247">
+        <v>7</v>
+      </c>
+      <c r="BB247">
+        <v>4</v>
+      </c>
+      <c r="BC247">
+        <v>11</v>
+      </c>
+      <c r="BD247">
+        <v>1.95</v>
+      </c>
+      <c r="BE247">
+        <v>6.1</v>
+      </c>
+      <c r="BF247">
+        <v>2.07</v>
+      </c>
+      <c r="BG247">
+        <v>1.5</v>
+      </c>
+      <c r="BH247">
+        <v>2.38</v>
+      </c>
+      <c r="BI247">
+        <v>1.7</v>
+      </c>
+      <c r="BJ247">
+        <v>2.05</v>
+      </c>
+      <c r="BK247">
+        <v>2.38</v>
+      </c>
+      <c r="BL247">
+        <v>1.5</v>
+      </c>
+      <c r="BM247">
+        <v>3.15</v>
+      </c>
+      <c r="BN247">
+        <v>1.3</v>
+      </c>
+      <c r="BO247">
+        <v>4.3</v>
+      </c>
+      <c r="BP247">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7509829</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F248">
+        <v>25</v>
+      </c>
+      <c r="G248" t="s">
+        <v>82</v>
+      </c>
+      <c r="H248" t="s">
+        <v>72</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>3</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>4</v>
+      </c>
+      <c r="O248" t="s">
+        <v>239</v>
+      </c>
+      <c r="P248" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q248">
+        <v>2.4</v>
+      </c>
+      <c r="R248">
+        <v>2.05</v>
+      </c>
+      <c r="S248">
+        <v>5.5</v>
+      </c>
+      <c r="T248">
+        <v>1.5</v>
+      </c>
+      <c r="U248">
+        <v>2.5</v>
+      </c>
+      <c r="V248">
+        <v>3.5</v>
+      </c>
+      <c r="W248">
+        <v>1.29</v>
+      </c>
+      <c r="X248">
+        <v>11</v>
+      </c>
+      <c r="Y248">
+        <v>1.05</v>
+      </c>
+      <c r="Z248">
+        <v>1.75</v>
+      </c>
+      <c r="AA248">
+        <v>3.66</v>
+      </c>
+      <c r="AB248">
+        <v>5.3</v>
+      </c>
+      <c r="AC248">
+        <v>1.08</v>
+      </c>
+      <c r="AD248">
+        <v>7.5</v>
+      </c>
+      <c r="AE248">
+        <v>1.42</v>
+      </c>
+      <c r="AF248">
+        <v>2.6</v>
+      </c>
+      <c r="AG248">
+        <v>2.15</v>
+      </c>
+      <c r="AH248">
+        <v>1.57</v>
+      </c>
+      <c r="AI248">
+        <v>2.2</v>
+      </c>
+      <c r="AJ248">
+        <v>1.62</v>
+      </c>
+      <c r="AK248">
+        <v>1.17</v>
+      </c>
+      <c r="AL248">
+        <v>1.29</v>
+      </c>
+      <c r="AM248">
+        <v>2.05</v>
+      </c>
+      <c r="AN248">
+        <v>1.42</v>
+      </c>
+      <c r="AO248">
+        <v>1.08</v>
+      </c>
+      <c r="AP248">
+        <v>1.54</v>
+      </c>
+      <c r="AQ248">
+        <v>1</v>
+      </c>
+      <c r="AR248">
+        <v>1.78</v>
+      </c>
+      <c r="AS248">
+        <v>1.24</v>
+      </c>
+      <c r="AT248">
+        <v>3.02</v>
+      </c>
+      <c r="AU248">
+        <v>7</v>
+      </c>
+      <c r="AV248">
+        <v>2</v>
+      </c>
+      <c r="AW248">
+        <v>10</v>
+      </c>
+      <c r="AX248">
+        <v>5</v>
+      </c>
+      <c r="AY248">
+        <v>19</v>
+      </c>
+      <c r="AZ248">
+        <v>7</v>
+      </c>
+      <c r="BA248">
+        <v>4</v>
+      </c>
+      <c r="BB248">
+        <v>4</v>
+      </c>
+      <c r="BC248">
+        <v>8</v>
+      </c>
+      <c r="BD248">
+        <v>1.49</v>
+      </c>
+      <c r="BE248">
+        <v>6.75</v>
+      </c>
+      <c r="BF248">
+        <v>2.95</v>
+      </c>
+      <c r="BG248">
+        <v>1.4</v>
+      </c>
+      <c r="BH248">
+        <v>2.7</v>
+      </c>
+      <c r="BI248">
+        <v>1.67</v>
+      </c>
+      <c r="BJ248">
+        <v>2.07</v>
+      </c>
+      <c r="BK248">
+        <v>2.07</v>
+      </c>
+      <c r="BL248">
+        <v>1.66</v>
+      </c>
+      <c r="BM248">
+        <v>2.65</v>
+      </c>
+      <c r="BN248">
+        <v>1.41</v>
+      </c>
+      <c r="BO248">
+        <v>3.45</v>
+      </c>
+      <c r="BP248">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7509834</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F249">
+        <v>25</v>
+      </c>
+      <c r="G249" t="s">
+        <v>77</v>
+      </c>
+      <c r="H249" t="s">
+        <v>76</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>0</v>
+      </c>
+      <c r="M249">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>102</v>
+      </c>
+      <c r="P249" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q249">
+        <v>3.1</v>
+      </c>
+      <c r="R249">
+        <v>1.95</v>
+      </c>
+      <c r="S249">
+        <v>4</v>
+      </c>
+      <c r="T249">
+        <v>1.53</v>
+      </c>
+      <c r="U249">
+        <v>2.38</v>
+      </c>
+      <c r="V249">
+        <v>3.75</v>
+      </c>
+      <c r="W249">
+        <v>1.25</v>
+      </c>
+      <c r="X249">
+        <v>11</v>
+      </c>
+      <c r="Y249">
+        <v>1.05</v>
+      </c>
+      <c r="Z249">
+        <v>2.62</v>
+      </c>
+      <c r="AA249">
+        <v>2.97</v>
+      </c>
+      <c r="AB249">
+        <v>3.16</v>
+      </c>
+      <c r="AC249">
+        <v>1.11</v>
+      </c>
+      <c r="AD249">
+        <v>6.25</v>
+      </c>
+      <c r="AE249">
+        <v>1.5</v>
+      </c>
+      <c r="AF249">
+        <v>2.4</v>
+      </c>
+      <c r="AG249">
+        <v>2.3</v>
+      </c>
+      <c r="AH249">
+        <v>1.5</v>
+      </c>
+      <c r="AI249">
+        <v>2</v>
+      </c>
+      <c r="AJ249">
+        <v>1.75</v>
+      </c>
+      <c r="AK249">
+        <v>1.34</v>
+      </c>
+      <c r="AL249">
+        <v>1.36</v>
+      </c>
+      <c r="AM249">
+        <v>1.55</v>
+      </c>
+      <c r="AN249">
+        <v>1.33</v>
+      </c>
+      <c r="AO249">
+        <v>0.67</v>
+      </c>
+      <c r="AP249">
+        <v>1.23</v>
+      </c>
+      <c r="AQ249">
+        <v>0.85</v>
+      </c>
+      <c r="AR249">
+        <v>1.33</v>
+      </c>
+      <c r="AS249">
+        <v>1.33</v>
+      </c>
+      <c r="AT249">
+        <v>2.66</v>
+      </c>
+      <c r="AU249">
+        <v>2</v>
+      </c>
+      <c r="AV249">
+        <v>8</v>
+      </c>
+      <c r="AW249">
+        <v>6</v>
+      </c>
+      <c r="AX249">
+        <v>3</v>
+      </c>
+      <c r="AY249">
+        <v>10</v>
+      </c>
+      <c r="AZ249">
+        <v>15</v>
+      </c>
+      <c r="BA249">
+        <v>3</v>
+      </c>
+      <c r="BB249">
+        <v>2</v>
+      </c>
+      <c r="BC249">
+        <v>5</v>
+      </c>
+      <c r="BD249">
+        <v>1.84</v>
+      </c>
+      <c r="BE249">
+        <v>5.8</v>
+      </c>
+      <c r="BF249">
+        <v>2.18</v>
+      </c>
+      <c r="BG249">
+        <v>1.57</v>
+      </c>
+      <c r="BH249">
+        <v>2.2</v>
+      </c>
+      <c r="BI249">
+        <v>1.8</v>
+      </c>
+      <c r="BJ249">
+        <v>1.91</v>
+      </c>
+      <c r="BK249">
+        <v>2.55</v>
+      </c>
+      <c r="BL249">
+        <v>1.45</v>
+      </c>
+      <c r="BM249">
+        <v>3.4</v>
+      </c>
+      <c r="BN249">
+        <v>1.26</v>
+      </c>
+      <c r="BO249">
+        <v>4.6</v>
+      </c>
+      <c r="BP249">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7509836</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45697.45833333334</v>
+      </c>
+      <c r="F250">
+        <v>25</v>
+      </c>
+      <c r="G250" t="s">
+        <v>83</v>
+      </c>
+      <c r="H250" t="s">
+        <v>89</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>1</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>2</v>
+      </c>
+      <c r="N250">
+        <v>4</v>
+      </c>
+      <c r="O250" t="s">
+        <v>240</v>
+      </c>
+      <c r="P250" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q250">
+        <v>2.6</v>
+      </c>
+      <c r="R250">
+        <v>2.1</v>
+      </c>
+      <c r="S250">
+        <v>4.75</v>
+      </c>
+      <c r="T250">
+        <v>1.44</v>
+      </c>
+      <c r="U250">
+        <v>2.63</v>
+      </c>
+      <c r="V250">
+        <v>3.25</v>
+      </c>
+      <c r="W250">
+        <v>1.33</v>
+      </c>
+      <c r="X250">
+        <v>9</v>
+      </c>
+      <c r="Y250">
+        <v>1.07</v>
+      </c>
+      <c r="Z250">
+        <v>1.86</v>
+      </c>
+      <c r="AA250">
+        <v>3.62</v>
+      </c>
+      <c r="AB250">
+        <v>4.5</v>
+      </c>
+      <c r="AC250">
+        <v>1.07</v>
+      </c>
+      <c r="AD250">
+        <v>8</v>
+      </c>
+      <c r="AE250">
+        <v>1.34</v>
+      </c>
+      <c r="AF250">
+        <v>2.95</v>
+      </c>
+      <c r="AG250">
+        <v>2.05</v>
+      </c>
+      <c r="AH250">
+        <v>1.65</v>
+      </c>
+      <c r="AI250">
+        <v>1.95</v>
+      </c>
+      <c r="AJ250">
+        <v>1.8</v>
+      </c>
+      <c r="AK250">
+        <v>1.22</v>
+      </c>
+      <c r="AL250">
+        <v>1.29</v>
+      </c>
+      <c r="AM250">
+        <v>1.9</v>
+      </c>
+      <c r="AN250">
+        <v>2.45</v>
+      </c>
+      <c r="AO250">
+        <v>1</v>
+      </c>
+      <c r="AP250">
+        <v>2.33</v>
+      </c>
+      <c r="AQ250">
+        <v>1</v>
+      </c>
+      <c r="AR250">
+        <v>1.79</v>
+      </c>
+      <c r="AS250">
+        <v>1.3</v>
+      </c>
+      <c r="AT250">
+        <v>3.09</v>
+      </c>
+      <c r="AU250">
+        <v>9</v>
+      </c>
+      <c r="AV250">
+        <v>4</v>
+      </c>
+      <c r="AW250">
+        <v>24</v>
+      </c>
+      <c r="AX250">
+        <v>3</v>
+      </c>
+      <c r="AY250">
+        <v>38</v>
+      </c>
+      <c r="AZ250">
+        <v>9</v>
+      </c>
+      <c r="BA250">
+        <v>13</v>
+      </c>
+      <c r="BB250">
+        <v>3</v>
+      </c>
+      <c r="BC250">
+        <v>16</v>
+      </c>
+      <c r="BD250">
+        <v>1.56</v>
+      </c>
+      <c r="BE250">
+        <v>6.5</v>
+      </c>
+      <c r="BF250">
+        <v>2.7</v>
+      </c>
+      <c r="BG250">
+        <v>1.34</v>
+      </c>
+      <c r="BH250">
+        <v>2.9</v>
+      </c>
+      <c r="BI250">
+        <v>1.58</v>
+      </c>
+      <c r="BJ250">
+        <v>2.18</v>
+      </c>
+      <c r="BK250">
+        <v>1.95</v>
+      </c>
+      <c r="BL250">
+        <v>1.75</v>
+      </c>
+      <c r="BM250">
+        <v>2.45</v>
+      </c>
+      <c r="BN250">
+        <v>1.48</v>
+      </c>
+      <c r="BO250">
+        <v>3.2</v>
+      </c>
+      <c r="BP250">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7509831</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45697.55208333334</v>
+      </c>
+      <c r="F251">
+        <v>25</v>
+      </c>
+      <c r="G251" t="s">
+        <v>88</v>
+      </c>
+      <c r="H251" t="s">
+        <v>71</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>3</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>4</v>
+      </c>
+      <c r="O251" t="s">
+        <v>241</v>
+      </c>
+      <c r="P251" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q251">
+        <v>3.2</v>
+      </c>
+      <c r="R251">
+        <v>1.95</v>
+      </c>
+      <c r="S251">
+        <v>4</v>
+      </c>
+      <c r="T251">
+        <v>1.53</v>
+      </c>
+      <c r="U251">
+        <v>2.38</v>
+      </c>
+      <c r="V251">
+        <v>3.75</v>
+      </c>
+      <c r="W251">
+        <v>1.25</v>
+      </c>
+      <c r="X251">
+        <v>11</v>
+      </c>
+      <c r="Y251">
+        <v>1.05</v>
+      </c>
+      <c r="Z251">
+        <v>2.51</v>
+      </c>
+      <c r="AA251">
+        <v>2.97</v>
+      </c>
+      <c r="AB251">
+        <v>3.33</v>
+      </c>
+      <c r="AC251">
+        <v>1.1</v>
+      </c>
+      <c r="AD251">
+        <v>6.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.54</v>
+      </c>
+      <c r="AF251">
+        <v>2.48</v>
+      </c>
+      <c r="AG251">
+        <v>2.37</v>
+      </c>
+      <c r="AH251">
+        <v>1.48</v>
+      </c>
+      <c r="AI251">
+        <v>2</v>
+      </c>
+      <c r="AJ251">
+        <v>1.75</v>
+      </c>
+      <c r="AK251">
+        <v>1.34</v>
+      </c>
+      <c r="AL251">
+        <v>1.36</v>
+      </c>
+      <c r="AM251">
+        <v>1.55</v>
+      </c>
+      <c r="AN251">
+        <v>1.64</v>
+      </c>
+      <c r="AO251">
+        <v>1.09</v>
+      </c>
+      <c r="AP251">
+        <v>1.75</v>
+      </c>
+      <c r="AQ251">
+        <v>1</v>
+      </c>
+      <c r="AR251">
+        <v>1.22</v>
+      </c>
+      <c r="AS251">
+        <v>1.28</v>
+      </c>
+      <c r="AT251">
+        <v>2.5</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>7</v>
+      </c>
+      <c r="AX251">
+        <v>10</v>
+      </c>
+      <c r="AY251">
+        <v>14</v>
+      </c>
+      <c r="AZ251">
+        <v>14</v>
+      </c>
+      <c r="BA251">
+        <v>4</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>9</v>
+      </c>
+      <c r="BD251">
+        <v>1.84</v>
+      </c>
+      <c r="BE251">
+        <v>6.25</v>
+      </c>
+      <c r="BF251">
+        <v>2.18</v>
+      </c>
+      <c r="BG251">
+        <v>1.5</v>
+      </c>
+      <c r="BH251">
+        <v>2.38</v>
+      </c>
+      <c r="BI251">
+        <v>1.84</v>
+      </c>
+      <c r="BJ251">
+        <v>1.84</v>
+      </c>
+      <c r="BK251">
+        <v>2.35</v>
+      </c>
+      <c r="BL251">
+        <v>1.5</v>
+      </c>
+      <c r="BM251">
+        <v>3.05</v>
+      </c>
+      <c r="BN251">
+        <v>1.3</v>
+      </c>
+      <c r="BO251">
+        <v>4.1</v>
+      </c>
+      <c r="BP251">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="345">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1410,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2571,7 +2571,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ10">
         <v>2.08</v>
@@ -4425,7 +4425,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ15">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR15">
         <v>1.84</v>
@@ -5658,7 +5658,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
         <v>1.15</v>
@@ -8133,7 +8133,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>1.54</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ41">
         <v>0.46</v>
@@ -12044,7 +12044,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ52">
         <v>1.67</v>
@@ -13695,7 +13695,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ60">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR60">
         <v>0.97</v>
@@ -16579,7 +16579,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ74">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR74">
         <v>1.29</v>
@@ -17812,7 +17812,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ80">
         <v>0.77</v>
@@ -21523,7 +21523,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR98">
         <v>1.24</v>
@@ -21726,7 +21726,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -25022,7 +25022,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ115">
         <v>0.83</v>
@@ -25849,7 +25849,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
         <v>1.61</v>
@@ -29348,7 +29348,7 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
         <v>0.6899999999999999</v>
@@ -29763,7 +29763,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ138">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR138">
         <v>1.4</v>
@@ -33880,7 +33880,7 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ158">
         <v>1.17</v>
@@ -34295,7 +34295,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ160">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR160">
         <v>1.62</v>
@@ -38206,7 +38206,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ179">
         <v>1.62</v>
@@ -39445,7 +39445,7 @@
         <v>1</v>
       </c>
       <c r="AQ185">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -42326,7 +42326,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ199">
         <v>0.58</v>
@@ -44389,7 +44389,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ209">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -46240,7 +46240,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ218">
         <v>1.75</v>
@@ -47891,7 +47891,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ226">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR226">
         <v>1.51</v>
@@ -49948,7 +49948,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ236">
         <v>0.85</v>
@@ -51393,7 +51393,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ243">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR243">
         <v>1.47</v>
@@ -53117,6 +53117,212 @@
       </c>
       <c r="BP251">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7509839</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45702.6875</v>
+      </c>
+      <c r="F252">
+        <v>26</v>
+      </c>
+      <c r="G252" t="s">
+        <v>78</v>
+      </c>
+      <c r="H252" t="s">
+        <v>87</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>1</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>1</v>
+      </c>
+      <c r="O252" t="s">
+        <v>174</v>
+      </c>
+      <c r="P252" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q252">
+        <v>2.65</v>
+      </c>
+      <c r="R252">
+        <v>2</v>
+      </c>
+      <c r="S252">
+        <v>4</v>
+      </c>
+      <c r="T252">
+        <v>1.44</v>
+      </c>
+      <c r="U252">
+        <v>2.55</v>
+      </c>
+      <c r="V252">
+        <v>3.1</v>
+      </c>
+      <c r="W252">
+        <v>1.32</v>
+      </c>
+      <c r="X252">
+        <v>8.25</v>
+      </c>
+      <c r="Y252">
+        <v>1.06</v>
+      </c>
+      <c r="Z252">
+        <v>2.11</v>
+      </c>
+      <c r="AA252">
+        <v>3.35</v>
+      </c>
+      <c r="AB252">
+        <v>3.79</v>
+      </c>
+      <c r="AC252">
+        <v>1.08</v>
+      </c>
+      <c r="AD252">
+        <v>7.5</v>
+      </c>
+      <c r="AE252">
+        <v>1.37</v>
+      </c>
+      <c r="AF252">
+        <v>2.8</v>
+      </c>
+      <c r="AG252">
+        <v>2.1</v>
+      </c>
+      <c r="AH252">
+        <v>1.6</v>
+      </c>
+      <c r="AI252">
+        <v>1.95</v>
+      </c>
+      <c r="AJ252">
+        <v>1.75</v>
+      </c>
+      <c r="AK252">
+        <v>1.27</v>
+      </c>
+      <c r="AL252">
+        <v>1.31</v>
+      </c>
+      <c r="AM252">
+        <v>1.73</v>
+      </c>
+      <c r="AN252">
+        <v>1.62</v>
+      </c>
+      <c r="AO252">
+        <v>1.46</v>
+      </c>
+      <c r="AP252">
+        <v>1.71</v>
+      </c>
+      <c r="AQ252">
+        <v>1.36</v>
+      </c>
+      <c r="AR252">
+        <v>1.3</v>
+      </c>
+      <c r="AS252">
+        <v>1.19</v>
+      </c>
+      <c r="AT252">
+        <v>2.49</v>
+      </c>
+      <c r="AU252">
+        <v>5</v>
+      </c>
+      <c r="AV252">
+        <v>2</v>
+      </c>
+      <c r="AW252">
+        <v>10</v>
+      </c>
+      <c r="AX252">
+        <v>4</v>
+      </c>
+      <c r="AY252">
+        <v>17</v>
+      </c>
+      <c r="AZ252">
+        <v>6</v>
+      </c>
+      <c r="BA252">
+        <v>5</v>
+      </c>
+      <c r="BB252">
+        <v>2</v>
+      </c>
+      <c r="BC252">
+        <v>7</v>
+      </c>
+      <c r="BD252">
+        <v>1.68</v>
+      </c>
+      <c r="BE252">
+        <v>6.4</v>
+      </c>
+      <c r="BF252">
+        <v>2.43</v>
+      </c>
+      <c r="BG252">
+        <v>1.49</v>
+      </c>
+      <c r="BH252">
+        <v>2.4</v>
+      </c>
+      <c r="BI252">
+        <v>1.81</v>
+      </c>
+      <c r="BJ252">
+        <v>1.89</v>
+      </c>
+      <c r="BK252">
+        <v>2.3</v>
+      </c>
+      <c r="BL252">
+        <v>1.54</v>
+      </c>
+      <c r="BM252">
+        <v>2.95</v>
+      </c>
+      <c r="BN252">
+        <v>1.33</v>
+      </c>
+      <c r="BO252">
+        <v>3.95</v>
+      </c>
+      <c r="BP252">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -742,6 +742,15 @@
     <t>['21', '47', '90+5']</t>
   </si>
   <si>
+    <t>['6', '88']</t>
+  </si>
+  <si>
+    <t>['34', '73']</t>
+  </si>
+  <si>
+    <t>['31', '41', '46']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1049,6 +1058,9 @@
   </si>
   <si>
     <t>['1', '72']</t>
+  </si>
+  <si>
+    <t>['11']</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1872,7 +1884,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1950,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -2078,7 +2090,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2156,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4">
         <v>0.77</v>
@@ -2284,7 +2296,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2365,7 +2377,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ5">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2696,7 +2708,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2777,7 +2789,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3108,7 +3120,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3314,7 +3326,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3601,7 +3613,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3726,7 +3738,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3804,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -3932,7 +3944,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4010,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ13">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -4138,7 +4150,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4756,7 +4768,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5246,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ19">
         <v>0.85</v>
@@ -5374,7 +5386,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5786,7 +5798,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5864,7 +5876,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ22">
         <v>2.08</v>
@@ -6070,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6198,7 +6210,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6279,7 +6291,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR24">
         <v>1.67</v>
@@ -6691,7 +6703,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ26">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -6816,7 +6828,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7515,7 +7527,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ30">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR30">
         <v>1.65</v>
@@ -8052,7 +8064,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8130,7 +8142,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ33">
         <v>1.36</v>
@@ -8464,7 +8476,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8542,10 +8554,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8670,7 +8682,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8748,10 +8760,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ36">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -9163,7 +9175,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ38">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR38">
         <v>1.18</v>
@@ -9288,7 +9300,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9494,7 +9506,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9700,7 +9712,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9906,7 +9918,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10396,7 +10408,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ44">
         <v>0.6899999999999999</v>
@@ -10730,7 +10742,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11017,7 +11029,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ47">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR47">
         <v>1.62</v>
@@ -11142,7 +11154,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11348,7 +11360,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11426,7 +11438,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ49">
         <v>2.08</v>
@@ -11554,7 +11566,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11635,7 +11647,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -11760,7 +11772,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11966,7 +11978,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12047,7 +12059,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12584,7 +12596,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12665,7 +12677,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ55">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR55">
         <v>1.42</v>
@@ -12871,7 +12883,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -13280,7 +13292,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ58">
         <v>1.15</v>
@@ -13408,7 +13420,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13820,7 +13832,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14026,7 +14038,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14310,10 +14322,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ63">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14438,7 +14450,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14516,7 +14528,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ64">
         <v>0.83</v>
@@ -14722,7 +14734,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14850,7 +14862,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15262,7 +15274,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15340,10 +15352,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15674,7 +15686,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15752,7 +15764,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15880,7 +15892,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -15961,7 +15973,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ71">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -16086,7 +16098,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16292,7 +16304,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16498,7 +16510,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16576,7 +16588,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ74">
         <v>1.36</v>
@@ -16910,7 +16922,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17116,7 +17128,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17322,7 +17334,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17403,7 +17415,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ78">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17528,7 +17540,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17734,7 +17746,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18021,7 +18033,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18224,7 +18236,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ82">
         <v>1.25</v>
@@ -18352,7 +18364,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18430,7 +18442,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83">
         <v>1.75</v>
@@ -18558,7 +18570,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18639,7 +18651,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ84">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR84">
         <v>1.72</v>
@@ -18970,7 +18982,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19048,7 +19060,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19176,7 +19188,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19382,7 +19394,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19463,7 +19475,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -19666,7 +19678,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ89">
         <v>0.6899999999999999</v>
@@ -20000,7 +20012,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20081,7 +20093,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR91">
         <v>1.67</v>
@@ -20493,7 +20505,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ93">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
         <v>1.54</v>
@@ -20905,7 +20917,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ95">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -21314,7 +21326,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ97">
         <v>0.77</v>
@@ -21520,7 +21532,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ98">
         <v>1.36</v>
@@ -22344,7 +22356,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ102">
         <v>0.46</v>
@@ -22553,7 +22565,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ103">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR103">
         <v>1.86</v>
@@ -22678,7 +22690,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22884,7 +22896,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -22962,10 +22974,10 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -23580,7 +23592,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ108">
         <v>0.83</v>
@@ -23789,7 +23801,7 @@
         <v>1</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR109">
         <v>1.52</v>
@@ -24532,7 +24544,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24610,7 +24622,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24816,7 +24828,7 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ114">
         <v>1.15</v>
@@ -25356,7 +25368,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25437,7 +25449,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ117">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -25562,7 +25574,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26055,7 +26067,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ120">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR120">
         <v>1.28</v>
@@ -26258,7 +26270,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ121">
         <v>0.6899999999999999</v>
@@ -26386,7 +26398,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26670,7 +26682,7 @@
         <v>2</v>
       </c>
       <c r="AP123">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ123">
         <v>2.08</v>
@@ -26879,7 +26891,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>1.36</v>
@@ -27082,7 +27094,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ125">
         <v>0.46</v>
@@ -27210,7 +27222,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27497,7 +27509,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27622,7 +27634,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27703,7 +27715,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ128">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR128">
         <v>1.36</v>
@@ -27828,7 +27840,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28034,7 +28046,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28240,7 +28252,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28446,7 +28458,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28730,10 +28742,10 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ133">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR133">
         <v>1.46</v>
@@ -28939,7 +28951,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ134">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29142,7 +29154,7 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ135">
         <v>1.75</v>
@@ -29270,7 +29282,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29682,7 +29694,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29760,7 +29772,7 @@
         <v>1.29</v>
       </c>
       <c r="AP138">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ138">
         <v>1.36</v>
@@ -30300,7 +30312,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30381,7 +30393,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR141">
         <v>1.62</v>
@@ -30506,7 +30518,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30712,7 +30724,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30918,7 +30930,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -30996,10 +31008,10 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31330,7 +31342,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31823,7 +31835,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ148">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR148">
         <v>1.81</v>
@@ -31948,7 +31960,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32154,7 +32166,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32566,7 +32578,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32850,7 +32862,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ153">
         <v>0.85</v>
@@ -33056,7 +33068,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154">
         <v>1</v>
@@ -33184,7 +33196,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33468,10 +33480,10 @@
         <v>0.71</v>
       </c>
       <c r="AP156">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ156">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33596,7 +33608,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33883,7 +33895,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ158">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR158">
         <v>1.22</v>
@@ -34008,7 +34020,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34420,7 +34432,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34498,10 +34510,10 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ161">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR161">
         <v>1.67</v>
@@ -34832,7 +34844,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34910,7 +34922,7 @@
         <v>0.38</v>
       </c>
       <c r="AP163">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ163">
         <v>0.6899999999999999</v>
@@ -35244,7 +35256,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35737,7 +35749,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ167">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR167">
         <v>1.43</v>
@@ -35862,7 +35874,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36355,7 +36367,7 @@
         <v>1</v>
       </c>
       <c r="AQ170">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36480,7 +36492,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36767,7 +36779,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ172">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR172">
         <v>1.72</v>
@@ -36970,7 +36982,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37176,7 +37188,7 @@
         <v>0.75</v>
       </c>
       <c r="AP174">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ174">
         <v>1</v>
@@ -37382,7 +37394,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ175">
         <v>0.83</v>
@@ -37794,7 +37806,7 @@
         <v>1.75</v>
       </c>
       <c r="AP177">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ177">
         <v>1.75</v>
@@ -37922,7 +37934,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38128,7 +38140,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38209,7 +38221,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ179">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR179">
         <v>1.23</v>
@@ -38621,7 +38633,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ181">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR181">
         <v>1.41</v>
@@ -39158,7 +39170,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39364,7 +39376,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39442,7 +39454,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ185">
         <v>1.36</v>
@@ -39857,7 +39869,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ187">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -39982,7 +39994,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40269,7 +40281,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ189">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
         <v>1.33</v>
@@ -40600,7 +40612,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40806,7 +40818,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40887,7 +40899,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ192">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR192">
         <v>1.54</v>
@@ -41090,10 +41102,10 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ193">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41296,7 +41308,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ194">
         <v>0.85</v>
@@ -41502,7 +41514,7 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ195">
         <v>0.83</v>
@@ -41708,7 +41720,7 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ196">
         <v>1</v>
@@ -41836,7 +41848,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42329,7 +42341,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ199">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR199">
         <v>1.22</v>
@@ -42454,7 +42466,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42866,7 +42878,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43278,7 +43290,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43356,7 +43368,7 @@
         <v>1.11</v>
       </c>
       <c r="AP204">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ204">
         <v>1.25</v>
@@ -43690,7 +43702,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43896,7 +43908,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44102,7 +44114,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44183,7 +44195,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ208">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR208">
         <v>1.42</v>
@@ -44595,7 +44607,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR210">
         <v>1.56</v>
@@ -44926,7 +44938,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45132,7 +45144,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45622,7 +45634,7 @@
         <v>0.9</v>
       </c>
       <c r="AP215">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ215">
         <v>0.83</v>
@@ -45750,7 +45762,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45956,7 +45968,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46034,10 +46046,10 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ217">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46574,7 +46586,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46652,7 +46664,7 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -46780,7 +46792,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46858,10 +46870,10 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ221">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR221">
         <v>1.33</v>
@@ -46986,7 +46998,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47398,7 +47410,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47604,7 +47616,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47810,7 +47822,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48016,7 +48028,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48097,7 +48109,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ227">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR227">
         <v>1.29</v>
@@ -48222,7 +48234,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48509,7 +48521,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ229">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -48840,7 +48852,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49046,7 +49058,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49536,7 +49548,7 @@
         <v>1.25</v>
       </c>
       <c r="AP234">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ234">
         <v>1.15</v>
@@ -49664,7 +49676,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49745,7 +49757,7 @@
         <v>1</v>
       </c>
       <c r="AQ235">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR235">
         <v>1.39</v>
@@ -49870,7 +49882,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50154,7 +50166,7 @@
         <v>0.75</v>
       </c>
       <c r="AP237">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ237">
         <v>0.6899999999999999</v>
@@ -50363,7 +50375,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ238">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR238">
         <v>1.73</v>
@@ -50488,7 +50500,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50566,10 +50578,10 @@
         <v>1</v>
       </c>
       <c r="AP239">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ239">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR239">
         <v>1.34</v>
@@ -50772,7 +50784,7 @@
         <v>1.09</v>
       </c>
       <c r="AP240">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ240">
         <v>1</v>
@@ -50900,7 +50912,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -50978,7 +50990,7 @@
         <v>0.91</v>
       </c>
       <c r="AP241">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ241">
         <v>0.83</v>
@@ -51187,7 +51199,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ242">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -51518,7 +51530,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -52754,7 +52766,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53323,6 +53335,1036 @@
       </c>
       <c r="BP252">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7509846</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F253">
+        <v>26</v>
+      </c>
+      <c r="G253" t="s">
+        <v>72</v>
+      </c>
+      <c r="H253" t="s">
+        <v>81</v>
+      </c>
+      <c r="I253">
+        <v>1</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253">
+        <v>2</v>
+      </c>
+      <c r="L253">
+        <v>2</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>3</v>
+      </c>
+      <c r="O253" t="s">
+        <v>242</v>
+      </c>
+      <c r="P253" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q253">
+        <v>3.4</v>
+      </c>
+      <c r="R253">
+        <v>1.95</v>
+      </c>
+      <c r="S253">
+        <v>3.6</v>
+      </c>
+      <c r="T253">
+        <v>1.53</v>
+      </c>
+      <c r="U253">
+        <v>2.38</v>
+      </c>
+      <c r="V253">
+        <v>3.5</v>
+      </c>
+      <c r="W253">
+        <v>1.29</v>
+      </c>
+      <c r="X253">
+        <v>11</v>
+      </c>
+      <c r="Y253">
+        <v>1.05</v>
+      </c>
+      <c r="Z253">
+        <v>2.79</v>
+      </c>
+      <c r="AA253">
+        <v>2.98</v>
+      </c>
+      <c r="AB253">
+        <v>2.93</v>
+      </c>
+      <c r="AC253">
+        <v>1.1</v>
+      </c>
+      <c r="AD253">
+        <v>6.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.44</v>
+      </c>
+      <c r="AF253">
+        <v>2.55</v>
+      </c>
+      <c r="AG253">
+        <v>2.25</v>
+      </c>
+      <c r="AH253">
+        <v>1.53</v>
+      </c>
+      <c r="AI253">
+        <v>1.95</v>
+      </c>
+      <c r="AJ253">
+        <v>1.8</v>
+      </c>
+      <c r="AK253">
+        <v>1.4</v>
+      </c>
+      <c r="AL253">
+        <v>1.37</v>
+      </c>
+      <c r="AM253">
+        <v>1.47</v>
+      </c>
+      <c r="AN253">
+        <v>1</v>
+      </c>
+      <c r="AO253">
+        <v>1</v>
+      </c>
+      <c r="AP253">
+        <v>1.15</v>
+      </c>
+      <c r="AQ253">
+        <v>0.92</v>
+      </c>
+      <c r="AR253">
+        <v>1.42</v>
+      </c>
+      <c r="AS253">
+        <v>1.24</v>
+      </c>
+      <c r="AT253">
+        <v>2.66</v>
+      </c>
+      <c r="AU253">
+        <v>9</v>
+      </c>
+      <c r="AV253">
+        <v>2</v>
+      </c>
+      <c r="AW253">
+        <v>9</v>
+      </c>
+      <c r="AX253">
+        <v>9</v>
+      </c>
+      <c r="AY253">
+        <v>19</v>
+      </c>
+      <c r="AZ253">
+        <v>11</v>
+      </c>
+      <c r="BA253">
+        <v>6</v>
+      </c>
+      <c r="BB253">
+        <v>6</v>
+      </c>
+      <c r="BC253">
+        <v>12</v>
+      </c>
+      <c r="BD253">
+        <v>2.02</v>
+      </c>
+      <c r="BE253">
+        <v>6.25</v>
+      </c>
+      <c r="BF253">
+        <v>1.98</v>
+      </c>
+      <c r="BG253">
+        <v>1.53</v>
+      </c>
+      <c r="BH253">
+        <v>2.32</v>
+      </c>
+      <c r="BI253">
+        <v>1.9</v>
+      </c>
+      <c r="BJ253">
+        <v>1.79</v>
+      </c>
+      <c r="BK253">
+        <v>2.4</v>
+      </c>
+      <c r="BL253">
+        <v>1.49</v>
+      </c>
+      <c r="BM253">
+        <v>3.15</v>
+      </c>
+      <c r="BN253">
+        <v>1.29</v>
+      </c>
+      <c r="BO253">
+        <v>4.3</v>
+      </c>
+      <c r="BP253">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7509843</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F254">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>80</v>
+      </c>
+      <c r="H254" t="s">
+        <v>83</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
+      </c>
+      <c r="K254">
+        <v>2</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>2</v>
+      </c>
+      <c r="O254" t="s">
+        <v>208</v>
+      </c>
+      <c r="P254" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q254">
+        <v>4</v>
+      </c>
+      <c r="R254">
+        <v>1.95</v>
+      </c>
+      <c r="S254">
+        <v>3.2</v>
+      </c>
+      <c r="T254">
+        <v>1.53</v>
+      </c>
+      <c r="U254">
+        <v>2.38</v>
+      </c>
+      <c r="V254">
+        <v>3.5</v>
+      </c>
+      <c r="W254">
+        <v>1.29</v>
+      </c>
+      <c r="X254">
+        <v>11</v>
+      </c>
+      <c r="Y254">
+        <v>1.05</v>
+      </c>
+      <c r="Z254">
+        <v>2.98</v>
+      </c>
+      <c r="AA254">
+        <v>3.01</v>
+      </c>
+      <c r="AB254">
+        <v>2.72</v>
+      </c>
+      <c r="AC254">
+        <v>1.1</v>
+      </c>
+      <c r="AD254">
+        <v>6.5</v>
+      </c>
+      <c r="AE254">
+        <v>1.48</v>
+      </c>
+      <c r="AF254">
+        <v>2.37</v>
+      </c>
+      <c r="AG254">
+        <v>2.42</v>
+      </c>
+      <c r="AH254">
+        <v>1.56</v>
+      </c>
+      <c r="AI254">
+        <v>2</v>
+      </c>
+      <c r="AJ254">
+        <v>1.75</v>
+      </c>
+      <c r="AK254">
+        <v>1.53</v>
+      </c>
+      <c r="AL254">
+        <v>1.34</v>
+      </c>
+      <c r="AM254">
+        <v>1.37</v>
+      </c>
+      <c r="AN254">
+        <v>1.67</v>
+      </c>
+      <c r="AO254">
+        <v>1.62</v>
+      </c>
+      <c r="AP254">
+        <v>1.62</v>
+      </c>
+      <c r="AQ254">
+        <v>1.57</v>
+      </c>
+      <c r="AR254">
+        <v>1.44</v>
+      </c>
+      <c r="AS254">
+        <v>1.43</v>
+      </c>
+      <c r="AT254">
+        <v>2.87</v>
+      </c>
+      <c r="AU254">
+        <v>3</v>
+      </c>
+      <c r="AV254">
+        <v>5</v>
+      </c>
+      <c r="AW254">
+        <v>5</v>
+      </c>
+      <c r="AX254">
+        <v>13</v>
+      </c>
+      <c r="AY254">
+        <v>9</v>
+      </c>
+      <c r="AZ254">
+        <v>22</v>
+      </c>
+      <c r="BA254">
+        <v>4</v>
+      </c>
+      <c r="BB254">
+        <v>4</v>
+      </c>
+      <c r="BC254">
+        <v>8</v>
+      </c>
+      <c r="BD254">
+        <v>2.17</v>
+      </c>
+      <c r="BE254">
+        <v>6.25</v>
+      </c>
+      <c r="BF254">
+        <v>1.88</v>
+      </c>
+      <c r="BG254">
+        <v>1.49</v>
+      </c>
+      <c r="BH254">
+        <v>2.43</v>
+      </c>
+      <c r="BI254">
+        <v>1.81</v>
+      </c>
+      <c r="BJ254">
+        <v>1.88</v>
+      </c>
+      <c r="BK254">
+        <v>2.3</v>
+      </c>
+      <c r="BL254">
+        <v>1.53</v>
+      </c>
+      <c r="BM254">
+        <v>2.95</v>
+      </c>
+      <c r="BN254">
+        <v>1.33</v>
+      </c>
+      <c r="BO254">
+        <v>3.95</v>
+      </c>
+      <c r="BP254">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7509845</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F255">
+        <v>26</v>
+      </c>
+      <c r="G255" t="s">
+        <v>84</v>
+      </c>
+      <c r="H255" t="s">
+        <v>70</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>1</v>
+      </c>
+      <c r="L255">
+        <v>2</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>2</v>
+      </c>
+      <c r="O255" t="s">
+        <v>243</v>
+      </c>
+      <c r="P255" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q255">
+        <v>2</v>
+      </c>
+      <c r="R255">
+        <v>2.4</v>
+      </c>
+      <c r="S255">
+        <v>5.5</v>
+      </c>
+      <c r="T255">
+        <v>1.3</v>
+      </c>
+      <c r="U255">
+        <v>3.4</v>
+      </c>
+      <c r="V255">
+        <v>2.5</v>
+      </c>
+      <c r="W255">
+        <v>1.5</v>
+      </c>
+      <c r="X255">
+        <v>6</v>
+      </c>
+      <c r="Y255">
+        <v>1.13</v>
+      </c>
+      <c r="Z255">
+        <v>1.54</v>
+      </c>
+      <c r="AA255">
+        <v>4.6</v>
+      </c>
+      <c r="AB255">
+        <v>5.9</v>
+      </c>
+      <c r="AC255">
+        <v>1.03</v>
+      </c>
+      <c r="AD255">
+        <v>11</v>
+      </c>
+      <c r="AE255">
+        <v>1.19</v>
+      </c>
+      <c r="AF255">
+        <v>4.3</v>
+      </c>
+      <c r="AG255">
+        <v>1.55</v>
+      </c>
+      <c r="AH255">
+        <v>2.2</v>
+      </c>
+      <c r="AI255">
+        <v>1.75</v>
+      </c>
+      <c r="AJ255">
+        <v>2</v>
+      </c>
+      <c r="AK255">
+        <v>1.13</v>
+      </c>
+      <c r="AL255">
+        <v>1.2</v>
+      </c>
+      <c r="AM255">
+        <v>2.5</v>
+      </c>
+      <c r="AN255">
+        <v>2.58</v>
+      </c>
+      <c r="AO255">
+        <v>1.17</v>
+      </c>
+      <c r="AP255">
+        <v>2.62</v>
+      </c>
+      <c r="AQ255">
+        <v>1.08</v>
+      </c>
+      <c r="AR255">
+        <v>1.73</v>
+      </c>
+      <c r="AS255">
+        <v>1.24</v>
+      </c>
+      <c r="AT255">
+        <v>2.97</v>
+      </c>
+      <c r="AU255">
+        <v>5</v>
+      </c>
+      <c r="AV255">
+        <v>2</v>
+      </c>
+      <c r="AW255">
+        <v>3</v>
+      </c>
+      <c r="AX255">
+        <v>8</v>
+      </c>
+      <c r="AY255">
+        <v>9</v>
+      </c>
+      <c r="AZ255">
+        <v>10</v>
+      </c>
+      <c r="BA255">
+        <v>2</v>
+      </c>
+      <c r="BB255">
+        <v>2</v>
+      </c>
+      <c r="BC255">
+        <v>4</v>
+      </c>
+      <c r="BD255">
+        <v>1.48</v>
+      </c>
+      <c r="BE255">
+        <v>6.75</v>
+      </c>
+      <c r="BF255">
+        <v>3.05</v>
+      </c>
+      <c r="BG255">
+        <v>1.35</v>
+      </c>
+      <c r="BH255">
+        <v>2.9</v>
+      </c>
+      <c r="BI255">
+        <v>1.58</v>
+      </c>
+      <c r="BJ255">
+        <v>2.18</v>
+      </c>
+      <c r="BK255">
+        <v>1.96</v>
+      </c>
+      <c r="BL255">
+        <v>1.74</v>
+      </c>
+      <c r="BM255">
+        <v>2.48</v>
+      </c>
+      <c r="BN255">
+        <v>1.46</v>
+      </c>
+      <c r="BO255">
+        <v>3.2</v>
+      </c>
+      <c r="BP255">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7509838</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45703.45833333334</v>
+      </c>
+      <c r="F256">
+        <v>26</v>
+      </c>
+      <c r="G256" t="s">
+        <v>86</v>
+      </c>
+      <c r="H256" t="s">
+        <v>74</v>
+      </c>
+      <c r="I256">
+        <v>2</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>2</v>
+      </c>
+      <c r="L256">
+        <v>3</v>
+      </c>
+      <c r="M256">
+        <v>2</v>
+      </c>
+      <c r="N256">
+        <v>5</v>
+      </c>
+      <c r="O256" t="s">
+        <v>244</v>
+      </c>
+      <c r="P256" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q256">
+        <v>3.2</v>
+      </c>
+      <c r="R256">
+        <v>2</v>
+      </c>
+      <c r="S256">
+        <v>3.75</v>
+      </c>
+      <c r="T256">
+        <v>1.5</v>
+      </c>
+      <c r="U256">
+        <v>2.5</v>
+      </c>
+      <c r="V256">
+        <v>3.4</v>
+      </c>
+      <c r="W256">
+        <v>1.3</v>
+      </c>
+      <c r="X256">
+        <v>10</v>
+      </c>
+      <c r="Y256">
+        <v>1.06</v>
+      </c>
+      <c r="Z256">
+        <v>2.54</v>
+      </c>
+      <c r="AA256">
+        <v>3.15</v>
+      </c>
+      <c r="AB256">
+        <v>3.1</v>
+      </c>
+      <c r="AC256">
+        <v>1.08</v>
+      </c>
+      <c r="AD256">
+        <v>7.5</v>
+      </c>
+      <c r="AE256">
+        <v>1.39</v>
+      </c>
+      <c r="AF256">
+        <v>2.7</v>
+      </c>
+      <c r="AG256">
+        <v>2.15</v>
+      </c>
+      <c r="AH256">
+        <v>1.57</v>
+      </c>
+      <c r="AI256">
+        <v>1.95</v>
+      </c>
+      <c r="AJ256">
+        <v>1.8</v>
+      </c>
+      <c r="AK256">
+        <v>1.38</v>
+      </c>
+      <c r="AL256">
+        <v>1.34</v>
+      </c>
+      <c r="AM256">
+        <v>1.53</v>
+      </c>
+      <c r="AN256">
+        <v>1.75</v>
+      </c>
+      <c r="AO256">
+        <v>0.58</v>
+      </c>
+      <c r="AP256">
+        <v>1.85</v>
+      </c>
+      <c r="AQ256">
+        <v>0.54</v>
+      </c>
+      <c r="AR256">
+        <v>1.38</v>
+      </c>
+      <c r="AS256">
+        <v>1.09</v>
+      </c>
+      <c r="AT256">
+        <v>2.47</v>
+      </c>
+      <c r="AU256">
+        <v>5</v>
+      </c>
+      <c r="AV256">
+        <v>6</v>
+      </c>
+      <c r="AW256">
+        <v>10</v>
+      </c>
+      <c r="AX256">
+        <v>13</v>
+      </c>
+      <c r="AY256">
+        <v>16</v>
+      </c>
+      <c r="AZ256">
+        <v>21</v>
+      </c>
+      <c r="BA256">
+        <v>1</v>
+      </c>
+      <c r="BB256">
+        <v>9</v>
+      </c>
+      <c r="BC256">
+        <v>10</v>
+      </c>
+      <c r="BD256">
+        <v>1.9</v>
+      </c>
+      <c r="BE256">
+        <v>6.25</v>
+      </c>
+      <c r="BF256">
+        <v>2.1</v>
+      </c>
+      <c r="BG256">
+        <v>1.49</v>
+      </c>
+      <c r="BH256">
+        <v>2.4</v>
+      </c>
+      <c r="BI256">
+        <v>1.82</v>
+      </c>
+      <c r="BJ256">
+        <v>1.86</v>
+      </c>
+      <c r="BK256">
+        <v>2.32</v>
+      </c>
+      <c r="BL256">
+        <v>1.52</v>
+      </c>
+      <c r="BM256">
+        <v>3.05</v>
+      </c>
+      <c r="BN256">
+        <v>1.3</v>
+      </c>
+      <c r="BO256">
+        <v>4.1</v>
+      </c>
+      <c r="BP256">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7509837</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45703.55208333334</v>
+      </c>
+      <c r="F257">
+        <v>26</v>
+      </c>
+      <c r="G257" t="s">
+        <v>71</v>
+      </c>
+      <c r="H257" t="s">
+        <v>82</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>1</v>
+      </c>
+      <c r="N257">
+        <v>2</v>
+      </c>
+      <c r="O257" t="s">
+        <v>91</v>
+      </c>
+      <c r="P257" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q257">
+        <v>3.4</v>
+      </c>
+      <c r="R257">
+        <v>1.98</v>
+      </c>
+      <c r="S257">
+        <v>3.1</v>
+      </c>
+      <c r="T257">
+        <v>1.46</v>
+      </c>
+      <c r="U257">
+        <v>2.5</v>
+      </c>
+      <c r="V257">
+        <v>3.1</v>
+      </c>
+      <c r="W257">
+        <v>1.32</v>
+      </c>
+      <c r="X257">
+        <v>8.5</v>
+      </c>
+      <c r="Y257">
+        <v>1.06</v>
+      </c>
+      <c r="Z257">
+        <v>2.95</v>
+      </c>
+      <c r="AA257">
+        <v>3.19</v>
+      </c>
+      <c r="AB257">
+        <v>2.62</v>
+      </c>
+      <c r="AC257">
+        <v>1.07</v>
+      </c>
+      <c r="AD257">
+        <v>8</v>
+      </c>
+      <c r="AE257">
+        <v>1.38</v>
+      </c>
+      <c r="AF257">
+        <v>2.8</v>
+      </c>
+      <c r="AG257">
+        <v>2.1</v>
+      </c>
+      <c r="AH257">
+        <v>1.6</v>
+      </c>
+      <c r="AI257">
+        <v>1.88</v>
+      </c>
+      <c r="AJ257">
+        <v>1.8</v>
+      </c>
+      <c r="AK257">
+        <v>1.5</v>
+      </c>
+      <c r="AL257">
+        <v>1.33</v>
+      </c>
+      <c r="AM257">
+        <v>1.41</v>
+      </c>
+      <c r="AN257">
+        <v>1.62</v>
+      </c>
+      <c r="AO257">
+        <v>1.67</v>
+      </c>
+      <c r="AP257">
+        <v>1.57</v>
+      </c>
+      <c r="AQ257">
+        <v>1.62</v>
+      </c>
+      <c r="AR257">
+        <v>1.38</v>
+      </c>
+      <c r="AS257">
+        <v>1.45</v>
+      </c>
+      <c r="AT257">
+        <v>2.83</v>
+      </c>
+      <c r="AU257">
+        <v>3</v>
+      </c>
+      <c r="AV257">
+        <v>6</v>
+      </c>
+      <c r="AW257">
+        <v>11</v>
+      </c>
+      <c r="AX257">
+        <v>12</v>
+      </c>
+      <c r="AY257">
+        <v>20</v>
+      </c>
+      <c r="AZ257">
+        <v>22</v>
+      </c>
+      <c r="BA257">
+        <v>3</v>
+      </c>
+      <c r="BB257">
+        <v>5</v>
+      </c>
+      <c r="BC257">
+        <v>8</v>
+      </c>
+      <c r="BD257">
+        <v>2.07</v>
+      </c>
+      <c r="BE257">
+        <v>6.4</v>
+      </c>
+      <c r="BF257">
+        <v>1.93</v>
+      </c>
+      <c r="BG257">
+        <v>1.35</v>
+      </c>
+      <c r="BH257">
+        <v>2.9</v>
+      </c>
+      <c r="BI257">
+        <v>1.58</v>
+      </c>
+      <c r="BJ257">
+        <v>2.18</v>
+      </c>
+      <c r="BK257">
+        <v>1.96</v>
+      </c>
+      <c r="BL257">
+        <v>1.74</v>
+      </c>
+      <c r="BM257">
+        <v>2.48</v>
+      </c>
+      <c r="BN257">
+        <v>1.47</v>
+      </c>
+      <c r="BO257">
+        <v>3.2</v>
+      </c>
+      <c r="BP257">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="354">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,18 @@
     <t>['31', '41', '46']</t>
   </si>
   <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['45', '58', '86']</t>
+  </si>
+  <si>
+    <t>['26', '68']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1061,6 +1073,9 @@
   </si>
   <si>
     <t>['11']</t>
+  </si>
+  <si>
+    <t>['46', '57']</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1884,7 +1899,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2090,7 +2105,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2296,7 +2311,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2708,7 +2723,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2786,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ7">
         <v>0.92</v>
@@ -2992,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ8">
         <v>0.46</v>
@@ -3120,7 +3135,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3201,7 +3216,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ9">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3326,7 +3341,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3738,7 +3753,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3944,7 +3959,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4150,7 +4165,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4768,7 +4783,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5386,7 +5401,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5467,7 +5482,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ20">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5798,7 +5813,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6210,7 +6225,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6497,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="AQ25">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6828,7 +6843,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7112,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ28">
         <v>0.77</v>
@@ -7318,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ29">
         <v>1.25</v>
@@ -7730,10 +7745,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ31">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -8064,7 +8079,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8476,7 +8491,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8682,7 +8697,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8966,7 +8981,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ37">
         <v>1.15</v>
@@ -9300,7 +9315,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9378,10 +9393,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ39">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9506,7 +9521,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9712,7 +9727,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9918,7 +9933,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -9996,7 +10011,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ42">
         <v>0.77</v>
@@ -10411,7 +10426,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ44">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10742,7 +10757,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10820,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11154,7 +11169,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11360,7 +11375,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11566,7 +11581,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11772,7 +11787,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11853,7 +11868,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ51">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -11978,7 +11993,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12468,7 +12483,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54">
         <v>0.85</v>
@@ -12596,7 +12611,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13420,7 +13435,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13498,7 +13513,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13832,7 +13847,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14038,7 +14053,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14450,7 +14465,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14531,7 +14546,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ64">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14862,7 +14877,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -14940,10 +14955,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ66">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15146,10 +15161,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ67">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -15274,7 +15289,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15686,7 +15701,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15892,7 +15907,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16098,7 +16113,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16304,7 +16319,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16382,7 +16397,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16510,7 +16525,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16922,7 +16937,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17128,7 +17143,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17334,7 +17349,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17540,7 +17555,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17746,7 +17761,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18030,7 +18045,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ81">
         <v>0.54</v>
@@ -18364,7 +18379,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18445,7 +18460,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ83">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -18570,7 +18585,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18857,7 +18872,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -18982,7 +18997,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19188,7 +19203,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19394,7 +19409,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19472,7 +19487,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ88">
         <v>1.62</v>
@@ -19681,7 +19696,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ89">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -20012,7 +20027,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20090,7 +20105,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ91">
         <v>0.92</v>
@@ -20502,7 +20517,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ93">
         <v>1.08</v>
@@ -21120,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21944,10 +21959,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -22153,7 +22168,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ101">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22690,7 +22705,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22768,7 +22783,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ104">
         <v>2.08</v>
@@ -22896,7 +22911,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23183,7 +23198,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ106">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -24544,7 +24559,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25240,7 +25255,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25368,7 +25383,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25574,7 +25589,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25655,7 +25670,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ118">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -25858,7 +25873,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ119">
         <v>1.36</v>
@@ -26273,7 +26288,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ121">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26398,7 +26413,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26476,7 +26491,7 @@
         <v>1.57</v>
       </c>
       <c r="AP122">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -27222,7 +27237,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27303,7 +27318,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ126">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -27634,7 +27649,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27712,7 +27727,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ128">
         <v>1.57</v>
@@ -27840,7 +27855,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28046,7 +28061,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28252,7 +28267,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28458,7 +28473,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28948,7 +28963,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ134">
         <v>1.08</v>
@@ -29157,7 +29172,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ135">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -29282,7 +29297,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29363,7 +29378,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29566,7 +29581,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29694,7 +29709,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30312,7 +30327,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30390,7 +30405,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ141">
         <v>0.92</v>
@@ -30518,7 +30533,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30724,7 +30739,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30930,7 +30945,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31342,7 +31357,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31832,7 +31847,7 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ148">
         <v>1.57</v>
@@ -31960,7 +31975,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32041,7 +32056,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ149">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32166,7 +32181,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32244,7 +32259,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ150">
         <v>0.85</v>
@@ -32578,7 +32593,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32656,7 +32671,7 @@
         <v>0.86</v>
       </c>
       <c r="AP152">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -33196,7 +33211,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33277,7 +33292,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ155">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -33608,7 +33623,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34020,7 +34035,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34432,7 +34447,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34844,7 +34859,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34925,7 +34940,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ163">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35256,7 +35271,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35334,7 +35349,7 @@
         <v>2.25</v>
       </c>
       <c r="AP165">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ165">
         <v>2.08</v>
@@ -35540,10 +35555,10 @@
         <v>1.43</v>
       </c>
       <c r="AP166">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ166">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35874,7 +35889,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -35952,7 +35967,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ168">
         <v>1.25</v>
@@ -36492,7 +36507,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37397,7 +37412,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ175">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37809,7 +37824,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ177">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -37934,7 +37949,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38140,7 +38155,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38424,7 +38439,7 @@
         <v>0.63</v>
       </c>
       <c r="AP180">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ180">
         <v>0.85</v>
@@ -39170,7 +39185,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39251,7 +39266,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ184">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39376,7 +39391,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39866,7 +39881,7 @@
         <v>1.56</v>
       </c>
       <c r="AP187">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ187">
         <v>1.62</v>
@@ -39994,7 +40009,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40278,7 +40293,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ189">
         <v>0.54</v>
@@ -40484,7 +40499,7 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40612,7 +40627,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40818,7 +40833,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41517,7 +41532,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ195">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41848,7 +41863,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42466,7 +42481,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42544,7 +42559,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ200">
         <v>0.83</v>
@@ -42753,7 +42768,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ201">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42878,7 +42893,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43290,7 +43305,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43574,7 +43589,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ205">
         <v>0.77</v>
@@ -43702,7 +43717,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43908,7 +43923,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -43989,7 +44004,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ207">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -44114,7 +44129,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44192,7 +44207,7 @@
         <v>1.7</v>
       </c>
       <c r="AP208">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ208">
         <v>1.62</v>
@@ -44398,7 +44413,7 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ209">
         <v>1.36</v>
@@ -44938,7 +44953,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45144,7 +45159,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45225,7 +45240,7 @@
         <v>1</v>
       </c>
       <c r="AQ213">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR213">
         <v>1.3</v>
@@ -45431,7 +45446,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ214">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR214">
         <v>1.56</v>
@@ -45762,7 +45777,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45968,7 +45983,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46255,7 +46270,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ218">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR218">
         <v>1.25</v>
@@ -46458,7 +46473,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ219">
         <v>1.15</v>
@@ -46586,7 +46601,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46792,7 +46807,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46998,7 +47013,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47282,7 +47297,7 @@
         <v>0.55</v>
       </c>
       <c r="AP223">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ223">
         <v>0.46</v>
@@ -47410,7 +47425,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47488,7 +47503,7 @@
         <v>0.91</v>
       </c>
       <c r="AP224">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -47616,7 +47631,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47694,7 +47709,7 @@
         <v>1.1</v>
       </c>
       <c r="AP225">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -47822,7 +47837,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48028,7 +48043,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48234,7 +48249,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48852,7 +48867,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49058,7 +49073,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49136,10 +49151,10 @@
         <v>1.64</v>
       </c>
       <c r="AP232">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ232">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR232">
         <v>1.79</v>
@@ -49345,7 +49360,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ233">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR233">
         <v>1.42</v>
@@ -49676,7 +49691,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49882,7 +49897,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50169,7 +50184,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ237">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AR237">
         <v>1.46</v>
@@ -50500,7 +50515,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50912,7 +50927,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51530,7 +51545,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51814,7 +51829,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ245">
         <v>1.25</v>
@@ -52766,7 +52781,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53050,7 +53065,7 @@
         <v>1.09</v>
       </c>
       <c r="AP251">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ251">
         <v>1</v>
@@ -53384,7 +53399,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53590,7 +53605,7 @@
         <v>208</v>
       </c>
       <c r="P254" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q254">
         <v>4</v>
@@ -54365,6 +54380,830 @@
       </c>
       <c r="BP257">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7509841</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F258">
+        <v>26</v>
+      </c>
+      <c r="G258" t="s">
+        <v>75</v>
+      </c>
+      <c r="H258" t="s">
+        <v>77</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258">
+        <v>1</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>2</v>
+      </c>
+      <c r="O258" t="s">
+        <v>245</v>
+      </c>
+      <c r="P258" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q258">
+        <v>3.25</v>
+      </c>
+      <c r="R258">
+        <v>1.9</v>
+      </c>
+      <c r="S258">
+        <v>3.5</v>
+      </c>
+      <c r="T258">
+        <v>1.52</v>
+      </c>
+      <c r="U258">
+        <v>2.35</v>
+      </c>
+      <c r="V258">
+        <v>3.3</v>
+      </c>
+      <c r="W258">
+        <v>1.28</v>
+      </c>
+      <c r="X258">
+        <v>9.5</v>
+      </c>
+      <c r="Y258">
+        <v>1.05</v>
+      </c>
+      <c r="Z258">
+        <v>2.75</v>
+      </c>
+      <c r="AA258">
+        <v>3.07</v>
+      </c>
+      <c r="AB258">
+        <v>2.89</v>
+      </c>
+      <c r="AC258">
+        <v>1.1</v>
+      </c>
+      <c r="AD258">
+        <v>6.6</v>
+      </c>
+      <c r="AE258">
+        <v>1.5</v>
+      </c>
+      <c r="AF258">
+        <v>2.4</v>
+      </c>
+      <c r="AG258">
+        <v>2.15</v>
+      </c>
+      <c r="AH258">
+        <v>1.57</v>
+      </c>
+      <c r="AI258">
+        <v>2</v>
+      </c>
+      <c r="AJ258">
+        <v>1.7</v>
+      </c>
+      <c r="AK258">
+        <v>1.4</v>
+      </c>
+      <c r="AL258">
+        <v>1.37</v>
+      </c>
+      <c r="AM258">
+        <v>1.47</v>
+      </c>
+      <c r="AN258">
+        <v>0.92</v>
+      </c>
+      <c r="AO258">
+        <v>1</v>
+      </c>
+      <c r="AP258">
+        <v>0.93</v>
+      </c>
+      <c r="AQ258">
+        <v>1</v>
+      </c>
+      <c r="AR258">
+        <v>1.41</v>
+      </c>
+      <c r="AS258">
+        <v>1.33</v>
+      </c>
+      <c r="AT258">
+        <v>2.74</v>
+      </c>
+      <c r="AU258">
+        <v>8</v>
+      </c>
+      <c r="AV258">
+        <v>3</v>
+      </c>
+      <c r="AW258">
+        <v>10</v>
+      </c>
+      <c r="AX258">
+        <v>9</v>
+      </c>
+      <c r="AY258">
+        <v>21</v>
+      </c>
+      <c r="AZ258">
+        <v>12</v>
+      </c>
+      <c r="BA258">
+        <v>8</v>
+      </c>
+      <c r="BB258">
+        <v>3</v>
+      </c>
+      <c r="BC258">
+        <v>11</v>
+      </c>
+      <c r="BD258">
+        <v>1.96</v>
+      </c>
+      <c r="BE258">
+        <v>6.25</v>
+      </c>
+      <c r="BF258">
+        <v>2.05</v>
+      </c>
+      <c r="BG258">
+        <v>1.55</v>
+      </c>
+      <c r="BH258">
+        <v>2.28</v>
+      </c>
+      <c r="BI258">
+        <v>1.92</v>
+      </c>
+      <c r="BJ258">
+        <v>1.78</v>
+      </c>
+      <c r="BK258">
+        <v>2.45</v>
+      </c>
+      <c r="BL258">
+        <v>1.48</v>
+      </c>
+      <c r="BM258">
+        <v>3.25</v>
+      </c>
+      <c r="BN258">
+        <v>1.28</v>
+      </c>
+      <c r="BO258">
+        <v>4.35</v>
+      </c>
+      <c r="BP258">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7509842</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F259">
+        <v>26</v>
+      </c>
+      <c r="G259" t="s">
+        <v>88</v>
+      </c>
+      <c r="H259" t="s">
+        <v>79</v>
+      </c>
+      <c r="I259">
+        <v>1</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>3</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
+      </c>
+      <c r="N259">
+        <v>3</v>
+      </c>
+      <c r="O259" t="s">
+        <v>246</v>
+      </c>
+      <c r="P259" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q259">
+        <v>2.8</v>
+      </c>
+      <c r="R259">
+        <v>1.9</v>
+      </c>
+      <c r="S259">
+        <v>4.2</v>
+      </c>
+      <c r="T259">
+        <v>1.53</v>
+      </c>
+      <c r="U259">
+        <v>2.3</v>
+      </c>
+      <c r="V259">
+        <v>3.4</v>
+      </c>
+      <c r="W259">
+        <v>1.27</v>
+      </c>
+      <c r="X259">
+        <v>9.75</v>
+      </c>
+      <c r="Y259">
+        <v>1.04</v>
+      </c>
+      <c r="Z259">
+        <v>2.27</v>
+      </c>
+      <c r="AA259">
+        <v>3.06</v>
+      </c>
+      <c r="AB259">
+        <v>3.74</v>
+      </c>
+      <c r="AC259">
+        <v>1.1</v>
+      </c>
+      <c r="AD259">
+        <v>6.5</v>
+      </c>
+      <c r="AE259">
+        <v>1.47</v>
+      </c>
+      <c r="AF259">
+        <v>2.44</v>
+      </c>
+      <c r="AG259">
+        <v>2.3</v>
+      </c>
+      <c r="AH259">
+        <v>1.5</v>
+      </c>
+      <c r="AI259">
+        <v>2.1</v>
+      </c>
+      <c r="AJ259">
+        <v>1.65</v>
+      </c>
+      <c r="AK259">
+        <v>1.27</v>
+      </c>
+      <c r="AL259">
+        <v>1.35</v>
+      </c>
+      <c r="AM259">
+        <v>1.68</v>
+      </c>
+      <c r="AN259">
+        <v>1.75</v>
+      </c>
+      <c r="AO259">
+        <v>0.83</v>
+      </c>
+      <c r="AP259">
+        <v>1.85</v>
+      </c>
+      <c r="AQ259">
+        <v>0.77</v>
+      </c>
+      <c r="AR259">
+        <v>1.26</v>
+      </c>
+      <c r="AS259">
+        <v>1.35</v>
+      </c>
+      <c r="AT259">
+        <v>2.61</v>
+      </c>
+      <c r="AU259">
+        <v>5</v>
+      </c>
+      <c r="AV259">
+        <v>7</v>
+      </c>
+      <c r="AW259">
+        <v>4</v>
+      </c>
+      <c r="AX259">
+        <v>12</v>
+      </c>
+      <c r="AY259">
+        <v>10</v>
+      </c>
+      <c r="AZ259">
+        <v>19</v>
+      </c>
+      <c r="BA259">
+        <v>4</v>
+      </c>
+      <c r="BB259">
+        <v>5</v>
+      </c>
+      <c r="BC259">
+        <v>9</v>
+      </c>
+      <c r="BD259">
+        <v>1.72</v>
+      </c>
+      <c r="BE259">
+        <v>6.5</v>
+      </c>
+      <c r="BF259">
+        <v>2.38</v>
+      </c>
+      <c r="BG259">
+        <v>1.38</v>
+      </c>
+      <c r="BH259">
+        <v>2.7</v>
+      </c>
+      <c r="BI259">
+        <v>1.65</v>
+      </c>
+      <c r="BJ259">
+        <v>2.08</v>
+      </c>
+      <c r="BK259">
+        <v>2.02</v>
+      </c>
+      <c r="BL259">
+        <v>1.68</v>
+      </c>
+      <c r="BM259">
+        <v>2.55</v>
+      </c>
+      <c r="BN259">
+        <v>1.43</v>
+      </c>
+      <c r="BO259">
+        <v>3.4</v>
+      </c>
+      <c r="BP259">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7509844</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45704.45833333334</v>
+      </c>
+      <c r="F260">
+        <v>26</v>
+      </c>
+      <c r="G260" t="s">
+        <v>89</v>
+      </c>
+      <c r="H260" t="s">
+        <v>85</v>
+      </c>
+      <c r="I260">
+        <v>1</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>2</v>
+      </c>
+      <c r="M260">
+        <v>2</v>
+      </c>
+      <c r="N260">
+        <v>4</v>
+      </c>
+      <c r="O260" t="s">
+        <v>247</v>
+      </c>
+      <c r="P260" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q260">
+        <v>2.3</v>
+      </c>
+      <c r="R260">
+        <v>2.1</v>
+      </c>
+      <c r="S260">
+        <v>4.75</v>
+      </c>
+      <c r="T260">
+        <v>1.39</v>
+      </c>
+      <c r="U260">
+        <v>2.75</v>
+      </c>
+      <c r="V260">
+        <v>2.7</v>
+      </c>
+      <c r="W260">
+        <v>1.4</v>
+      </c>
+      <c r="X260">
+        <v>7</v>
+      </c>
+      <c r="Y260">
+        <v>1.09</v>
+      </c>
+      <c r="Z260">
+        <v>1.78</v>
+      </c>
+      <c r="AA260">
+        <v>3.25</v>
+      </c>
+      <c r="AB260">
+        <v>6.2</v>
+      </c>
+      <c r="AC260">
+        <v>1.06</v>
+      </c>
+      <c r="AD260">
+        <v>8.5</v>
+      </c>
+      <c r="AE260">
+        <v>1.28</v>
+      </c>
+      <c r="AF260">
+        <v>3.35</v>
+      </c>
+      <c r="AG260">
+        <v>1.93</v>
+      </c>
+      <c r="AH260">
+        <v>1.88</v>
+      </c>
+      <c r="AI260">
+        <v>1.83</v>
+      </c>
+      <c r="AJ260">
+        <v>1.85</v>
+      </c>
+      <c r="AK260">
+        <v>1.18</v>
+      </c>
+      <c r="AL260">
+        <v>1.28</v>
+      </c>
+      <c r="AM260">
+        <v>2.05</v>
+      </c>
+      <c r="AN260">
+        <v>1.5</v>
+      </c>
+      <c r="AO260">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP260">
+        <v>1.46</v>
+      </c>
+      <c r="AQ260">
+        <v>0.71</v>
+      </c>
+      <c r="AR260">
+        <v>1.76</v>
+      </c>
+      <c r="AS260">
+        <v>1.23</v>
+      </c>
+      <c r="AT260">
+        <v>2.99</v>
+      </c>
+      <c r="AU260">
+        <v>5</v>
+      </c>
+      <c r="AV260">
+        <v>5</v>
+      </c>
+      <c r="AW260">
+        <v>11</v>
+      </c>
+      <c r="AX260">
+        <v>12</v>
+      </c>
+      <c r="AY260">
+        <v>18</v>
+      </c>
+      <c r="AZ260">
+        <v>21</v>
+      </c>
+      <c r="BA260">
+        <v>6</v>
+      </c>
+      <c r="BB260">
+        <v>9</v>
+      </c>
+      <c r="BC260">
+        <v>15</v>
+      </c>
+      <c r="BD260">
+        <v>1.46</v>
+      </c>
+      <c r="BE260">
+        <v>6.75</v>
+      </c>
+      <c r="BF260">
+        <v>3.05</v>
+      </c>
+      <c r="BG260">
+        <v>1.41</v>
+      </c>
+      <c r="BH260">
+        <v>2.65</v>
+      </c>
+      <c r="BI260">
+        <v>1.7</v>
+      </c>
+      <c r="BJ260">
+        <v>2</v>
+      </c>
+      <c r="BK260">
+        <v>2.12</v>
+      </c>
+      <c r="BL260">
+        <v>1.63</v>
+      </c>
+      <c r="BM260">
+        <v>2.75</v>
+      </c>
+      <c r="BN260">
+        <v>1.38</v>
+      </c>
+      <c r="BO260">
+        <v>3.65</v>
+      </c>
+      <c r="BP260">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7509840</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45704.55208333334</v>
+      </c>
+      <c r="F261">
+        <v>26</v>
+      </c>
+      <c r="G261" t="s">
+        <v>76</v>
+      </c>
+      <c r="H261" t="s">
+        <v>73</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+      <c r="J261">
+        <v>1</v>
+      </c>
+      <c r="K261">
+        <v>1</v>
+      </c>
+      <c r="L261">
+        <v>1</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>2</v>
+      </c>
+      <c r="O261" t="s">
+        <v>248</v>
+      </c>
+      <c r="P261" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q261">
+        <v>3.2</v>
+      </c>
+      <c r="R261">
+        <v>1.93</v>
+      </c>
+      <c r="S261">
+        <v>3.4</v>
+      </c>
+      <c r="T261">
+        <v>1.49</v>
+      </c>
+      <c r="U261">
+        <v>2.45</v>
+      </c>
+      <c r="V261">
+        <v>3.2</v>
+      </c>
+      <c r="W261">
+        <v>1.3</v>
+      </c>
+      <c r="X261">
+        <v>9</v>
+      </c>
+      <c r="Y261">
+        <v>1.06</v>
+      </c>
+      <c r="Z261">
+        <v>2.72</v>
+      </c>
+      <c r="AA261">
+        <v>3.12</v>
+      </c>
+      <c r="AB261">
+        <v>2.88</v>
+      </c>
+      <c r="AC261">
+        <v>1.09</v>
+      </c>
+      <c r="AD261">
+        <v>7</v>
+      </c>
+      <c r="AE261">
+        <v>1.42</v>
+      </c>
+      <c r="AF261">
+        <v>2.8</v>
+      </c>
+      <c r="AG261">
+        <v>2.2</v>
+      </c>
+      <c r="AH261">
+        <v>1.55</v>
+      </c>
+      <c r="AI261">
+        <v>1.95</v>
+      </c>
+      <c r="AJ261">
+        <v>1.75</v>
+      </c>
+      <c r="AK261">
+        <v>1.43</v>
+      </c>
+      <c r="AL261">
+        <v>1.35</v>
+      </c>
+      <c r="AM261">
+        <v>1.47</v>
+      </c>
+      <c r="AN261">
+        <v>1.83</v>
+      </c>
+      <c r="AO261">
+        <v>1.75</v>
+      </c>
+      <c r="AP261">
+        <v>1.77</v>
+      </c>
+      <c r="AQ261">
+        <v>1.69</v>
+      </c>
+      <c r="AR261">
+        <v>1.47</v>
+      </c>
+      <c r="AS261">
+        <v>1.11</v>
+      </c>
+      <c r="AT261">
+        <v>2.58</v>
+      </c>
+      <c r="AU261">
+        <v>4</v>
+      </c>
+      <c r="AV261">
+        <v>4</v>
+      </c>
+      <c r="AW261">
+        <v>2</v>
+      </c>
+      <c r="AX261">
+        <v>13</v>
+      </c>
+      <c r="AY261">
+        <v>7</v>
+      </c>
+      <c r="AZ261">
+        <v>19</v>
+      </c>
+      <c r="BA261">
+        <v>1</v>
+      </c>
+      <c r="BB261">
+        <v>2</v>
+      </c>
+      <c r="BC261">
+        <v>3</v>
+      </c>
+      <c r="BD261">
+        <v>1.97</v>
+      </c>
+      <c r="BE261">
+        <v>6.25</v>
+      </c>
+      <c r="BF261">
+        <v>2.05</v>
+      </c>
+      <c r="BG261">
+        <v>1.5</v>
+      </c>
+      <c r="BH261">
+        <v>2.4</v>
+      </c>
+      <c r="BI261">
+        <v>1.84</v>
+      </c>
+      <c r="BJ261">
+        <v>1.84</v>
+      </c>
+      <c r="BK261">
+        <v>2.33</v>
+      </c>
+      <c r="BL261">
+        <v>1.5</v>
+      </c>
+      <c r="BM261">
+        <v>3.05</v>
+      </c>
+      <c r="BN261">
+        <v>1.3</v>
+      </c>
+      <c r="BO261">
+        <v>4.1</v>
+      </c>
+      <c r="BP261">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="354">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1437,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3422,7 +3422,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ10">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -5894,7 +5894,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ22">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -11456,7 +11456,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ49">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -12280,7 +12280,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ53">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -13101,7 +13101,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -16191,7 +16191,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ72">
         <v>1.15</v>
@@ -19284,7 +19284,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ87">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -22165,7 +22165,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ101">
         <v>0.71</v>
@@ -22786,7 +22786,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ104">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -26079,7 +26079,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ120">
         <v>1.08</v>
@@ -26700,7 +26700,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ123">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -30614,7 +30614,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ142">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30817,7 +30817,7 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ143">
         <v>1.25</v>
@@ -35352,7 +35352,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ165">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35761,7 +35761,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ167">
         <v>1.57</v>
@@ -38854,7 +38854,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ182">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -40705,7 +40705,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ191">
         <v>0.46</v>
@@ -42765,7 +42765,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ201">
         <v>1.69</v>
@@ -42974,7 +42974,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ202">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR202">
         <v>1.7</v>
@@ -45031,7 +45031,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ212">
         <v>0.85</v>
@@ -47094,7 +47094,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ222">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR222">
         <v>1.73</v>
@@ -49357,7 +49357,7 @@
         <v>0.91</v>
       </c>
       <c r="AP233">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ233">
         <v>0.77</v>
@@ -51626,7 +51626,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ244">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR244">
         <v>1.33</v>
@@ -52241,7 +52241,7 @@
         <v>0.83</v>
       </c>
       <c r="AP247">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ247">
         <v>0.77</v>
@@ -55204,6 +55204,212 @@
       </c>
       <c r="BP261">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7509855</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45709.6875</v>
+      </c>
+      <c r="F262">
+        <v>27</v>
+      </c>
+      <c r="G262" t="s">
+        <v>81</v>
+      </c>
+      <c r="H262" t="s">
+        <v>84</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>0</v>
+      </c>
+      <c r="L262">
+        <v>0</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>0</v>
+      </c>
+      <c r="O262" t="s">
+        <v>102</v>
+      </c>
+      <c r="P262" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q262">
+        <v>3.6</v>
+      </c>
+      <c r="R262">
+        <v>2.1</v>
+      </c>
+      <c r="S262">
+        <v>2.7</v>
+      </c>
+      <c r="T262">
+        <v>1.37</v>
+      </c>
+      <c r="U262">
+        <v>2.85</v>
+      </c>
+      <c r="V262">
+        <v>2.65</v>
+      </c>
+      <c r="W262">
+        <v>1.41</v>
+      </c>
+      <c r="X262">
+        <v>6.75</v>
+      </c>
+      <c r="Y262">
+        <v>1.09</v>
+      </c>
+      <c r="Z262">
+        <v>3.37</v>
+      </c>
+      <c r="AA262">
+        <v>3.47</v>
+      </c>
+      <c r="AB262">
+        <v>2.22</v>
+      </c>
+      <c r="AC262">
+        <v>1.05</v>
+      </c>
+      <c r="AD262">
+        <v>9</v>
+      </c>
+      <c r="AE262">
+        <v>1.26</v>
+      </c>
+      <c r="AF262">
+        <v>3.5</v>
+      </c>
+      <c r="AG262">
+        <v>1.84</v>
+      </c>
+      <c r="AH262">
+        <v>1.97</v>
+      </c>
+      <c r="AI262">
+        <v>1.68</v>
+      </c>
+      <c r="AJ262">
+        <v>2.05</v>
+      </c>
+      <c r="AK262">
+        <v>1.66</v>
+      </c>
+      <c r="AL262">
+        <v>1.29</v>
+      </c>
+      <c r="AM262">
+        <v>1.34</v>
+      </c>
+      <c r="AN262">
+        <v>1.23</v>
+      </c>
+      <c r="AO262">
+        <v>2.08</v>
+      </c>
+      <c r="AP262">
+        <v>1.21</v>
+      </c>
+      <c r="AQ262">
+        <v>2</v>
+      </c>
+      <c r="AR262">
+        <v>1.44</v>
+      </c>
+      <c r="AS262">
+        <v>1.41</v>
+      </c>
+      <c r="AT262">
+        <v>2.85</v>
+      </c>
+      <c r="AU262">
+        <v>3</v>
+      </c>
+      <c r="AV262">
+        <v>3</v>
+      </c>
+      <c r="AW262">
+        <v>2</v>
+      </c>
+      <c r="AX262">
+        <v>3</v>
+      </c>
+      <c r="AY262">
+        <v>5</v>
+      </c>
+      <c r="AZ262">
+        <v>7</v>
+      </c>
+      <c r="BA262">
+        <v>5</v>
+      </c>
+      <c r="BB262">
+        <v>3</v>
+      </c>
+      <c r="BC262">
+        <v>8</v>
+      </c>
+      <c r="BD262">
+        <v>2.52</v>
+      </c>
+      <c r="BE262">
+        <v>8</v>
+      </c>
+      <c r="BF262">
+        <v>1.75</v>
+      </c>
+      <c r="BG262">
+        <v>1.39</v>
+      </c>
+      <c r="BH262">
+        <v>2.77</v>
+      </c>
+      <c r="BI262">
+        <v>1.7</v>
+      </c>
+      <c r="BJ262">
+        <v>2.05</v>
+      </c>
+      <c r="BK262">
+        <v>2.11</v>
+      </c>
+      <c r="BL262">
+        <v>1.68</v>
+      </c>
+      <c r="BM262">
+        <v>2.7</v>
+      </c>
+      <c r="BN262">
+        <v>1.41</v>
+      </c>
+      <c r="BO262">
+        <v>3.65</v>
+      </c>
+      <c r="BP262">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="359">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -763,10 +763,16 @@
     <t>['79']</t>
   </si>
   <si>
-    <t>['24', '45+2', '80']</t>
+    <t>['64', '66', '77']</t>
+  </si>
+  <si>
+    <t>['26', '82']</t>
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['24', '45+2', '80']</t>
   </si>
   <si>
     <t>['21', '45+2']</t>
@@ -1076,6 +1082,15 @@
   </si>
   <si>
     <t>['46', '57']</t>
+  </si>
+  <si>
+    <t>['27', '86']</t>
+  </si>
+  <si>
+    <t>['10', '57']</t>
+  </si>
+  <si>
+    <t>['14', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1437,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP267"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1899,7 +1914,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -1980,7 +1995,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2105,7 +2120,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>3.5</v>
@@ -2186,7 +2201,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ4">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2311,7 +2326,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2389,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2723,7 +2738,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3010,7 +3025,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ8">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3135,7 +3150,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3213,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ9">
         <v>0.71</v>
@@ -3341,7 +3356,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3753,7 +3768,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3834,7 +3849,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3959,7 +3974,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4165,7 +4180,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4655,10 +4670,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ16">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4783,7 +4798,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5067,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5276,7 +5291,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ19">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5401,7 +5416,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5479,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20">
         <v>0.77</v>
@@ -5688,7 +5703,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ21">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR21">
         <v>1.33</v>
@@ -5813,7 +5828,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6225,7 +6240,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6509,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ25">
         <v>1.69</v>
@@ -6715,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ26">
         <v>1.08</v>
@@ -6843,7 +6858,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -6921,7 +6936,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -7130,7 +7145,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ28">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7954,7 +7969,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -8079,7 +8094,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8363,7 +8378,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8491,7 +8506,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8697,7 +8712,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8984,7 +8999,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ37">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR37">
         <v>1.58</v>
@@ -9187,7 +9202,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
         <v>0.54</v>
@@ -9315,7 +9330,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9521,7 +9536,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9602,7 +9617,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.5</v>
@@ -9727,7 +9742,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9808,7 +9823,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ41">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR41">
         <v>1.16</v>
@@ -9933,7 +9948,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10014,7 +10029,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ42">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10217,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ43">
         <v>1.25</v>
@@ -10757,7 +10772,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11041,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47">
         <v>1.57</v>
@@ -11169,7 +11184,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11247,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11375,7 +11390,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11581,7 +11596,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11787,7 +11802,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11993,7 +12008,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12486,7 +12501,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>2.1</v>
@@ -12611,7 +12626,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12689,7 +12704,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ55">
         <v>1.08</v>
@@ -12895,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ56">
         <v>0.54</v>
@@ -13310,7 +13325,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ58">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR58">
         <v>1.74</v>
@@ -13435,7 +13450,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13516,7 +13531,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13719,7 +13734,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ60">
         <v>1.36</v>
@@ -13847,7 +13862,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13928,7 +13943,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ61">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR61">
         <v>1.42</v>
@@ -14053,7 +14068,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14131,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ62">
         <v>0.83</v>
@@ -14465,7 +14480,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14877,7 +14892,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15289,7 +15304,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15701,7 +15716,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15907,7 +15922,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16113,7 +16128,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16194,7 +16209,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ72">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR72">
         <v>0.97</v>
@@ -16319,7 +16334,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16400,7 +16415,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ73">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16525,7 +16540,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16937,7 +16952,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17015,10 +17030,10 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ76">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.44</v>
@@ -17143,7 +17158,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17349,7 +17364,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17427,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ78">
         <v>1.08</v>
@@ -17555,7 +17570,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17633,10 +17648,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17761,7 +17776,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17842,7 +17857,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ80">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18379,7 +18394,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18585,7 +18600,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18869,7 +18884,7 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ85">
         <v>0.77</v>
@@ -18997,7 +19012,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19203,7 +19218,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19409,7 +19424,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19899,7 +19914,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ90">
         <v>0.83</v>
@@ -20027,7 +20042,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20314,7 +20329,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -20726,7 +20741,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ94">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20929,7 +20944,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ95">
         <v>0.54</v>
@@ -21344,7 +21359,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ97">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -22374,7 +22389,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ102">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22705,7 +22720,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22911,7 +22926,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23195,7 +23210,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ106">
         <v>0.77</v>
@@ -23404,7 +23419,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ107">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23813,7 +23828,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ109">
         <v>0.92</v>
@@ -24019,7 +24034,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24225,7 +24240,7 @@
         <v>0.75</v>
       </c>
       <c r="AP111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ111">
         <v>1.25</v>
@@ -24434,7 +24449,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ112">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24559,7 +24574,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24846,7 +24861,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ114">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR114">
         <v>1.23</v>
@@ -25383,7 +25398,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25589,7 +25604,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25667,7 +25682,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ118">
         <v>1.69</v>
@@ -26413,7 +26428,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26903,7 +26918,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ124">
         <v>0.92</v>
@@ -27112,7 +27127,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ125">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR125">
         <v>1.55</v>
@@ -27237,7 +27252,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27521,7 +27536,7 @@
         <v>1.67</v>
       </c>
       <c r="AP127">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ127">
         <v>1.62</v>
@@ -27649,7 +27664,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27855,7 +27870,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27933,10 +27948,10 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ129">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR129">
         <v>1.41</v>
@@ -28061,7 +28076,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28139,7 +28154,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ130">
         <v>1.25</v>
@@ -28267,7 +28282,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28348,7 +28363,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28473,7 +28488,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28554,7 +28569,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ132">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -29297,7 +29312,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29709,7 +29724,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30199,7 +30214,7 @@
         <v>0.83</v>
       </c>
       <c r="AP140">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ140">
         <v>0.83</v>
@@ -30327,7 +30342,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30533,7 +30548,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30611,7 +30626,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ142">
         <v>2</v>
@@ -30739,7 +30754,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30945,7 +30960,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31232,7 +31247,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ145">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31357,7 +31372,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31435,10 +31450,10 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ146">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR146">
         <v>1.34</v>
@@ -31641,10 +31656,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ147">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -31975,7 +31990,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32053,7 +32068,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ149">
         <v>0.77</v>
@@ -32181,7 +32196,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32262,7 +32277,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ150">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR150">
         <v>1.37</v>
@@ -32468,7 +32483,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ151">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR151">
         <v>1.67</v>
@@ -32593,7 +32608,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32880,7 +32895,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ153">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR153">
         <v>1.41</v>
@@ -33211,7 +33226,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33289,7 +33304,7 @@
         <v>1.57</v>
       </c>
       <c r="AP155">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ155">
         <v>1.69</v>
@@ -33623,7 +33638,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34035,7 +34050,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34113,7 +34128,7 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -34447,7 +34462,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34731,10 +34746,10 @@
         <v>1.43</v>
       </c>
       <c r="AP162">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ162">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34859,7 +34874,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35143,10 +35158,10 @@
         <v>0.63</v>
       </c>
       <c r="AP164">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ164">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35271,7 +35286,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35889,7 +35904,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36176,7 +36191,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ169">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36379,7 +36394,7 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ170">
         <v>1.62</v>
@@ -36507,7 +36522,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36588,7 +36603,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR171">
         <v>1.73</v>
@@ -37615,7 +37630,7 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ176">
         <v>0.83</v>
@@ -37949,7 +37964,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38027,7 +38042,7 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38155,7 +38170,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38442,7 +38457,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ180">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR180">
         <v>1.28</v>
@@ -38645,7 +38660,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ181">
         <v>0.92</v>
@@ -38851,7 +38866,7 @@
         <v>2.33</v>
       </c>
       <c r="AP182">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ182">
         <v>2</v>
@@ -39057,10 +39072,10 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ183">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39185,7 +39200,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39391,7 +39406,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -40009,7 +40024,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40090,7 +40105,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ188">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40502,7 +40517,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40627,7 +40642,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40708,7 +40723,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ191">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
         <v>1.37</v>
@@ -40833,7 +40848,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40911,7 +40926,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ192">
         <v>1.08</v>
@@ -41326,7 +41341,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ194">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR194">
         <v>1.3</v>
@@ -41863,7 +41878,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -41941,7 +41956,7 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ197">
         <v>1</v>
@@ -42147,7 +42162,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42481,7 +42496,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42893,7 +42908,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43177,10 +43192,10 @@
         <v>1.11</v>
       </c>
       <c r="AP203">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR203">
         <v>1.37</v>
@@ -43305,7 +43320,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43592,7 +43607,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ205">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR205">
         <v>1.88</v>
@@ -43717,7 +43732,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43798,7 +43813,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ206">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR206">
         <v>1.74</v>
@@ -43923,7 +43938,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44129,7 +44144,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44825,10 +44840,10 @@
         <v>0.6</v>
       </c>
       <c r="AP211">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ211">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR211">
         <v>1.37</v>
@@ -44953,7 +44968,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45034,7 +45049,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ212">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.48</v>
@@ -45159,7 +45174,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45237,7 +45252,7 @@
         <v>0.55</v>
       </c>
       <c r="AP213">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ213">
         <v>0.71</v>
@@ -45443,7 +45458,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ214">
         <v>0.77</v>
@@ -45777,7 +45792,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45983,7 +45998,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46476,7 +46491,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ219">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR219">
         <v>1.84</v>
@@ -46601,7 +46616,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46807,7 +46822,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47013,7 +47028,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47300,7 +47315,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ223">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR223">
         <v>1.25</v>
@@ -47425,7 +47440,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47631,7 +47646,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47712,7 +47727,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ225">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR225">
         <v>1.49</v>
@@ -47837,7 +47852,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48043,7 +48058,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48121,7 +48136,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ227">
         <v>0.92</v>
@@ -48249,7 +48264,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48533,7 +48548,7 @@
         <v>0.6</v>
       </c>
       <c r="AP229">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ229">
         <v>0.54</v>
@@ -48739,7 +48754,7 @@
         <v>1.09</v>
       </c>
       <c r="AP230">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ230">
         <v>1</v>
@@ -48867,7 +48882,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -48945,10 +48960,10 @@
         <v>0.82</v>
       </c>
       <c r="AP231">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ231">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49073,7 +49088,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49566,7 +49581,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ234">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR234">
         <v>1.78</v>
@@ -49691,7 +49706,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49769,7 +49784,7 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ235">
         <v>1.57</v>
@@ -49897,7 +49912,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -49978,7 +49993,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ236">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR236">
         <v>1.29</v>
@@ -50515,7 +50530,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50927,7 +50942,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51417,7 +51432,7 @@
         <v>1.33</v>
       </c>
       <c r="AP243">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ243">
         <v>1.36</v>
@@ -51545,7 +51560,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51623,7 +51638,7 @@
         <v>2</v>
       </c>
       <c r="AP244">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ244">
         <v>2</v>
@@ -52038,7 +52053,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ246">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR246">
         <v>1.59</v>
@@ -52244,7 +52259,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ247">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="AR247">
         <v>1.4</v>
@@ -52447,7 +52462,7 @@
         <v>1.08</v>
       </c>
       <c r="AP248">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AQ248">
         <v>1</v>
@@ -52653,10 +52668,10 @@
         <v>0.67</v>
       </c>
       <c r="AP249">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ249">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR249">
         <v>1.33</v>
@@ -52781,7 +52796,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53068,7 +53083,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ251">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR251">
         <v>1.22</v>
@@ -53399,7 +53414,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53605,7 +53620,7 @@
         <v>208</v>
       </c>
       <c r="P254" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q254">
         <v>4</v>
@@ -54841,7 +54856,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55409,6 +55424,1036 @@
         <v>3.65</v>
       </c>
       <c r="BP262">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7509848</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F263">
+        <v>27</v>
+      </c>
+      <c r="G263" t="s">
+        <v>87</v>
+      </c>
+      <c r="H263" t="s">
+        <v>80</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263">
+        <v>1</v>
+      </c>
+      <c r="L263">
+        <v>0</v>
+      </c>
+      <c r="M263">
+        <v>2</v>
+      </c>
+      <c r="N263">
+        <v>2</v>
+      </c>
+      <c r="O263" t="s">
+        <v>102</v>
+      </c>
+      <c r="P263" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q263">
+        <v>3.5</v>
+      </c>
+      <c r="R263">
+        <v>1.9</v>
+      </c>
+      <c r="S263">
+        <v>3.2</v>
+      </c>
+      <c r="T263">
+        <v>1.51</v>
+      </c>
+      <c r="U263">
+        <v>2.35</v>
+      </c>
+      <c r="V263">
+        <v>3.4</v>
+      </c>
+      <c r="W263">
+        <v>1.28</v>
+      </c>
+      <c r="X263">
+        <v>9.5</v>
+      </c>
+      <c r="Y263">
+        <v>1.05</v>
+      </c>
+      <c r="Z263">
+        <v>3.1</v>
+      </c>
+      <c r="AA263">
+        <v>3</v>
+      </c>
+      <c r="AB263">
+        <v>2.64</v>
+      </c>
+      <c r="AC263">
+        <v>1.06</v>
+      </c>
+      <c r="AD263">
+        <v>6.3</v>
+      </c>
+      <c r="AE263">
+        <v>1.42</v>
+      </c>
+      <c r="AF263">
+        <v>2.56</v>
+      </c>
+      <c r="AG263">
+        <v>2.3</v>
+      </c>
+      <c r="AH263">
+        <v>1.5</v>
+      </c>
+      <c r="AI263">
+        <v>2</v>
+      </c>
+      <c r="AJ263">
+        <v>1.7</v>
+      </c>
+      <c r="AK263">
+        <v>1.5</v>
+      </c>
+      <c r="AL263">
+        <v>1.36</v>
+      </c>
+      <c r="AM263">
+        <v>1.38</v>
+      </c>
+      <c r="AN263">
+        <v>1</v>
+      </c>
+      <c r="AO263">
+        <v>0.77</v>
+      </c>
+      <c r="AP263">
+        <v>0.92</v>
+      </c>
+      <c r="AQ263">
+        <v>0.93</v>
+      </c>
+      <c r="AR263">
+        <v>1.4</v>
+      </c>
+      <c r="AS263">
+        <v>1.19</v>
+      </c>
+      <c r="AT263">
+        <v>2.59</v>
+      </c>
+      <c r="AU263">
+        <v>5</v>
+      </c>
+      <c r="AV263">
+        <v>10</v>
+      </c>
+      <c r="AW263">
+        <v>10</v>
+      </c>
+      <c r="AX263">
+        <v>11</v>
+      </c>
+      <c r="AY263">
+        <v>17</v>
+      </c>
+      <c r="AZ263">
+        <v>24</v>
+      </c>
+      <c r="BA263">
+        <v>5</v>
+      </c>
+      <c r="BB263">
+        <v>2</v>
+      </c>
+      <c r="BC263">
+        <v>7</v>
+      </c>
+      <c r="BD263">
+        <v>1.91</v>
+      </c>
+      <c r="BE263">
+        <v>7.5</v>
+      </c>
+      <c r="BF263">
+        <v>2.2</v>
+      </c>
+      <c r="BG263">
+        <v>1.43</v>
+      </c>
+      <c r="BH263">
+        <v>2.63</v>
+      </c>
+      <c r="BI263">
+        <v>1.74</v>
+      </c>
+      <c r="BJ263">
+        <v>2.02</v>
+      </c>
+      <c r="BK263">
+        <v>2.22</v>
+      </c>
+      <c r="BL263">
+        <v>1.62</v>
+      </c>
+      <c r="BM263">
+        <v>2.85</v>
+      </c>
+      <c r="BN263">
+        <v>1.37</v>
+      </c>
+      <c r="BO263">
+        <v>3.9</v>
+      </c>
+      <c r="BP263">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7509851</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F264">
+        <v>27</v>
+      </c>
+      <c r="G264" t="s">
+        <v>85</v>
+      </c>
+      <c r="H264" t="s">
+        <v>71</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>1</v>
+      </c>
+      <c r="O264" t="s">
+        <v>102</v>
+      </c>
+      <c r="P264" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q264">
+        <v>3.1</v>
+      </c>
+      <c r="R264">
+        <v>2</v>
+      </c>
+      <c r="S264">
+        <v>3.25</v>
+      </c>
+      <c r="T264">
+        <v>1.42</v>
+      </c>
+      <c r="U264">
+        <v>2.65</v>
+      </c>
+      <c r="V264">
+        <v>2.85</v>
+      </c>
+      <c r="W264">
+        <v>1.36</v>
+      </c>
+      <c r="X264">
+        <v>7.5</v>
+      </c>
+      <c r="Y264">
+        <v>1.07</v>
+      </c>
+      <c r="Z264">
+        <v>2.62</v>
+      </c>
+      <c r="AA264">
+        <v>3.31</v>
+      </c>
+      <c r="AB264">
+        <v>2.85</v>
+      </c>
+      <c r="AC264">
+        <v>1.07</v>
+      </c>
+      <c r="AD264">
+        <v>8</v>
+      </c>
+      <c r="AE264">
+        <v>1.33</v>
+      </c>
+      <c r="AF264">
+        <v>3.25</v>
+      </c>
+      <c r="AG264">
+        <v>2.02</v>
+      </c>
+      <c r="AH264">
+        <v>1.8</v>
+      </c>
+      <c r="AI264">
+        <v>1.77</v>
+      </c>
+      <c r="AJ264">
+        <v>1.93</v>
+      </c>
+      <c r="AK264">
+        <v>1.43</v>
+      </c>
+      <c r="AL264">
+        <v>1.32</v>
+      </c>
+      <c r="AM264">
+        <v>1.49</v>
+      </c>
+      <c r="AN264">
+        <v>1.58</v>
+      </c>
+      <c r="AO264">
+        <v>1</v>
+      </c>
+      <c r="AP264">
+        <v>1.46</v>
+      </c>
+      <c r="AQ264">
+        <v>1.15</v>
+      </c>
+      <c r="AR264">
+        <v>1.31</v>
+      </c>
+      <c r="AS264">
+        <v>1.3</v>
+      </c>
+      <c r="AT264">
+        <v>2.61</v>
+      </c>
+      <c r="AU264">
+        <v>5</v>
+      </c>
+      <c r="AV264">
+        <v>4</v>
+      </c>
+      <c r="AW264">
+        <v>4</v>
+      </c>
+      <c r="AX264">
+        <v>10</v>
+      </c>
+      <c r="AY264">
+        <v>10</v>
+      </c>
+      <c r="AZ264">
+        <v>18</v>
+      </c>
+      <c r="BA264">
+        <v>1</v>
+      </c>
+      <c r="BB264">
+        <v>9</v>
+      </c>
+      <c r="BC264">
+        <v>10</v>
+      </c>
+      <c r="BD264">
+        <v>2.1</v>
+      </c>
+      <c r="BE264">
+        <v>7.5</v>
+      </c>
+      <c r="BF264">
+        <v>1.95</v>
+      </c>
+      <c r="BG264">
+        <v>1.47</v>
+      </c>
+      <c r="BH264">
+        <v>2.5</v>
+      </c>
+      <c r="BI264">
+        <v>1.82</v>
+      </c>
+      <c r="BJ264">
+        <v>1.93</v>
+      </c>
+      <c r="BK264">
+        <v>2.34</v>
+      </c>
+      <c r="BL264">
+        <v>1.56</v>
+      </c>
+      <c r="BM264">
+        <v>3.02</v>
+      </c>
+      <c r="BN264">
+        <v>1.33</v>
+      </c>
+      <c r="BO264">
+        <v>4.2</v>
+      </c>
+      <c r="BP264">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7509852</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F265">
+        <v>27</v>
+      </c>
+      <c r="G265" t="s">
+        <v>73</v>
+      </c>
+      <c r="H265" t="s">
+        <v>88</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>0</v>
+      </c>
+      <c r="L265">
+        <v>3</v>
+      </c>
+      <c r="M265">
+        <v>1</v>
+      </c>
+      <c r="N265">
+        <v>4</v>
+      </c>
+      <c r="O265" t="s">
+        <v>249</v>
+      </c>
+      <c r="P265" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q265">
+        <v>2.55</v>
+      </c>
+      <c r="R265">
+        <v>1.93</v>
+      </c>
+      <c r="S265">
+        <v>4.8</v>
+      </c>
+      <c r="T265">
+        <v>1.51</v>
+      </c>
+      <c r="U265">
+        <v>2.35</v>
+      </c>
+      <c r="V265">
+        <v>3.3</v>
+      </c>
+      <c r="W265">
+        <v>1.29</v>
+      </c>
+      <c r="X265">
+        <v>9.25</v>
+      </c>
+      <c r="Y265">
+        <v>1.05</v>
+      </c>
+      <c r="Z265">
+        <v>1.78</v>
+      </c>
+      <c r="AA265">
+        <v>3.56</v>
+      </c>
+      <c r="AB265">
+        <v>5.2</v>
+      </c>
+      <c r="AC265">
+        <v>1.09</v>
+      </c>
+      <c r="AD265">
+        <v>7</v>
+      </c>
+      <c r="AE265">
+        <v>1.48</v>
+      </c>
+      <c r="AF265">
+        <v>2.65</v>
+      </c>
+      <c r="AG265">
+        <v>2.3</v>
+      </c>
+      <c r="AH265">
+        <v>1.5</v>
+      </c>
+      <c r="AI265">
+        <v>2.1</v>
+      </c>
+      <c r="AJ265">
+        <v>1.63</v>
+      </c>
+      <c r="AK265">
+        <v>1.2</v>
+      </c>
+      <c r="AL265">
+        <v>1.34</v>
+      </c>
+      <c r="AM265">
+        <v>1.85</v>
+      </c>
+      <c r="AN265">
+        <v>2.31</v>
+      </c>
+      <c r="AO265">
+        <v>1.15</v>
+      </c>
+      <c r="AP265">
+        <v>2.36</v>
+      </c>
+      <c r="AQ265">
+        <v>1.07</v>
+      </c>
+      <c r="AR265">
+        <v>1.48</v>
+      </c>
+      <c r="AS265">
+        <v>1.11</v>
+      </c>
+      <c r="AT265">
+        <v>2.59</v>
+      </c>
+      <c r="AU265">
+        <v>8</v>
+      </c>
+      <c r="AV265">
+        <v>7</v>
+      </c>
+      <c r="AW265">
+        <v>7</v>
+      </c>
+      <c r="AX265">
+        <v>1</v>
+      </c>
+      <c r="AY265">
+        <v>18</v>
+      </c>
+      <c r="AZ265">
+        <v>9</v>
+      </c>
+      <c r="BA265">
+        <v>4</v>
+      </c>
+      <c r="BB265">
+        <v>0</v>
+      </c>
+      <c r="BC265">
+        <v>4</v>
+      </c>
+      <c r="BD265">
+        <v>1.59</v>
+      </c>
+      <c r="BE265">
+        <v>8</v>
+      </c>
+      <c r="BF265">
+        <v>2.8</v>
+      </c>
+      <c r="BG265">
+        <v>1.43</v>
+      </c>
+      <c r="BH265">
+        <v>2.63</v>
+      </c>
+      <c r="BI265">
+        <v>1.7</v>
+      </c>
+      <c r="BJ265">
+        <v>2.05</v>
+      </c>
+      <c r="BK265">
+        <v>2.22</v>
+      </c>
+      <c r="BL265">
+        <v>1.62</v>
+      </c>
+      <c r="BM265">
+        <v>2.85</v>
+      </c>
+      <c r="BN265">
+        <v>1.37</v>
+      </c>
+      <c r="BO265">
+        <v>3.9</v>
+      </c>
+      <c r="BP265">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7509853</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45710.45833333334</v>
+      </c>
+      <c r="F266">
+        <v>27</v>
+      </c>
+      <c r="G266" t="s">
+        <v>77</v>
+      </c>
+      <c r="H266" t="s">
+        <v>86</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266">
+        <v>2</v>
+      </c>
+      <c r="L266">
+        <v>2</v>
+      </c>
+      <c r="M266">
+        <v>2</v>
+      </c>
+      <c r="N266">
+        <v>4</v>
+      </c>
+      <c r="O266" t="s">
+        <v>250</v>
+      </c>
+      <c r="P266" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q266">
+        <v>2.85</v>
+      </c>
+      <c r="R266">
+        <v>1.9</v>
+      </c>
+      <c r="S266">
+        <v>4.1</v>
+      </c>
+      <c r="T266">
+        <v>1.53</v>
+      </c>
+      <c r="U266">
+        <v>2.3</v>
+      </c>
+      <c r="V266">
+        <v>3.4</v>
+      </c>
+      <c r="W266">
+        <v>1.27</v>
+      </c>
+      <c r="X266">
+        <v>9.75</v>
+      </c>
+      <c r="Y266">
+        <v>1.04</v>
+      </c>
+      <c r="Z266">
+        <v>2.21</v>
+      </c>
+      <c r="AA266">
+        <v>3.17</v>
+      </c>
+      <c r="AB266">
+        <v>3.75</v>
+      </c>
+      <c r="AC266">
+        <v>1.11</v>
+      </c>
+      <c r="AD266">
+        <v>6.25</v>
+      </c>
+      <c r="AE266">
+        <v>1.5</v>
+      </c>
+      <c r="AF266">
+        <v>2.55</v>
+      </c>
+      <c r="AG266">
+        <v>2.37</v>
+      </c>
+      <c r="AH266">
+        <v>1.48</v>
+      </c>
+      <c r="AI266">
+        <v>2.05</v>
+      </c>
+      <c r="AJ266">
+        <v>1.66</v>
+      </c>
+      <c r="AK266">
+        <v>1.28</v>
+      </c>
+      <c r="AL266">
+        <v>1.36</v>
+      </c>
+      <c r="AM266">
+        <v>1.65</v>
+      </c>
+      <c r="AN266">
+        <v>1.23</v>
+      </c>
+      <c r="AO266">
+        <v>0.46</v>
+      </c>
+      <c r="AP266">
+        <v>1.21</v>
+      </c>
+      <c r="AQ266">
+        <v>0.5</v>
+      </c>
+      <c r="AR266">
+        <v>1.3</v>
+      </c>
+      <c r="AS266">
+        <v>1.2</v>
+      </c>
+      <c r="AT266">
+        <v>2.5</v>
+      </c>
+      <c r="AU266">
+        <v>5</v>
+      </c>
+      <c r="AV266">
+        <v>3</v>
+      </c>
+      <c r="AW266">
+        <v>6</v>
+      </c>
+      <c r="AX266">
+        <v>5</v>
+      </c>
+      <c r="AY266">
+        <v>14</v>
+      </c>
+      <c r="AZ266">
+        <v>8</v>
+      </c>
+      <c r="BA266">
+        <v>5</v>
+      </c>
+      <c r="BB266">
+        <v>4</v>
+      </c>
+      <c r="BC266">
+        <v>9</v>
+      </c>
+      <c r="BD266">
+        <v>1.95</v>
+      </c>
+      <c r="BE266">
+        <v>7.5</v>
+      </c>
+      <c r="BF266">
+        <v>2.1</v>
+      </c>
+      <c r="BG266">
+        <v>1.43</v>
+      </c>
+      <c r="BH266">
+        <v>2.63</v>
+      </c>
+      <c r="BI266">
+        <v>1.7</v>
+      </c>
+      <c r="BJ266">
+        <v>2.05</v>
+      </c>
+      <c r="BK266">
+        <v>2.22</v>
+      </c>
+      <c r="BL266">
+        <v>1.62</v>
+      </c>
+      <c r="BM266">
+        <v>2.85</v>
+      </c>
+      <c r="BN266">
+        <v>1.37</v>
+      </c>
+      <c r="BO266">
+        <v>3.9</v>
+      </c>
+      <c r="BP266">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7509850</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45710.55208333334</v>
+      </c>
+      <c r="F267">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>82</v>
+      </c>
+      <c r="H267" t="s">
+        <v>76</v>
+      </c>
+      <c r="I267">
+        <v>1</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267">
+        <v>2</v>
+      </c>
+      <c r="L267">
+        <v>1</v>
+      </c>
+      <c r="M267">
+        <v>2</v>
+      </c>
+      <c r="N267">
+        <v>3</v>
+      </c>
+      <c r="O267" t="s">
+        <v>251</v>
+      </c>
+      <c r="P267" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q267">
+        <v>2.4</v>
+      </c>
+      <c r="R267">
+        <v>2</v>
+      </c>
+      <c r="S267">
+        <v>4.75</v>
+      </c>
+      <c r="T267">
+        <v>1.44</v>
+      </c>
+      <c r="U267">
+        <v>2.55</v>
+      </c>
+      <c r="V267">
+        <v>3</v>
+      </c>
+      <c r="W267">
+        <v>1.34</v>
+      </c>
+      <c r="X267">
+        <v>8</v>
+      </c>
+      <c r="Y267">
+        <v>1.07</v>
+      </c>
+      <c r="Z267">
+        <v>1.84</v>
+      </c>
+      <c r="AA267">
+        <v>3.62</v>
+      </c>
+      <c r="AB267">
+        <v>4.6</v>
+      </c>
+      <c r="AC267">
+        <v>1.06</v>
+      </c>
+      <c r="AD267">
+        <v>8.5</v>
+      </c>
+      <c r="AE267">
+        <v>1.36</v>
+      </c>
+      <c r="AF267">
+        <v>3.1</v>
+      </c>
+      <c r="AG267">
+        <v>2</v>
+      </c>
+      <c r="AH267">
+        <v>1.67</v>
+      </c>
+      <c r="AI267">
+        <v>1.95</v>
+      </c>
+      <c r="AJ267">
+        <v>1.75</v>
+      </c>
+      <c r="AK267">
+        <v>1.19</v>
+      </c>
+      <c r="AL267">
+        <v>1.3</v>
+      </c>
+      <c r="AM267">
+        <v>1.95</v>
+      </c>
+      <c r="AN267">
+        <v>1.54</v>
+      </c>
+      <c r="AO267">
+        <v>0.85</v>
+      </c>
+      <c r="AP267">
+        <v>1.43</v>
+      </c>
+      <c r="AQ267">
+        <v>1</v>
+      </c>
+      <c r="AR267">
+        <v>1.78</v>
+      </c>
+      <c r="AS267">
+        <v>1.34</v>
+      </c>
+      <c r="AT267">
+        <v>3.12</v>
+      </c>
+      <c r="AU267">
+        <v>9</v>
+      </c>
+      <c r="AV267">
+        <v>3</v>
+      </c>
+      <c r="AW267">
+        <v>7</v>
+      </c>
+      <c r="AX267">
+        <v>10</v>
+      </c>
+      <c r="AY267">
+        <v>16</v>
+      </c>
+      <c r="AZ267">
+        <v>17</v>
+      </c>
+      <c r="BA267">
+        <v>4</v>
+      </c>
+      <c r="BB267">
+        <v>6</v>
+      </c>
+      <c r="BC267">
+        <v>10</v>
+      </c>
+      <c r="BD267">
+        <v>1.64</v>
+      </c>
+      <c r="BE267">
+        <v>8</v>
+      </c>
+      <c r="BF267">
+        <v>2.67</v>
+      </c>
+      <c r="BG267">
+        <v>1.39</v>
+      </c>
+      <c r="BH267">
+        <v>2.77</v>
+      </c>
+      <c r="BI267">
+        <v>1.68</v>
+      </c>
+      <c r="BJ267">
+        <v>2.12</v>
+      </c>
+      <c r="BK267">
+        <v>2.11</v>
+      </c>
+      <c r="BL267">
+        <v>1.68</v>
+      </c>
+      <c r="BM267">
+        <v>2.7</v>
+      </c>
+      <c r="BN267">
+        <v>1.41</v>
+      </c>
+      <c r="BO267">
+        <v>3.65</v>
+      </c>
+      <c r="BP267">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1092,6 +1092,9 @@
   <si>
     <t>['14', '90+4']</t>
   </si>
+  <si>
+    <t>['30', '56', '65']</t>
+  </si>
 </sst>
 </file>
 
@@ -1452,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP267"/>
+  <dimension ref="A1:BP271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1786,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2610,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6">
         <v>1.36</v>
@@ -3640,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ11">
         <v>1.62</v>
@@ -4464,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ15">
         <v>1.36</v>
@@ -4876,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5085,7 +5088,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR18">
         <v>1.49</v>
@@ -6318,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24">
         <v>0.92</v>
@@ -6939,7 +6942,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR27">
         <v>1.54</v>
@@ -7351,7 +7354,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR29">
         <v>1.89</v>
@@ -7554,7 +7557,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ30">
         <v>1.57</v>
@@ -9614,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -10235,7 +10238,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.15</v>
@@ -10644,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ45">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR45">
         <v>1.98</v>
@@ -10853,7 +10856,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR46">
         <v>0.96</v>
@@ -11674,7 +11677,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ50">
         <v>0.92</v>
@@ -11880,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51">
         <v>1.69</v>
@@ -12292,7 +12295,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -13940,7 +13943,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ61">
         <v>0.5</v>
@@ -14149,7 +14152,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR62">
         <v>1.33</v>
@@ -15588,10 +15591,10 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
+        <v>1.36</v>
+      </c>
+      <c r="AQ69">
         <v>1.38</v>
-      </c>
-      <c r="AQ69">
-        <v>1.25</v>
       </c>
       <c r="AR69">
         <v>1.8</v>
@@ -15797,7 +15800,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR70">
         <v>1.7</v>
@@ -16000,7 +16003,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ71">
         <v>1.62</v>
@@ -16824,7 +16827,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ75">
         <v>1</v>
@@ -17236,7 +17239,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -18269,7 +18272,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ82">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR82">
         <v>1.28</v>
@@ -18678,7 +18681,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>1.57</v>
@@ -19093,7 +19096,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR86">
         <v>1.48</v>
@@ -19296,7 +19299,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ87">
         <v>2</v>
@@ -19917,7 +19920,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ90">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -20326,7 +20329,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ92">
         <v>1.15</v>
@@ -20738,7 +20741,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ94">
         <v>1.07</v>
@@ -22592,7 +22595,7 @@
         <v>1.4</v>
       </c>
       <c r="AP103">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ103">
         <v>1.57</v>
@@ -23416,7 +23419,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23625,7 +23628,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ108">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR108">
         <v>1.52</v>
@@ -24037,7 +24040,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR110">
         <v>1.32</v>
@@ -24243,7 +24246,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ111">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR111">
         <v>1.35</v>
@@ -24446,7 +24449,7 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ112">
         <v>0.93</v>
@@ -25067,7 +25070,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ115">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR115">
         <v>1.26</v>
@@ -25476,7 +25479,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ117">
         <v>0.54</v>
@@ -26509,7 +26512,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -27330,7 +27333,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ126">
         <v>0.77</v>
@@ -28157,7 +28160,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ130">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR130">
         <v>1.24</v>
@@ -28360,7 +28363,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ131">
         <v>1.15</v>
@@ -28566,7 +28569,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ132">
         <v>0.93</v>
@@ -30008,7 +30011,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -30217,7 +30220,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ140">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30835,7 +30838,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ143">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR143">
         <v>1.37</v>
@@ -31244,7 +31247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ145">
         <v>1.15</v>
@@ -32480,7 +32483,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ151">
         <v>0.5</v>
@@ -33101,7 +33104,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR154">
         <v>1.17</v>
@@ -33716,10 +33719,10 @@
         <v>0.71</v>
       </c>
       <c r="AP157">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ157">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR157">
         <v>1.58</v>
@@ -34334,7 +34337,7 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ160">
         <v>1.36</v>
@@ -35985,7 +35988,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ168">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -36188,7 +36191,7 @@
         <v>0.5</v>
       </c>
       <c r="AP169">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ169">
         <v>0.5</v>
@@ -36600,7 +36603,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ171">
         <v>1.07</v>
@@ -36806,7 +36809,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ172">
         <v>1.08</v>
@@ -37015,7 +37018,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR173">
         <v>1.69</v>
@@ -37633,7 +37636,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ176">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR176">
         <v>1.34</v>
@@ -39278,7 +39281,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ184">
         <v>0.71</v>
@@ -39690,10 +39693,10 @@
         <v>1.13</v>
       </c>
       <c r="AP186">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ186">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR186">
         <v>1.56</v>
@@ -40102,7 +40105,7 @@
         <v>0.89</v>
       </c>
       <c r="AP188">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
         <v>0.93</v>
@@ -42165,7 +42168,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR198">
         <v>1.28</v>
@@ -42577,7 +42580,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ200">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42986,7 +42989,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ202">
         <v>2</v>
@@ -43401,7 +43404,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ204">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR204">
         <v>1.39</v>
@@ -43810,7 +43813,7 @@
         <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ206">
         <v>1.07</v>
@@ -44016,7 +44019,7 @@
         <v>0.5</v>
       </c>
       <c r="AP207">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ207">
         <v>0.71</v>
@@ -44634,7 +44637,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ210">
         <v>0.92</v>
@@ -45667,7 +45670,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ215">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45870,7 +45873,7 @@
         <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ216">
         <v>1</v>
@@ -47106,7 +47109,7 @@
         <v>2.18</v>
       </c>
       <c r="AP222">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ222">
         <v>2</v>
@@ -47930,7 +47933,7 @@
         <v>1.18</v>
       </c>
       <c r="AP226">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ226">
         <v>1.36</v>
@@ -48342,10 +48345,10 @@
         <v>1.1</v>
       </c>
       <c r="AP228">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ228">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48757,7 +48760,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ230">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR230">
         <v>1.34</v>
@@ -50402,7 +50405,7 @@
         <v>1.82</v>
       </c>
       <c r="AP238">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ238">
         <v>1.62</v>
@@ -51023,7 +51026,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ241">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AR241">
         <v>1.41</v>
@@ -51226,7 +51229,7 @@
         <v>0.55</v>
       </c>
       <c r="AP242">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ242">
         <v>0.54</v>
@@ -51847,7 +51850,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ245">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR245">
         <v>1.4</v>
@@ -52050,7 +52053,7 @@
         <v>0.5</v>
       </c>
       <c r="AP246">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ246">
         <v>0.5</v>
@@ -52874,10 +52877,10 @@
         <v>1</v>
       </c>
       <c r="AP250">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AQ250">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR250">
         <v>1.79</v>
@@ -56455,6 +56458,830 @@
       </c>
       <c r="BP267">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7509849</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F268">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>79</v>
+      </c>
+      <c r="H268" t="s">
+        <v>89</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>1</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>0</v>
+      </c>
+      <c r="M268">
+        <v>3</v>
+      </c>
+      <c r="N268">
+        <v>3</v>
+      </c>
+      <c r="O268" t="s">
+        <v>102</v>
+      </c>
+      <c r="P268" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q268">
+        <v>3.4</v>
+      </c>
+      <c r="R268">
+        <v>1.98</v>
+      </c>
+      <c r="S268">
+        <v>3.1</v>
+      </c>
+      <c r="T268">
+        <v>1.46</v>
+      </c>
+      <c r="U268">
+        <v>2.55</v>
+      </c>
+      <c r="V268">
+        <v>3</v>
+      </c>
+      <c r="W268">
+        <v>1.33</v>
+      </c>
+      <c r="X268">
+        <v>8.25</v>
+      </c>
+      <c r="Y268">
+        <v>1.06</v>
+      </c>
+      <c r="Z268">
+        <v>3.08</v>
+      </c>
+      <c r="AA268">
+        <v>3.2</v>
+      </c>
+      <c r="AB268">
+        <v>2.52</v>
+      </c>
+      <c r="AC268">
+        <v>1.08</v>
+      </c>
+      <c r="AD268">
+        <v>7.5</v>
+      </c>
+      <c r="AE268">
+        <v>1.37</v>
+      </c>
+      <c r="AF268">
+        <v>2.85</v>
+      </c>
+      <c r="AG268">
+        <v>2.1</v>
+      </c>
+      <c r="AH268">
+        <v>1.61</v>
+      </c>
+      <c r="AI268">
+        <v>1.87</v>
+      </c>
+      <c r="AJ268">
+        <v>1.82</v>
+      </c>
+      <c r="AK268">
+        <v>1.49</v>
+      </c>
+      <c r="AL268">
+        <v>1.33</v>
+      </c>
+      <c r="AM268">
+        <v>1.39</v>
+      </c>
+      <c r="AN268">
+        <v>1.15</v>
+      </c>
+      <c r="AO268">
+        <v>1</v>
+      </c>
+      <c r="AP268">
+        <v>1.07</v>
+      </c>
+      <c r="AQ268">
+        <v>1.14</v>
+      </c>
+      <c r="AR268">
+        <v>1.56</v>
+      </c>
+      <c r="AS268">
+        <v>1.27</v>
+      </c>
+      <c r="AT268">
+        <v>2.83</v>
+      </c>
+      <c r="AU268">
+        <v>7</v>
+      </c>
+      <c r="AV268">
+        <v>7</v>
+      </c>
+      <c r="AW268">
+        <v>12</v>
+      </c>
+      <c r="AX268">
+        <v>6</v>
+      </c>
+      <c r="AY268">
+        <v>23</v>
+      </c>
+      <c r="AZ268">
+        <v>15</v>
+      </c>
+      <c r="BA268">
+        <v>11</v>
+      </c>
+      <c r="BB268">
+        <v>2</v>
+      </c>
+      <c r="BC268">
+        <v>13</v>
+      </c>
+      <c r="BD268">
+        <v>2.1</v>
+      </c>
+      <c r="BE268">
+        <v>8</v>
+      </c>
+      <c r="BF268">
+        <v>1.91</v>
+      </c>
+      <c r="BG268">
+        <v>1.28</v>
+      </c>
+      <c r="BH268">
+        <v>3.25</v>
+      </c>
+      <c r="BI268">
+        <v>1.52</v>
+      </c>
+      <c r="BJ268">
+        <v>2.37</v>
+      </c>
+      <c r="BK268">
+        <v>1.8</v>
+      </c>
+      <c r="BL268">
+        <v>1.91</v>
+      </c>
+      <c r="BM268">
+        <v>2.38</v>
+      </c>
+      <c r="BN268">
+        <v>1.54</v>
+      </c>
+      <c r="BO268">
+        <v>3.12</v>
+      </c>
+      <c r="BP268">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7509856</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F269">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>83</v>
+      </c>
+      <c r="H269" t="s">
+        <v>78</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+      <c r="L269">
+        <v>0</v>
+      </c>
+      <c r="M269">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>1</v>
+      </c>
+      <c r="O269" t="s">
+        <v>102</v>
+      </c>
+      <c r="P269" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q269">
+        <v>2.2</v>
+      </c>
+      <c r="R269">
+        <v>2.15</v>
+      </c>
+      <c r="S269">
+        <v>5</v>
+      </c>
+      <c r="T269">
+        <v>1.4</v>
+      </c>
+      <c r="U269">
+        <v>2.7</v>
+      </c>
+      <c r="V269">
+        <v>2.8</v>
+      </c>
+      <c r="W269">
+        <v>1.37</v>
+      </c>
+      <c r="X269">
+        <v>7.25</v>
+      </c>
+      <c r="Y269">
+        <v>1.08</v>
+      </c>
+      <c r="Z269">
+        <v>1.68</v>
+      </c>
+      <c r="AA269">
+        <v>3.92</v>
+      </c>
+      <c r="AB269">
+        <v>5.5</v>
+      </c>
+      <c r="AC269">
+        <v>1.05</v>
+      </c>
+      <c r="AD269">
+        <v>9</v>
+      </c>
+      <c r="AE269">
+        <v>1.3</v>
+      </c>
+      <c r="AF269">
+        <v>3.2</v>
+      </c>
+      <c r="AG269">
+        <v>1.98</v>
+      </c>
+      <c r="AH269">
+        <v>1.83</v>
+      </c>
+      <c r="AI269">
+        <v>1.95</v>
+      </c>
+      <c r="AJ269">
+        <v>1.75</v>
+      </c>
+      <c r="AK269">
+        <v>1.16</v>
+      </c>
+      <c r="AL269">
+        <v>1.25</v>
+      </c>
+      <c r="AM269">
+        <v>2.2</v>
+      </c>
+      <c r="AN269">
+        <v>2.33</v>
+      </c>
+      <c r="AO269">
+        <v>1.25</v>
+      </c>
+      <c r="AP269">
+        <v>2.15</v>
+      </c>
+      <c r="AQ269">
+        <v>1.38</v>
+      </c>
+      <c r="AR269">
+        <v>1.9</v>
+      </c>
+      <c r="AS269">
+        <v>1.21</v>
+      </c>
+      <c r="AT269">
+        <v>3.11</v>
+      </c>
+      <c r="AU269">
+        <v>7</v>
+      </c>
+      <c r="AV269">
+        <v>5</v>
+      </c>
+      <c r="AW269">
+        <v>15</v>
+      </c>
+      <c r="AX269">
+        <v>7</v>
+      </c>
+      <c r="AY269">
+        <v>25</v>
+      </c>
+      <c r="AZ269">
+        <v>15</v>
+      </c>
+      <c r="BA269">
+        <v>4</v>
+      </c>
+      <c r="BB269">
+        <v>1</v>
+      </c>
+      <c r="BC269">
+        <v>5</v>
+      </c>
+      <c r="BD269">
+        <v>1.31</v>
+      </c>
+      <c r="BE269">
+        <v>9.5</v>
+      </c>
+      <c r="BF269">
+        <v>4.13</v>
+      </c>
+      <c r="BG269">
+        <v>1.39</v>
+      </c>
+      <c r="BH269">
+        <v>2.77</v>
+      </c>
+      <c r="BI269">
+        <v>1.68</v>
+      </c>
+      <c r="BJ269">
+        <v>2.12</v>
+      </c>
+      <c r="BK269">
+        <v>2.05</v>
+      </c>
+      <c r="BL269">
+        <v>1.7</v>
+      </c>
+      <c r="BM269">
+        <v>2.7</v>
+      </c>
+      <c r="BN269">
+        <v>1.41</v>
+      </c>
+      <c r="BO269">
+        <v>3.65</v>
+      </c>
+      <c r="BP269">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7509847</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45711.45833333334</v>
+      </c>
+      <c r="F270">
+        <v>27</v>
+      </c>
+      <c r="G270" t="s">
+        <v>70</v>
+      </c>
+      <c r="H270" t="s">
+        <v>72</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>0</v>
+      </c>
+      <c r="L270">
+        <v>0</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>0</v>
+      </c>
+      <c r="O270" t="s">
+        <v>102</v>
+      </c>
+      <c r="P270" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q270">
+        <v>2.95</v>
+      </c>
+      <c r="R270">
+        <v>1.93</v>
+      </c>
+      <c r="S270">
+        <v>3.75</v>
+      </c>
+      <c r="T270">
+        <v>1.49</v>
+      </c>
+      <c r="U270">
+        <v>2.45</v>
+      </c>
+      <c r="V270">
+        <v>3.2</v>
+      </c>
+      <c r="W270">
+        <v>1.31</v>
+      </c>
+      <c r="X270">
+        <v>8.75</v>
+      </c>
+      <c r="Y270">
+        <v>1.06</v>
+      </c>
+      <c r="Z270">
+        <v>2.39</v>
+      </c>
+      <c r="AA270">
+        <v>3.09</v>
+      </c>
+      <c r="AB270">
+        <v>3.41</v>
+      </c>
+      <c r="AC270">
+        <v>1.09</v>
+      </c>
+      <c r="AD270">
+        <v>7</v>
+      </c>
+      <c r="AE270">
+        <v>1.4</v>
+      </c>
+      <c r="AF270">
+        <v>2.65</v>
+      </c>
+      <c r="AG270">
+        <v>2.3</v>
+      </c>
+      <c r="AH270">
+        <v>1.5</v>
+      </c>
+      <c r="AI270">
+        <v>1.93</v>
+      </c>
+      <c r="AJ270">
+        <v>1.75</v>
+      </c>
+      <c r="AK270">
+        <v>1.33</v>
+      </c>
+      <c r="AL270">
+        <v>1.35</v>
+      </c>
+      <c r="AM270">
+        <v>1.58</v>
+      </c>
+      <c r="AN270">
+        <v>1.15</v>
+      </c>
+      <c r="AO270">
+        <v>1</v>
+      </c>
+      <c r="AP270">
+        <v>1.14</v>
+      </c>
+      <c r="AQ270">
+        <v>1</v>
+      </c>
+      <c r="AR270">
+        <v>1.61</v>
+      </c>
+      <c r="AS270">
+        <v>1.22</v>
+      </c>
+      <c r="AT270">
+        <v>2.83</v>
+      </c>
+      <c r="AU270">
+        <v>8</v>
+      </c>
+      <c r="AV270">
+        <v>4</v>
+      </c>
+      <c r="AW270">
+        <v>19</v>
+      </c>
+      <c r="AX270">
+        <v>5</v>
+      </c>
+      <c r="AY270">
+        <v>32</v>
+      </c>
+      <c r="AZ270">
+        <v>11</v>
+      </c>
+      <c r="BA270">
+        <v>5</v>
+      </c>
+      <c r="BB270">
+        <v>5</v>
+      </c>
+      <c r="BC270">
+        <v>10</v>
+      </c>
+      <c r="BD270">
+        <v>1.82</v>
+      </c>
+      <c r="BE270">
+        <v>7.5</v>
+      </c>
+      <c r="BF270">
+        <v>2.4</v>
+      </c>
+      <c r="BG270">
+        <v>1.39</v>
+      </c>
+      <c r="BH270">
+        <v>2.77</v>
+      </c>
+      <c r="BI270">
+        <v>1.7</v>
+      </c>
+      <c r="BJ270">
+        <v>2.05</v>
+      </c>
+      <c r="BK270">
+        <v>2.11</v>
+      </c>
+      <c r="BL270">
+        <v>1.68</v>
+      </c>
+      <c r="BM270">
+        <v>2.7</v>
+      </c>
+      <c r="BN270">
+        <v>1.41</v>
+      </c>
+      <c r="BO270">
+        <v>3.65</v>
+      </c>
+      <c r="BP270">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7509854</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45711.55208333334</v>
+      </c>
+      <c r="F271">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>74</v>
+      </c>
+      <c r="H271" t="s">
+        <v>75</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>1</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>2</v>
+      </c>
+      <c r="O271" t="s">
+        <v>165</v>
+      </c>
+      <c r="P271" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q271">
+        <v>2.65</v>
+      </c>
+      <c r="R271">
+        <v>1.98</v>
+      </c>
+      <c r="S271">
+        <v>4.2</v>
+      </c>
+      <c r="T271">
+        <v>1.46</v>
+      </c>
+      <c r="U271">
+        <v>2.5</v>
+      </c>
+      <c r="V271">
+        <v>3</v>
+      </c>
+      <c r="W271">
+        <v>1.34</v>
+      </c>
+      <c r="X271">
+        <v>8</v>
+      </c>
+      <c r="Y271">
+        <v>1.07</v>
+      </c>
+      <c r="Z271">
+        <v>2.03</v>
+      </c>
+      <c r="AA271">
+        <v>3.45</v>
+      </c>
+      <c r="AB271">
+        <v>3.94</v>
+      </c>
+      <c r="AC271">
+        <v>1.08</v>
+      </c>
+      <c r="AD271">
+        <v>7.5</v>
+      </c>
+      <c r="AE271">
+        <v>1.37</v>
+      </c>
+      <c r="AF271">
+        <v>2.85</v>
+      </c>
+      <c r="AG271">
+        <v>2.05</v>
+      </c>
+      <c r="AH271">
+        <v>1.61</v>
+      </c>
+      <c r="AI271">
+        <v>1.9</v>
+      </c>
+      <c r="AJ271">
+        <v>1.78</v>
+      </c>
+      <c r="AK271">
+        <v>1.26</v>
+      </c>
+      <c r="AL271">
+        <v>1.34</v>
+      </c>
+      <c r="AM271">
+        <v>1.72</v>
+      </c>
+      <c r="AN271">
+        <v>1.38</v>
+      </c>
+      <c r="AO271">
+        <v>0.83</v>
+      </c>
+      <c r="AP271">
+        <v>1.36</v>
+      </c>
+      <c r="AQ271">
+        <v>0.85</v>
+      </c>
+      <c r="AR271">
+        <v>1.71</v>
+      </c>
+      <c r="AS271">
+        <v>1.24</v>
+      </c>
+      <c r="AT271">
+        <v>2.95</v>
+      </c>
+      <c r="AU271">
+        <v>6</v>
+      </c>
+      <c r="AV271">
+        <v>4</v>
+      </c>
+      <c r="AW271">
+        <v>11</v>
+      </c>
+      <c r="AX271">
+        <v>5</v>
+      </c>
+      <c r="AY271">
+        <v>18</v>
+      </c>
+      <c r="AZ271">
+        <v>11</v>
+      </c>
+      <c r="BA271">
+        <v>3</v>
+      </c>
+      <c r="BB271">
+        <v>3</v>
+      </c>
+      <c r="BC271">
+        <v>6</v>
+      </c>
+      <c r="BD271">
+        <v>1.75</v>
+      </c>
+      <c r="BE271">
+        <v>8</v>
+      </c>
+      <c r="BF271">
+        <v>2.52</v>
+      </c>
+      <c r="BG271">
+        <v>1.36</v>
+      </c>
+      <c r="BH271">
+        <v>2.92</v>
+      </c>
+      <c r="BI271">
+        <v>1.62</v>
+      </c>
+      <c r="BJ271">
+        <v>2.22</v>
+      </c>
+      <c r="BK271">
+        <v>2.02</v>
+      </c>
+      <c r="BL271">
+        <v>1.74</v>
+      </c>
+      <c r="BM271">
+        <v>2.57</v>
+      </c>
+      <c r="BN271">
+        <v>1.45</v>
+      </c>
+      <c r="BO271">
+        <v>3.42</v>
+      </c>
+      <c r="BP271">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="361">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,9 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['26']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1455,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP271"/>
+  <dimension ref="A1:BP272"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1917,7 +1920,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2201,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>0.93</v>
@@ -2329,7 +2332,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2410,7 +2413,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ5">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2741,7 +2744,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3153,7 +3156,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3359,7 +3362,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3771,7 +3774,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3977,7 +3980,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4055,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13">
         <v>0.54</v>
@@ -4183,7 +4186,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4801,7 +4804,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5419,7 +5422,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5831,7 +5834,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6243,7 +6246,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6861,7 +6864,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7560,7 +7563,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ30">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR30">
         <v>1.65</v>
@@ -8097,7 +8100,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8509,7 +8512,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8715,7 +8718,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8793,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36">
         <v>1.08</v>
@@ -9539,7 +9542,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9745,7 +9748,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9951,7 +9954,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10775,7 +10778,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11062,7 +11065,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ47">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR47">
         <v>1.62</v>
@@ -11187,7 +11190,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11393,7 +11396,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11599,7 +11602,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11805,7 +11808,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12011,7 +12014,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12629,7 +12632,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -13453,7 +13456,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13865,7 +13868,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14071,7 +14074,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14358,7 +14361,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ63">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14483,7 +14486,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14895,7 +14898,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15307,7 +15310,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15719,7 +15722,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15797,7 +15800,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ70">
         <v>1.14</v>
@@ -15925,7 +15928,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16131,7 +16134,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16337,7 +16340,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16543,7 +16546,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16955,7 +16958,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17161,7 +17164,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17367,7 +17370,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17573,7 +17576,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17779,7 +17782,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18397,7 +18400,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18475,7 +18478,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ83">
         <v>1.69</v>
@@ -18603,7 +18606,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18684,7 +18687,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ84">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR84">
         <v>1.72</v>
@@ -19015,7 +19018,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19221,7 +19224,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19427,7 +19430,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -20045,7 +20048,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -22598,7 +22601,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ103">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR103">
         <v>1.86</v>
@@ -22723,7 +22726,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22929,7 +22932,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23625,7 +23628,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
         <v>0.85</v>
@@ -24577,7 +24580,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25401,7 +25404,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25607,7 +25610,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26431,7 +26434,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26715,7 +26718,7 @@
         <v>2</v>
       </c>
       <c r="AP123">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ123">
         <v>2</v>
@@ -27255,7 +27258,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27667,7 +27670,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27748,7 +27751,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ128">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR128">
         <v>1.36</v>
@@ -27873,7 +27876,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28079,7 +28082,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28285,7 +28288,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28491,7 +28494,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29315,7 +29318,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29727,7 +29730,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30345,7 +30348,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30551,7 +30554,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30757,7 +30760,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30963,7 +30966,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31041,7 +31044,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ144">
         <v>1.62</v>
@@ -31375,7 +31378,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31868,7 +31871,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ148">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR148">
         <v>1.81</v>
@@ -31993,7 +31996,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32199,7 +32202,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32611,7 +32614,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33229,7 +33232,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33641,7 +33644,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34053,7 +34056,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34465,7 +34468,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34877,7 +34880,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34955,7 +34958,7 @@
         <v>0.38</v>
       </c>
       <c r="AP163">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ163">
         <v>0.71</v>
@@ -35289,7 +35292,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35782,7 +35785,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ167">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR167">
         <v>1.43</v>
@@ -35907,7 +35910,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36525,7 +36528,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37967,7 +37970,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38173,7 +38176,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38254,7 +38257,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ179">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR179">
         <v>1.23</v>
@@ -39203,7 +39206,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39409,7 +39412,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39487,7 +39490,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ185">
         <v>1.36</v>
@@ -40027,7 +40030,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40645,7 +40648,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40851,7 +40854,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41138,7 +41141,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ193">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41881,7 +41884,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42499,7 +42502,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42911,7 +42914,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43323,7 +43326,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43401,7 +43404,7 @@
         <v>1.11</v>
       </c>
       <c r="AP204">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
         <v>1.38</v>
@@ -43735,7 +43738,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43941,7 +43944,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44147,7 +44150,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44971,7 +44974,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45177,7 +45180,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45795,7 +45798,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46001,7 +46004,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46619,7 +46622,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46825,7 +46828,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46906,7 +46909,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ221">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR221">
         <v>1.33</v>
@@ -47031,7 +47034,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47443,7 +47446,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47649,7 +47652,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47855,7 +47858,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48061,7 +48064,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48267,7 +48270,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48885,7 +48888,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49091,7 +49094,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49709,7 +49712,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49790,7 +49793,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ235">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR235">
         <v>1.39</v>
@@ -49915,7 +49918,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50533,7 +50536,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50817,7 +50820,7 @@
         <v>1.09</v>
       </c>
       <c r="AP240">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ240">
         <v>1</v>
@@ -50945,7 +50948,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51563,7 +51566,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -52799,7 +52802,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53417,7 +53420,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53495,7 +53498,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ253">
         <v>0.92</v>
@@ -53623,7 +53626,7 @@
         <v>208</v>
       </c>
       <c r="P254" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q254">
         <v>4</v>
@@ -53704,7 +53707,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ254">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR254">
         <v>1.44</v>
@@ -54859,7 +54862,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55477,7 +55480,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -56095,7 +56098,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56301,7 +56304,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56507,7 +56510,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -57125,7 +57128,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57282,6 +57285,212 @@
       </c>
       <c r="BP271">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7509866</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45716.64583333334</v>
+      </c>
+      <c r="F272">
+        <v>28</v>
+      </c>
+      <c r="G272" t="s">
+        <v>72</v>
+      </c>
+      <c r="H272" t="s">
+        <v>83</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>1</v>
+      </c>
+      <c r="K272">
+        <v>2</v>
+      </c>
+      <c r="L272">
+        <v>1</v>
+      </c>
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>2</v>
+      </c>
+      <c r="O272" t="s">
+        <v>252</v>
+      </c>
+      <c r="P272" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q272">
+        <v>4.9</v>
+      </c>
+      <c r="R272">
+        <v>2.03</v>
+      </c>
+      <c r="S272">
+        <v>2.55</v>
+      </c>
+      <c r="T272">
+        <v>1.52</v>
+      </c>
+      <c r="U272">
+        <v>2.4</v>
+      </c>
+      <c r="V272">
+        <v>3.25</v>
+      </c>
+      <c r="W272">
+        <v>1.3</v>
+      </c>
+      <c r="X272">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y272">
+        <v>1.02</v>
+      </c>
+      <c r="Z272">
+        <v>3.99</v>
+      </c>
+      <c r="AA272">
+        <v>3.19</v>
+      </c>
+      <c r="AB272">
+        <v>2.12</v>
+      </c>
+      <c r="AC272">
+        <v>1.08</v>
+      </c>
+      <c r="AD272">
+        <v>7.5</v>
+      </c>
+      <c r="AE272">
+        <v>1.43</v>
+      </c>
+      <c r="AF272">
+        <v>2.55</v>
+      </c>
+      <c r="AG272">
+        <v>2.25</v>
+      </c>
+      <c r="AH272">
+        <v>1.53</v>
+      </c>
+      <c r="AI272">
+        <v>2.07</v>
+      </c>
+      <c r="AJ272">
+        <v>1.69</v>
+      </c>
+      <c r="AK272">
+        <v>1.81</v>
+      </c>
+      <c r="AL272">
+        <v>1.3</v>
+      </c>
+      <c r="AM272">
+        <v>1.22</v>
+      </c>
+      <c r="AN272">
+        <v>1.15</v>
+      </c>
+      <c r="AO272">
+        <v>1.57</v>
+      </c>
+      <c r="AP272">
+        <v>1.14</v>
+      </c>
+      <c r="AQ272">
+        <v>1.53</v>
+      </c>
+      <c r="AR272">
+        <v>1.47</v>
+      </c>
+      <c r="AS272">
+        <v>1.46</v>
+      </c>
+      <c r="AT272">
+        <v>2.93</v>
+      </c>
+      <c r="AU272">
+        <v>5</v>
+      </c>
+      <c r="AV272">
+        <v>5</v>
+      </c>
+      <c r="AW272">
+        <v>10</v>
+      </c>
+      <c r="AX272">
+        <v>19</v>
+      </c>
+      <c r="AY272">
+        <v>16</v>
+      </c>
+      <c r="AZ272">
+        <v>31</v>
+      </c>
+      <c r="BA272">
+        <v>2</v>
+      </c>
+      <c r="BB272">
+        <v>6</v>
+      </c>
+      <c r="BC272">
+        <v>8</v>
+      </c>
+      <c r="BD272">
+        <v>2.55</v>
+      </c>
+      <c r="BE272">
+        <v>6.4</v>
+      </c>
+      <c r="BF272">
+        <v>1.65</v>
+      </c>
+      <c r="BG272">
+        <v>1.44</v>
+      </c>
+      <c r="BH272">
+        <v>2.55</v>
+      </c>
+      <c r="BI272">
+        <v>1.74</v>
+      </c>
+      <c r="BJ272">
+        <v>1.97</v>
+      </c>
+      <c r="BK272">
+        <v>2.17</v>
+      </c>
+      <c r="BL272">
+        <v>1.6</v>
+      </c>
+      <c r="BM272">
+        <v>2.8</v>
+      </c>
+      <c r="BN272">
+        <v>1.38</v>
+      </c>
+      <c r="BO272">
+        <v>3.65</v>
+      </c>
+      <c r="BP272">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="365">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,18 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['26', '42']</t>
+  </si>
+  <si>
+    <t>['84', '90+5']</t>
+  </si>
+  <si>
+    <t>['2', '18']</t>
+  </si>
+  <si>
+    <t>['23']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1048,9 +1060,6 @@
     <t>['20', '29', '89']</t>
   </si>
   <si>
-    <t>['23']</t>
-  </si>
-  <si>
     <t>['22', '24']</t>
   </si>
   <si>
@@ -1097,6 +1106,9 @@
   </si>
   <si>
     <t>['30', '56', '65']</t>
+  </si>
+  <si>
+    <t>['12', '87']</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP272"/>
+  <dimension ref="A1:BP277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1920,7 +1932,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2332,7 +2344,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2619,7 +2631,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ6">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2744,7 +2756,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2822,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ7">
         <v>0.92</v>
@@ -3028,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8">
         <v>0.5</v>
@@ -3156,7 +3168,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3237,7 +3249,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ9">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3362,7 +3374,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3649,7 +3661,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3774,7 +3786,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3980,7 +3992,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4061,7 +4073,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ13">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -4186,7 +4198,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4473,7 +4485,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ15">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR15">
         <v>1.84</v>
@@ -4804,7 +4816,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5294,7 +5306,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5422,7 +5434,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5834,7 +5846,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6118,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6246,7 +6258,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6533,7 +6545,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ25">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6864,7 +6876,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7148,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28">
         <v>0.93</v>
@@ -7354,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29">
         <v>1.38</v>
@@ -7766,10 +7778,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ31">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -8100,7 +8112,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8181,7 +8193,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR33">
         <v>1.54</v>
@@ -8512,7 +8524,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8590,10 +8602,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ35">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8718,7 +8730,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9002,7 +9014,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ37">
         <v>1.07</v>
@@ -9211,7 +9223,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ38">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>1.18</v>
@@ -9542,7 +9554,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9748,7 +9760,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9954,7 +9966,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10032,7 +10044,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ42">
         <v>0.93</v>
@@ -10447,7 +10459,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ44">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10778,7 +10790,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10856,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ46">
         <v>1.14</v>
@@ -11190,7 +11202,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11396,7 +11408,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11474,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11602,7 +11614,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11808,7 +11820,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11889,7 +11901,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -12014,7 +12026,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12095,7 +12107,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12632,7 +12644,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12919,7 +12931,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ56">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -13456,7 +13468,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13534,7 +13546,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ59">
         <v>1.15</v>
@@ -13743,7 +13755,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ60">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR60">
         <v>0.97</v>
@@ -13868,7 +13880,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14074,7 +14086,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14358,7 +14370,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ63">
         <v>1.53</v>
@@ -14486,7 +14498,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14770,7 +14782,7 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14898,7 +14910,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -14976,10 +14988,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ66">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15182,10 +15194,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ67">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -15310,7 +15322,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15722,7 +15734,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15928,7 +15940,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16009,7 +16021,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ71">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -16134,7 +16146,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16340,7 +16352,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16418,7 +16430,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ73">
         <v>0.5</v>
@@ -16546,7 +16558,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16624,10 +16636,10 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ74">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR74">
         <v>1.29</v>
@@ -16958,7 +16970,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17164,7 +17176,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17370,7 +17382,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17576,7 +17588,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17782,7 +17794,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18069,7 +18081,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ81">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18400,7 +18412,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18481,7 +18493,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ83">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -18606,7 +18618,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -19018,7 +19030,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19224,7 +19236,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19430,7 +19442,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19508,10 +19520,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ88">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -19714,10 +19726,10 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -20048,7 +20060,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20126,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>0.92</v>
@@ -20538,7 +20550,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ93">
         <v>1.08</v>
@@ -20953,7 +20965,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ95">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -21362,7 +21374,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ97">
         <v>0.93</v>
@@ -21568,10 +21580,10 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ98">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR98">
         <v>1.24</v>
@@ -21980,10 +21992,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ100">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -22189,7 +22201,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ101">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22726,7 +22738,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22804,7 +22816,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ104">
         <v>2</v>
@@ -22932,7 +22944,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23013,7 +23025,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ105">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -24580,7 +24592,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24864,7 +24876,7 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ114">
         <v>1.07</v>
@@ -25276,7 +25288,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25404,7 +25416,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25485,7 +25497,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ117">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -25610,7 +25622,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25691,7 +25703,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ118">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -25897,7 +25909,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ119">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR119">
         <v>1.61</v>
@@ -26306,10 +26318,10 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ121">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26434,7 +26446,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26512,7 +26524,7 @@
         <v>1.57</v>
       </c>
       <c r="AP122">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ122">
         <v>1.14</v>
@@ -27258,7 +27270,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27545,7 +27557,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ127">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27670,7 +27682,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27748,7 +27760,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ128">
         <v>1.53</v>
@@ -27876,7 +27888,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28082,7 +28094,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28288,7 +28300,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28494,7 +28506,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28778,10 +28790,10 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ133">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR133">
         <v>1.46</v>
@@ -28984,7 +28996,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ134">
         <v>1.08</v>
@@ -29190,10 +29202,10 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ135">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -29318,7 +29330,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29399,7 +29411,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29602,7 +29614,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29730,7 +29742,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29811,7 +29823,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ138">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR138">
         <v>1.4</v>
@@ -30348,7 +30360,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30554,7 +30566,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30760,7 +30772,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30966,7 +30978,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31047,7 +31059,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ144">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31378,7 +31390,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31996,7 +32008,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32202,7 +32214,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32280,7 +32292,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32614,7 +32626,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32692,7 +32704,7 @@
         <v>0.86</v>
       </c>
       <c r="AP152">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -33104,7 +33116,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ154">
         <v>1.14</v>
@@ -33232,7 +33244,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33313,7 +33325,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ155">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -33519,7 +33531,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ156">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33644,7 +33656,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34056,7 +34068,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34343,7 +34355,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ160">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR160">
         <v>1.62</v>
@@ -34468,7 +34480,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34546,7 +34558,7 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ161">
         <v>0.92</v>
@@ -34880,7 +34892,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34961,7 +34973,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ163">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35292,7 +35304,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35370,7 +35382,7 @@
         <v>2.25</v>
       </c>
       <c r="AP165">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ165">
         <v>2</v>
@@ -35576,7 +35588,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ166">
         <v>0.77</v>
@@ -35910,7 +35922,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36403,7 +36415,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ170">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36528,7 +36540,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37018,7 +37030,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ173">
         <v>1.14</v>
@@ -37430,7 +37442,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ175">
         <v>0.77</v>
@@ -37845,7 +37857,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ177">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -37970,7 +37982,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38176,7 +38188,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38460,7 +38472,7 @@
         <v>0.63</v>
       </c>
       <c r="AP180">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -39206,7 +39218,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39287,7 +39299,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ184">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39412,7 +39424,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39493,7 +39505,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ185">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39902,10 +39914,10 @@
         <v>1.56</v>
       </c>
       <c r="AP187">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ187">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -40030,7 +40042,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40314,10 +40326,10 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.33</v>
@@ -40648,7 +40660,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40854,7 +40866,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41344,7 +41356,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41550,7 +41562,7 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ195">
         <v>0.77</v>
@@ -41884,7 +41896,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42377,7 +42389,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ199">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR199">
         <v>1.22</v>
@@ -42502,7 +42514,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42580,7 +42592,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ200">
         <v>0.85</v>
@@ -42789,7 +42801,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ201">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42914,7 +42926,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43326,7 +43338,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43738,7 +43750,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -43944,7 +43956,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44025,7 +44037,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ207">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -44150,7 +44162,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44228,10 +44240,10 @@
         <v>1.7</v>
       </c>
       <c r="AP208">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ208">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR208">
         <v>1.42</v>
@@ -44434,10 +44446,10 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ209">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -44974,7 +44986,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45180,7 +45192,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45261,7 +45273,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ213">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR213">
         <v>1.3</v>
@@ -45798,7 +45810,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46004,7 +46016,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46291,7 +46303,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ218">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR218">
         <v>1.25</v>
@@ -46622,7 +46634,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46700,7 +46712,7 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ220">
         <v>1</v>
@@ -46828,7 +46840,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46906,7 +46918,7 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221">
         <v>1.53</v>
@@ -47034,7 +47046,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47318,7 +47330,7 @@
         <v>0.55</v>
       </c>
       <c r="AP223">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ223">
         <v>0.5</v>
@@ -47446,7 +47458,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47524,7 +47536,7 @@
         <v>0.91</v>
       </c>
       <c r="AP224">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -47652,7 +47664,7 @@
         <v>138</v>
       </c>
       <c r="P225" t="s">
-        <v>344</v>
+        <v>256</v>
       </c>
       <c r="Q225">
         <v>2.7</v>
@@ -47730,7 +47742,7 @@
         <v>1.1</v>
       </c>
       <c r="AP225">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ225">
         <v>1.15</v>
@@ -47858,7 +47870,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47939,7 +47951,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ226">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR226">
         <v>1.51</v>
@@ -48064,7 +48076,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48270,7 +48282,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48557,7 +48569,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ229">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -48888,7 +48900,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49094,7 +49106,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49175,7 +49187,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ232">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR232">
         <v>1.79</v>
@@ -49584,7 +49596,7 @@
         <v>1.25</v>
       </c>
       <c r="AP234">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -49712,7 +49724,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49918,7 +49930,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50205,7 +50217,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ237">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR237">
         <v>1.46</v>
@@ -50411,7 +50423,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ238">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR238">
         <v>1.73</v>
@@ -50536,7 +50548,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50614,7 +50626,7 @@
         <v>1</v>
       </c>
       <c r="AP239">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ239">
         <v>1.08</v>
@@ -50948,7 +50960,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51235,7 +51247,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ242">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -51441,7 +51453,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ243">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR243">
         <v>1.47</v>
@@ -51566,7 +51578,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51850,7 +51862,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ245">
         <v>1.38</v>
@@ -52802,7 +52814,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53086,7 +53098,7 @@
         <v>1.09</v>
       </c>
       <c r="AP251">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ251">
         <v>1.15</v>
@@ -53295,7 +53307,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ252">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR252">
         <v>1.3</v>
@@ -53420,7 +53432,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53626,7 +53638,7 @@
         <v>208</v>
       </c>
       <c r="P254" t="s">
-        <v>344</v>
+        <v>256</v>
       </c>
       <c r="Q254">
         <v>4</v>
@@ -53910,7 +53922,7 @@
         <v>1.17</v>
       </c>
       <c r="AP255">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AQ255">
         <v>1.08</v>
@@ -54116,10 +54128,10 @@
         <v>0.58</v>
       </c>
       <c r="AP256">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ256">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR256">
         <v>1.38</v>
@@ -54325,7 +54337,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ257">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR257">
         <v>1.38</v>
@@ -54528,7 +54540,7 @@
         <v>1</v>
       </c>
       <c r="AP258">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ258">
         <v>1</v>
@@ -54734,7 +54746,7 @@
         <v>0.83</v>
       </c>
       <c r="AP259">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ259">
         <v>0.77</v>
@@ -54862,7 +54874,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -54943,7 +54955,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ260">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AR260">
         <v>1.76</v>
@@ -55146,10 +55158,10 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ261">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR261">
         <v>1.47</v>
@@ -55480,7 +55492,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -56098,7 +56110,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56304,7 +56316,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56510,7 +56522,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -57128,7 +57140,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57491,6 +57503,1036 @@
       </c>
       <c r="BP272">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7509858</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F273">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>86</v>
+      </c>
+      <c r="H273" t="s">
+        <v>82</v>
+      </c>
+      <c r="I273">
+        <v>2</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273">
+        <v>3</v>
+      </c>
+      <c r="L273">
+        <v>2</v>
+      </c>
+      <c r="M273">
+        <v>2</v>
+      </c>
+      <c r="N273">
+        <v>4</v>
+      </c>
+      <c r="O273" t="s">
+        <v>253</v>
+      </c>
+      <c r="P273" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q273">
+        <v>4.2</v>
+      </c>
+      <c r="R273">
+        <v>2.08</v>
+      </c>
+      <c r="S273">
+        <v>2.7</v>
+      </c>
+      <c r="T273">
+        <v>1.46</v>
+      </c>
+      <c r="U273">
+        <v>2.55</v>
+      </c>
+      <c r="V273">
+        <v>3</v>
+      </c>
+      <c r="W273">
+        <v>1.34</v>
+      </c>
+      <c r="X273">
+        <v>8.5</v>
+      </c>
+      <c r="Y273">
+        <v>1.01</v>
+      </c>
+      <c r="Z273">
+        <v>3.79</v>
+      </c>
+      <c r="AA273">
+        <v>3.23</v>
+      </c>
+      <c r="AB273">
+        <v>2.17</v>
+      </c>
+      <c r="AC273">
+        <v>1.08</v>
+      </c>
+      <c r="AD273">
+        <v>7.5</v>
+      </c>
+      <c r="AE273">
+        <v>1.37</v>
+      </c>
+      <c r="AF273">
+        <v>2.85</v>
+      </c>
+      <c r="AG273">
+        <v>2.1</v>
+      </c>
+      <c r="AH273">
+        <v>1.61</v>
+      </c>
+      <c r="AI273">
+        <v>1.87</v>
+      </c>
+      <c r="AJ273">
+        <v>1.84</v>
+      </c>
+      <c r="AK273">
+        <v>1.67</v>
+      </c>
+      <c r="AL273">
+        <v>1.32</v>
+      </c>
+      <c r="AM273">
+        <v>1.28</v>
+      </c>
+      <c r="AN273">
+        <v>1.85</v>
+      </c>
+      <c r="AO273">
+        <v>1.62</v>
+      </c>
+      <c r="AP273">
+        <v>1.79</v>
+      </c>
+      <c r="AQ273">
+        <v>1.57</v>
+      </c>
+      <c r="AR273">
+        <v>1.39</v>
+      </c>
+      <c r="AS273">
+        <v>1.47</v>
+      </c>
+      <c r="AT273">
+        <v>2.86</v>
+      </c>
+      <c r="AU273">
+        <v>4</v>
+      </c>
+      <c r="AV273">
+        <v>6</v>
+      </c>
+      <c r="AW273">
+        <v>3</v>
+      </c>
+      <c r="AX273">
+        <v>13</v>
+      </c>
+      <c r="AY273">
+        <v>7</v>
+      </c>
+      <c r="AZ273">
+        <v>21</v>
+      </c>
+      <c r="BA273">
+        <v>0</v>
+      </c>
+      <c r="BB273">
+        <v>7</v>
+      </c>
+      <c r="BC273">
+        <v>7</v>
+      </c>
+      <c r="BD273">
+        <v>2.48</v>
+      </c>
+      <c r="BE273">
+        <v>6.5</v>
+      </c>
+      <c r="BF273">
+        <v>1.65</v>
+      </c>
+      <c r="BG273">
+        <v>1.36</v>
+      </c>
+      <c r="BH273">
+        <v>2.8</v>
+      </c>
+      <c r="BI273">
+        <v>1.63</v>
+      </c>
+      <c r="BJ273">
+        <v>2.12</v>
+      </c>
+      <c r="BK273">
+        <v>1.98</v>
+      </c>
+      <c r="BL273">
+        <v>1.72</v>
+      </c>
+      <c r="BM273">
+        <v>2.5</v>
+      </c>
+      <c r="BN273">
+        <v>1.46</v>
+      </c>
+      <c r="BO273">
+        <v>3.3</v>
+      </c>
+      <c r="BP273">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7509860</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F274">
+        <v>28</v>
+      </c>
+      <c r="G274" t="s">
+        <v>76</v>
+      </c>
+      <c r="H274" t="s">
+        <v>74</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>0</v>
+      </c>
+      <c r="L274">
+        <v>2</v>
+      </c>
+      <c r="M274">
+        <v>0</v>
+      </c>
+      <c r="N274">
+        <v>2</v>
+      </c>
+      <c r="O274" t="s">
+        <v>254</v>
+      </c>
+      <c r="P274" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q274">
+        <v>2.95</v>
+      </c>
+      <c r="R274">
+        <v>1.9</v>
+      </c>
+      <c r="S274">
+        <v>3.8</v>
+      </c>
+      <c r="T274">
+        <v>1.5</v>
+      </c>
+      <c r="U274">
+        <v>2.4</v>
+      </c>
+      <c r="V274">
+        <v>3.2</v>
+      </c>
+      <c r="W274">
+        <v>1.3</v>
+      </c>
+      <c r="X274">
+        <v>9</v>
+      </c>
+      <c r="Y274">
+        <v>1.06</v>
+      </c>
+      <c r="Z274">
+        <v>2.23</v>
+      </c>
+      <c r="AA274">
+        <v>3.26</v>
+      </c>
+      <c r="AB274">
+        <v>3.57</v>
+      </c>
+      <c r="AC274">
+        <v>1.09</v>
+      </c>
+      <c r="AD274">
+        <v>7</v>
+      </c>
+      <c r="AE274">
+        <v>1.41</v>
+      </c>
+      <c r="AF274">
+        <v>2.65</v>
+      </c>
+      <c r="AG274">
+        <v>2.2</v>
+      </c>
+      <c r="AH274">
+        <v>1.55</v>
+      </c>
+      <c r="AI274">
+        <v>1.93</v>
+      </c>
+      <c r="AJ274">
+        <v>1.75</v>
+      </c>
+      <c r="AK274">
+        <v>1.33</v>
+      </c>
+      <c r="AL274">
+        <v>1.36</v>
+      </c>
+      <c r="AM274">
+        <v>1.57</v>
+      </c>
+      <c r="AN274">
+        <v>1.77</v>
+      </c>
+      <c r="AO274">
+        <v>0.54</v>
+      </c>
+      <c r="AP274">
+        <v>1.86</v>
+      </c>
+      <c r="AQ274">
+        <v>0.5</v>
+      </c>
+      <c r="AR274">
+        <v>1.43</v>
+      </c>
+      <c r="AS274">
+        <v>1.17</v>
+      </c>
+      <c r="AT274">
+        <v>2.6</v>
+      </c>
+      <c r="AU274">
+        <v>5</v>
+      </c>
+      <c r="AV274">
+        <v>7</v>
+      </c>
+      <c r="AW274">
+        <v>12</v>
+      </c>
+      <c r="AX274">
+        <v>7</v>
+      </c>
+      <c r="AY274">
+        <v>17</v>
+      </c>
+      <c r="AZ274">
+        <v>16</v>
+      </c>
+      <c r="BA274">
+        <v>9</v>
+      </c>
+      <c r="BB274">
+        <v>2</v>
+      </c>
+      <c r="BC274">
+        <v>11</v>
+      </c>
+      <c r="BD274">
+        <v>1.74</v>
+      </c>
+      <c r="BE274">
+        <v>6.1</v>
+      </c>
+      <c r="BF274">
+        <v>2.38</v>
+      </c>
+      <c r="BG274">
+        <v>1.55</v>
+      </c>
+      <c r="BH274">
+        <v>2.28</v>
+      </c>
+      <c r="BI274">
+        <v>1.93</v>
+      </c>
+      <c r="BJ274">
+        <v>1.77</v>
+      </c>
+      <c r="BK274">
+        <v>2.48</v>
+      </c>
+      <c r="BL274">
+        <v>1.48</v>
+      </c>
+      <c r="BM274">
+        <v>3.3</v>
+      </c>
+      <c r="BN274">
+        <v>1.28</v>
+      </c>
+      <c r="BO274">
+        <v>4.4</v>
+      </c>
+      <c r="BP274">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7509861</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F275">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>75</v>
+      </c>
+      <c r="H275" t="s">
+        <v>85</v>
+      </c>
+      <c r="I275">
+        <v>2</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275">
+        <v>3</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>3</v>
+      </c>
+      <c r="O275" t="s">
+        <v>255</v>
+      </c>
+      <c r="P275" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q275">
+        <v>2.7</v>
+      </c>
+      <c r="R275">
+        <v>1.98</v>
+      </c>
+      <c r="S275">
+        <v>4.1</v>
+      </c>
+      <c r="T275">
+        <v>1.46</v>
+      </c>
+      <c r="U275">
+        <v>2.5</v>
+      </c>
+      <c r="V275">
+        <v>3</v>
+      </c>
+      <c r="W275">
+        <v>1.33</v>
+      </c>
+      <c r="X275">
+        <v>8.25</v>
+      </c>
+      <c r="Y275">
+        <v>1.06</v>
+      </c>
+      <c r="Z275">
+        <v>2.11</v>
+      </c>
+      <c r="AA275">
+        <v>3.37</v>
+      </c>
+      <c r="AB275">
+        <v>3.78</v>
+      </c>
+      <c r="AC275">
+        <v>1.07</v>
+      </c>
+      <c r="AD275">
+        <v>8</v>
+      </c>
+      <c r="AE275">
+        <v>1.36</v>
+      </c>
+      <c r="AF275">
+        <v>2.9</v>
+      </c>
+      <c r="AG275">
+        <v>2.05</v>
+      </c>
+      <c r="AH275">
+        <v>1.61</v>
+      </c>
+      <c r="AI275">
+        <v>1.9</v>
+      </c>
+      <c r="AJ275">
+        <v>1.8</v>
+      </c>
+      <c r="AK275">
+        <v>1.27</v>
+      </c>
+      <c r="AL275">
+        <v>1.33</v>
+      </c>
+      <c r="AM275">
+        <v>1.71</v>
+      </c>
+      <c r="AN275">
+        <v>0.93</v>
+      </c>
+      <c r="AO275">
+        <v>0.71</v>
+      </c>
+      <c r="AP275">
+        <v>1.07</v>
+      </c>
+      <c r="AQ275">
+        <v>0.67</v>
+      </c>
+      <c r="AR275">
+        <v>1.45</v>
+      </c>
+      <c r="AS275">
+        <v>1.26</v>
+      </c>
+      <c r="AT275">
+        <v>2.71</v>
+      </c>
+      <c r="AU275">
+        <v>4</v>
+      </c>
+      <c r="AV275">
+        <v>4</v>
+      </c>
+      <c r="AW275">
+        <v>8</v>
+      </c>
+      <c r="AX275">
+        <v>19</v>
+      </c>
+      <c r="AY275">
+        <v>13</v>
+      </c>
+      <c r="AZ275">
+        <v>28</v>
+      </c>
+      <c r="BA275">
+        <v>3</v>
+      </c>
+      <c r="BB275">
+        <v>9</v>
+      </c>
+      <c r="BC275">
+        <v>12</v>
+      </c>
+      <c r="BD275">
+        <v>1.63</v>
+      </c>
+      <c r="BE275">
+        <v>6.5</v>
+      </c>
+      <c r="BF275">
+        <v>2.55</v>
+      </c>
+      <c r="BG275">
+        <v>1.45</v>
+      </c>
+      <c r="BH275">
+        <v>2.55</v>
+      </c>
+      <c r="BI275">
+        <v>1.74</v>
+      </c>
+      <c r="BJ275">
+        <v>1.96</v>
+      </c>
+      <c r="BK275">
+        <v>2.18</v>
+      </c>
+      <c r="BL275">
+        <v>1.58</v>
+      </c>
+      <c r="BM275">
+        <v>2.9</v>
+      </c>
+      <c r="BN275">
+        <v>1.35</v>
+      </c>
+      <c r="BO275">
+        <v>3.9</v>
+      </c>
+      <c r="BP275">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7509862</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45717.45833333334</v>
+      </c>
+      <c r="F276">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>88</v>
+      </c>
+      <c r="H276" t="s">
+        <v>87</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276">
+        <v>1</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+      <c r="M276">
+        <v>1</v>
+      </c>
+      <c r="N276">
+        <v>1</v>
+      </c>
+      <c r="O276" t="s">
+        <v>102</v>
+      </c>
+      <c r="P276" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q276">
+        <v>2.6</v>
+      </c>
+      <c r="R276">
+        <v>2.03</v>
+      </c>
+      <c r="S276">
+        <v>4.8</v>
+      </c>
+      <c r="T276">
+        <v>1.51</v>
+      </c>
+      <c r="U276">
+        <v>2.4</v>
+      </c>
+      <c r="V276">
+        <v>3.25</v>
+      </c>
+      <c r="W276">
+        <v>1.3</v>
+      </c>
+      <c r="X276">
+        <v>9</v>
+      </c>
+      <c r="Y276">
+        <v>1.04</v>
+      </c>
+      <c r="Z276">
+        <v>2.02</v>
+      </c>
+      <c r="AA276">
+        <v>3.3</v>
+      </c>
+      <c r="AB276">
+        <v>4.2</v>
+      </c>
+      <c r="AC276">
+        <v>1.09</v>
+      </c>
+      <c r="AD276">
+        <v>7</v>
+      </c>
+      <c r="AE276">
+        <v>1.43</v>
+      </c>
+      <c r="AF276">
+        <v>2.6</v>
+      </c>
+      <c r="AG276">
+        <v>2.25</v>
+      </c>
+      <c r="AH276">
+        <v>1.53</v>
+      </c>
+      <c r="AI276">
+        <v>2.05</v>
+      </c>
+      <c r="AJ276">
+        <v>1.7</v>
+      </c>
+      <c r="AK276">
+        <v>1.23</v>
+      </c>
+      <c r="AL276">
+        <v>1.31</v>
+      </c>
+      <c r="AM276">
+        <v>1.78</v>
+      </c>
+      <c r="AN276">
+        <v>1.85</v>
+      </c>
+      <c r="AO276">
+        <v>1.36</v>
+      </c>
+      <c r="AP276">
+        <v>1.71</v>
+      </c>
+      <c r="AQ276">
+        <v>1.47</v>
+      </c>
+      <c r="AR276">
+        <v>1.25</v>
+      </c>
+      <c r="AS276">
+        <v>1.16</v>
+      </c>
+      <c r="AT276">
+        <v>2.41</v>
+      </c>
+      <c r="AU276">
+        <v>5</v>
+      </c>
+      <c r="AV276">
+        <v>5</v>
+      </c>
+      <c r="AW276">
+        <v>8</v>
+      </c>
+      <c r="AX276">
+        <v>7</v>
+      </c>
+      <c r="AY276">
+        <v>13</v>
+      </c>
+      <c r="AZ276">
+        <v>14</v>
+      </c>
+      <c r="BA276">
+        <v>8</v>
+      </c>
+      <c r="BB276">
+        <v>4</v>
+      </c>
+      <c r="BC276">
+        <v>12</v>
+      </c>
+      <c r="BD276">
+        <v>1.64</v>
+      </c>
+      <c r="BE276">
+        <v>6.5</v>
+      </c>
+      <c r="BF276">
+        <v>2.55</v>
+      </c>
+      <c r="BG276">
+        <v>1.41</v>
+      </c>
+      <c r="BH276">
+        <v>2.65</v>
+      </c>
+      <c r="BI276">
+        <v>1.68</v>
+      </c>
+      <c r="BJ276">
+        <v>2.05</v>
+      </c>
+      <c r="BK276">
+        <v>2.08</v>
+      </c>
+      <c r="BL276">
+        <v>1.66</v>
+      </c>
+      <c r="BM276">
+        <v>2.65</v>
+      </c>
+      <c r="BN276">
+        <v>1.42</v>
+      </c>
+      <c r="BO276">
+        <v>3.45</v>
+      </c>
+      <c r="BP276">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7509865</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45717.55208333334</v>
+      </c>
+      <c r="F277">
+        <v>28</v>
+      </c>
+      <c r="G277" t="s">
+        <v>84</v>
+      </c>
+      <c r="H277" t="s">
+        <v>73</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>1</v>
+      </c>
+      <c r="L277">
+        <v>1</v>
+      </c>
+      <c r="M277">
+        <v>0</v>
+      </c>
+      <c r="N277">
+        <v>1</v>
+      </c>
+      <c r="O277" t="s">
+        <v>256</v>
+      </c>
+      <c r="P277" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q277">
+        <v>2.55</v>
+      </c>
+      <c r="R277">
+        <v>2.05</v>
+      </c>
+      <c r="S277">
+        <v>4.1</v>
+      </c>
+      <c r="T277">
+        <v>1.4</v>
+      </c>
+      <c r="U277">
+        <v>2.7</v>
+      </c>
+      <c r="V277">
+        <v>2.75</v>
+      </c>
+      <c r="W277">
+        <v>1.38</v>
+      </c>
+      <c r="X277">
+        <v>7.25</v>
+      </c>
+      <c r="Y277">
+        <v>1.08</v>
+      </c>
+      <c r="Z277">
+        <v>2.01</v>
+      </c>
+      <c r="AA277">
+        <v>3.4</v>
+      </c>
+      <c r="AB277">
+        <v>4.1</v>
+      </c>
+      <c r="AC277">
+        <v>1.06</v>
+      </c>
+      <c r="AD277">
+        <v>8.5</v>
+      </c>
+      <c r="AE277">
+        <v>1.31</v>
+      </c>
+      <c r="AF277">
+        <v>3.1</v>
+      </c>
+      <c r="AG277">
+        <v>2.02</v>
+      </c>
+      <c r="AH277">
+        <v>1.8</v>
+      </c>
+      <c r="AI277">
+        <v>1.78</v>
+      </c>
+      <c r="AJ277">
+        <v>1.9</v>
+      </c>
+      <c r="AK277">
+        <v>1.25</v>
+      </c>
+      <c r="AL277">
+        <v>1.3</v>
+      </c>
+      <c r="AM277">
+        <v>1.8</v>
+      </c>
+      <c r="AN277">
+        <v>2.62</v>
+      </c>
+      <c r="AO277">
+        <v>1.69</v>
+      </c>
+      <c r="AP277">
+        <v>2.64</v>
+      </c>
+      <c r="AQ277">
+        <v>1.57</v>
+      </c>
+      <c r="AR277">
+        <v>1.68</v>
+      </c>
+      <c r="AS277">
+        <v>1.16</v>
+      </c>
+      <c r="AT277">
+        <v>2.84</v>
+      </c>
+      <c r="AU277">
+        <v>4</v>
+      </c>
+      <c r="AV277">
+        <v>4</v>
+      </c>
+      <c r="AW277">
+        <v>11</v>
+      </c>
+      <c r="AX277">
+        <v>7</v>
+      </c>
+      <c r="AY277">
+        <v>20</v>
+      </c>
+      <c r="AZ277">
+        <v>13</v>
+      </c>
+      <c r="BA277">
+        <v>8</v>
+      </c>
+      <c r="BB277">
+        <v>10</v>
+      </c>
+      <c r="BC277">
+        <v>18</v>
+      </c>
+      <c r="BD277">
+        <v>1.57</v>
+      </c>
+      <c r="BE277">
+        <v>6.4</v>
+      </c>
+      <c r="BF277">
+        <v>2.7</v>
+      </c>
+      <c r="BG277">
+        <v>1.47</v>
+      </c>
+      <c r="BH277">
+        <v>2.48</v>
+      </c>
+      <c r="BI277">
+        <v>1.77</v>
+      </c>
+      <c r="BJ277">
+        <v>1.92</v>
+      </c>
+      <c r="BK277">
+        <v>2.23</v>
+      </c>
+      <c r="BL277">
+        <v>1.56</v>
+      </c>
+      <c r="BM277">
+        <v>2.95</v>
+      </c>
+      <c r="BN277">
+        <v>1.33</v>
+      </c>
+      <c r="BO277">
+        <v>3.95</v>
+      </c>
+      <c r="BP277">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -57460,10 +57460,10 @@
         <v>2</v>
       </c>
       <c r="BB272">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC272">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD272">
         <v>2.55</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -787,6 +787,12 @@
     <t>['23']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -850,9 +856,6 @@
     <t>['77', '90+4']</t>
   </si>
   <si>
-    <t>['48']</t>
-  </si>
-  <si>
     <t>['2', '45+4', '62']</t>
   </si>
   <si>
@@ -866,9 +869,6 @@
   </si>
   <si>
     <t>['35', '63']</t>
-  </si>
-  <si>
-    <t>['87']</t>
   </si>
   <si>
     <t>['58', '84']</t>
@@ -1109,6 +1109,12 @@
   </si>
   <si>
     <t>['12', '87']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP277"/>
+  <dimension ref="A1:BP281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1932,7 +1938,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2010,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ3">
         <v>1.07</v>
@@ -2344,7 +2350,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2756,7 +2762,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2837,7 +2843,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ7">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3168,7 +3174,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3374,7 +3380,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3452,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ10">
         <v>2</v>
@@ -3786,7 +3792,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3864,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12">
         <v>1.15</v>
@@ -3992,7 +3998,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4198,7 +4204,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4816,7 +4822,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5434,7 +5440,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5515,7 +5521,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ20">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5718,7 +5724,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
         <v>1.07</v>
@@ -5846,7 +5852,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5924,7 +5930,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -6258,7 +6264,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6339,7 +6345,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR24">
         <v>1.67</v>
@@ -6751,7 +6757,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ26">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -6876,7 +6882,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -8112,7 +8118,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8190,7 +8196,7 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ33">
         <v>1.47</v>
@@ -8524,7 +8530,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8730,7 +8736,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8811,7 +8817,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -9426,10 +9432,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9554,7 +9560,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9760,7 +9766,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9838,7 +9844,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ41">
         <v>0.5</v>
@@ -9966,7 +9972,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10456,7 +10462,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -10790,7 +10796,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11202,7 +11208,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11408,7 +11414,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11614,7 +11620,7 @@
         <v>127</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11695,7 +11701,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ50">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -11820,7 +11826,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12026,7 +12032,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12104,7 +12110,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>1.57</v>
@@ -12516,7 +12522,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12644,7 +12650,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -12725,7 +12731,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ55">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.42</v>
@@ -13340,7 +13346,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ58">
         <v>1.07</v>
@@ -13468,7 +13474,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13880,7 +13886,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14086,7 +14092,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14498,7 +14504,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="Q64">
         <v>2.9</v>
@@ -14576,10 +14582,10 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ64">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -15400,10 +15406,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ68">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -16558,7 +16564,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16970,7 +16976,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17463,7 +17469,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ78">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17872,7 +17878,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ80">
         <v>0.93</v>
@@ -18078,7 +18084,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -18284,7 +18290,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ82">
         <v>1.38</v>
@@ -18905,7 +18911,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ85">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -19108,7 +19114,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ86">
         <v>1.14</v>
@@ -20141,7 +20147,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR91">
         <v>1.67</v>
@@ -20553,7 +20559,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.54</v>
@@ -21168,7 +21174,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21786,7 +21792,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -22404,7 +22410,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ102">
         <v>0.5</v>
@@ -23022,7 +23028,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ105">
         <v>1.57</v>
@@ -23231,7 +23237,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ106">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -23849,7 +23855,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ109">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR109">
         <v>1.52</v>
@@ -24670,7 +24676,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -25082,7 +25088,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ115">
         <v>0.85</v>
@@ -25906,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ119">
         <v>1.47</v>
@@ -26115,7 +26121,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ120">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR120">
         <v>1.28</v>
@@ -26939,7 +26945,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR124">
         <v>1.36</v>
@@ -27142,7 +27148,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ125">
         <v>0.5</v>
@@ -27351,7 +27357,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ126">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -28999,7 +29005,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ134">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29408,7 +29414,7 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ136">
         <v>0.67</v>
@@ -29820,7 +29826,7 @@
         <v>1.29</v>
       </c>
       <c r="AP138">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ138">
         <v>1.47</v>
@@ -30360,7 +30366,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30438,10 +30444,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ141">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR141">
         <v>1.62</v>
@@ -31880,7 +31886,7 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ148">
         <v>1.53</v>
@@ -32089,7 +32095,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ149">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32910,7 +32916,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -33528,7 +33534,7 @@
         <v>0.71</v>
       </c>
       <c r="AP156">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ156">
         <v>0.5</v>
@@ -33940,10 +33946,10 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ158">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR158">
         <v>1.22</v>
@@ -34561,7 +34567,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ161">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR161">
         <v>1.67</v>
@@ -35591,7 +35597,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ166">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -36000,7 +36006,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ168">
         <v>1.38</v>
@@ -36827,7 +36833,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ172">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR172">
         <v>1.72</v>
@@ -37236,7 +37242,7 @@
         <v>0.75</v>
       </c>
       <c r="AP174">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ174">
         <v>1</v>
@@ -37445,7 +37451,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ175">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -37854,7 +37860,7 @@
         <v>1.75</v>
       </c>
       <c r="AP177">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ177">
         <v>1.57</v>
@@ -37982,7 +37988,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38266,7 +38272,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179">
         <v>1.53</v>
@@ -38681,7 +38687,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ181">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR181">
         <v>1.41</v>
@@ -40532,7 +40538,7 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ190">
         <v>1.15</v>
@@ -40947,7 +40953,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ192">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR192">
         <v>1.54</v>
@@ -41150,7 +41156,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ193">
         <v>1.53</v>
@@ -41565,7 +41571,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ195">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41768,7 +41774,7 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ196">
         <v>1</v>
@@ -42386,7 +42392,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199">
         <v>0.5</v>
@@ -43622,7 +43628,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ205">
         <v>0.93</v>
@@ -43750,7 +43756,7 @@
         <v>197</v>
       </c>
       <c r="P206" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="Q206">
         <v>2.5</v>
@@ -44655,7 +44661,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ210">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
         <v>1.56</v>
@@ -45479,7 +45485,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ214">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR214">
         <v>1.56</v>
@@ -45682,7 +45688,7 @@
         <v>0.9</v>
       </c>
       <c r="AP215">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ215">
         <v>0.85</v>
@@ -46094,10 +46100,10 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ217">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46300,7 +46306,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ218">
         <v>1.57</v>
@@ -46506,7 +46512,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ219">
         <v>1.07</v>
@@ -47870,7 +47876,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48157,7 +48163,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ227">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR227">
         <v>1.29</v>
@@ -49184,7 +49190,7 @@
         <v>1.64</v>
       </c>
       <c r="AP232">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ232">
         <v>1.57</v>
@@ -49393,7 +49399,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ233">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR233">
         <v>1.42</v>
@@ -50008,7 +50014,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ236">
         <v>1</v>
@@ -50214,7 +50220,7 @@
         <v>0.75</v>
       </c>
       <c r="AP237">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ237">
         <v>0.67</v>
@@ -50629,7 +50635,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ239">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR239">
         <v>1.34</v>
@@ -51038,7 +51044,7 @@
         <v>0.91</v>
       </c>
       <c r="AP241">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ241">
         <v>0.85</v>
@@ -53304,7 +53310,7 @@
         <v>1.46</v>
       </c>
       <c r="AP252">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ252">
         <v>1.47</v>
@@ -53513,7 +53519,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ253">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR253">
         <v>1.42</v>
@@ -53716,7 +53722,7 @@
         <v>1.62</v>
       </c>
       <c r="AP254">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ254">
         <v>1.53</v>
@@ -53925,7 +53931,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ255">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR255">
         <v>1.73</v>
@@ -54334,7 +54340,7 @@
         <v>1.67</v>
       </c>
       <c r="AP257">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ257">
         <v>1.57</v>
@@ -54749,7 +54755,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ259">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR259">
         <v>1.26</v>
@@ -54952,7 +54958,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP260">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ260">
         <v>0.67</v>
@@ -58533,6 +58539,830 @@
       </c>
       <c r="BP277">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7509864</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>89</v>
+      </c>
+      <c r="H278" t="s">
+        <v>70</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>0</v>
+      </c>
+      <c r="L278">
+        <v>1</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
+      </c>
+      <c r="N278">
+        <v>1</v>
+      </c>
+      <c r="O278" t="s">
+        <v>257</v>
+      </c>
+      <c r="P278" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q278">
+        <v>2.35</v>
+      </c>
+      <c r="R278">
+        <v>2.1</v>
+      </c>
+      <c r="S278">
+        <v>4.4</v>
+      </c>
+      <c r="T278">
+        <v>1.38</v>
+      </c>
+      <c r="U278">
+        <v>2.8</v>
+      </c>
+      <c r="V278">
+        <v>2.7</v>
+      </c>
+      <c r="W278">
+        <v>1.4</v>
+      </c>
+      <c r="X278">
+        <v>6.75</v>
+      </c>
+      <c r="Y278">
+        <v>1.09</v>
+      </c>
+      <c r="Z278">
+        <v>1.83</v>
+      </c>
+      <c r="AA278">
+        <v>3.66</v>
+      </c>
+      <c r="AB278">
+        <v>4.6</v>
+      </c>
+      <c r="AC278">
+        <v>1.06</v>
+      </c>
+      <c r="AD278">
+        <v>8.5</v>
+      </c>
+      <c r="AE278">
+        <v>1.29</v>
+      </c>
+      <c r="AF278">
+        <v>3.25</v>
+      </c>
+      <c r="AG278">
+        <v>1.95</v>
+      </c>
+      <c r="AH278">
+        <v>1.86</v>
+      </c>
+      <c r="AI278">
+        <v>1.8</v>
+      </c>
+      <c r="AJ278">
+        <v>1.88</v>
+      </c>
+      <c r="AK278">
+        <v>1.21</v>
+      </c>
+      <c r="AL278">
+        <v>1.28</v>
+      </c>
+      <c r="AM278">
+        <v>1.95</v>
+      </c>
+      <c r="AN278">
+        <v>1.46</v>
+      </c>
+      <c r="AO278">
+        <v>1.08</v>
+      </c>
+      <c r="AP278">
+        <v>1.57</v>
+      </c>
+      <c r="AQ278">
+        <v>1</v>
+      </c>
+      <c r="AR278">
+        <v>1.76</v>
+      </c>
+      <c r="AS278">
+        <v>1.23</v>
+      </c>
+      <c r="AT278">
+        <v>2.99</v>
+      </c>
+      <c r="AU278">
+        <v>10</v>
+      </c>
+      <c r="AV278">
+        <v>2</v>
+      </c>
+      <c r="AW278">
+        <v>17</v>
+      </c>
+      <c r="AX278">
+        <v>7</v>
+      </c>
+      <c r="AY278">
+        <v>32</v>
+      </c>
+      <c r="AZ278">
+        <v>10</v>
+      </c>
+      <c r="BA278">
+        <v>8</v>
+      </c>
+      <c r="BB278">
+        <v>6</v>
+      </c>
+      <c r="BC278">
+        <v>14</v>
+      </c>
+      <c r="BD278">
+        <v>1.6</v>
+      </c>
+      <c r="BE278">
+        <v>6.4</v>
+      </c>
+      <c r="BF278">
+        <v>2.63</v>
+      </c>
+      <c r="BG278">
+        <v>1.36</v>
+      </c>
+      <c r="BH278">
+        <v>2.8</v>
+      </c>
+      <c r="BI278">
+        <v>1.63</v>
+      </c>
+      <c r="BJ278">
+        <v>2.12</v>
+      </c>
+      <c r="BK278">
+        <v>2</v>
+      </c>
+      <c r="BL278">
+        <v>1.71</v>
+      </c>
+      <c r="BM278">
+        <v>2.55</v>
+      </c>
+      <c r="BN278">
+        <v>1.44</v>
+      </c>
+      <c r="BO278">
+        <v>3.35</v>
+      </c>
+      <c r="BP278">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7509859</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F279">
+        <v>28</v>
+      </c>
+      <c r="G279" t="s">
+        <v>78</v>
+      </c>
+      <c r="H279" t="s">
+        <v>77</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>2</v>
+      </c>
+      <c r="O279" t="s">
+        <v>235</v>
+      </c>
+      <c r="P279" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q279">
+        <v>2.8</v>
+      </c>
+      <c r="R279">
+        <v>1.95</v>
+      </c>
+      <c r="S279">
+        <v>3.9</v>
+      </c>
+      <c r="T279">
+        <v>1.47</v>
+      </c>
+      <c r="U279">
+        <v>2.45</v>
+      </c>
+      <c r="V279">
+        <v>3.2</v>
+      </c>
+      <c r="W279">
+        <v>1.3</v>
+      </c>
+      <c r="X279">
+        <v>9</v>
+      </c>
+      <c r="Y279">
+        <v>1.06</v>
+      </c>
+      <c r="Z279">
+        <v>2.22</v>
+      </c>
+      <c r="AA279">
+        <v>3.28</v>
+      </c>
+      <c r="AB279">
+        <v>3.58</v>
+      </c>
+      <c r="AC279">
+        <v>1.08</v>
+      </c>
+      <c r="AD279">
+        <v>7.5</v>
+      </c>
+      <c r="AE279">
+        <v>1.41</v>
+      </c>
+      <c r="AF279">
+        <v>2.65</v>
+      </c>
+      <c r="AG279">
+        <v>2.2</v>
+      </c>
+      <c r="AH279">
+        <v>1.55</v>
+      </c>
+      <c r="AI279">
+        <v>1.98</v>
+      </c>
+      <c r="AJ279">
+        <v>1.72</v>
+      </c>
+      <c r="AK279">
+        <v>1.3</v>
+      </c>
+      <c r="AL279">
+        <v>1.33</v>
+      </c>
+      <c r="AM279">
+        <v>1.65</v>
+      </c>
+      <c r="AN279">
+        <v>1.71</v>
+      </c>
+      <c r="AO279">
+        <v>1</v>
+      </c>
+      <c r="AP279">
+        <v>1.67</v>
+      </c>
+      <c r="AQ279">
+        <v>1</v>
+      </c>
+      <c r="AR279">
+        <v>1.32</v>
+      </c>
+      <c r="AS279">
+        <v>1.32</v>
+      </c>
+      <c r="AT279">
+        <v>2.64</v>
+      </c>
+      <c r="AU279">
+        <v>4</v>
+      </c>
+      <c r="AV279">
+        <v>5</v>
+      </c>
+      <c r="AW279">
+        <v>19</v>
+      </c>
+      <c r="AX279">
+        <v>9</v>
+      </c>
+      <c r="AY279">
+        <v>27</v>
+      </c>
+      <c r="AZ279">
+        <v>17</v>
+      </c>
+      <c r="BA279">
+        <v>9</v>
+      </c>
+      <c r="BB279">
+        <v>3</v>
+      </c>
+      <c r="BC279">
+        <v>12</v>
+      </c>
+      <c r="BD279">
+        <v>1.74</v>
+      </c>
+      <c r="BE279">
+        <v>6.4</v>
+      </c>
+      <c r="BF279">
+        <v>2.33</v>
+      </c>
+      <c r="BG279">
+        <v>1.52</v>
+      </c>
+      <c r="BH279">
+        <v>2.33</v>
+      </c>
+      <c r="BI279">
+        <v>1.89</v>
+      </c>
+      <c r="BJ279">
+        <v>1.81</v>
+      </c>
+      <c r="BK279">
+        <v>2.4</v>
+      </c>
+      <c r="BL279">
+        <v>1.49</v>
+      </c>
+      <c r="BM279">
+        <v>3.15</v>
+      </c>
+      <c r="BN279">
+        <v>1.3</v>
+      </c>
+      <c r="BO279">
+        <v>4.3</v>
+      </c>
+      <c r="BP279">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7509863</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45718.45833333334</v>
+      </c>
+      <c r="F280">
+        <v>28</v>
+      </c>
+      <c r="G280" t="s">
+        <v>80</v>
+      </c>
+      <c r="H280" t="s">
+        <v>79</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280">
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <v>1</v>
+      </c>
+      <c r="M280">
+        <v>1</v>
+      </c>
+      <c r="N280">
+        <v>2</v>
+      </c>
+      <c r="O280" t="s">
+        <v>117</v>
+      </c>
+      <c r="P280" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q280">
+        <v>2.5</v>
+      </c>
+      <c r="R280">
+        <v>1.98</v>
+      </c>
+      <c r="S280">
+        <v>4.6</v>
+      </c>
+      <c r="T280">
+        <v>1.47</v>
+      </c>
+      <c r="U280">
+        <v>2.45</v>
+      </c>
+      <c r="V280">
+        <v>3.2</v>
+      </c>
+      <c r="W280">
+        <v>1.31</v>
+      </c>
+      <c r="X280">
+        <v>8.75</v>
+      </c>
+      <c r="Y280">
+        <v>1.06</v>
+      </c>
+      <c r="Z280">
+        <v>2.07</v>
+      </c>
+      <c r="AA280">
+        <v>3.19</v>
+      </c>
+      <c r="AB280">
+        <v>4.2</v>
+      </c>
+      <c r="AC280">
+        <v>1.08</v>
+      </c>
+      <c r="AD280">
+        <v>7.5</v>
+      </c>
+      <c r="AE280">
+        <v>1.41</v>
+      </c>
+      <c r="AF280">
+        <v>2.65</v>
+      </c>
+      <c r="AG280">
+        <v>2.25</v>
+      </c>
+      <c r="AH280">
+        <v>1.53</v>
+      </c>
+      <c r="AI280">
+        <v>2.05</v>
+      </c>
+      <c r="AJ280">
+        <v>1.66</v>
+      </c>
+      <c r="AK280">
+        <v>1.21</v>
+      </c>
+      <c r="AL280">
+        <v>1.32</v>
+      </c>
+      <c r="AM280">
+        <v>1.87</v>
+      </c>
+      <c r="AN280">
+        <v>1.62</v>
+      </c>
+      <c r="AO280">
+        <v>0.77</v>
+      </c>
+      <c r="AP280">
+        <v>1.57</v>
+      </c>
+      <c r="AQ280">
+        <v>0.79</v>
+      </c>
+      <c r="AR280">
+        <v>1.4</v>
+      </c>
+      <c r="AS280">
+        <v>1.4</v>
+      </c>
+      <c r="AT280">
+        <v>2.8</v>
+      </c>
+      <c r="AU280">
+        <v>4</v>
+      </c>
+      <c r="AV280">
+        <v>4</v>
+      </c>
+      <c r="AW280">
+        <v>13</v>
+      </c>
+      <c r="AX280">
+        <v>10</v>
+      </c>
+      <c r="AY280">
+        <v>20</v>
+      </c>
+      <c r="AZ280">
+        <v>17</v>
+      </c>
+      <c r="BA280">
+        <v>4</v>
+      </c>
+      <c r="BB280">
+        <v>1</v>
+      </c>
+      <c r="BC280">
+        <v>5</v>
+      </c>
+      <c r="BD280">
+        <v>1.5</v>
+      </c>
+      <c r="BE280">
+        <v>6.75</v>
+      </c>
+      <c r="BF280">
+        <v>2.8</v>
+      </c>
+      <c r="BG280">
+        <v>1.41</v>
+      </c>
+      <c r="BH280">
+        <v>2.65</v>
+      </c>
+      <c r="BI280">
+        <v>1.71</v>
+      </c>
+      <c r="BJ280">
+        <v>2</v>
+      </c>
+      <c r="BK280">
+        <v>2.08</v>
+      </c>
+      <c r="BL280">
+        <v>1.65</v>
+      </c>
+      <c r="BM280">
+        <v>2.65</v>
+      </c>
+      <c r="BN280">
+        <v>1.41</v>
+      </c>
+      <c r="BO280">
+        <v>3.55</v>
+      </c>
+      <c r="BP280">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7509857</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45718.55208333334</v>
+      </c>
+      <c r="F281">
+        <v>28</v>
+      </c>
+      <c r="G281" t="s">
+        <v>71</v>
+      </c>
+      <c r="H281" t="s">
+        <v>81</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>1</v>
+      </c>
+      <c r="M281">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>2</v>
+      </c>
+      <c r="O281" t="s">
+        <v>258</v>
+      </c>
+      <c r="P281" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q281">
+        <v>3</v>
+      </c>
+      <c r="R281">
+        <v>1.93</v>
+      </c>
+      <c r="S281">
+        <v>3.7</v>
+      </c>
+      <c r="T281">
+        <v>1.49</v>
+      </c>
+      <c r="U281">
+        <v>2.4</v>
+      </c>
+      <c r="V281">
+        <v>3.3</v>
+      </c>
+      <c r="W281">
+        <v>1.29</v>
+      </c>
+      <c r="X281">
+        <v>9.25</v>
+      </c>
+      <c r="Y281">
+        <v>1.05</v>
+      </c>
+      <c r="Z281">
+        <v>2.44</v>
+      </c>
+      <c r="AA281">
+        <v>3.11</v>
+      </c>
+      <c r="AB281">
+        <v>3.3</v>
+      </c>
+      <c r="AC281">
+        <v>1.1</v>
+      </c>
+      <c r="AD281">
+        <v>6.5</v>
+      </c>
+      <c r="AE281">
+        <v>1.45</v>
+      </c>
+      <c r="AF281">
+        <v>2.49</v>
+      </c>
+      <c r="AG281">
+        <v>2.25</v>
+      </c>
+      <c r="AH281">
+        <v>1.53</v>
+      </c>
+      <c r="AI281">
+        <v>2</v>
+      </c>
+      <c r="AJ281">
+        <v>1.71</v>
+      </c>
+      <c r="AK281">
+        <v>1.35</v>
+      </c>
+      <c r="AL281">
+        <v>1.34</v>
+      </c>
+      <c r="AM281">
+        <v>1.57</v>
+      </c>
+      <c r="AN281">
+        <v>1.57</v>
+      </c>
+      <c r="AO281">
+        <v>0.92</v>
+      </c>
+      <c r="AP281">
+        <v>1.53</v>
+      </c>
+      <c r="AQ281">
+        <v>0.93</v>
+      </c>
+      <c r="AR281">
+        <v>1.38</v>
+      </c>
+      <c r="AS281">
+        <v>1.23</v>
+      </c>
+      <c r="AT281">
+        <v>2.61</v>
+      </c>
+      <c r="AU281">
+        <v>3</v>
+      </c>
+      <c r="AV281">
+        <v>4</v>
+      </c>
+      <c r="AW281">
+        <v>4</v>
+      </c>
+      <c r="AX281">
+        <v>17</v>
+      </c>
+      <c r="AY281">
+        <v>7</v>
+      </c>
+      <c r="AZ281">
+        <v>29</v>
+      </c>
+      <c r="BA281">
+        <v>4</v>
+      </c>
+      <c r="BB281">
+        <v>6</v>
+      </c>
+      <c r="BC281">
+        <v>10</v>
+      </c>
+      <c r="BD281">
+        <v>1.72</v>
+      </c>
+      <c r="BE281">
+        <v>6.25</v>
+      </c>
+      <c r="BF281">
+        <v>2.4</v>
+      </c>
+      <c r="BG281">
+        <v>1.49</v>
+      </c>
+      <c r="BH281">
+        <v>2.4</v>
+      </c>
+      <c r="BI281">
+        <v>1.82</v>
+      </c>
+      <c r="BJ281">
+        <v>1.86</v>
+      </c>
+      <c r="BK281">
+        <v>2.32</v>
+      </c>
+      <c r="BL281">
+        <v>1.53</v>
+      </c>
+      <c r="BM281">
+        <v>3</v>
+      </c>
+      <c r="BN281">
+        <v>1.32</v>
+      </c>
+      <c r="BO281">
+        <v>4.1</v>
+      </c>
+      <c r="BP281">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="369">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,9 @@
     <t>['48']</t>
   </si>
   <si>
+    <t>['31', '65', '70', '76']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1115,6 +1118,9 @@
   </si>
   <si>
     <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP281"/>
+  <dimension ref="A1:BP288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1810,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1938,7 +1944,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2225,7 +2231,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2350,7 +2356,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2634,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ6">
         <v>1.47</v>
@@ -2762,7 +2768,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3174,7 +3180,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3380,7 +3386,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3664,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ11">
         <v>1.57</v>
@@ -3792,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3998,7 +4004,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4204,7 +4210,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4282,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4488,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ15">
         <v>1.47</v>
@@ -4694,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ16">
         <v>0.5</v>
@@ -4822,7 +4828,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4903,7 +4909,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ17">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5109,7 +5115,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR18">
         <v>1.49</v>
@@ -5440,7 +5446,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5518,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ20">
         <v>0.79</v>
@@ -5852,7 +5858,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6136,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
         <v>1</v>
@@ -6264,7 +6270,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6342,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ24">
         <v>0.93</v>
@@ -6882,7 +6888,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -6960,10 +6966,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR27">
         <v>1.54</v>
@@ -7169,7 +7175,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ28">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7375,7 +7381,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ29">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR29">
         <v>1.89</v>
@@ -7578,7 +7584,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30">
         <v>1.53</v>
@@ -7990,7 +7996,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ32">
         <v>1.15</v>
@@ -8118,7 +8124,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8405,7 +8411,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8530,7 +8536,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8736,7 +8742,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9226,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ38">
         <v>0.5</v>
@@ -9560,7 +9566,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9766,7 +9772,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9972,7 +9978,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10053,7 +10059,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10259,7 +10265,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR43">
         <v>1.15</v>
@@ -10668,10 +10674,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ45">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.98</v>
@@ -10796,7 +10802,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10877,7 +10883,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR46">
         <v>0.96</v>
@@ -11080,7 +11086,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ47">
         <v>1.53</v>
@@ -11208,7 +11214,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11414,7 +11420,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11492,7 +11498,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49">
         <v>2</v>
@@ -11698,7 +11704,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
@@ -11826,7 +11832,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11904,7 +11910,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ51">
         <v>1.57</v>
@@ -12032,7 +12038,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12316,7 +12322,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -13140,7 +13146,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13474,7 +13480,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13758,7 +13764,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ60">
         <v>1.47</v>
@@ -13886,7 +13892,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14092,7 +14098,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14173,7 +14179,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ62">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.33</v>
@@ -14788,10 +14794,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14916,7 +14922,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15328,7 +15334,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15612,10 +15618,10 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR69">
         <v>1.8</v>
@@ -15740,7 +15746,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15821,7 +15827,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR70">
         <v>1.7</v>
@@ -15946,7 +15952,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16024,7 +16030,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ71">
         <v>1.57</v>
@@ -16152,7 +16158,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16230,7 +16236,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
         <v>1.07</v>
@@ -16358,7 +16364,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16564,7 +16570,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16851,7 +16857,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ75">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16976,7 +16982,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17182,7 +17188,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17260,7 +17266,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17388,7 +17394,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17466,7 +17472,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17594,7 +17600,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17672,7 +17678,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ79">
         <v>1.15</v>
@@ -17800,7 +17806,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17881,7 +17887,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18293,7 +18299,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ82">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR82">
         <v>1.28</v>
@@ -18418,7 +18424,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18624,7 +18630,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18702,7 +18708,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ84">
         <v>1.53</v>
@@ -19036,7 +19042,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19117,7 +19123,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR86">
         <v>1.48</v>
@@ -19242,7 +19248,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19320,7 +19326,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ87">
         <v>2</v>
@@ -19448,7 +19454,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19732,7 +19738,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ89">
         <v>0.67</v>
@@ -19941,7 +19947,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ90">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -20066,7 +20072,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20762,7 +20768,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ94">
         <v>1.07</v>
@@ -20968,7 +20974,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ95">
         <v>0.5</v>
@@ -21177,7 +21183,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21383,7 +21389,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ97">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -21586,7 +21592,7 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
         <v>1.47</v>
@@ -22204,7 +22210,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ101">
         <v>0.67</v>
@@ -22616,7 +22622,7 @@
         <v>1.4</v>
       </c>
       <c r="AP103">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ103">
         <v>1.53</v>
@@ -22744,7 +22750,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22950,7 +22956,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23440,7 +23446,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -23649,7 +23655,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ108">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.52</v>
@@ -24058,10 +24064,10 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ110">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR110">
         <v>1.32</v>
@@ -24267,7 +24273,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR111">
         <v>1.35</v>
@@ -24473,7 +24479,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ112">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24598,7 +24604,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24679,7 +24685,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR113">
         <v>1.36</v>
@@ -24882,7 +24888,7 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114">
         <v>1.07</v>
@@ -25091,7 +25097,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.26</v>
@@ -25422,7 +25428,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25500,7 +25506,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ117">
         <v>0.5</v>
@@ -25628,7 +25634,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25706,7 +25712,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ118">
         <v>1.57</v>
@@ -26118,7 +26124,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -26452,7 +26458,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26533,7 +26539,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ122">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -27276,7 +27282,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27354,7 +27360,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ126">
         <v>0.79</v>
@@ -27560,7 +27566,7 @@
         <v>1.67</v>
       </c>
       <c r="AP127">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ127">
         <v>1.57</v>
@@ -27688,7 +27694,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27894,7 +27900,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28100,7 +28106,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28181,7 +28187,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ130">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR130">
         <v>1.24</v>
@@ -28306,7 +28312,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28384,7 +28390,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ131">
         <v>1.15</v>
@@ -28512,7 +28518,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28590,10 +28596,10 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ132">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -29208,7 +29214,7 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>1.57</v>
@@ -29336,7 +29342,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29623,7 +29629,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR137">
         <v>1.49</v>
@@ -29748,7 +29754,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30238,10 +30244,10 @@
         <v>0.83</v>
       </c>
       <c r="AP140">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ140">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30366,7 +30372,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30572,7 +30578,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30778,7 +30784,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30856,10 +30862,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ143">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR143">
         <v>1.37</v>
@@ -30984,7 +30990,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31268,7 +31274,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ145">
         <v>1.15</v>
@@ -31396,7 +31402,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31680,10 +31686,10 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ147">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -32014,7 +32020,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32220,7 +32226,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32504,7 +32510,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ151">
         <v>0.5</v>
@@ -32632,7 +32638,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33122,10 +33128,10 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR154">
         <v>1.17</v>
@@ -33250,7 +33256,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33328,7 +33334,7 @@
         <v>1.57</v>
       </c>
       <c r="AP155">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ155">
         <v>1.57</v>
@@ -33662,7 +33668,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33740,10 +33746,10 @@
         <v>0.71</v>
       </c>
       <c r="AP157">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ157">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.58</v>
@@ -34074,7 +34080,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34152,10 +34158,10 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159">
         <v>1.43</v>
@@ -34486,7 +34492,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34898,7 +34904,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35185,7 +35191,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ164">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35310,7 +35316,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35800,7 +35806,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ167">
         <v>1.53</v>
@@ -35928,7 +35934,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36009,7 +36015,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ168">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -36212,7 +36218,7 @@
         <v>0.5</v>
       </c>
       <c r="AP169">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ169">
         <v>0.5</v>
@@ -36546,7 +36552,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36624,7 +36630,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ171">
         <v>1.07</v>
@@ -36830,7 +36836,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37039,7 +37045,7 @@
         <v>2.64</v>
       </c>
       <c r="AQ173">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR173">
         <v>1.69</v>
@@ -37448,7 +37454,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ175">
         <v>0.79</v>
@@ -37654,10 +37660,10 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ176">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.34</v>
@@ -37988,7 +37994,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38069,7 +38075,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ178">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR178">
         <v>1.29</v>
@@ -38194,7 +38200,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38684,7 +38690,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ181">
         <v>0.93</v>
@@ -39224,7 +39230,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39430,7 +39436,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39714,10 +39720,10 @@
         <v>1.13</v>
       </c>
       <c r="AP186">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ186">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR186">
         <v>1.56</v>
@@ -40048,7 +40054,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40126,10 +40132,10 @@
         <v>0.89</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ188">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40666,7 +40672,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40744,7 +40750,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ191">
         <v>0.5</v>
@@ -40872,7 +40878,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40950,7 +40956,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ192">
         <v>1</v>
@@ -41362,7 +41368,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41902,7 +41908,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -41980,10 +41986,10 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ197">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR197">
         <v>1.37</v>
@@ -42189,7 +42195,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ198">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR198">
         <v>1.28</v>
@@ -42520,7 +42526,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42601,7 +42607,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ200">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42804,7 +42810,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ201">
         <v>1.57</v>
@@ -42932,7 +42938,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43010,7 +43016,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ202">
         <v>2</v>
@@ -43344,7 +43350,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43425,7 +43431,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR204">
         <v>1.39</v>
@@ -43631,7 +43637,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ205">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR205">
         <v>1.88</v>
@@ -43962,7 +43968,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44040,7 +44046,7 @@
         <v>0.5</v>
       </c>
       <c r="AP207">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ207">
         <v>0.67</v>
@@ -44168,7 +44174,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44658,7 +44664,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ210">
         <v>0.93</v>
@@ -44992,7 +44998,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45070,7 +45076,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45198,7 +45204,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45482,7 +45488,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ214">
         <v>0.79</v>
@@ -45691,7 +45697,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ215">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45816,7 +45822,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45894,10 +45900,10 @@
         <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ216">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR216">
         <v>1.68</v>
@@ -46022,7 +46028,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46640,7 +46646,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46846,7 +46852,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46924,7 +46930,7 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ221">
         <v>1.53</v>
@@ -47052,7 +47058,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47464,7 +47470,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47876,7 +47882,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -47954,7 +47960,7 @@
         <v>1.18</v>
       </c>
       <c r="AP226">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ226">
         <v>1.47</v>
@@ -48082,7 +48088,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48160,7 +48166,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ227">
         <v>0.93</v>
@@ -48288,7 +48294,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48366,10 +48372,10 @@
         <v>1.1</v>
       </c>
       <c r="AP228">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ228">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48781,7 +48787,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ230">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR230">
         <v>1.34</v>
@@ -48906,7 +48912,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -48984,10 +48990,10 @@
         <v>0.82</v>
       </c>
       <c r="AP231">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ231">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49112,7 +49118,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49396,7 +49402,7 @@
         <v>0.91</v>
       </c>
       <c r="AP233">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ233">
         <v>0.79</v>
@@ -49730,7 +49736,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49936,7 +49942,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50426,7 +50432,7 @@
         <v>1.82</v>
       </c>
       <c r="AP238">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ238">
         <v>1.57</v>
@@ -50554,7 +50560,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50632,7 +50638,7 @@
         <v>1</v>
       </c>
       <c r="AP239">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ239">
         <v>1</v>
@@ -50841,7 +50847,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ240">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR240">
         <v>1.42</v>
@@ -50966,7 +50972,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51047,7 +51053,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ241">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR241">
         <v>1.41</v>
@@ -51250,7 +51256,7 @@
         <v>0.55</v>
       </c>
       <c r="AP242">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ242">
         <v>0.5</v>
@@ -51584,7 +51590,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51662,7 +51668,7 @@
         <v>2</v>
       </c>
       <c r="AP244">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ244">
         <v>2</v>
@@ -51871,7 +51877,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ245">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR245">
         <v>1.4</v>
@@ -52074,7 +52080,7 @@
         <v>0.5</v>
       </c>
       <c r="AP246">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ246">
         <v>0.5</v>
@@ -52280,10 +52286,10 @@
         <v>0.83</v>
       </c>
       <c r="AP247">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ247">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR247">
         <v>1.4</v>
@@ -52486,7 +52492,7 @@
         <v>1.08</v>
       </c>
       <c r="AP248">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ248">
         <v>1</v>
@@ -52820,7 +52826,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -52901,7 +52907,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ250">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR250">
         <v>1.79</v>
@@ -53438,7 +53444,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -54134,7 +54140,7 @@
         <v>0.58</v>
       </c>
       <c r="AP256">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ256">
         <v>0.5</v>
@@ -54549,7 +54555,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ258">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR258">
         <v>1.41</v>
@@ -54880,7 +54886,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55370,7 +55376,7 @@
         <v>2.08</v>
       </c>
       <c r="AP262">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ262">
         <v>2</v>
@@ -55498,7 +55504,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55579,7 +55585,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ263">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR263">
         <v>1.4</v>
@@ -55782,7 +55788,7 @@
         <v>1</v>
       </c>
       <c r="AP264">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ264">
         <v>1.15</v>
@@ -56116,7 +56122,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56322,7 +56328,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56400,7 +56406,7 @@
         <v>0.85</v>
       </c>
       <c r="AP267">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ267">
         <v>1</v>
@@ -56528,7 +56534,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -56606,10 +56612,10 @@
         <v>1</v>
       </c>
       <c r="AP268">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AQ268">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR268">
         <v>1.56</v>
@@ -56815,7 +56821,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ269">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR269">
         <v>1.9</v>
@@ -57018,7 +57024,7 @@
         <v>1</v>
       </c>
       <c r="AP270">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ270">
         <v>1</v>
@@ -57146,7 +57152,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57224,10 +57230,10 @@
         <v>0.83</v>
       </c>
       <c r="AP271">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ271">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR271">
         <v>1.71</v>
@@ -57558,7 +57564,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -57636,7 +57642,7 @@
         <v>1.62</v>
       </c>
       <c r="AP273">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ273">
         <v>1.57</v>
@@ -57970,7 +57976,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58794,7 +58800,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -58875,7 +58881,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ279">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR279">
         <v>1.32</v>
@@ -59206,7 +59212,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -59362,6 +59368,1448 @@
         <v>4.1</v>
       </c>
       <c r="BP281">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7509870</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45723.6875</v>
+      </c>
+      <c r="F282">
+        <v>29</v>
+      </c>
+      <c r="G282" t="s">
+        <v>79</v>
+      </c>
+      <c r="H282" t="s">
+        <v>77</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>1</v>
+      </c>
+      <c r="L282">
+        <v>1</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
+      </c>
+      <c r="N282">
+        <v>1</v>
+      </c>
+      <c r="O282" t="s">
+        <v>252</v>
+      </c>
+      <c r="P282" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q282">
+        <v>3.25</v>
+      </c>
+      <c r="R282">
+        <v>1.9</v>
+      </c>
+      <c r="S282">
+        <v>3.5</v>
+      </c>
+      <c r="T282">
+        <v>1.52</v>
+      </c>
+      <c r="U282">
+        <v>2.35</v>
+      </c>
+      <c r="V282">
+        <v>3.4</v>
+      </c>
+      <c r="W282">
+        <v>1.28</v>
+      </c>
+      <c r="X282">
+        <v>9.5</v>
+      </c>
+      <c r="Y282">
+        <v>1.04</v>
+      </c>
+      <c r="Z282">
+        <v>2.54</v>
+      </c>
+      <c r="AA282">
+        <v>3.26</v>
+      </c>
+      <c r="AB282">
+        <v>2.99</v>
+      </c>
+      <c r="AC282">
+        <v>1.1</v>
+      </c>
+      <c r="AD282">
+        <v>6.5</v>
+      </c>
+      <c r="AE282">
+        <v>1.5</v>
+      </c>
+      <c r="AF282">
+        <v>2.4</v>
+      </c>
+      <c r="AG282">
+        <v>2.2</v>
+      </c>
+      <c r="AH282">
+        <v>1.55</v>
+      </c>
+      <c r="AI282">
+        <v>2.05</v>
+      </c>
+      <c r="AJ282">
+        <v>1.68</v>
+      </c>
+      <c r="AK282">
+        <v>1.4</v>
+      </c>
+      <c r="AL282">
+        <v>1.37</v>
+      </c>
+      <c r="AM282">
+        <v>1.47</v>
+      </c>
+      <c r="AN282">
+        <v>1.07</v>
+      </c>
+      <c r="AO282">
+        <v>1</v>
+      </c>
+      <c r="AP282">
+        <v>1.2</v>
+      </c>
+      <c r="AQ282">
+        <v>0.93</v>
+      </c>
+      <c r="AR282">
+        <v>1.6</v>
+      </c>
+      <c r="AS282">
+        <v>1.33</v>
+      </c>
+      <c r="AT282">
+        <v>2.93</v>
+      </c>
+      <c r="AU282">
+        <v>6</v>
+      </c>
+      <c r="AV282">
+        <v>2</v>
+      </c>
+      <c r="AW282">
+        <v>2</v>
+      </c>
+      <c r="AX282">
+        <v>8</v>
+      </c>
+      <c r="AY282">
+        <v>8</v>
+      </c>
+      <c r="AZ282">
+        <v>15</v>
+      </c>
+      <c r="BA282">
+        <v>5</v>
+      </c>
+      <c r="BB282">
+        <v>6</v>
+      </c>
+      <c r="BC282">
+        <v>11</v>
+      </c>
+      <c r="BD282">
+        <v>1.9</v>
+      </c>
+      <c r="BE282">
+        <v>6.4</v>
+      </c>
+      <c r="BF282">
+        <v>2.1</v>
+      </c>
+      <c r="BG282">
+        <v>1.42</v>
+      </c>
+      <c r="BH282">
+        <v>2.65</v>
+      </c>
+      <c r="BI282">
+        <v>1.7</v>
+      </c>
+      <c r="BJ282">
+        <v>2.02</v>
+      </c>
+      <c r="BK282">
+        <v>2.12</v>
+      </c>
+      <c r="BL282">
+        <v>1.64</v>
+      </c>
+      <c r="BM282">
+        <v>2.7</v>
+      </c>
+      <c r="BN282">
+        <v>1.38</v>
+      </c>
+      <c r="BO282">
+        <v>3.65</v>
+      </c>
+      <c r="BP282">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7509871</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F283">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>82</v>
+      </c>
+      <c r="H283" t="s">
+        <v>78</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>4</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>4</v>
+      </c>
+      <c r="O283" t="s">
+        <v>259</v>
+      </c>
+      <c r="P283" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q283">
+        <v>2.3</v>
+      </c>
+      <c r="R283">
+        <v>2.1</v>
+      </c>
+      <c r="S283">
+        <v>4.75</v>
+      </c>
+      <c r="T283">
+        <v>1.4</v>
+      </c>
+      <c r="U283">
+        <v>2.7</v>
+      </c>
+      <c r="V283">
+        <v>2.8</v>
+      </c>
+      <c r="W283">
+        <v>1.37</v>
+      </c>
+      <c r="X283">
+        <v>7.25</v>
+      </c>
+      <c r="Y283">
+        <v>1.08</v>
+      </c>
+      <c r="Z283">
+        <v>1.58</v>
+      </c>
+      <c r="AA283">
+        <v>4.33</v>
+      </c>
+      <c r="AB283">
+        <v>5.9</v>
+      </c>
+      <c r="AC283">
+        <v>1.06</v>
+      </c>
+      <c r="AD283">
+        <v>8.5</v>
+      </c>
+      <c r="AE283">
+        <v>1.33</v>
+      </c>
+      <c r="AF283">
+        <v>3.25</v>
+      </c>
+      <c r="AG283">
+        <v>1.97</v>
+      </c>
+      <c r="AH283">
+        <v>1.84</v>
+      </c>
+      <c r="AI283">
+        <v>1.9</v>
+      </c>
+      <c r="AJ283">
+        <v>1.78</v>
+      </c>
+      <c r="AK283">
+        <v>1.19</v>
+      </c>
+      <c r="AL283">
+        <v>1.27</v>
+      </c>
+      <c r="AM283">
+        <v>2.05</v>
+      </c>
+      <c r="AN283">
+        <v>1.43</v>
+      </c>
+      <c r="AO283">
+        <v>1.38</v>
+      </c>
+      <c r="AP283">
+        <v>1.53</v>
+      </c>
+      <c r="AQ283">
+        <v>1.29</v>
+      </c>
+      <c r="AR283">
+        <v>1.8</v>
+      </c>
+      <c r="AS283">
+        <v>1.22</v>
+      </c>
+      <c r="AT283">
+        <v>3.02</v>
+      </c>
+      <c r="AU283">
+        <v>8</v>
+      </c>
+      <c r="AV283">
+        <v>2</v>
+      </c>
+      <c r="AW283">
+        <v>16</v>
+      </c>
+      <c r="AX283">
+        <v>7</v>
+      </c>
+      <c r="AY283">
+        <v>29</v>
+      </c>
+      <c r="AZ283">
+        <v>10</v>
+      </c>
+      <c r="BA283">
+        <v>7</v>
+      </c>
+      <c r="BB283">
+        <v>1</v>
+      </c>
+      <c r="BC283">
+        <v>8</v>
+      </c>
+      <c r="BD283">
+        <v>1.41</v>
+      </c>
+      <c r="BE283">
+        <v>6.75</v>
+      </c>
+      <c r="BF283">
+        <v>3.3</v>
+      </c>
+      <c r="BG283">
+        <v>1.36</v>
+      </c>
+      <c r="BH283">
+        <v>2.8</v>
+      </c>
+      <c r="BI283">
+        <v>1.61</v>
+      </c>
+      <c r="BJ283">
+        <v>2.15</v>
+      </c>
+      <c r="BK283">
+        <v>1.98</v>
+      </c>
+      <c r="BL283">
+        <v>1.72</v>
+      </c>
+      <c r="BM283">
+        <v>2.55</v>
+      </c>
+      <c r="BN283">
+        <v>1.45</v>
+      </c>
+      <c r="BO283">
+        <v>3.3</v>
+      </c>
+      <c r="BP283">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7509872</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F284">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>85</v>
+      </c>
+      <c r="H284" t="s">
+        <v>88</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>0</v>
+      </c>
+      <c r="L284">
+        <v>1</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>2</v>
+      </c>
+      <c r="O284" t="s">
+        <v>119</v>
+      </c>
+      <c r="P284" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q284">
+        <v>3.2</v>
+      </c>
+      <c r="R284">
+        <v>1.95</v>
+      </c>
+      <c r="S284">
+        <v>3.4</v>
+      </c>
+      <c r="T284">
+        <v>1.47</v>
+      </c>
+      <c r="U284">
+        <v>2.5</v>
+      </c>
+      <c r="V284">
+        <v>3.1</v>
+      </c>
+      <c r="W284">
+        <v>1.32</v>
+      </c>
+      <c r="X284">
+        <v>8.5</v>
+      </c>
+      <c r="Y284">
+        <v>1.06</v>
+      </c>
+      <c r="Z284">
+        <v>2.66</v>
+      </c>
+      <c r="AA284">
+        <v>3.21</v>
+      </c>
+      <c r="AB284">
+        <v>2.87</v>
+      </c>
+      <c r="AC284">
+        <v>1.08</v>
+      </c>
+      <c r="AD284">
+        <v>7.5</v>
+      </c>
+      <c r="AE284">
+        <v>1.42</v>
+      </c>
+      <c r="AF284">
+        <v>2.85</v>
+      </c>
+      <c r="AG284">
+        <v>2.1</v>
+      </c>
+      <c r="AH284">
+        <v>1.6</v>
+      </c>
+      <c r="AI284">
+        <v>1.88</v>
+      </c>
+      <c r="AJ284">
+        <v>1.8</v>
+      </c>
+      <c r="AK284">
+        <v>1.42</v>
+      </c>
+      <c r="AL284">
+        <v>1.34</v>
+      </c>
+      <c r="AM284">
+        <v>1.47</v>
+      </c>
+      <c r="AN284">
+        <v>1.46</v>
+      </c>
+      <c r="AO284">
+        <v>1.07</v>
+      </c>
+      <c r="AP284">
+        <v>1.43</v>
+      </c>
+      <c r="AQ284">
+        <v>1.07</v>
+      </c>
+      <c r="AR284">
+        <v>1.3</v>
+      </c>
+      <c r="AS284">
+        <v>1.11</v>
+      </c>
+      <c r="AT284">
+        <v>2.41</v>
+      </c>
+      <c r="AU284">
+        <v>5</v>
+      </c>
+      <c r="AV284">
+        <v>6</v>
+      </c>
+      <c r="AW284">
+        <v>2</v>
+      </c>
+      <c r="AX284">
+        <v>2</v>
+      </c>
+      <c r="AY284">
+        <v>9</v>
+      </c>
+      <c r="AZ284">
+        <v>9</v>
+      </c>
+      <c r="BA284">
+        <v>4</v>
+      </c>
+      <c r="BB284">
+        <v>4</v>
+      </c>
+      <c r="BC284">
+        <v>8</v>
+      </c>
+      <c r="BD284">
+        <v>1.95</v>
+      </c>
+      <c r="BE284">
+        <v>6.25</v>
+      </c>
+      <c r="BF284">
+        <v>2.05</v>
+      </c>
+      <c r="BG284">
+        <v>1.44</v>
+      </c>
+      <c r="BH284">
+        <v>2.55</v>
+      </c>
+      <c r="BI284">
+        <v>1.73</v>
+      </c>
+      <c r="BJ284">
+        <v>1.98</v>
+      </c>
+      <c r="BK284">
+        <v>2.17</v>
+      </c>
+      <c r="BL284">
+        <v>1.6</v>
+      </c>
+      <c r="BM284">
+        <v>2.8</v>
+      </c>
+      <c r="BN284">
+        <v>1.37</v>
+      </c>
+      <c r="BO284">
+        <v>3.7</v>
+      </c>
+      <c r="BP284">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7509873</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F285">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>74</v>
+      </c>
+      <c r="H285" t="s">
+        <v>80</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>0</v>
+      </c>
+      <c r="L285">
+        <v>1</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
+      </c>
+      <c r="N285">
+        <v>1</v>
+      </c>
+      <c r="O285" t="s">
+        <v>165</v>
+      </c>
+      <c r="P285" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q285">
+        <v>2.87</v>
+      </c>
+      <c r="R285">
+        <v>2</v>
+      </c>
+      <c r="S285">
+        <v>3.6</v>
+      </c>
+      <c r="T285">
+        <v>1.46</v>
+      </c>
+      <c r="U285">
+        <v>2.5</v>
+      </c>
+      <c r="V285">
+        <v>3.2</v>
+      </c>
+      <c r="W285">
+        <v>1.3</v>
+      </c>
+      <c r="X285">
+        <v>8.75</v>
+      </c>
+      <c r="Y285">
+        <v>1.06</v>
+      </c>
+      <c r="Z285">
+        <v>2.53</v>
+      </c>
+      <c r="AA285">
+        <v>3.37</v>
+      </c>
+      <c r="AB285">
+        <v>2.92</v>
+      </c>
+      <c r="AC285">
+        <v>1.08</v>
+      </c>
+      <c r="AD285">
+        <v>7.5</v>
+      </c>
+      <c r="AE285">
+        <v>1.42</v>
+      </c>
+      <c r="AF285">
+        <v>2.85</v>
+      </c>
+      <c r="AG285">
+        <v>2.05</v>
+      </c>
+      <c r="AH285">
+        <v>1.65</v>
+      </c>
+      <c r="AI285">
+        <v>1.98</v>
+      </c>
+      <c r="AJ285">
+        <v>1.73</v>
+      </c>
+      <c r="AK285">
+        <v>1.35</v>
+      </c>
+      <c r="AL285">
+        <v>1.32</v>
+      </c>
+      <c r="AM285">
+        <v>1.6</v>
+      </c>
+      <c r="AN285">
+        <v>1.36</v>
+      </c>
+      <c r="AO285">
+        <v>0.93</v>
+      </c>
+      <c r="AP285">
+        <v>1.47</v>
+      </c>
+      <c r="AQ285">
+        <v>0.87</v>
+      </c>
+      <c r="AR285">
+        <v>1.71</v>
+      </c>
+      <c r="AS285">
+        <v>1.26</v>
+      </c>
+      <c r="AT285">
+        <v>2.97</v>
+      </c>
+      <c r="AU285">
+        <v>6</v>
+      </c>
+      <c r="AV285">
+        <v>2</v>
+      </c>
+      <c r="AW285">
+        <v>10</v>
+      </c>
+      <c r="AX285">
+        <v>8</v>
+      </c>
+      <c r="AY285">
+        <v>18</v>
+      </c>
+      <c r="AZ285">
+        <v>13</v>
+      </c>
+      <c r="BA285">
+        <v>5</v>
+      </c>
+      <c r="BB285">
+        <v>1</v>
+      </c>
+      <c r="BC285">
+        <v>6</v>
+      </c>
+      <c r="BD285">
+        <v>1.74</v>
+      </c>
+      <c r="BE285">
+        <v>6.25</v>
+      </c>
+      <c r="BF285">
+        <v>2.32</v>
+      </c>
+      <c r="BG285">
+        <v>1.45</v>
+      </c>
+      <c r="BH285">
+        <v>2.55</v>
+      </c>
+      <c r="BI285">
+        <v>1.75</v>
+      </c>
+      <c r="BJ285">
+        <v>1.95</v>
+      </c>
+      <c r="BK285">
+        <v>2.2</v>
+      </c>
+      <c r="BL285">
+        <v>1.58</v>
+      </c>
+      <c r="BM285">
+        <v>2.85</v>
+      </c>
+      <c r="BN285">
+        <v>1.36</v>
+      </c>
+      <c r="BO285">
+        <v>3.8</v>
+      </c>
+      <c r="BP285">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7509868</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45724.45833333334</v>
+      </c>
+      <c r="F286">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>86</v>
+      </c>
+      <c r="H286" t="s">
+        <v>75</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>0</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+      <c r="M286">
+        <v>1</v>
+      </c>
+      <c r="N286">
+        <v>1</v>
+      </c>
+      <c r="O286" t="s">
+        <v>102</v>
+      </c>
+      <c r="P286" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q286">
+        <v>3.1</v>
+      </c>
+      <c r="R286">
+        <v>1.88</v>
+      </c>
+      <c r="S286">
+        <v>3.75</v>
+      </c>
+      <c r="T286">
+        <v>1.55</v>
+      </c>
+      <c r="U286">
+        <v>2.3</v>
+      </c>
+      <c r="V286">
+        <v>3.5</v>
+      </c>
+      <c r="W286">
+        <v>1.26</v>
+      </c>
+      <c r="X286">
+        <v>10</v>
+      </c>
+      <c r="Y286">
+        <v>1.04</v>
+      </c>
+      <c r="Z286">
+        <v>2.45</v>
+      </c>
+      <c r="AA286">
+        <v>3.06</v>
+      </c>
+      <c r="AB286">
+        <v>3.32</v>
+      </c>
+      <c r="AC286">
+        <v>1.1</v>
+      </c>
+      <c r="AD286">
+        <v>6.5</v>
+      </c>
+      <c r="AE286">
+        <v>1.5</v>
+      </c>
+      <c r="AF286">
+        <v>2.55</v>
+      </c>
+      <c r="AG286">
+        <v>2.37</v>
+      </c>
+      <c r="AH286">
+        <v>1.48</v>
+      </c>
+      <c r="AI286">
+        <v>2.1</v>
+      </c>
+      <c r="AJ286">
+        <v>1.65</v>
+      </c>
+      <c r="AK286">
+        <v>1.34</v>
+      </c>
+      <c r="AL286">
+        <v>1.36</v>
+      </c>
+      <c r="AM286">
+        <v>1.55</v>
+      </c>
+      <c r="AN286">
+        <v>1.79</v>
+      </c>
+      <c r="AO286">
+        <v>0.85</v>
+      </c>
+      <c r="AP286">
+        <v>1.67</v>
+      </c>
+      <c r="AQ286">
+        <v>1</v>
+      </c>
+      <c r="AR286">
+        <v>1.36</v>
+      </c>
+      <c r="AS286">
+        <v>1.22</v>
+      </c>
+      <c r="AT286">
+        <v>2.58</v>
+      </c>
+      <c r="AU286">
+        <v>4</v>
+      </c>
+      <c r="AV286">
+        <v>3</v>
+      </c>
+      <c r="AW286">
+        <v>14</v>
+      </c>
+      <c r="AX286">
+        <v>10</v>
+      </c>
+      <c r="AY286">
+        <v>22</v>
+      </c>
+      <c r="AZ286">
+        <v>17</v>
+      </c>
+      <c r="BA286">
+        <v>4</v>
+      </c>
+      <c r="BB286">
+        <v>5</v>
+      </c>
+      <c r="BC286">
+        <v>9</v>
+      </c>
+      <c r="BD286">
+        <v>1.84</v>
+      </c>
+      <c r="BE286">
+        <v>6.25</v>
+      </c>
+      <c r="BF286">
+        <v>2.18</v>
+      </c>
+      <c r="BG286">
+        <v>1.53</v>
+      </c>
+      <c r="BH286">
+        <v>2.32</v>
+      </c>
+      <c r="BI286">
+        <v>1.89</v>
+      </c>
+      <c r="BJ286">
+        <v>1.8</v>
+      </c>
+      <c r="BK286">
+        <v>2.4</v>
+      </c>
+      <c r="BL286">
+        <v>1.5</v>
+      </c>
+      <c r="BM286">
+        <v>3.15</v>
+      </c>
+      <c r="BN286">
+        <v>1.3</v>
+      </c>
+      <c r="BO286">
+        <v>4.2</v>
+      </c>
+      <c r="BP286">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7509874</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45724.55208333334</v>
+      </c>
+      <c r="F287">
+        <v>29</v>
+      </c>
+      <c r="G287" t="s">
+        <v>81</v>
+      </c>
+      <c r="H287" t="s">
+        <v>89</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287">
+        <v>2</v>
+      </c>
+      <c r="L287">
+        <v>1</v>
+      </c>
+      <c r="M287">
+        <v>1</v>
+      </c>
+      <c r="N287">
+        <v>2</v>
+      </c>
+      <c r="O287" t="s">
+        <v>180</v>
+      </c>
+      <c r="P287" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q287">
+        <v>3.2</v>
+      </c>
+      <c r="R287">
+        <v>2</v>
+      </c>
+      <c r="S287">
+        <v>3.2</v>
+      </c>
+      <c r="T287">
+        <v>1.43</v>
+      </c>
+      <c r="U287">
+        <v>2.6</v>
+      </c>
+      <c r="V287">
+        <v>2.95</v>
+      </c>
+      <c r="W287">
+        <v>1.35</v>
+      </c>
+      <c r="X287">
+        <v>7.75</v>
+      </c>
+      <c r="Y287">
+        <v>1.07</v>
+      </c>
+      <c r="Z287">
+        <v>2.42</v>
+      </c>
+      <c r="AA287">
+        <v>3.45</v>
+      </c>
+      <c r="AB287">
+        <v>3.02</v>
+      </c>
+      <c r="AC287">
+        <v>1.07</v>
+      </c>
+      <c r="AD287">
+        <v>8</v>
+      </c>
+      <c r="AE287">
+        <v>1.38</v>
+      </c>
+      <c r="AF287">
+        <v>3</v>
+      </c>
+      <c r="AG287">
+        <v>2.03</v>
+      </c>
+      <c r="AH287">
+        <v>1.79</v>
+      </c>
+      <c r="AI287">
+        <v>1.82</v>
+      </c>
+      <c r="AJ287">
+        <v>1.87</v>
+      </c>
+      <c r="AK287">
+        <v>1.46</v>
+      </c>
+      <c r="AL287">
+        <v>1.33</v>
+      </c>
+      <c r="AM287">
+        <v>1.46</v>
+      </c>
+      <c r="AN287">
+        <v>1.21</v>
+      </c>
+      <c r="AO287">
+        <v>1.14</v>
+      </c>
+      <c r="AP287">
+        <v>1.2</v>
+      </c>
+      <c r="AQ287">
+        <v>1.13</v>
+      </c>
+      <c r="AR287">
+        <v>1.39</v>
+      </c>
+      <c r="AS287">
+        <v>1.28</v>
+      </c>
+      <c r="AT287">
+        <v>2.67</v>
+      </c>
+      <c r="AU287">
+        <v>6</v>
+      </c>
+      <c r="AV287">
+        <v>4</v>
+      </c>
+      <c r="AW287">
+        <v>10</v>
+      </c>
+      <c r="AX287">
+        <v>20</v>
+      </c>
+      <c r="AY287">
+        <v>20</v>
+      </c>
+      <c r="AZ287">
+        <v>34</v>
+      </c>
+      <c r="BA287">
+        <v>6</v>
+      </c>
+      <c r="BB287">
+        <v>8</v>
+      </c>
+      <c r="BC287">
+        <v>14</v>
+      </c>
+      <c r="BD287">
+        <v>1.85</v>
+      </c>
+      <c r="BE287">
+        <v>6.4</v>
+      </c>
+      <c r="BF287">
+        <v>2.17</v>
+      </c>
+      <c r="BG287">
+        <v>1.38</v>
+      </c>
+      <c r="BH287">
+        <v>2.7</v>
+      </c>
+      <c r="BI287">
+        <v>1.67</v>
+      </c>
+      <c r="BJ287">
+        <v>2.07</v>
+      </c>
+      <c r="BK287">
+        <v>2.07</v>
+      </c>
+      <c r="BL287">
+        <v>1.66</v>
+      </c>
+      <c r="BM287">
+        <v>2.65</v>
+      </c>
+      <c r="BN287">
+        <v>1.41</v>
+      </c>
+      <c r="BO287">
+        <v>3.45</v>
+      </c>
+      <c r="BP287">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7509867</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45724.64583333334</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288" t="s">
+        <v>70</v>
+      </c>
+      <c r="H288" t="s">
+        <v>76</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>1</v>
+      </c>
+      <c r="L288">
+        <v>1</v>
+      </c>
+      <c r="M288">
+        <v>1</v>
+      </c>
+      <c r="N288">
+        <v>2</v>
+      </c>
+      <c r="O288" t="s">
+        <v>231</v>
+      </c>
+      <c r="P288" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q288">
+        <v>3.25</v>
+      </c>
+      <c r="R288">
+        <v>1.95</v>
+      </c>
+      <c r="S288">
+        <v>3.3</v>
+      </c>
+      <c r="T288">
+        <v>1.46</v>
+      </c>
+      <c r="U288">
+        <v>2.5</v>
+      </c>
+      <c r="V288">
+        <v>3</v>
+      </c>
+      <c r="W288">
+        <v>1.33</v>
+      </c>
+      <c r="X288">
+        <v>8.25</v>
+      </c>
+      <c r="Y288">
+        <v>1.06</v>
+      </c>
+      <c r="Z288">
+        <v>2.35</v>
+      </c>
+      <c r="AA288">
+        <v>3.37</v>
+      </c>
+      <c r="AB288">
+        <v>3.2</v>
+      </c>
+      <c r="AC288">
+        <v>1.09</v>
+      </c>
+      <c r="AD288">
+        <v>7</v>
+      </c>
+      <c r="AE288">
+        <v>1.44</v>
+      </c>
+      <c r="AF288">
+        <v>2.75</v>
+      </c>
+      <c r="AG288">
+        <v>2.05</v>
+      </c>
+      <c r="AH288">
+        <v>1.65</v>
+      </c>
+      <c r="AI288">
+        <v>1.87</v>
+      </c>
+      <c r="AJ288">
+        <v>1.8</v>
+      </c>
+      <c r="AK288">
+        <v>1.43</v>
+      </c>
+      <c r="AL288">
+        <v>1.35</v>
+      </c>
+      <c r="AM288">
+        <v>1.46</v>
+      </c>
+      <c r="AN288">
+        <v>1.14</v>
+      </c>
+      <c r="AO288">
+        <v>1</v>
+      </c>
+      <c r="AP288">
+        <v>1.13</v>
+      </c>
+      <c r="AQ288">
+        <v>1</v>
+      </c>
+      <c r="AR288">
+        <v>1.68</v>
+      </c>
+      <c r="AS288">
+        <v>1.33</v>
+      </c>
+      <c r="AT288">
+        <v>3.01</v>
+      </c>
+      <c r="AU288">
+        <v>6</v>
+      </c>
+      <c r="AV288">
+        <v>3</v>
+      </c>
+      <c r="AW288">
+        <v>7</v>
+      </c>
+      <c r="AX288">
+        <v>9</v>
+      </c>
+      <c r="AY288">
+        <v>14</v>
+      </c>
+      <c r="AZ288">
+        <v>17</v>
+      </c>
+      <c r="BA288">
+        <v>3</v>
+      </c>
+      <c r="BB288">
+        <v>3</v>
+      </c>
+      <c r="BC288">
+        <v>6</v>
+      </c>
+      <c r="BD288">
+        <v>1.94</v>
+      </c>
+      <c r="BE288">
+        <v>6.1</v>
+      </c>
+      <c r="BF288">
+        <v>2.08</v>
+      </c>
+      <c r="BG288">
+        <v>1.49</v>
+      </c>
+      <c r="BH288">
+        <v>2.4</v>
+      </c>
+      <c r="BI288">
+        <v>1.82</v>
+      </c>
+      <c r="BJ288">
+        <v>1.86</v>
+      </c>
+      <c r="BK288">
+        <v>2.32</v>
+      </c>
+      <c r="BL288">
+        <v>1.52</v>
+      </c>
+      <c r="BM288">
+        <v>3.05</v>
+      </c>
+      <c r="BN288">
+        <v>1.32</v>
+      </c>
+      <c r="BO288">
+        <v>4.1</v>
+      </c>
+      <c r="BP288">
         <v>1.19</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,9 @@
     <t>['31', '65', '70', '76']</t>
   </si>
   <si>
+    <t>['45', '58', '65']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1121,6 +1124,12 @@
   </si>
   <si>
     <t>['50']</t>
+  </si>
+  <si>
+    <t>['37', '47']</t>
+  </si>
+  <si>
+    <t>['58', '59', '61', '71', '76']</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1944,7 +1953,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2356,7 +2365,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2768,7 +2777,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3180,7 +3189,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3386,7 +3395,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3798,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3879,7 +3888,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4004,7 +4013,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4210,7 +4219,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4828,7 +4837,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4906,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -5318,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5446,7 +5455,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5858,7 +5867,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6145,7 +6154,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6270,7 +6279,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6554,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ25">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6888,7 +6897,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7999,7 +8008,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -8124,7 +8133,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8536,7 +8545,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8614,7 +8623,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ35">
         <v>1.57</v>
@@ -8742,7 +8751,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9566,7 +9575,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9644,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9772,7 +9781,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9978,7 +9987,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10262,7 +10271,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ43">
         <v>1.29</v>
@@ -10802,7 +10811,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11214,7 +11223,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11295,7 +11304,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR48">
         <v>1.25</v>
@@ -11420,7 +11429,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11832,7 +11841,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11913,7 +11922,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ51">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -12038,7 +12047,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -13149,7 +13158,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
         <v>0.86</v>
@@ -13480,7 +13489,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13561,7 +13570,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13892,7 +13901,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13970,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ61">
         <v>0.5</v>
@@ -14098,7 +14107,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14176,7 +14185,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14382,7 +14391,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ63">
         <v>1.53</v>
@@ -14922,7 +14931,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15209,7 +15218,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ67">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -15334,7 +15343,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15746,7 +15755,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15952,7 +15961,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16158,7 +16167,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16364,7 +16373,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16570,7 +16579,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16648,7 +16657,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ74">
         <v>1.47</v>
@@ -16854,7 +16863,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ75">
         <v>0.93</v>
@@ -16982,7 +16991,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17188,7 +17197,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17269,7 +17278,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17394,7 +17403,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17600,7 +17609,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17681,7 +17690,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17806,7 +17815,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18424,7 +18433,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18505,7 +18514,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ83">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -18630,7 +18639,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18914,7 +18923,7 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ85">
         <v>0.79</v>
@@ -19042,7 +19051,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19248,7 +19257,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19454,7 +19463,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -20072,7 +20081,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20356,10 +20365,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ92">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -21386,7 +21395,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ97">
         <v>0.87</v>
@@ -21801,7 +21810,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR99">
         <v>1.26</v>
@@ -22007,7 +22016,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ100">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -22750,7 +22759,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22956,7 +22965,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23858,7 +23867,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ109">
         <v>0.93</v>
@@ -24476,7 +24485,7 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ112">
         <v>0.87</v>
@@ -24604,7 +24613,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25303,7 +25312,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ116">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR116">
         <v>1.53</v>
@@ -25428,7 +25437,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25634,7 +25643,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25715,7 +25724,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ118">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -26330,7 +26339,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ121">
         <v>0.67</v>
@@ -26458,7 +26467,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -27282,7 +27291,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27694,7 +27703,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27900,7 +27909,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27978,7 +27987,7 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28106,7 +28115,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28312,7 +28321,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28393,7 +28402,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ131">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28518,7 +28527,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28802,7 +28811,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ133">
         <v>0.5</v>
@@ -29217,7 +29226,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ135">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -29342,7 +29351,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29754,7 +29763,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30038,10 +30047,10 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR139">
         <v>1.53</v>
@@ -30372,7 +30381,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30578,7 +30587,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30784,7 +30793,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30990,7 +30999,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31277,7 +31286,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ145">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31402,7 +31411,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31480,7 +31489,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ146">
         <v>1.07</v>
@@ -32020,7 +32029,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32226,7 +32235,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32638,7 +32647,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32719,7 +32728,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ152">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR152">
         <v>1.26</v>
@@ -33256,7 +33265,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33337,7 +33346,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ155">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -33668,7 +33677,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34080,7 +34089,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34364,7 +34373,7 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ160">
         <v>1.47</v>
@@ -34492,7 +34501,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34570,7 +34579,7 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ161">
         <v>0.93</v>
@@ -34779,7 +34788,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ162">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34904,7 +34913,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35316,7 +35325,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35934,7 +35943,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36424,7 +36433,7 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ170">
         <v>1.57</v>
@@ -36552,7 +36561,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37042,7 +37051,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ173">
         <v>1.13</v>
@@ -37251,7 +37260,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37869,7 +37878,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ177">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -37994,7 +38003,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38072,7 +38081,7 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
@@ -38200,7 +38209,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -39230,7 +39239,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39308,7 +39317,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ184">
         <v>0.67</v>
@@ -39436,7 +39445,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -40054,7 +40063,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40547,7 +40556,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ190">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40672,7 +40681,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40878,7 +40887,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41574,7 +41583,7 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ195">
         <v>0.79</v>
@@ -41783,7 +41792,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR196">
         <v>1.41</v>
@@ -41908,7 +41917,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42192,7 +42201,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ198">
         <v>1.13</v>
@@ -42526,7 +42535,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42813,7 +42822,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ201">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42938,7 +42947,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43225,7 +43234,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR203">
         <v>1.37</v>
@@ -43350,7 +43359,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43840,7 +43849,7 @@
         <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ206">
         <v>1.07</v>
@@ -43968,7 +43977,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44174,7 +44183,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44998,7 +45007,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45204,7 +45213,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45282,7 +45291,7 @@
         <v>0.55</v>
       </c>
       <c r="AP213">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ213">
         <v>0.67</v>
@@ -45822,7 +45831,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46028,7 +46037,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46315,7 +46324,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ218">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR218">
         <v>1.25</v>
@@ -46646,7 +46655,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46724,10 +46733,10 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ220">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -46852,7 +46861,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47058,7 +47067,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47136,7 +47145,7 @@
         <v>2.18</v>
       </c>
       <c r="AP222">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ222">
         <v>2</v>
@@ -47470,7 +47479,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47551,7 +47560,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR224">
         <v>1.39</v>
@@ -47757,7 +47766,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ225">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR225">
         <v>1.49</v>
@@ -47882,7 +47891,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48088,7 +48097,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48294,7 +48303,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48912,7 +48921,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49118,7 +49127,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49199,7 +49208,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ232">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR232">
         <v>1.79</v>
@@ -49608,7 +49617,7 @@
         <v>1.25</v>
       </c>
       <c r="AP234">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -49736,7 +49745,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49814,7 +49823,7 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ235">
         <v>1.53</v>
@@ -49942,7 +49951,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50560,7 +50569,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50972,7 +50981,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51590,7 +51599,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -52495,7 +52504,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ248">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR248">
         <v>1.78</v>
@@ -52826,7 +52835,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -52904,7 +52913,7 @@
         <v>1</v>
       </c>
       <c r="AP250">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ250">
         <v>1.13</v>
@@ -53113,7 +53122,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ251">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR251">
         <v>1.22</v>
@@ -53444,7 +53453,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53934,7 +53943,7 @@
         <v>1.17</v>
       </c>
       <c r="AP255">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ255">
         <v>1</v>
@@ -54886,7 +54895,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55173,7 +55182,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ261">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR261">
         <v>1.47</v>
@@ -55504,7 +55513,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55582,7 +55591,7 @@
         <v>0.77</v>
       </c>
       <c r="AP263">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ263">
         <v>0.87</v>
@@ -55791,7 +55800,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ264">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR264">
         <v>1.31</v>
@@ -56122,7 +56131,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56328,7 +56337,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56534,7 +56543,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -56818,7 +56827,7 @@
         <v>1.25</v>
       </c>
       <c r="AP269">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ269">
         <v>1.29</v>
@@ -57027,7 +57036,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ270">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR270">
         <v>1.61</v>
@@ -57152,7 +57161,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57564,7 +57573,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -57976,7 +57985,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58466,10 +58475,10 @@
         <v>1.69</v>
       </c>
       <c r="AP277">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="AQ277">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR277">
         <v>1.68</v>
@@ -58800,7 +58809,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -59212,7 +59221,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60654,7 +60663,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -60811,6 +60820,624 @@
       </c>
       <c r="BP288">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7509875</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
+      <c r="G289" t="s">
+        <v>84</v>
+      </c>
+      <c r="H289" t="s">
+        <v>71</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289">
+        <v>1</v>
+      </c>
+      <c r="L289">
+        <v>1</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>2</v>
+      </c>
+      <c r="O289" t="s">
+        <v>144</v>
+      </c>
+      <c r="P289" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q289">
+        <v>2.25</v>
+      </c>
+      <c r="R289">
+        <v>2.2</v>
+      </c>
+      <c r="S289">
+        <v>5.5</v>
+      </c>
+      <c r="T289">
+        <v>1.4</v>
+      </c>
+      <c r="U289">
+        <v>2.75</v>
+      </c>
+      <c r="V289">
+        <v>3</v>
+      </c>
+      <c r="W289">
+        <v>1.36</v>
+      </c>
+      <c r="X289">
+        <v>8</v>
+      </c>
+      <c r="Y289">
+        <v>1.08</v>
+      </c>
+      <c r="Z289">
+        <v>1.73</v>
+      </c>
+      <c r="AA289">
+        <v>3.9</v>
+      </c>
+      <c r="AB289">
+        <v>5</v>
+      </c>
+      <c r="AC289">
+        <v>1.05</v>
+      </c>
+      <c r="AD289">
+        <v>9</v>
+      </c>
+      <c r="AE289">
+        <v>1.3</v>
+      </c>
+      <c r="AF289">
+        <v>3.45</v>
+      </c>
+      <c r="AG289">
+        <v>1.97</v>
+      </c>
+      <c r="AH289">
+        <v>1.84</v>
+      </c>
+      <c r="AI289">
+        <v>1.95</v>
+      </c>
+      <c r="AJ289">
+        <v>1.8</v>
+      </c>
+      <c r="AK289">
+        <v>1.18</v>
+      </c>
+      <c r="AL289">
+        <v>1.26</v>
+      </c>
+      <c r="AM289">
+        <v>2.1</v>
+      </c>
+      <c r="AN289">
+        <v>2.64</v>
+      </c>
+      <c r="AO289">
+        <v>1.15</v>
+      </c>
+      <c r="AP289">
+        <v>2.53</v>
+      </c>
+      <c r="AQ289">
+        <v>1.14</v>
+      </c>
+      <c r="AR289">
+        <v>1.67</v>
+      </c>
+      <c r="AS289">
+        <v>1.31</v>
+      </c>
+      <c r="AT289">
+        <v>2.98</v>
+      </c>
+      <c r="AU289">
+        <v>4</v>
+      </c>
+      <c r="AV289">
+        <v>7</v>
+      </c>
+      <c r="AW289">
+        <v>7</v>
+      </c>
+      <c r="AX289">
+        <v>4</v>
+      </c>
+      <c r="AY289">
+        <v>14</v>
+      </c>
+      <c r="AZ289">
+        <v>12</v>
+      </c>
+      <c r="BA289">
+        <v>5</v>
+      </c>
+      <c r="BB289">
+        <v>4</v>
+      </c>
+      <c r="BC289">
+        <v>9</v>
+      </c>
+      <c r="BD289">
+        <v>1.49</v>
+      </c>
+      <c r="BE289">
+        <v>6.75</v>
+      </c>
+      <c r="BF289">
+        <v>2.9</v>
+      </c>
+      <c r="BG289">
+        <v>1.36</v>
+      </c>
+      <c r="BH289">
+        <v>2.8</v>
+      </c>
+      <c r="BI289">
+        <v>1.61</v>
+      </c>
+      <c r="BJ289">
+        <v>2.15</v>
+      </c>
+      <c r="BK289">
+        <v>1.98</v>
+      </c>
+      <c r="BL289">
+        <v>1.72</v>
+      </c>
+      <c r="BM289">
+        <v>2.55</v>
+      </c>
+      <c r="BN289">
+        <v>1.44</v>
+      </c>
+      <c r="BO289">
+        <v>3.4</v>
+      </c>
+      <c r="BP289">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7509876</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45725.45833333334</v>
+      </c>
+      <c r="F290">
+        <v>29</v>
+      </c>
+      <c r="G290" t="s">
+        <v>83</v>
+      </c>
+      <c r="H290" t="s">
+        <v>73</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290">
+        <v>2</v>
+      </c>
+      <c r="L290">
+        <v>3</v>
+      </c>
+      <c r="M290">
+        <v>2</v>
+      </c>
+      <c r="N290">
+        <v>5</v>
+      </c>
+      <c r="O290" t="s">
+        <v>260</v>
+      </c>
+      <c r="P290" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q290">
+        <v>2.6</v>
+      </c>
+      <c r="R290">
+        <v>2.05</v>
+      </c>
+      <c r="S290">
+        <v>4.75</v>
+      </c>
+      <c r="T290">
+        <v>1.5</v>
+      </c>
+      <c r="U290">
+        <v>2.5</v>
+      </c>
+      <c r="V290">
+        <v>3.4</v>
+      </c>
+      <c r="W290">
+        <v>1.3</v>
+      </c>
+      <c r="X290">
+        <v>10</v>
+      </c>
+      <c r="Y290">
+        <v>1.06</v>
+      </c>
+      <c r="Z290">
+        <v>1.91</v>
+      </c>
+      <c r="AA290">
+        <v>3.5</v>
+      </c>
+      <c r="AB290">
+        <v>4.4</v>
+      </c>
+      <c r="AC290">
+        <v>1.07</v>
+      </c>
+      <c r="AD290">
+        <v>8</v>
+      </c>
+      <c r="AE290">
+        <v>1.38</v>
+      </c>
+      <c r="AF290">
+        <v>2.95</v>
+      </c>
+      <c r="AG290">
+        <v>1.95</v>
+      </c>
+      <c r="AH290">
+        <v>1.7</v>
+      </c>
+      <c r="AI290">
+        <v>2</v>
+      </c>
+      <c r="AJ290">
+        <v>1.75</v>
+      </c>
+      <c r="AK290">
+        <v>1.22</v>
+      </c>
+      <c r="AL290">
+        <v>1.3</v>
+      </c>
+      <c r="AM290">
+        <v>1.87</v>
+      </c>
+      <c r="AN290">
+        <v>2.15</v>
+      </c>
+      <c r="AO290">
+        <v>1.57</v>
+      </c>
+      <c r="AP290">
+        <v>2.21</v>
+      </c>
+      <c r="AQ290">
+        <v>1.47</v>
+      </c>
+      <c r="AR290">
+        <v>1.93</v>
+      </c>
+      <c r="AS290">
+        <v>1.18</v>
+      </c>
+      <c r="AT290">
+        <v>3.11</v>
+      </c>
+      <c r="AU290">
+        <v>4</v>
+      </c>
+      <c r="AV290">
+        <v>5</v>
+      </c>
+      <c r="AW290">
+        <v>6</v>
+      </c>
+      <c r="AX290">
+        <v>7</v>
+      </c>
+      <c r="AY290">
+        <v>11</v>
+      </c>
+      <c r="AZ290">
+        <v>14</v>
+      </c>
+      <c r="BA290">
+        <v>2</v>
+      </c>
+      <c r="BB290">
+        <v>0</v>
+      </c>
+      <c r="BC290">
+        <v>2</v>
+      </c>
+      <c r="BD290">
+        <v>1.63</v>
+      </c>
+      <c r="BE290">
+        <v>6.4</v>
+      </c>
+      <c r="BF290">
+        <v>2.55</v>
+      </c>
+      <c r="BG290">
+        <v>1.44</v>
+      </c>
+      <c r="BH290">
+        <v>2.55</v>
+      </c>
+      <c r="BI290">
+        <v>1.74</v>
+      </c>
+      <c r="BJ290">
+        <v>1.95</v>
+      </c>
+      <c r="BK290">
+        <v>2.2</v>
+      </c>
+      <c r="BL290">
+        <v>1.58</v>
+      </c>
+      <c r="BM290">
+        <v>2.9</v>
+      </c>
+      <c r="BN290">
+        <v>1.35</v>
+      </c>
+      <c r="BO290">
+        <v>3.8</v>
+      </c>
+      <c r="BP290">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7509869</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45725.55208333334</v>
+      </c>
+      <c r="F291">
+        <v>29</v>
+      </c>
+      <c r="G291" t="s">
+        <v>87</v>
+      </c>
+      <c r="H291" t="s">
+        <v>72</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>0</v>
+      </c>
+      <c r="L291">
+        <v>1</v>
+      </c>
+      <c r="M291">
+        <v>5</v>
+      </c>
+      <c r="N291">
+        <v>6</v>
+      </c>
+      <c r="O291" t="s">
+        <v>245</v>
+      </c>
+      <c r="P291" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q291">
+        <v>3.5</v>
+      </c>
+      <c r="R291">
+        <v>1.91</v>
+      </c>
+      <c r="S291">
+        <v>3.75</v>
+      </c>
+      <c r="T291">
+        <v>1.57</v>
+      </c>
+      <c r="U291">
+        <v>2.25</v>
+      </c>
+      <c r="V291">
+        <v>3.75</v>
+      </c>
+      <c r="W291">
+        <v>1.25</v>
+      </c>
+      <c r="X291">
+        <v>13</v>
+      </c>
+      <c r="Y291">
+        <v>1.04</v>
+      </c>
+      <c r="Z291">
+        <v>2.71</v>
+      </c>
+      <c r="AA291">
+        <v>2.97</v>
+      </c>
+      <c r="AB291">
+        <v>3.03</v>
+      </c>
+      <c r="AC291">
+        <v>1.1</v>
+      </c>
+      <c r="AD291">
+        <v>6.5</v>
+      </c>
+      <c r="AE291">
+        <v>1.5</v>
+      </c>
+      <c r="AF291">
+        <v>2.55</v>
+      </c>
+      <c r="AG291">
+        <v>2.1</v>
+      </c>
+      <c r="AH291">
+        <v>1.6</v>
+      </c>
+      <c r="AI291">
+        <v>2.05</v>
+      </c>
+      <c r="AJ291">
+        <v>1.7</v>
+      </c>
+      <c r="AK291">
+        <v>1.38</v>
+      </c>
+      <c r="AL291">
+        <v>1.36</v>
+      </c>
+      <c r="AM291">
+        <v>1.5</v>
+      </c>
+      <c r="AN291">
+        <v>0.92</v>
+      </c>
+      <c r="AO291">
+        <v>1</v>
+      </c>
+      <c r="AP291">
+        <v>0.86</v>
+      </c>
+      <c r="AQ291">
+        <v>1.13</v>
+      </c>
+      <c r="AR291">
+        <v>1.41</v>
+      </c>
+      <c r="AS291">
+        <v>1.22</v>
+      </c>
+      <c r="AT291">
+        <v>2.63</v>
+      </c>
+      <c r="AU291">
+        <v>4</v>
+      </c>
+      <c r="AV291">
+        <v>7</v>
+      </c>
+      <c r="AW291">
+        <v>4</v>
+      </c>
+      <c r="AX291">
+        <v>12</v>
+      </c>
+      <c r="AY291">
+        <v>8</v>
+      </c>
+      <c r="AZ291">
+        <v>23</v>
+      </c>
+      <c r="BA291">
+        <v>3</v>
+      </c>
+      <c r="BB291">
+        <v>4</v>
+      </c>
+      <c r="BC291">
+        <v>7</v>
+      </c>
+      <c r="BD291">
+        <v>1.76</v>
+      </c>
+      <c r="BE291">
+        <v>6.5</v>
+      </c>
+      <c r="BF291">
+        <v>2.3</v>
+      </c>
+      <c r="BG291">
+        <v>1.46</v>
+      </c>
+      <c r="BH291">
+        <v>2.5</v>
+      </c>
+      <c r="BI291">
+        <v>1.75</v>
+      </c>
+      <c r="BJ291">
+        <v>1.95</v>
+      </c>
+      <c r="BK291">
+        <v>2.18</v>
+      </c>
+      <c r="BL291">
+        <v>1.58</v>
+      </c>
+      <c r="BM291">
+        <v>2.8</v>
+      </c>
+      <c r="BN291">
+        <v>1.37</v>
+      </c>
+      <c r="BO291">
+        <v>3.7</v>
+      </c>
+      <c r="BP291">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -799,6 +799,15 @@
     <t>['45', '58', '65']</t>
   </si>
   <si>
+    <t>['55', '72']</t>
+  </si>
+  <si>
+    <t>['16', '61']</t>
+  </si>
+  <si>
+    <t>['10', '64']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1130,6 +1139,12 @@
   </si>
   <si>
     <t>['58', '59', '61', '71', '76']</t>
+  </si>
+  <si>
+    <t>['74', '86', '90+5']</t>
+  </si>
+  <si>
+    <t>['15', '46']</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1953,7 +1968,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2240,7 +2255,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2365,7 +2380,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2446,7 +2461,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2777,7 +2792,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2855,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ7">
         <v>0.93</v>
@@ -3061,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8">
         <v>0.5</v>
@@ -3189,7 +3204,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3395,7 +3410,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3476,7 +3491,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3682,7 +3697,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ11">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3807,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -4013,7 +4028,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4219,7 +4234,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4837,7 +4852,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5455,7 +5470,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5867,7 +5882,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5948,7 +5963,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -6279,7 +6294,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6563,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ25">
         <v>1.47</v>
@@ -6772,7 +6787,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ26">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -6897,7 +6912,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7181,10 +7196,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ28">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7387,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>1.29</v>
@@ -7596,7 +7611,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ30">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.65</v>
@@ -7799,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31">
         <v>0.67</v>
@@ -8133,7 +8148,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8545,7 +8560,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8626,7 +8641,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ35">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8751,7 +8766,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8832,7 +8847,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -9035,7 +9050,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ37">
         <v>1.07</v>
@@ -9447,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ39">
         <v>0.79</v>
@@ -9575,7 +9590,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9781,7 +9796,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9987,7 +10002,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10065,10 +10080,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ42">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10271,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ43">
         <v>1.29</v>
@@ -10811,7 +10826,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10889,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46">
         <v>1.13</v>
@@ -11098,7 +11113,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ47">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR47">
         <v>1.62</v>
@@ -11223,7 +11238,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11429,7 +11444,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11510,7 +11525,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -11841,7 +11856,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12047,7 +12062,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12128,7 +12143,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12334,7 +12349,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -12537,7 +12552,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12746,7 +12761,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ55">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR55">
         <v>1.42</v>
@@ -13489,7 +13504,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13567,7 +13582,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ59">
         <v>1.14</v>
@@ -13901,7 +13916,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14107,7 +14122,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14185,7 +14200,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14394,7 +14409,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.29</v>
@@ -14931,7 +14946,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15009,7 +15024,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -15215,7 +15230,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ67">
         <v>1.47</v>
@@ -15343,7 +15358,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15755,7 +15770,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15961,7 +15976,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16042,7 +16057,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ71">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -16167,7 +16182,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16373,7 +16388,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16451,7 +16466,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ73">
         <v>0.5</v>
@@ -16579,7 +16594,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16991,7 +17006,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17197,7 +17212,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17403,7 +17418,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17484,7 +17499,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -17609,7 +17624,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17815,7 +17830,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17896,7 +17911,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ80">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18099,7 +18114,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -18433,7 +18448,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18639,7 +18654,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18720,7 +18735,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ84">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR84">
         <v>1.72</v>
@@ -18923,7 +18938,7 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ85">
         <v>0.79</v>
@@ -19051,7 +19066,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19257,7 +19272,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19338,7 +19353,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19463,7 +19478,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19541,10 +19556,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ88">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -20081,7 +20096,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20159,7 +20174,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ91">
         <v>0.93</v>
@@ -20571,10 +20586,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR93">
         <v>1.54</v>
@@ -21189,7 +21204,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ96">
         <v>0.93</v>
@@ -21398,7 +21413,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ97">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -22013,7 +22028,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ100">
         <v>1.47</v>
@@ -22634,7 +22649,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ103">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.86</v>
@@ -22759,7 +22774,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22837,10 +22852,10 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ104">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -22965,7 +22980,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23046,7 +23061,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ105">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -23867,7 +23882,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ109">
         <v>0.93</v>
@@ -24488,7 +24503,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ112">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24613,7 +24628,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25309,7 +25324,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ116">
         <v>1.13</v>
@@ -25437,7 +25452,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25643,7 +25658,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25927,7 +25942,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ119">
         <v>1.47</v>
@@ -26136,7 +26151,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR120">
         <v>1.28</v>
@@ -26467,7 +26482,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26545,7 +26560,7 @@
         <v>1.57</v>
       </c>
       <c r="AP122">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ122">
         <v>1.13</v>
@@ -26754,7 +26769,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ123">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -27291,7 +27306,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27578,7 +27593,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ127">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27703,7 +27718,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27781,10 +27796,10 @@
         <v>1.33</v>
       </c>
       <c r="AP128">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ128">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.36</v>
@@ -27909,7 +27924,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -27987,7 +28002,7 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28115,7 +28130,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28321,7 +28336,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28527,7 +28542,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28608,7 +28623,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ132">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -29017,10 +29032,10 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ134">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29351,7 +29366,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29635,7 +29650,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ137">
         <v>0.93</v>
@@ -29763,7 +29778,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30381,7 +30396,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30459,7 +30474,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ141">
         <v>0.93</v>
@@ -30587,7 +30602,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30668,7 +30683,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ142">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30793,7 +30808,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30999,7 +31014,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31080,7 +31095,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ144">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31411,7 +31426,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31489,7 +31504,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ146">
         <v>1.07</v>
@@ -31698,7 +31713,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ147">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -31901,10 +31916,10 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ148">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR148">
         <v>1.81</v>
@@ -32029,7 +32044,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32235,7 +32250,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32313,7 +32328,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32647,7 +32662,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32725,7 +32740,7 @@
         <v>0.86</v>
       </c>
       <c r="AP152">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ152">
         <v>1.13</v>
@@ -33265,7 +33280,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33677,7 +33692,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33964,7 +33979,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR158">
         <v>1.22</v>
@@ -34089,7 +34104,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34501,7 +34516,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34913,7 +34928,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35200,7 +35215,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ164">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35325,7 +35340,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35403,10 +35418,10 @@
         <v>2.25</v>
       </c>
       <c r="AP165">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ165">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -35609,7 +35624,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ166">
         <v>0.79</v>
@@ -35818,7 +35833,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ167">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
         <v>1.43</v>
@@ -35943,7 +35958,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36021,7 +36036,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ168">
         <v>1.29</v>
@@ -36433,10 +36448,10 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ170">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36561,7 +36576,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36848,7 +36863,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ172">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR172">
         <v>1.72</v>
@@ -38003,7 +38018,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38081,7 +38096,7 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ178">
         <v>0.93</v>
@@ -38209,7 +38224,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38290,7 +38305,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ179">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR179">
         <v>1.23</v>
@@ -38493,7 +38508,7 @@
         <v>0.63</v>
       </c>
       <c r="AP180">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -38908,7 +38923,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ182">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39239,7 +39254,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39445,7 +39460,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39935,10 +39950,10 @@
         <v>1.56</v>
       </c>
       <c r="AP187">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ187">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -40063,7 +40078,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40144,7 +40159,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ188">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40347,7 +40362,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ189">
         <v>0.5</v>
@@ -40553,7 +40568,7 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ190">
         <v>1.14</v>
@@ -40681,7 +40696,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40887,7 +40902,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40968,7 +40983,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR192">
         <v>1.54</v>
@@ -41174,7 +41189,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ193">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR193">
         <v>1.34</v>
@@ -41917,7 +41932,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42201,7 +42216,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ198">
         <v>1.13</v>
@@ -42535,7 +42550,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42613,7 +42628,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ200">
         <v>1</v>
@@ -42947,7 +42962,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43028,7 +43043,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ202">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR202">
         <v>1.7</v>
@@ -43359,7 +43374,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43643,10 +43658,10 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ205">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR205">
         <v>1.88</v>
@@ -43977,7 +43992,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44183,7 +44198,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44261,10 +44276,10 @@
         <v>1.7</v>
       </c>
       <c r="AP208">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ208">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR208">
         <v>1.42</v>
@@ -44467,7 +44482,7 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ209">
         <v>1.47</v>
@@ -45007,7 +45022,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45213,7 +45228,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45291,7 +45306,7 @@
         <v>0.55</v>
       </c>
       <c r="AP213">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ213">
         <v>0.67</v>
@@ -45831,7 +45846,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46037,7 +46052,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46118,7 +46133,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46527,7 +46542,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ219">
         <v>1.07</v>
@@ -46655,7 +46670,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46861,7 +46876,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46942,7 +46957,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ221">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR221">
         <v>1.33</v>
@@ -47067,7 +47082,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47148,7 +47163,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ222">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR222">
         <v>1.73</v>
@@ -47351,7 +47366,7 @@
         <v>0.55</v>
       </c>
       <c r="AP223">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ223">
         <v>0.5</v>
@@ -47479,7 +47494,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47557,7 +47572,7 @@
         <v>0.91</v>
       </c>
       <c r="AP224">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ224">
         <v>1.13</v>
@@ -47763,7 +47778,7 @@
         <v>1.1</v>
       </c>
       <c r="AP225">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ225">
         <v>1.14</v>
@@ -47891,7 +47906,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48097,7 +48112,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48303,7 +48318,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48921,7 +48936,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49002,7 +49017,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ231">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49127,7 +49142,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49205,7 +49220,7 @@
         <v>1.64</v>
       </c>
       <c r="AP232">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ232">
         <v>1.47</v>
@@ -49745,7 +49760,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49823,10 +49838,10 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ235">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR235">
         <v>1.39</v>
@@ -49951,7 +49966,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50444,7 +50459,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ238">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR238">
         <v>1.73</v>
@@ -50569,7 +50584,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50650,7 +50665,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ239">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR239">
         <v>1.34</v>
@@ -50981,7 +50996,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51599,7 +51614,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51680,7 +51695,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ244">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR244">
         <v>1.33</v>
@@ -51883,7 +51898,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ245">
         <v>1.29</v>
@@ -52298,7 +52313,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ247">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR247">
         <v>1.4</v>
@@ -52835,7 +52850,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53119,7 +53134,7 @@
         <v>1.09</v>
       </c>
       <c r="AP251">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ251">
         <v>1.14</v>
@@ -53453,7 +53468,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53740,7 +53755,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ254">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR254">
         <v>1.44</v>
@@ -53946,7 +53961,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ255">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR255">
         <v>1.73</v>
@@ -54358,7 +54373,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ257">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR257">
         <v>1.38</v>
@@ -54561,7 +54576,7 @@
         <v>1</v>
       </c>
       <c r="AP258">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ258">
         <v>0.93</v>
@@ -54767,7 +54782,7 @@
         <v>0.83</v>
       </c>
       <c r="AP259">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ259">
         <v>0.79</v>
@@ -54895,7 +54910,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -54973,7 +54988,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP260">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ260">
         <v>0.67</v>
@@ -55179,7 +55194,7 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ261">
         <v>1.47</v>
@@ -55388,7 +55403,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ262">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AR262">
         <v>1.44</v>
@@ -55513,7 +55528,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55591,10 +55606,10 @@
         <v>0.77</v>
       </c>
       <c r="AP263">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ263">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR263">
         <v>1.4</v>
@@ -56131,7 +56146,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56337,7 +56352,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56543,7 +56558,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -57161,7 +57176,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57448,7 +57463,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ272">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR272">
         <v>1.47</v>
@@ -57573,7 +57588,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -57654,7 +57669,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ273">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR273">
         <v>1.39</v>
@@ -57857,7 +57872,7 @@
         <v>0.54</v>
       </c>
       <c r="AP274">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ274">
         <v>0.5</v>
@@ -57985,7 +58000,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58063,7 +58078,7 @@
         <v>0.71</v>
       </c>
       <c r="AP275">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ275">
         <v>0.67</v>
@@ -58269,7 +58284,7 @@
         <v>1.36</v>
       </c>
       <c r="AP276">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ276">
         <v>1.47</v>
@@ -58681,10 +58696,10 @@
         <v>1.08</v>
       </c>
       <c r="AP278">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ278">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR278">
         <v>1.76</v>
@@ -58809,7 +58824,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -59221,7 +59236,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60126,7 +60141,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ285">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR285">
         <v>1.71</v>
@@ -60663,7 +60678,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -61075,7 +61090,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61281,7 +61296,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61359,7 +61374,7 @@
         <v>1</v>
       </c>
       <c r="AP291">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ291">
         <v>1.13</v>
@@ -61438,6 +61453,1036 @@
       </c>
       <c r="BP291">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7509883</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45730.6875</v>
+      </c>
+      <c r="F292">
+        <v>30</v>
+      </c>
+      <c r="G292" t="s">
+        <v>89</v>
+      </c>
+      <c r="H292" t="s">
+        <v>82</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>0</v>
+      </c>
+      <c r="L292">
+        <v>2</v>
+      </c>
+      <c r="M292">
+        <v>3</v>
+      </c>
+      <c r="N292">
+        <v>5</v>
+      </c>
+      <c r="O292" t="s">
+        <v>261</v>
+      </c>
+      <c r="P292" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q292">
+        <v>3.1</v>
+      </c>
+      <c r="R292">
+        <v>2</v>
+      </c>
+      <c r="S292">
+        <v>3.25</v>
+      </c>
+      <c r="T292">
+        <v>1.42</v>
+      </c>
+      <c r="U292">
+        <v>2.65</v>
+      </c>
+      <c r="V292">
+        <v>2.8</v>
+      </c>
+      <c r="W292">
+        <v>1.37</v>
+      </c>
+      <c r="X292">
+        <v>7.25</v>
+      </c>
+      <c r="Y292">
+        <v>1.08</v>
+      </c>
+      <c r="Z292">
+        <v>2.79</v>
+      </c>
+      <c r="AA292">
+        <v>3.03</v>
+      </c>
+      <c r="AB292">
+        <v>2.88</v>
+      </c>
+      <c r="AC292">
+        <v>1.08</v>
+      </c>
+      <c r="AD292">
+        <v>7.5</v>
+      </c>
+      <c r="AE292">
+        <v>1.38</v>
+      </c>
+      <c r="AF292">
+        <v>3</v>
+      </c>
+      <c r="AG292">
+        <v>1.96</v>
+      </c>
+      <c r="AH292">
+        <v>1.85</v>
+      </c>
+      <c r="AI292">
+        <v>1.78</v>
+      </c>
+      <c r="AJ292">
+        <v>1.9</v>
+      </c>
+      <c r="AK292">
+        <v>1.43</v>
+      </c>
+      <c r="AL292">
+        <v>1.34</v>
+      </c>
+      <c r="AM292">
+        <v>1.47</v>
+      </c>
+      <c r="AN292">
+        <v>1.57</v>
+      </c>
+      <c r="AO292">
+        <v>1.57</v>
+      </c>
+      <c r="AP292">
+        <v>1.47</v>
+      </c>
+      <c r="AQ292">
+        <v>1.67</v>
+      </c>
+      <c r="AR292">
+        <v>1.84</v>
+      </c>
+      <c r="AS292">
+        <v>1.51</v>
+      </c>
+      <c r="AT292">
+        <v>3.35</v>
+      </c>
+      <c r="AU292">
+        <v>4</v>
+      </c>
+      <c r="AV292">
+        <v>9</v>
+      </c>
+      <c r="AW292">
+        <v>7</v>
+      </c>
+      <c r="AX292">
+        <v>11</v>
+      </c>
+      <c r="AY292">
+        <v>15</v>
+      </c>
+      <c r="AZ292">
+        <v>22</v>
+      </c>
+      <c r="BA292">
+        <v>1</v>
+      </c>
+      <c r="BB292">
+        <v>7</v>
+      </c>
+      <c r="BC292">
+        <v>8</v>
+      </c>
+      <c r="BD292">
+        <v>2</v>
+      </c>
+      <c r="BE292">
+        <v>6.4</v>
+      </c>
+      <c r="BF292">
+        <v>1.98</v>
+      </c>
+      <c r="BG292">
+        <v>1.35</v>
+      </c>
+      <c r="BH292">
+        <v>2.9</v>
+      </c>
+      <c r="BI292">
+        <v>1.6</v>
+      </c>
+      <c r="BJ292">
+        <v>2.17</v>
+      </c>
+      <c r="BK292">
+        <v>1.98</v>
+      </c>
+      <c r="BL292">
+        <v>1.73</v>
+      </c>
+      <c r="BM292">
+        <v>2.5</v>
+      </c>
+      <c r="BN292">
+        <v>1.46</v>
+      </c>
+      <c r="BO292">
+        <v>3.3</v>
+      </c>
+      <c r="BP292">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7509879</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F293">
+        <v>30</v>
+      </c>
+      <c r="G293" t="s">
+        <v>76</v>
+      </c>
+      <c r="H293" t="s">
+        <v>83</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>0</v>
+      </c>
+      <c r="L293">
+        <v>0</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>0</v>
+      </c>
+      <c r="O293" t="s">
+        <v>102</v>
+      </c>
+      <c r="P293" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q293">
+        <v>4.5</v>
+      </c>
+      <c r="R293">
+        <v>2</v>
+      </c>
+      <c r="S293">
+        <v>2.88</v>
+      </c>
+      <c r="T293">
+        <v>1.5</v>
+      </c>
+      <c r="U293">
+        <v>2.5</v>
+      </c>
+      <c r="V293">
+        <v>3.5</v>
+      </c>
+      <c r="W293">
+        <v>1.29</v>
+      </c>
+      <c r="X293">
+        <v>11</v>
+      </c>
+      <c r="Y293">
+        <v>1.05</v>
+      </c>
+      <c r="Z293">
+        <v>3.72</v>
+      </c>
+      <c r="AA293">
+        <v>3.13</v>
+      </c>
+      <c r="AB293">
+        <v>2.24</v>
+      </c>
+      <c r="AC293">
+        <v>1.07</v>
+      </c>
+      <c r="AD293">
+        <v>7</v>
+      </c>
+      <c r="AE293">
+        <v>1.42</v>
+      </c>
+      <c r="AF293">
+        <v>2.62</v>
+      </c>
+      <c r="AG293">
+        <v>2.05</v>
+      </c>
+      <c r="AH293">
+        <v>1.61</v>
+      </c>
+      <c r="AI293">
+        <v>1.95</v>
+      </c>
+      <c r="AJ293">
+        <v>1.8</v>
+      </c>
+      <c r="AK293">
+        <v>1.7</v>
+      </c>
+      <c r="AL293">
+        <v>1.4</v>
+      </c>
+      <c r="AM293">
+        <v>1.25</v>
+      </c>
+      <c r="AN293">
+        <v>1.86</v>
+      </c>
+      <c r="AO293">
+        <v>1.53</v>
+      </c>
+      <c r="AP293">
+        <v>1.8</v>
+      </c>
+      <c r="AQ293">
+        <v>1.5</v>
+      </c>
+      <c r="AR293">
+        <v>1.45</v>
+      </c>
+      <c r="AS293">
+        <v>1.51</v>
+      </c>
+      <c r="AT293">
+        <v>2.96</v>
+      </c>
+      <c r="AU293">
+        <v>2</v>
+      </c>
+      <c r="AV293">
+        <v>4</v>
+      </c>
+      <c r="AW293">
+        <v>9</v>
+      </c>
+      <c r="AX293">
+        <v>12</v>
+      </c>
+      <c r="AY293">
+        <v>18</v>
+      </c>
+      <c r="AZ293">
+        <v>20</v>
+      </c>
+      <c r="BA293">
+        <v>8</v>
+      </c>
+      <c r="BB293">
+        <v>7</v>
+      </c>
+      <c r="BC293">
+        <v>15</v>
+      </c>
+      <c r="BD293">
+        <v>2.3</v>
+      </c>
+      <c r="BE293">
+        <v>8</v>
+      </c>
+      <c r="BF293">
+        <v>1.75</v>
+      </c>
+      <c r="BG293">
+        <v>1.37</v>
+      </c>
+      <c r="BH293">
+        <v>2.75</v>
+      </c>
+      <c r="BI293">
+        <v>1.75</v>
+      </c>
+      <c r="BJ293">
+        <v>2.05</v>
+      </c>
+      <c r="BK293">
+        <v>2.2</v>
+      </c>
+      <c r="BL293">
+        <v>1.65</v>
+      </c>
+      <c r="BM293">
+        <v>2.88</v>
+      </c>
+      <c r="BN293">
+        <v>1.32</v>
+      </c>
+      <c r="BO293">
+        <v>4.05</v>
+      </c>
+      <c r="BP293">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7509880</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F294">
+        <v>30</v>
+      </c>
+      <c r="G294" t="s">
+        <v>87</v>
+      </c>
+      <c r="H294" t="s">
+        <v>84</v>
+      </c>
+      <c r="I294">
+        <v>0</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>1</v>
+      </c>
+      <c r="M294">
+        <v>2</v>
+      </c>
+      <c r="N294">
+        <v>3</v>
+      </c>
+      <c r="O294" t="s">
+        <v>90</v>
+      </c>
+      <c r="P294" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q294">
+        <v>4.5</v>
+      </c>
+      <c r="R294">
+        <v>2.2</v>
+      </c>
+      <c r="S294">
+        <v>2.5</v>
+      </c>
+      <c r="T294">
+        <v>1.4</v>
+      </c>
+      <c r="U294">
+        <v>2.75</v>
+      </c>
+      <c r="V294">
+        <v>3</v>
+      </c>
+      <c r="W294">
+        <v>1.36</v>
+      </c>
+      <c r="X294">
+        <v>8</v>
+      </c>
+      <c r="Y294">
+        <v>1.08</v>
+      </c>
+      <c r="Z294">
+        <v>4.3</v>
+      </c>
+      <c r="AA294">
+        <v>3.47</v>
+      </c>
+      <c r="AB294">
+        <v>1.95</v>
+      </c>
+      <c r="AC294">
+        <v>1.03</v>
+      </c>
+      <c r="AD294">
+        <v>9</v>
+      </c>
+      <c r="AE294">
+        <v>1.3</v>
+      </c>
+      <c r="AF294">
+        <v>3.2</v>
+      </c>
+      <c r="AG294">
+        <v>1.92</v>
+      </c>
+      <c r="AH294">
+        <v>1.83</v>
+      </c>
+      <c r="AI294">
+        <v>1.8</v>
+      </c>
+      <c r="AJ294">
+        <v>1.95</v>
+      </c>
+      <c r="AK294">
+        <v>1.88</v>
+      </c>
+      <c r="AL294">
+        <v>1.29</v>
+      </c>
+      <c r="AM294">
+        <v>1.23</v>
+      </c>
+      <c r="AN294">
+        <v>0.86</v>
+      </c>
+      <c r="AO294">
+        <v>2</v>
+      </c>
+      <c r="AP294">
+        <v>0.8</v>
+      </c>
+      <c r="AQ294">
+        <v>2.07</v>
+      </c>
+      <c r="AR294">
+        <v>1.39</v>
+      </c>
+      <c r="AS294">
+        <v>1.37</v>
+      </c>
+      <c r="AT294">
+        <v>2.76</v>
+      </c>
+      <c r="AU294">
+        <v>5</v>
+      </c>
+      <c r="AV294">
+        <v>9</v>
+      </c>
+      <c r="AW294">
+        <v>7</v>
+      </c>
+      <c r="AX294">
+        <v>10</v>
+      </c>
+      <c r="AY294">
+        <v>13</v>
+      </c>
+      <c r="AZ294">
+        <v>22</v>
+      </c>
+      <c r="BA294">
+        <v>3</v>
+      </c>
+      <c r="BB294">
+        <v>5</v>
+      </c>
+      <c r="BC294">
+        <v>8</v>
+      </c>
+      <c r="BD294">
+        <v>2.38</v>
+      </c>
+      <c r="BE294">
+        <v>8</v>
+      </c>
+      <c r="BF294">
+        <v>1.75</v>
+      </c>
+      <c r="BG294">
+        <v>1.38</v>
+      </c>
+      <c r="BH294">
+        <v>2.71</v>
+      </c>
+      <c r="BI294">
+        <v>1.73</v>
+      </c>
+      <c r="BJ294">
+        <v>2.06</v>
+      </c>
+      <c r="BK294">
+        <v>2.17</v>
+      </c>
+      <c r="BL294">
+        <v>1.65</v>
+      </c>
+      <c r="BM294">
+        <v>2.88</v>
+      </c>
+      <c r="BN294">
+        <v>1.32</v>
+      </c>
+      <c r="BO294">
+        <v>4.1</v>
+      </c>
+      <c r="BP294">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7509881</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F295">
+        <v>30</v>
+      </c>
+      <c r="G295" t="s">
+        <v>75</v>
+      </c>
+      <c r="H295" t="s">
+        <v>70</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295">
+        <v>2</v>
+      </c>
+      <c r="L295">
+        <v>2</v>
+      </c>
+      <c r="M295">
+        <v>1</v>
+      </c>
+      <c r="N295">
+        <v>3</v>
+      </c>
+      <c r="O295" t="s">
+        <v>262</v>
+      </c>
+      <c r="P295" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q295">
+        <v>3.1</v>
+      </c>
+      <c r="R295">
+        <v>2</v>
+      </c>
+      <c r="S295">
+        <v>4</v>
+      </c>
+      <c r="T295">
+        <v>1.53</v>
+      </c>
+      <c r="U295">
+        <v>2.38</v>
+      </c>
+      <c r="V295">
+        <v>3.5</v>
+      </c>
+      <c r="W295">
+        <v>1.29</v>
+      </c>
+      <c r="X295">
+        <v>11</v>
+      </c>
+      <c r="Y295">
+        <v>1.05</v>
+      </c>
+      <c r="Z295">
+        <v>2.53</v>
+      </c>
+      <c r="AA295">
+        <v>2.61</v>
+      </c>
+      <c r="AB295">
+        <v>3.9</v>
+      </c>
+      <c r="AC295">
+        <v>1.08</v>
+      </c>
+      <c r="AD295">
+        <v>6.5</v>
+      </c>
+      <c r="AE295">
+        <v>1.4</v>
+      </c>
+      <c r="AF295">
+        <v>2.7</v>
+      </c>
+      <c r="AG295">
+        <v>2.1</v>
+      </c>
+      <c r="AH295">
+        <v>1.61</v>
+      </c>
+      <c r="AI295">
+        <v>1.91</v>
+      </c>
+      <c r="AJ295">
+        <v>1.91</v>
+      </c>
+      <c r="AK295">
+        <v>1.29</v>
+      </c>
+      <c r="AL295">
+        <v>1.36</v>
+      </c>
+      <c r="AM295">
+        <v>1.6</v>
+      </c>
+      <c r="AN295">
+        <v>1.07</v>
+      </c>
+      <c r="AO295">
+        <v>1</v>
+      </c>
+      <c r="AP295">
+        <v>1.19</v>
+      </c>
+      <c r="AQ295">
+        <v>0.93</v>
+      </c>
+      <c r="AR295">
+        <v>1.44</v>
+      </c>
+      <c r="AS295">
+        <v>1.21</v>
+      </c>
+      <c r="AT295">
+        <v>2.65</v>
+      </c>
+      <c r="AU295">
+        <v>5</v>
+      </c>
+      <c r="AV295">
+        <v>5</v>
+      </c>
+      <c r="AW295">
+        <v>9</v>
+      </c>
+      <c r="AX295">
+        <v>10</v>
+      </c>
+      <c r="AY295">
+        <v>18</v>
+      </c>
+      <c r="AZ295">
+        <v>21</v>
+      </c>
+      <c r="BA295">
+        <v>5</v>
+      </c>
+      <c r="BB295">
+        <v>11</v>
+      </c>
+      <c r="BC295">
+        <v>16</v>
+      </c>
+      <c r="BD295">
+        <v>1.6</v>
+      </c>
+      <c r="BE295">
+        <v>8.5</v>
+      </c>
+      <c r="BF295">
+        <v>2.6</v>
+      </c>
+      <c r="BG295">
+        <v>1.27</v>
+      </c>
+      <c r="BH295">
+        <v>3.14</v>
+      </c>
+      <c r="BI295">
+        <v>1.61</v>
+      </c>
+      <c r="BJ295">
+        <v>2.25</v>
+      </c>
+      <c r="BK295">
+        <v>2.01</v>
+      </c>
+      <c r="BL295">
+        <v>1.79</v>
+      </c>
+      <c r="BM295">
+        <v>2.57</v>
+      </c>
+      <c r="BN295">
+        <v>1.47</v>
+      </c>
+      <c r="BO295">
+        <v>3.34</v>
+      </c>
+      <c r="BP295">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7509882</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45731.45833333334</v>
+      </c>
+      <c r="F296">
+        <v>30</v>
+      </c>
+      <c r="G296" t="s">
+        <v>88</v>
+      </c>
+      <c r="H296" t="s">
+        <v>80</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>2</v>
+      </c>
+      <c r="M296">
+        <v>1</v>
+      </c>
+      <c r="N296">
+        <v>3</v>
+      </c>
+      <c r="O296" t="s">
+        <v>263</v>
+      </c>
+      <c r="P296" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q296">
+        <v>3.4</v>
+      </c>
+      <c r="R296">
+        <v>1.91</v>
+      </c>
+      <c r="S296">
+        <v>3.75</v>
+      </c>
+      <c r="T296">
+        <v>1.57</v>
+      </c>
+      <c r="U296">
+        <v>2.25</v>
+      </c>
+      <c r="V296">
+        <v>3.75</v>
+      </c>
+      <c r="W296">
+        <v>1.25</v>
+      </c>
+      <c r="X296">
+        <v>13</v>
+      </c>
+      <c r="Y296">
+        <v>1.04</v>
+      </c>
+      <c r="Z296">
+        <v>2.7</v>
+      </c>
+      <c r="AA296">
+        <v>2.84</v>
+      </c>
+      <c r="AB296">
+        <v>3.2</v>
+      </c>
+      <c r="AC296">
+        <v>1.09</v>
+      </c>
+      <c r="AD296">
+        <v>6</v>
+      </c>
+      <c r="AE296">
+        <v>1.48</v>
+      </c>
+      <c r="AF296">
+        <v>2.37</v>
+      </c>
+      <c r="AG296">
+        <v>2.5</v>
+      </c>
+      <c r="AH296">
+        <v>1.47</v>
+      </c>
+      <c r="AI296">
+        <v>2.05</v>
+      </c>
+      <c r="AJ296">
+        <v>1.7</v>
+      </c>
+      <c r="AK296">
+        <v>1.36</v>
+      </c>
+      <c r="AL296">
+        <v>1.38</v>
+      </c>
+      <c r="AM296">
+        <v>1.5</v>
+      </c>
+      <c r="AN296">
+        <v>1.71</v>
+      </c>
+      <c r="AO296">
+        <v>0.87</v>
+      </c>
+      <c r="AP296">
+        <v>1.8</v>
+      </c>
+      <c r="AQ296">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR296">
+        <v>1.27</v>
+      </c>
+      <c r="AS296">
+        <v>1.25</v>
+      </c>
+      <c r="AT296">
+        <v>2.52</v>
+      </c>
+      <c r="AU296">
+        <v>5</v>
+      </c>
+      <c r="AV296">
+        <v>3</v>
+      </c>
+      <c r="AW296">
+        <v>9</v>
+      </c>
+      <c r="AX296">
+        <v>8</v>
+      </c>
+      <c r="AY296">
+        <v>16</v>
+      </c>
+      <c r="AZ296">
+        <v>12</v>
+      </c>
+      <c r="BA296">
+        <v>7</v>
+      </c>
+      <c r="BB296">
+        <v>5</v>
+      </c>
+      <c r="BC296">
+        <v>12</v>
+      </c>
+      <c r="BD296">
+        <v>1.8</v>
+      </c>
+      <c r="BE296">
+        <v>8</v>
+      </c>
+      <c r="BF296">
+        <v>2.25</v>
+      </c>
+      <c r="BG296">
+        <v>1.37</v>
+      </c>
+      <c r="BH296">
+        <v>2.75</v>
+      </c>
+      <c r="BI296">
+        <v>1.73</v>
+      </c>
+      <c r="BJ296">
+        <v>2.05</v>
+      </c>
+      <c r="BK296">
+        <v>2.19</v>
+      </c>
+      <c r="BL296">
+        <v>1.64</v>
+      </c>
+      <c r="BM296">
+        <v>2.88</v>
+      </c>
+      <c r="BN296">
+        <v>1.32</v>
+      </c>
+      <c r="BO296">
+        <v>4.05</v>
+      </c>
+      <c r="BP296">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="377">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1506,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP296"/>
+  <dimension ref="A1:BP297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>1.07</v>
@@ -4109,7 +4109,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>2.07</v>
@@ -9259,7 +9259,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR38">
         <v>1.18</v>
@@ -10492,7 +10492,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -12967,7 +12967,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ56">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -14612,7 +14612,7 @@
         <v>0.5</v>
       </c>
       <c r="AP64">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>0.79</v>
@@ -18117,7 +18117,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18320,7 +18320,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ82">
         <v>1.29</v>
@@ -21001,7 +21001,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -22440,7 +22440,7 @@
         <v>0.6</v>
       </c>
       <c r="AP102">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ102">
         <v>0.5</v>
@@ -24706,7 +24706,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ113">
         <v>0.93</v>
@@ -25533,7 +25533,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -28829,7 +28829,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ133">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR133">
         <v>1.46</v>
@@ -29856,7 +29856,7 @@
         <v>1.29</v>
       </c>
       <c r="AP138">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
         <v>1.47</v>
@@ -32946,7 +32946,7 @@
         <v>0.71</v>
       </c>
       <c r="AP153">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -33567,7 +33567,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ156">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -37272,7 +37272,7 @@
         <v>0.75</v>
       </c>
       <c r="AP174">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ174">
         <v>1.13</v>
@@ -40365,7 +40365,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ189">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR189">
         <v>1.33</v>
@@ -41186,7 +41186,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193">
         <v>1.5</v>
@@ -42425,7 +42425,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ199">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR199">
         <v>1.22</v>
@@ -46130,7 +46130,7 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ217">
         <v>0.93</v>
@@ -48605,7 +48605,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ229">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -51074,7 +51074,7 @@
         <v>0.91</v>
       </c>
       <c r="AP241">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ241">
         <v>1</v>
@@ -51283,7 +51283,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ242">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -54167,7 +54167,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ256">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR256">
         <v>1.38</v>
@@ -54370,7 +54370,7 @@
         <v>1.67</v>
       </c>
       <c r="AP257">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ257">
         <v>1.67</v>
@@ -57875,7 +57875,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ274">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR274">
         <v>1.43</v>
@@ -59314,7 +59314,7 @@
         <v>0.92</v>
       </c>
       <c r="AP281">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ281">
         <v>0.93</v>
@@ -62483,6 +62483,212 @@
       </c>
       <c r="BP296">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7509877</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45731.64583333334</v>
+      </c>
+      <c r="F297">
+        <v>30</v>
+      </c>
+      <c r="G297" t="s">
+        <v>71</v>
+      </c>
+      <c r="H297" t="s">
+        <v>74</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+      <c r="M297">
+        <v>0</v>
+      </c>
+      <c r="N297">
+        <v>0</v>
+      </c>
+      <c r="O297" t="s">
+        <v>102</v>
+      </c>
+      <c r="P297" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q297">
+        <v>3.1</v>
+      </c>
+      <c r="R297">
+        <v>2</v>
+      </c>
+      <c r="S297">
+        <v>3.75</v>
+      </c>
+      <c r="T297">
+        <v>1.5</v>
+      </c>
+      <c r="U297">
+        <v>2.5</v>
+      </c>
+      <c r="V297">
+        <v>3.4</v>
+      </c>
+      <c r="W297">
+        <v>1.3</v>
+      </c>
+      <c r="X297">
+        <v>10</v>
+      </c>
+      <c r="Y297">
+        <v>1.06</v>
+      </c>
+      <c r="Z297">
+        <v>2.53</v>
+      </c>
+      <c r="AA297">
+        <v>3.25</v>
+      </c>
+      <c r="AB297">
+        <v>3.02</v>
+      </c>
+      <c r="AC297">
+        <v>1.06</v>
+      </c>
+      <c r="AD297">
+        <v>7.5</v>
+      </c>
+      <c r="AE297">
+        <v>1.38</v>
+      </c>
+      <c r="AF297">
+        <v>2.8</v>
+      </c>
+      <c r="AG297">
+        <v>2.05</v>
+      </c>
+      <c r="AH297">
+        <v>1.65</v>
+      </c>
+      <c r="AI297">
+        <v>1.95</v>
+      </c>
+      <c r="AJ297">
+        <v>1.8</v>
+      </c>
+      <c r="AK297">
+        <v>1.36</v>
+      </c>
+      <c r="AL297">
+        <v>1.36</v>
+      </c>
+      <c r="AM297">
+        <v>1.53</v>
+      </c>
+      <c r="AN297">
+        <v>1.53</v>
+      </c>
+      <c r="AO297">
+        <v>0.5</v>
+      </c>
+      <c r="AP297">
+        <v>1.5</v>
+      </c>
+      <c r="AQ297">
+        <v>0.53</v>
+      </c>
+      <c r="AR297">
+        <v>1.35</v>
+      </c>
+      <c r="AS297">
+        <v>1.2</v>
+      </c>
+      <c r="AT297">
+        <v>2.55</v>
+      </c>
+      <c r="AU297">
+        <v>4</v>
+      </c>
+      <c r="AV297">
+        <v>5</v>
+      </c>
+      <c r="AW297">
+        <v>8</v>
+      </c>
+      <c r="AX297">
+        <v>8</v>
+      </c>
+      <c r="AY297">
+        <v>13</v>
+      </c>
+      <c r="AZ297">
+        <v>17</v>
+      </c>
+      <c r="BA297">
+        <v>8</v>
+      </c>
+      <c r="BB297">
+        <v>4</v>
+      </c>
+      <c r="BC297">
+        <v>12</v>
+      </c>
+      <c r="BD297">
+        <v>1.65</v>
+      </c>
+      <c r="BE297">
+        <v>8.5</v>
+      </c>
+      <c r="BF297">
+        <v>2.5</v>
+      </c>
+      <c r="BG297">
+        <v>1.33</v>
+      </c>
+      <c r="BH297">
+        <v>2.83</v>
+      </c>
+      <c r="BI297">
+        <v>1.69</v>
+      </c>
+      <c r="BJ297">
+        <v>2.11</v>
+      </c>
+      <c r="BK297">
+        <v>2.12</v>
+      </c>
+      <c r="BL297">
+        <v>1.68</v>
+      </c>
+      <c r="BM297">
+        <v>2.78</v>
+      </c>
+      <c r="BN297">
+        <v>1.36</v>
+      </c>
+      <c r="BO297">
+        <v>3.84</v>
+      </c>
+      <c r="BP297">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="383">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -808,6 +808,18 @@
     <t>['10', '64']</t>
   </si>
   <si>
+    <t>['12', '49', '65']</t>
+  </si>
+  <si>
+    <t>['33', '60']</t>
+  </si>
+  <si>
+    <t>['59', '73']</t>
+  </si>
+  <si>
+    <t>['20', '46', '54', '68']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1145,6 +1157,12 @@
   </si>
   <si>
     <t>['15', '46']</t>
+  </si>
+  <si>
+    <t>['67', '74']</t>
+  </si>
+  <si>
+    <t>['17', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP297"/>
+  <dimension ref="A1:BP301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1968,7 +1986,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2252,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ4">
         <v>0.8100000000000001</v>
@@ -2380,7 +2398,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2458,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2792,7 +2810,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3079,7 +3097,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3204,7 +3222,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3282,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3410,7 +3428,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3488,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ10">
         <v>2.07</v>
@@ -3822,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -4028,7 +4046,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4106,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13">
         <v>0.53</v>
@@ -4234,7 +4252,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4727,7 +4745,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ16">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4852,7 +4870,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5136,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18">
         <v>1.13</v>
@@ -5470,7 +5488,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5551,7 +5569,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ20">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5754,7 +5772,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21">
         <v>1.07</v>
@@ -5882,7 +5900,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6294,7 +6312,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6784,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26">
         <v>0.93</v>
@@ -6912,7 +6930,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7817,7 +7835,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ31">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -8148,7 +8166,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8432,7 +8450,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ34">
         <v>0.93</v>
@@ -8560,7 +8578,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8766,7 +8784,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -8844,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ36">
         <v>0.93</v>
@@ -9465,7 +9483,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ39">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9590,7 +9608,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9796,7 +9814,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9874,10 +9892,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR41">
         <v>1.16</v>
@@ -10002,7 +10020,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10495,7 +10513,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10826,7 +10844,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11238,7 +11256,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11316,7 +11334,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
         <v>1.13</v>
@@ -11444,7 +11462,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11856,7 +11874,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12062,7 +12080,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12140,7 +12158,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ52">
         <v>1.67</v>
@@ -12758,7 +12776,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ55">
         <v>0.93</v>
@@ -12964,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56">
         <v>0.53</v>
@@ -13504,7 +13522,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13916,7 +13934,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -13997,7 +14015,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR61">
         <v>1.42</v>
@@ -14122,7 +14140,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14615,7 +14633,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14946,7 +14964,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15027,7 +15045,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ66">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15358,7 +15376,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15770,7 +15788,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15848,7 +15866,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ70">
         <v>1.13</v>
@@ -15976,7 +15994,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16182,7 +16200,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16388,7 +16406,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16469,7 +16487,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16594,7 +16612,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17006,7 +17024,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17084,7 +17102,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17212,7 +17230,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17418,7 +17436,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17624,7 +17642,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17830,7 +17848,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17908,7 +17926,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ80">
         <v>0.8100000000000001</v>
@@ -18448,7 +18466,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18526,7 +18544,7 @@
         <v>1.33</v>
       </c>
       <c r="AP83">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ83">
         <v>1.47</v>
@@ -18654,7 +18672,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18941,7 +18959,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ85">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -19066,7 +19084,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19272,7 +19290,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19478,7 +19496,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19765,7 +19783,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -19968,7 +19986,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20096,7 +20114,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -21822,7 +21840,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ99">
         <v>1.13</v>
@@ -22237,7 +22255,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ101">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22443,7 +22461,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22774,7 +22792,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22980,7 +22998,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23264,10 +23282,10 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -23676,7 +23694,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -24294,7 +24312,7 @@
         <v>0.75</v>
       </c>
       <c r="AP111">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ111">
         <v>1.29</v>
@@ -24628,7 +24646,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25118,7 +25136,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -25452,7 +25470,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25658,7 +25676,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26357,7 +26375,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ121">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26482,7 +26500,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26766,7 +26784,7 @@
         <v>2</v>
       </c>
       <c r="AP123">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ123">
         <v>2.07</v>
@@ -26972,7 +26990,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ124">
         <v>0.93</v>
@@ -27181,7 +27199,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ125">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR125">
         <v>1.55</v>
@@ -27306,7 +27324,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27387,7 +27405,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ126">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -27718,7 +27736,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27924,7 +27942,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28130,7 +28148,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28208,7 +28226,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ130">
         <v>1.29</v>
@@ -28336,7 +28354,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28542,7 +28560,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29366,7 +29384,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29444,10 +29462,10 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ136">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29778,7 +29796,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30396,7 +30414,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30602,7 +30620,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30680,7 +30698,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ142">
         <v>2.07</v>
@@ -30808,7 +30826,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -31014,7 +31032,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31092,7 +31110,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ144">
         <v>1.67</v>
@@ -31426,7 +31444,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -32044,7 +32062,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32122,10 +32140,10 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ149">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32250,7 +32268,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32537,7 +32555,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ151">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR151">
         <v>1.67</v>
@@ -32662,7 +32680,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33280,7 +33298,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33692,7 +33710,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33976,7 +33994,7 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
         <v>0.93</v>
@@ -34104,7 +34122,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34516,7 +34534,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34800,7 +34818,7 @@
         <v>1.43</v>
       </c>
       <c r="AP162">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ162">
         <v>1.14</v>
@@ -34928,7 +34946,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35006,10 +35024,10 @@
         <v>0.38</v>
       </c>
       <c r="AP163">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ163">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35212,7 +35230,7 @@
         <v>0.63</v>
       </c>
       <c r="AP164">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ164">
         <v>0.8100000000000001</v>
@@ -35340,7 +35358,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35627,7 +35645,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ166">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35958,7 +35976,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36245,7 +36263,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ169">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36576,7 +36594,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37481,7 +37499,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ175">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -38018,7 +38036,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38224,7 +38242,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38302,7 +38320,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ179">
         <v>1.5</v>
@@ -38920,7 +38938,7 @@
         <v>2.33</v>
       </c>
       <c r="AP182">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ182">
         <v>2.07</v>
@@ -39126,7 +39144,7 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ183">
         <v>1.07</v>
@@ -39254,7 +39272,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39335,7 +39353,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ184">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39460,7 +39478,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39538,7 +39556,7 @@
         <v>1</v>
       </c>
       <c r="AP185">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ185">
         <v>1.47</v>
@@ -40078,7 +40096,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40696,7 +40714,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40777,7 +40795,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ191">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR191">
         <v>1.37</v>
@@ -40902,7 +40920,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41601,7 +41619,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ195">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41932,7 +41950,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42422,7 +42440,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ199">
         <v>0.53</v>
@@ -42550,7 +42568,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42962,7 +42980,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43246,7 +43264,7 @@
         <v>1.11</v>
       </c>
       <c r="AP203">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ203">
         <v>1.14</v>
@@ -43374,7 +43392,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43452,7 +43470,7 @@
         <v>1.11</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ204">
         <v>1.29</v>
@@ -43992,7 +44010,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44073,7 +44091,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ207">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -44198,7 +44216,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44894,10 +44912,10 @@
         <v>0.6</v>
       </c>
       <c r="AP211">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR211">
         <v>1.37</v>
@@ -45022,7 +45040,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45228,7 +45246,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45309,7 +45327,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ213">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR213">
         <v>1.3</v>
@@ -45515,7 +45533,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ214">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR214">
         <v>1.56</v>
@@ -45846,7 +45864,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46052,7 +46070,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46336,7 +46354,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ218">
         <v>1.47</v>
@@ -46670,7 +46688,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46876,7 +46894,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47082,7 +47100,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47369,7 +47387,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ223">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR223">
         <v>1.25</v>
@@ -47494,7 +47512,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47906,7 +47924,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48112,7 +48130,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48318,7 +48336,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48602,7 +48620,7 @@
         <v>0.6</v>
       </c>
       <c r="AP229">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ229">
         <v>0.53</v>
@@ -48808,7 +48826,7 @@
         <v>1.09</v>
       </c>
       <c r="AP230">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ230">
         <v>1.13</v>
@@ -48936,7 +48954,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49142,7 +49160,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49429,7 +49447,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ233">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR233">
         <v>1.42</v>
@@ -49760,7 +49778,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49966,7 +49984,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50044,7 +50062,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ236">
         <v>1</v>
@@ -50253,7 +50271,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ237">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR237">
         <v>1.46</v>
@@ -50584,7 +50602,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50868,7 +50886,7 @@
         <v>1.09</v>
       </c>
       <c r="AP240">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ240">
         <v>0.93</v>
@@ -50996,7 +51014,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51486,7 +51504,7 @@
         <v>1.33</v>
       </c>
       <c r="AP243">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ243">
         <v>1.47</v>
@@ -51614,7 +51632,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -52107,7 +52125,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ246">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR246">
         <v>1.59</v>
@@ -52722,7 +52740,7 @@
         <v>0.67</v>
       </c>
       <c r="AP249">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ249">
         <v>1</v>
@@ -52850,7 +52868,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53340,7 +53358,7 @@
         <v>1.46</v>
       </c>
       <c r="AP252">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ252">
         <v>1.47</v>
@@ -53468,7 +53486,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53546,7 +53564,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ253">
         <v>0.93</v>
@@ -54785,7 +54803,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ259">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR259">
         <v>1.26</v>
@@ -54910,7 +54928,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -54991,7 +55009,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ260">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR260">
         <v>1.76</v>
@@ -55528,7 +55546,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -56018,7 +56036,7 @@
         <v>1.15</v>
       </c>
       <c r="AP265">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ265">
         <v>1.07</v>
@@ -56146,7 +56164,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56224,10 +56242,10 @@
         <v>0.46</v>
       </c>
       <c r="AP266">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ266">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR266">
         <v>1.3</v>
@@ -56352,7 +56370,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56558,7 +56576,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -57176,7 +57194,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57460,7 +57478,7 @@
         <v>1.57</v>
       </c>
       <c r="AP272">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ272">
         <v>1.5</v>
@@ -57588,7 +57606,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -58000,7 +58018,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58081,7 +58099,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ275">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AR275">
         <v>1.45</v>
@@ -58824,7 +58842,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -58902,7 +58920,7 @@
         <v>1</v>
       </c>
       <c r="AP279">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ279">
         <v>0.93</v>
@@ -59111,7 +59129,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ280">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR280">
         <v>1.4</v>
@@ -59236,7 +59254,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60678,7 +60696,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -61090,7 +61108,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61296,7 +61314,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61502,7 +61520,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61914,7 +61932,7 @@
         <v>90</v>
       </c>
       <c r="P294" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q294">
         <v>4.5</v>
@@ -62689,6 +62707,830 @@
       </c>
       <c r="BP297">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7509884</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F298">
+        <v>30</v>
+      </c>
+      <c r="G298" t="s">
+        <v>73</v>
+      </c>
+      <c r="H298" t="s">
+        <v>85</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298">
+        <v>2</v>
+      </c>
+      <c r="L298">
+        <v>3</v>
+      </c>
+      <c r="M298">
+        <v>1</v>
+      </c>
+      <c r="N298">
+        <v>4</v>
+      </c>
+      <c r="O298" t="s">
+        <v>264</v>
+      </c>
+      <c r="P298" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q298">
+        <v>2.25</v>
+      </c>
+      <c r="R298">
+        <v>2.2</v>
+      </c>
+      <c r="S298">
+        <v>5.5</v>
+      </c>
+      <c r="T298">
+        <v>1.4</v>
+      </c>
+      <c r="U298">
+        <v>2.75</v>
+      </c>
+      <c r="V298">
+        <v>3</v>
+      </c>
+      <c r="W298">
+        <v>1.36</v>
+      </c>
+      <c r="X298">
+        <v>8</v>
+      </c>
+      <c r="Y298">
+        <v>1.08</v>
+      </c>
+      <c r="Z298">
+        <v>1.68</v>
+      </c>
+      <c r="AA298">
+        <v>3.93</v>
+      </c>
+      <c r="AB298">
+        <v>5.4</v>
+      </c>
+      <c r="AC298">
+        <v>1.03</v>
+      </c>
+      <c r="AD298">
+        <v>9</v>
+      </c>
+      <c r="AE298">
+        <v>1.3</v>
+      </c>
+      <c r="AF298">
+        <v>3.2</v>
+      </c>
+      <c r="AG298">
+        <v>2.01</v>
+      </c>
+      <c r="AH298">
+        <v>1.81</v>
+      </c>
+      <c r="AI298">
+        <v>1.95</v>
+      </c>
+      <c r="AJ298">
+        <v>1.8</v>
+      </c>
+      <c r="AK298">
+        <v>1.16</v>
+      </c>
+      <c r="AL298">
+        <v>1.25</v>
+      </c>
+      <c r="AM298">
+        <v>2.15</v>
+      </c>
+      <c r="AN298">
+        <v>2.36</v>
+      </c>
+      <c r="AO298">
+        <v>0.67</v>
+      </c>
+      <c r="AP298">
+        <v>2.4</v>
+      </c>
+      <c r="AQ298">
+        <v>0.63</v>
+      </c>
+      <c r="AR298">
+        <v>1.5</v>
+      </c>
+      <c r="AS298">
+        <v>1.33</v>
+      </c>
+      <c r="AT298">
+        <v>2.83</v>
+      </c>
+      <c r="AU298">
+        <v>9</v>
+      </c>
+      <c r="AV298">
+        <v>0</v>
+      </c>
+      <c r="AW298">
+        <v>11</v>
+      </c>
+      <c r="AX298">
+        <v>7</v>
+      </c>
+      <c r="AY298">
+        <v>23</v>
+      </c>
+      <c r="AZ298">
+        <v>8</v>
+      </c>
+      <c r="BA298">
+        <v>9</v>
+      </c>
+      <c r="BB298">
+        <v>1</v>
+      </c>
+      <c r="BC298">
+        <v>10</v>
+      </c>
+      <c r="BD298">
+        <v>1.57</v>
+      </c>
+      <c r="BE298">
+        <v>8.5</v>
+      </c>
+      <c r="BF298">
+        <v>2.7</v>
+      </c>
+      <c r="BG298">
+        <v>1.39</v>
+      </c>
+      <c r="BH298">
+        <v>2.67</v>
+      </c>
+      <c r="BI298">
+        <v>1.76</v>
+      </c>
+      <c r="BJ298">
+        <v>2.02</v>
+      </c>
+      <c r="BK298">
+        <v>2.24</v>
+      </c>
+      <c r="BL298">
+        <v>1.61</v>
+      </c>
+      <c r="BM298">
+        <v>2.97</v>
+      </c>
+      <c r="BN298">
+        <v>1.3</v>
+      </c>
+      <c r="BO298">
+        <v>4.2</v>
+      </c>
+      <c r="BP298">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7509885</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F299">
+        <v>30</v>
+      </c>
+      <c r="G299" t="s">
+        <v>77</v>
+      </c>
+      <c r="H299" t="s">
+        <v>81</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>1</v>
+      </c>
+      <c r="L299">
+        <v>2</v>
+      </c>
+      <c r="M299">
+        <v>2</v>
+      </c>
+      <c r="N299">
+        <v>4</v>
+      </c>
+      <c r="O299" t="s">
+        <v>265</v>
+      </c>
+      <c r="P299" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q299">
+        <v>3.5</v>
+      </c>
+      <c r="R299">
+        <v>1.91</v>
+      </c>
+      <c r="S299">
+        <v>3.75</v>
+      </c>
+      <c r="T299">
+        <v>1.57</v>
+      </c>
+      <c r="U299">
+        <v>2.25</v>
+      </c>
+      <c r="V299">
+        <v>3.75</v>
+      </c>
+      <c r="W299">
+        <v>1.25</v>
+      </c>
+      <c r="X299">
+        <v>13</v>
+      </c>
+      <c r="Y299">
+        <v>1.04</v>
+      </c>
+      <c r="Z299">
+        <v>2.67</v>
+      </c>
+      <c r="AA299">
+        <v>2.9</v>
+      </c>
+      <c r="AB299">
+        <v>3.18</v>
+      </c>
+      <c r="AC299">
+        <v>1.09</v>
+      </c>
+      <c r="AD299">
+        <v>6</v>
+      </c>
+      <c r="AE299">
+        <v>1.48</v>
+      </c>
+      <c r="AF299">
+        <v>2.5</v>
+      </c>
+      <c r="AG299">
+        <v>2.37</v>
+      </c>
+      <c r="AH299">
+        <v>1.48</v>
+      </c>
+      <c r="AI299">
+        <v>2.05</v>
+      </c>
+      <c r="AJ299">
+        <v>1.7</v>
+      </c>
+      <c r="AK299">
+        <v>1.38</v>
+      </c>
+      <c r="AL299">
+        <v>1.39</v>
+      </c>
+      <c r="AM299">
+        <v>1.46</v>
+      </c>
+      <c r="AN299">
+        <v>1.21</v>
+      </c>
+      <c r="AO299">
+        <v>0.93</v>
+      </c>
+      <c r="AP299">
+        <v>1.2</v>
+      </c>
+      <c r="AQ299">
+        <v>0.93</v>
+      </c>
+      <c r="AR299">
+        <v>1.31</v>
+      </c>
+      <c r="AS299">
+        <v>1.28</v>
+      </c>
+      <c r="AT299">
+        <v>2.59</v>
+      </c>
+      <c r="AU299">
+        <v>7</v>
+      </c>
+      <c r="AV299">
+        <v>5</v>
+      </c>
+      <c r="AW299">
+        <v>5</v>
+      </c>
+      <c r="AX299">
+        <v>8</v>
+      </c>
+      <c r="AY299">
+        <v>15</v>
+      </c>
+      <c r="AZ299">
+        <v>16</v>
+      </c>
+      <c r="BA299">
+        <v>2</v>
+      </c>
+      <c r="BB299">
+        <v>8</v>
+      </c>
+      <c r="BC299">
+        <v>10</v>
+      </c>
+      <c r="BD299">
+        <v>1.98</v>
+      </c>
+      <c r="BE299">
+        <v>6.25</v>
+      </c>
+      <c r="BF299">
+        <v>2.38</v>
+      </c>
+      <c r="BG299">
+        <v>1.34</v>
+      </c>
+      <c r="BH299">
+        <v>2.78</v>
+      </c>
+      <c r="BI299">
+        <v>1.7</v>
+      </c>
+      <c r="BJ299">
+        <v>2.1</v>
+      </c>
+      <c r="BK299">
+        <v>2.13</v>
+      </c>
+      <c r="BL299">
+        <v>1.68</v>
+      </c>
+      <c r="BM299">
+        <v>2.84</v>
+      </c>
+      <c r="BN299">
+        <v>1.35</v>
+      </c>
+      <c r="BO299">
+        <v>3.92</v>
+      </c>
+      <c r="BP299">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7509886</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45732.45833333334</v>
+      </c>
+      <c r="F300">
+        <v>30</v>
+      </c>
+      <c r="G300" t="s">
+        <v>72</v>
+      </c>
+      <c r="H300" t="s">
+        <v>86</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>1</v>
+      </c>
+      <c r="K300">
+        <v>1</v>
+      </c>
+      <c r="L300">
+        <v>2</v>
+      </c>
+      <c r="M300">
+        <v>2</v>
+      </c>
+      <c r="N300">
+        <v>4</v>
+      </c>
+      <c r="O300" t="s">
+        <v>266</v>
+      </c>
+      <c r="P300" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q300">
+        <v>3</v>
+      </c>
+      <c r="R300">
+        <v>1.95</v>
+      </c>
+      <c r="S300">
+        <v>4</v>
+      </c>
+      <c r="T300">
+        <v>1.53</v>
+      </c>
+      <c r="U300">
+        <v>2.38</v>
+      </c>
+      <c r="V300">
+        <v>3.5</v>
+      </c>
+      <c r="W300">
+        <v>1.29</v>
+      </c>
+      <c r="X300">
+        <v>11</v>
+      </c>
+      <c r="Y300">
+        <v>1.05</v>
+      </c>
+      <c r="Z300">
+        <v>2.33</v>
+      </c>
+      <c r="AA300">
+        <v>2.99</v>
+      </c>
+      <c r="AB300">
+        <v>3.68</v>
+      </c>
+      <c r="AC300">
+        <v>1.08</v>
+      </c>
+      <c r="AD300">
+        <v>6.5</v>
+      </c>
+      <c r="AE300">
+        <v>1.48</v>
+      </c>
+      <c r="AF300">
+        <v>2.37</v>
+      </c>
+      <c r="AG300">
+        <v>2.32</v>
+      </c>
+      <c r="AH300">
+        <v>1.54</v>
+      </c>
+      <c r="AI300">
+        <v>2</v>
+      </c>
+      <c r="AJ300">
+        <v>1.75</v>
+      </c>
+      <c r="AK300">
+        <v>1.3</v>
+      </c>
+      <c r="AL300">
+        <v>1.36</v>
+      </c>
+      <c r="AM300">
+        <v>1.61</v>
+      </c>
+      <c r="AN300">
+        <v>1.14</v>
+      </c>
+      <c r="AO300">
+        <v>0.5</v>
+      </c>
+      <c r="AP300">
+        <v>1.13</v>
+      </c>
+      <c r="AQ300">
+        <v>0.53</v>
+      </c>
+      <c r="AR300">
+        <v>1.47</v>
+      </c>
+      <c r="AS300">
+        <v>1.18</v>
+      </c>
+      <c r="AT300">
+        <v>2.65</v>
+      </c>
+      <c r="AU300">
+        <v>5</v>
+      </c>
+      <c r="AV300">
+        <v>4</v>
+      </c>
+      <c r="AW300">
+        <v>5</v>
+      </c>
+      <c r="AX300">
+        <v>4</v>
+      </c>
+      <c r="AY300">
+        <v>11</v>
+      </c>
+      <c r="AZ300">
+        <v>9</v>
+      </c>
+      <c r="BA300">
+        <v>4</v>
+      </c>
+      <c r="BB300">
+        <v>7</v>
+      </c>
+      <c r="BC300">
+        <v>11</v>
+      </c>
+      <c r="BD300">
+        <v>1.79</v>
+      </c>
+      <c r="BE300">
+        <v>6.5</v>
+      </c>
+      <c r="BF300">
+        <v>2.68</v>
+      </c>
+      <c r="BG300">
+        <v>1.32</v>
+      </c>
+      <c r="BH300">
+        <v>2.88</v>
+      </c>
+      <c r="BI300">
+        <v>1.67</v>
+      </c>
+      <c r="BJ300">
+        <v>2.14</v>
+      </c>
+      <c r="BK300">
+        <v>2.09</v>
+      </c>
+      <c r="BL300">
+        <v>1.7</v>
+      </c>
+      <c r="BM300">
+        <v>2.71</v>
+      </c>
+      <c r="BN300">
+        <v>1.38</v>
+      </c>
+      <c r="BO300">
+        <v>3.76</v>
+      </c>
+      <c r="BP300">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7509878</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45732.55208333334</v>
+      </c>
+      <c r="F301">
+        <v>30</v>
+      </c>
+      <c r="G301" t="s">
+        <v>78</v>
+      </c>
+      <c r="H301" t="s">
+        <v>79</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>1</v>
+      </c>
+      <c r="L301">
+        <v>4</v>
+      </c>
+      <c r="M301">
+        <v>0</v>
+      </c>
+      <c r="N301">
+        <v>4</v>
+      </c>
+      <c r="O301" t="s">
+        <v>267</v>
+      </c>
+      <c r="P301" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q301">
+        <v>2.75</v>
+      </c>
+      <c r="R301">
+        <v>2.05</v>
+      </c>
+      <c r="S301">
+        <v>4.33</v>
+      </c>
+      <c r="T301">
+        <v>1.5</v>
+      </c>
+      <c r="U301">
+        <v>2.5</v>
+      </c>
+      <c r="V301">
+        <v>3.4</v>
+      </c>
+      <c r="W301">
+        <v>1.3</v>
+      </c>
+      <c r="X301">
+        <v>10</v>
+      </c>
+      <c r="Y301">
+        <v>1.06</v>
+      </c>
+      <c r="Z301">
+        <v>2.12</v>
+      </c>
+      <c r="AA301">
+        <v>3.36</v>
+      </c>
+      <c r="AB301">
+        <v>3.77</v>
+      </c>
+      <c r="AC301">
+        <v>1.05</v>
+      </c>
+      <c r="AD301">
+        <v>8</v>
+      </c>
+      <c r="AE301">
+        <v>1.36</v>
+      </c>
+      <c r="AF301">
+        <v>2.9</v>
+      </c>
+      <c r="AG301">
+        <v>2.05</v>
+      </c>
+      <c r="AH301">
+        <v>1.61</v>
+      </c>
+      <c r="AI301">
+        <v>1.95</v>
+      </c>
+      <c r="AJ301">
+        <v>1.8</v>
+      </c>
+      <c r="AK301">
+        <v>1.29</v>
+      </c>
+      <c r="AL301">
+        <v>1.31</v>
+      </c>
+      <c r="AM301">
+        <v>1.7</v>
+      </c>
+      <c r="AN301">
+        <v>1.67</v>
+      </c>
+      <c r="AO301">
+        <v>0.79</v>
+      </c>
+      <c r="AP301">
+        <v>1.75</v>
+      </c>
+      <c r="AQ301">
+        <v>0.73</v>
+      </c>
+      <c r="AR301">
+        <v>1.38</v>
+      </c>
+      <c r="AS301">
+        <v>1.4</v>
+      </c>
+      <c r="AT301">
+        <v>2.78</v>
+      </c>
+      <c r="AU301">
+        <v>6</v>
+      </c>
+      <c r="AV301">
+        <v>4</v>
+      </c>
+      <c r="AW301">
+        <v>3</v>
+      </c>
+      <c r="AX301">
+        <v>5</v>
+      </c>
+      <c r="AY301">
+        <v>9</v>
+      </c>
+      <c r="AZ301">
+        <v>10</v>
+      </c>
+      <c r="BA301">
+        <v>1</v>
+      </c>
+      <c r="BB301">
+        <v>1</v>
+      </c>
+      <c r="BC301">
+        <v>2</v>
+      </c>
+      <c r="BD301">
+        <v>1.72</v>
+      </c>
+      <c r="BE301">
+        <v>6.6</v>
+      </c>
+      <c r="BF301">
+        <v>2.84</v>
+      </c>
+      <c r="BG301">
+        <v>1.27</v>
+      </c>
+      <c r="BH301">
+        <v>3.14</v>
+      </c>
+      <c r="BI301">
+        <v>1.59</v>
+      </c>
+      <c r="BJ301">
+        <v>2.29</v>
+      </c>
+      <c r="BK301">
+        <v>1.98</v>
+      </c>
+      <c r="BL301">
+        <v>1.81</v>
+      </c>
+      <c r="BM301">
+        <v>2.52</v>
+      </c>
+      <c r="BN301">
+        <v>1.48</v>
+      </c>
+      <c r="BO301">
+        <v>3.34</v>
+      </c>
+      <c r="BP301">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="383">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1524,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP301"/>
+  <dimension ref="A1:BP302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -6805,7 +6805,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ26">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR26">
         <v>1.28</v>
@@ -8865,7 +8865,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR36">
         <v>1.54</v>
@@ -9686,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -12779,7 +12779,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ55">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR55">
         <v>1.42</v>
@@ -14012,7 +14012,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ61">
         <v>0.53</v>
@@ -16896,7 +16896,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ75">
         <v>0.93</v>
@@ -17517,7 +17517,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ78">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR78">
         <v>1.18</v>
@@ -20398,7 +20398,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ92">
         <v>1.14</v>
@@ -20607,7 +20607,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ93">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR93">
         <v>1.54</v>
@@ -24518,7 +24518,7 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ112">
         <v>0.8100000000000001</v>
@@ -26169,7 +26169,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ120">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR120">
         <v>1.28</v>
@@ -29053,7 +29053,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ134">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -30080,7 +30080,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ139">
         <v>1.13</v>
@@ -33997,7 +33997,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR158">
         <v>1.22</v>
@@ -34406,7 +34406,7 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ160">
         <v>1.47</v>
@@ -36881,7 +36881,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ172">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR172">
         <v>1.72</v>
@@ -39350,7 +39350,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ184">
         <v>0.63</v>
@@ -41001,7 +41001,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ192">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR192">
         <v>1.54</v>
@@ -43882,7 +43882,7 @@
         <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ206">
         <v>1.07</v>
@@ -46151,7 +46151,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ217">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -47178,7 +47178,7 @@
         <v>2.18</v>
       </c>
       <c r="AP222">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ222">
         <v>2.07</v>
@@ -50683,7 +50683,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ239">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR239">
         <v>1.34</v>
@@ -52946,7 +52946,7 @@
         <v>1</v>
       </c>
       <c r="AP250">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ250">
         <v>1.13</v>
@@ -53979,7 +53979,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ255">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR255">
         <v>1.73</v>
@@ -56860,7 +56860,7 @@
         <v>1.25</v>
       </c>
       <c r="AP269">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ269">
         <v>1.29</v>
@@ -58717,7 +58717,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ278">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR278">
         <v>1.76</v>
@@ -61186,7 +61186,7 @@
         <v>1.57</v>
       </c>
       <c r="AP290">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AQ290">
         <v>1.47</v>
@@ -62219,7 +62219,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ295">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR295">
         <v>1.44</v>
@@ -63531,6 +63531,212 @@
       </c>
       <c r="BP301">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7509896</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45744.6875</v>
+      </c>
+      <c r="F302">
+        <v>31</v>
+      </c>
+      <c r="G302" t="s">
+        <v>83</v>
+      </c>
+      <c r="H302" t="s">
+        <v>70</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>1</v>
+      </c>
+      <c r="K302">
+        <v>1</v>
+      </c>
+      <c r="L302">
+        <v>0</v>
+      </c>
+      <c r="M302">
+        <v>1</v>
+      </c>
+      <c r="N302">
+        <v>1</v>
+      </c>
+      <c r="O302" t="s">
+        <v>102</v>
+      </c>
+      <c r="P302" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q302">
+        <v>2.1</v>
+      </c>
+      <c r="R302">
+        <v>2.2</v>
+      </c>
+      <c r="S302">
+        <v>6.5</v>
+      </c>
+      <c r="T302">
+        <v>1.4</v>
+      </c>
+      <c r="U302">
+        <v>2.75</v>
+      </c>
+      <c r="V302">
+        <v>3</v>
+      </c>
+      <c r="W302">
+        <v>1.36</v>
+      </c>
+      <c r="X302">
+        <v>8</v>
+      </c>
+      <c r="Y302">
+        <v>1.08</v>
+      </c>
+      <c r="Z302">
+        <v>1.55</v>
+      </c>
+      <c r="AA302">
+        <v>4.2</v>
+      </c>
+      <c r="AB302">
+        <v>6.6</v>
+      </c>
+      <c r="AC302">
+        <v>0</v>
+      </c>
+      <c r="AD302">
+        <v>0</v>
+      </c>
+      <c r="AE302">
+        <v>0</v>
+      </c>
+      <c r="AF302">
+        <v>0</v>
+      </c>
+      <c r="AG302">
+        <v>2.01</v>
+      </c>
+      <c r="AH302">
+        <v>1.81</v>
+      </c>
+      <c r="AI302">
+        <v>2.05</v>
+      </c>
+      <c r="AJ302">
+        <v>1.7</v>
+      </c>
+      <c r="AK302">
+        <v>0</v>
+      </c>
+      <c r="AL302">
+        <v>0</v>
+      </c>
+      <c r="AM302">
+        <v>0</v>
+      </c>
+      <c r="AN302">
+        <v>2.21</v>
+      </c>
+      <c r="AO302">
+        <v>0.93</v>
+      </c>
+      <c r="AP302">
+        <v>2.07</v>
+      </c>
+      <c r="AQ302">
+        <v>1.06</v>
+      </c>
+      <c r="AR302">
+        <v>1.88</v>
+      </c>
+      <c r="AS302">
+        <v>1.24</v>
+      </c>
+      <c r="AT302">
+        <v>3.12</v>
+      </c>
+      <c r="AU302">
+        <v>6</v>
+      </c>
+      <c r="AV302">
+        <v>9</v>
+      </c>
+      <c r="AW302">
+        <v>18</v>
+      </c>
+      <c r="AX302">
+        <v>6</v>
+      </c>
+      <c r="AY302">
+        <v>25</v>
+      </c>
+      <c r="AZ302">
+        <v>17</v>
+      </c>
+      <c r="BA302">
+        <v>16</v>
+      </c>
+      <c r="BB302">
+        <v>2</v>
+      </c>
+      <c r="BC302">
+        <v>18</v>
+      </c>
+      <c r="BD302">
+        <v>0</v>
+      </c>
+      <c r="BE302">
+        <v>0</v>
+      </c>
+      <c r="BF302">
+        <v>0</v>
+      </c>
+      <c r="BG302">
+        <v>0</v>
+      </c>
+      <c r="BH302">
+        <v>0</v>
+      </c>
+      <c r="BI302">
+        <v>0</v>
+      </c>
+      <c r="BJ302">
+        <v>0</v>
+      </c>
+      <c r="BK302">
+        <v>0</v>
+      </c>
+      <c r="BL302">
+        <v>0</v>
+      </c>
+      <c r="BM302">
+        <v>0</v>
+      </c>
+      <c r="BN302">
+        <v>0</v>
+      </c>
+      <c r="BO302">
+        <v>0</v>
+      </c>
+      <c r="BP302">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="392">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -820,6 +820,21 @@
     <t>['20', '46', '54', '68']</t>
   </si>
   <si>
+    <t>['11', '41']</t>
+  </si>
+  <si>
+    <t>['33', '67']</t>
+  </si>
+  <si>
+    <t>['73', '75']</t>
+  </si>
+  <si>
+    <t>['15', '18', '35', '38', '86']</t>
+  </si>
+  <si>
+    <t>['45', '51']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1163,6 +1178,18 @@
   </si>
   <si>
     <t>['17', '90+2']</t>
+  </si>
+  <si>
+    <t>['23', '30', '43']</t>
+  </si>
+  <si>
+    <t>['55', '69', '85']</t>
+  </si>
+  <si>
+    <t>['38', '46']</t>
+  </si>
+  <si>
+    <t>['21', '53']</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP302"/>
+  <dimension ref="A1:BP310"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1986,7 +2013,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2067,7 +2094,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2398,7 +2425,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2685,7 +2712,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ6">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2810,7 +2837,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3094,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ8">
         <v>0.53</v>
@@ -3222,7 +3249,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3428,7 +3455,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3712,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
         <v>1.67</v>
@@ -3840,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3918,10 +3945,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4046,7 +4073,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4252,7 +4279,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4330,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4539,7 +4566,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ15">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR15">
         <v>1.84</v>
@@ -4742,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>0.53</v>
@@ -4870,7 +4897,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4951,7 +4978,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5360,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5488,7 +5515,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5566,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ20">
         <v>0.73</v>
@@ -5775,7 +5802,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR21">
         <v>1.33</v>
@@ -5900,7 +5927,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6184,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ23">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6312,7 +6339,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6599,7 +6626,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ25">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6930,7 +6957,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7008,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>1.13</v>
@@ -7420,10 +7447,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ29">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR29">
         <v>1.89</v>
@@ -7626,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ30">
         <v>1.5</v>
@@ -8038,10 +8065,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -8166,7 +8193,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8244,10 +8271,10 @@
         <v>1.5</v>
       </c>
       <c r="AP33">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR33">
         <v>1.54</v>
@@ -8453,7 +8480,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ34">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR34">
         <v>1.4</v>
@@ -8578,7 +8605,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8656,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ35">
         <v>1.67</v>
@@ -8784,7 +8811,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9071,7 +9098,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ37">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR37">
         <v>1.58</v>
@@ -9274,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ38">
         <v>0.53</v>
@@ -9608,7 +9635,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9814,7 +9841,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -10020,7 +10047,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10098,7 +10125,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ42">
         <v>0.8100000000000001</v>
@@ -10307,7 +10334,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ43">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR43">
         <v>1.15</v>
@@ -10719,7 +10746,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR45">
         <v>1.98</v>
@@ -10844,7 +10871,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11128,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>1.5</v>
@@ -11256,7 +11283,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11337,7 +11364,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR48">
         <v>1.25</v>
@@ -11462,7 +11489,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11540,7 +11567,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ49">
         <v>2.07</v>
@@ -11746,7 +11773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ50">
         <v>0.93</v>
@@ -11874,7 +11901,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11955,7 +11982,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ51">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR51">
         <v>1.83</v>
@@ -12080,7 +12107,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12364,7 +12391,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ53">
         <v>2.07</v>
@@ -13188,10 +13215,10 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ57">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR57">
         <v>0.86</v>
@@ -13394,10 +13421,10 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR58">
         <v>1.74</v>
@@ -13522,7 +13549,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13603,7 +13630,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ59">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13806,10 +13833,10 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ60">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR60">
         <v>0.97</v>
@@ -13934,7 +13961,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14140,7 +14167,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14221,7 +14248,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR62">
         <v>1.33</v>
@@ -14424,7 +14451,7 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ63">
         <v>1.5</v>
@@ -14836,10 +14863,10 @@
         <v>1.5</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ65">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR65">
         <v>1.09</v>
@@ -14964,7 +14991,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15042,7 +15069,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ66">
         <v>0.63</v>
@@ -15251,7 +15278,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ67">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR67">
         <v>1.2</v>
@@ -15376,7 +15403,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15454,7 +15481,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
         <v>0.93</v>
@@ -15663,7 +15690,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ69">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR69">
         <v>1.8</v>
@@ -15788,7 +15815,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15994,7 +16021,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16200,7 +16227,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16278,10 +16305,10 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ72">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR72">
         <v>0.97</v>
@@ -16406,7 +16433,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16612,7 +16639,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16690,10 +16717,10 @@
         <v>1.5</v>
       </c>
       <c r="AP74">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ74">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR74">
         <v>1.29</v>
@@ -16899,7 +16926,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ75">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -17024,7 +17051,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17230,7 +17257,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17308,10 +17335,10 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR77">
         <v>1.41</v>
@@ -17436,7 +17463,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17514,7 +17541,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ78">
         <v>1.06</v>
@@ -17642,7 +17669,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17720,10 +17747,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17848,7 +17875,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18341,7 +18368,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR82">
         <v>1.28</v>
@@ -18466,7 +18493,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18547,7 +18574,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ83">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR83">
         <v>1.66</v>
@@ -18672,7 +18699,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -19084,7 +19111,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19162,7 +19189,7 @@
         <v>1.8</v>
       </c>
       <c r="AP86">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
         <v>1.13</v>
@@ -19290,7 +19317,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19496,7 +19523,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19780,7 +19807,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ89">
         <v>0.63</v>
@@ -19989,7 +20016,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
         <v>1.38</v>
@@ -20114,7 +20141,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20192,7 +20219,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ91">
         <v>0.93</v>
@@ -20401,7 +20428,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ92">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -20604,7 +20631,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ93">
         <v>1.06</v>
@@ -20810,10 +20837,10 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ94">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -21016,7 +21043,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
         <v>0.53</v>
@@ -21225,7 +21252,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ96">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR96">
         <v>1.62</v>
@@ -21428,7 +21455,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ97">
         <v>0.8100000000000001</v>
@@ -21634,10 +21661,10 @@
         <v>1.2</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ98">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR98">
         <v>1.24</v>
@@ -21843,7 +21870,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ99">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR99">
         <v>1.26</v>
@@ -22049,7 +22076,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ100">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -22252,7 +22279,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
         <v>0.63</v>
@@ -22792,7 +22819,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22998,7 +23025,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23076,7 +23103,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105">
         <v>1.67</v>
@@ -23697,7 +23724,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR108">
         <v>1.52</v>
@@ -24106,7 +24133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ110">
         <v>1.13</v>
@@ -24315,7 +24342,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ111">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR111">
         <v>1.35</v>
@@ -24646,7 +24673,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -24727,7 +24754,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR113">
         <v>1.36</v>
@@ -24930,10 +24957,10 @@
         <v>1.5</v>
       </c>
       <c r="AP114">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ114">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR114">
         <v>1.23</v>
@@ -25139,7 +25166,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR115">
         <v>1.26</v>
@@ -25342,10 +25369,10 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ116">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR116">
         <v>1.53</v>
@@ -25470,7 +25497,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25548,7 +25575,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ117">
         <v>0.53</v>
@@ -25676,7 +25703,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -25754,10 +25781,10 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ118">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR118">
         <v>1.42</v>
@@ -25963,7 +25990,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ119">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR119">
         <v>1.61</v>
@@ -26166,7 +26193,7 @@
         <v>0.8</v>
       </c>
       <c r="AP120">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ120">
         <v>1.06</v>
@@ -26372,7 +26399,7 @@
         <v>0.33</v>
       </c>
       <c r="AP121">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ121">
         <v>0.63</v>
@@ -26500,7 +26527,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -27196,7 +27223,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ125">
         <v>0.53</v>
@@ -27324,7 +27351,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27608,7 +27635,7 @@
         <v>1.67</v>
       </c>
       <c r="AP127">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ127">
         <v>1.67</v>
@@ -27736,7 +27763,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27942,7 +27969,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28148,7 +28175,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28229,7 +28256,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ130">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR130">
         <v>1.24</v>
@@ -28354,7 +28381,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28435,7 +28462,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ131">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28560,7 +28587,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28638,7 +28665,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ132">
         <v>0.8100000000000001</v>
@@ -28844,7 +28871,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ133">
         <v>0.53</v>
@@ -29256,10 +29283,10 @@
         <v>1.83</v>
       </c>
       <c r="AP135">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ135">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR135">
         <v>1.13</v>
@@ -29384,7 +29411,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29668,10 +29695,10 @@
         <v>0.83</v>
       </c>
       <c r="AP137">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ137">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR137">
         <v>1.49</v>
@@ -29796,7 +29823,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -29877,7 +29904,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ138">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR138">
         <v>1.4</v>
@@ -30083,7 +30110,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ139">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR139">
         <v>1.53</v>
@@ -30286,10 +30313,10 @@
         <v>0.83</v>
       </c>
       <c r="AP140">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR140">
         <v>1.37</v>
@@ -30414,7 +30441,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30620,7 +30647,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30826,7 +30853,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -30904,10 +30931,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143">
+        <v>1.13</v>
+      </c>
+      <c r="AQ143">
         <v>1.2</v>
-      </c>
-      <c r="AQ143">
-        <v>1.29</v>
       </c>
       <c r="AR143">
         <v>1.37</v>
@@ -31032,7 +31059,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31319,7 +31346,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ145">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31444,7 +31471,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31525,7 +31552,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ146">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR146">
         <v>1.34</v>
@@ -31728,7 +31755,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ147">
         <v>0.8100000000000001</v>
@@ -32062,7 +32089,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32268,7 +32295,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32680,7 +32707,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32761,7 +32788,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ152">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR152">
         <v>1.26</v>
@@ -33170,7 +33197,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ154">
         <v>1.13</v>
@@ -33298,7 +33325,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33376,10 +33403,10 @@
         <v>1.57</v>
       </c>
       <c r="AP155">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ155">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR155">
         <v>1.27</v>
@@ -33582,7 +33609,7 @@
         <v>0.71</v>
       </c>
       <c r="AP156">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156">
         <v>0.53</v>
@@ -33710,7 +33737,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -33788,10 +33815,10 @@
         <v>0.71</v>
       </c>
       <c r="AP157">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR157">
         <v>1.58</v>
@@ -34122,7 +34149,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34200,10 +34227,10 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ159">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR159">
         <v>1.43</v>
@@ -34409,7 +34436,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ160">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR160">
         <v>1.62</v>
@@ -34534,7 +34561,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34612,7 +34639,7 @@
         <v>1.13</v>
       </c>
       <c r="AP161">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ161">
         <v>0.93</v>
@@ -34821,7 +34848,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ162">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34946,7 +34973,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35358,7 +35385,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35642,7 +35669,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166">
         <v>0.73</v>
@@ -35848,7 +35875,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ167">
         <v>1.5</v>
@@ -35976,7 +36003,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36057,7 +36084,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ168">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR168">
         <v>1.83</v>
@@ -36594,7 +36621,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36675,7 +36702,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ171">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR171">
         <v>1.73</v>
@@ -37084,7 +37111,7 @@
         <v>1.33</v>
       </c>
       <c r="AP173">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ173">
         <v>1.13</v>
@@ -37293,7 +37320,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ174">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR174">
         <v>1.36</v>
@@ -37496,7 +37523,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ175">
         <v>0.73</v>
@@ -37702,10 +37729,10 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR176">
         <v>1.34</v>
@@ -37908,10 +37935,10 @@
         <v>1.75</v>
       </c>
       <c r="AP177">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ177">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR177">
         <v>1.48</v>
@@ -38036,7 +38063,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38117,7 +38144,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ178">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR178">
         <v>1.29</v>
@@ -38242,7 +38269,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38732,7 +38759,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ181">
         <v>0.93</v>
@@ -39147,7 +39174,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ183">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39272,7 +39299,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39478,7 +39505,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -39559,7 +39586,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ185">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39762,10 +39789,10 @@
         <v>1.13</v>
       </c>
       <c r="AP186">
+        <v>1.13</v>
+      </c>
+      <c r="AQ186">
         <v>1.2</v>
-      </c>
-      <c r="AQ186">
-        <v>1.29</v>
       </c>
       <c r="AR186">
         <v>1.56</v>
@@ -39968,7 +39995,7 @@
         <v>1.56</v>
       </c>
       <c r="AP187">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ187">
         <v>1.67</v>
@@ -40096,7 +40123,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40589,7 +40616,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ190">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40714,7 +40741,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40792,7 +40819,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ191">
         <v>0.53</v>
@@ -40920,7 +40947,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -40998,7 +41025,7 @@
         <v>1</v>
       </c>
       <c r="AP192">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ192">
         <v>1.06</v>
@@ -41410,7 +41437,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP194">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41616,7 +41643,7 @@
         <v>1.11</v>
       </c>
       <c r="AP195">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ195">
         <v>0.73</v>
@@ -41822,10 +41849,10 @@
         <v>1</v>
       </c>
       <c r="AP196">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR196">
         <v>1.41</v>
@@ -41950,7 +41977,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42028,10 +42055,10 @@
         <v>1</v>
       </c>
       <c r="AP197">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ197">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR197">
         <v>1.37</v>
@@ -42568,7 +42595,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42649,7 +42676,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR200">
         <v>1.24</v>
@@ -42852,10 +42879,10 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ201">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR201">
         <v>1.5</v>
@@ -42980,7 +43007,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43267,7 +43294,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ203">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR203">
         <v>1.37</v>
@@ -43392,7 +43419,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43473,7 +43500,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ204">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR204">
         <v>1.39</v>
@@ -43885,7 +43912,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ206">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR206">
         <v>1.74</v>
@@ -44010,7 +44037,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44088,7 +44115,7 @@
         <v>0.5</v>
       </c>
       <c r="AP207">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ207">
         <v>0.63</v>
@@ -44216,7 +44243,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44500,10 +44527,10 @@
         <v>1.2</v>
       </c>
       <c r="AP209">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ209">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR209">
         <v>1.52</v>
@@ -45040,7 +45067,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45118,7 +45145,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45246,7 +45273,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45530,7 +45557,7 @@
         <v>1</v>
       </c>
       <c r="AP214">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ214">
         <v>0.73</v>
@@ -45736,10 +45763,10 @@
         <v>0.9</v>
       </c>
       <c r="AP215">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ215">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR215">
         <v>1.37</v>
@@ -45864,7 +45891,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45945,7 +45972,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ216">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR216">
         <v>1.68</v>
@@ -46070,7 +46097,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46357,7 +46384,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ218">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR218">
         <v>1.25</v>
@@ -46563,7 +46590,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ219">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR219">
         <v>1.84</v>
@@ -46688,7 +46715,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46766,10 +46793,10 @@
         <v>1</v>
       </c>
       <c r="AP220">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ220">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -46894,7 +46921,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -46972,7 +46999,7 @@
         <v>1.36</v>
       </c>
       <c r="AP221">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ221">
         <v>1.5</v>
@@ -47100,7 +47127,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47512,7 +47539,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47593,7 +47620,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ224">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR224">
         <v>1.39</v>
@@ -47796,10 +47823,10 @@
         <v>1.1</v>
       </c>
       <c r="AP225">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ225">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR225">
         <v>1.49</v>
@@ -47924,7 +47951,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48002,10 +48029,10 @@
         <v>1.18</v>
       </c>
       <c r="AP226">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ226">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR226">
         <v>1.51</v>
@@ -48130,7 +48157,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48208,7 +48235,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ227">
         <v>0.93</v>
@@ -48336,7 +48363,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48417,7 +48444,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ228">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48954,7 +48981,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49032,7 +49059,7 @@
         <v>0.82</v>
       </c>
       <c r="AP231">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ231">
         <v>0.8100000000000001</v>
@@ -49160,7 +49187,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49241,7 +49268,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ232">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR232">
         <v>1.79</v>
@@ -49444,7 +49471,7 @@
         <v>0.91</v>
       </c>
       <c r="AP233">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ233">
         <v>0.73</v>
@@ -49650,10 +49677,10 @@
         <v>1.25</v>
       </c>
       <c r="AP234">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ234">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR234">
         <v>1.78</v>
@@ -49778,7 +49805,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49984,7 +50011,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50268,7 +50295,7 @@
         <v>0.75</v>
       </c>
       <c r="AP237">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ237">
         <v>0.63</v>
@@ -50602,7 +50629,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -50680,7 +50707,7 @@
         <v>1</v>
       </c>
       <c r="AP239">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ239">
         <v>1.06</v>
@@ -50889,7 +50916,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ240">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR240">
         <v>1.42</v>
@@ -51014,7 +51041,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51095,7 +51122,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ241">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR241">
         <v>1.41</v>
@@ -51507,7 +51534,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ243">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR243">
         <v>1.47</v>
@@ -51632,7 +51659,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51710,7 +51737,7 @@
         <v>2</v>
       </c>
       <c r="AP244">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ244">
         <v>2.07</v>
@@ -51919,7 +51946,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ245">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR245">
         <v>1.4</v>
@@ -52122,7 +52149,7 @@
         <v>0.5</v>
       </c>
       <c r="AP246">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ246">
         <v>0.53</v>
@@ -52328,7 +52355,7 @@
         <v>0.83</v>
       </c>
       <c r="AP247">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ247">
         <v>0.8100000000000001</v>
@@ -52534,10 +52561,10 @@
         <v>1.08</v>
       </c>
       <c r="AP248">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ248">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR248">
         <v>1.78</v>
@@ -52868,7 +52895,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53155,7 +53182,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ251">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR251">
         <v>1.22</v>
@@ -53361,7 +53388,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ252">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR252">
         <v>1.3</v>
@@ -53486,7 +53513,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53770,7 +53797,7 @@
         <v>1.62</v>
       </c>
       <c r="AP254">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ254">
         <v>1.5</v>
@@ -53976,7 +54003,7 @@
         <v>1.17</v>
       </c>
       <c r="AP255">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ255">
         <v>1.06</v>
@@ -54182,7 +54209,7 @@
         <v>0.58</v>
       </c>
       <c r="AP256">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ256">
         <v>0.53</v>
@@ -54597,7 +54624,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ258">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR258">
         <v>1.41</v>
@@ -54928,7 +54955,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55212,10 +55239,10 @@
         <v>1.75</v>
       </c>
       <c r="AP261">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ261">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR261">
         <v>1.47</v>
@@ -55418,7 +55445,7 @@
         <v>2.08</v>
       </c>
       <c r="AP262">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ262">
         <v>2.07</v>
@@ -55546,7 +55573,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55830,10 +55857,10 @@
         <v>1</v>
       </c>
       <c r="AP264">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ264">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR264">
         <v>1.31</v>
@@ -56039,7 +56066,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ265">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR265">
         <v>1.48</v>
@@ -56164,7 +56191,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56370,7 +56397,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56448,7 +56475,7 @@
         <v>0.85</v>
       </c>
       <c r="AP267">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ267">
         <v>1</v>
@@ -56576,7 +56603,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -56654,7 +56681,7 @@
         <v>1</v>
       </c>
       <c r="AP268">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ268">
         <v>1.13</v>
@@ -56863,7 +56890,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ269">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR269">
         <v>1.9</v>
@@ -57069,7 +57096,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ270">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR270">
         <v>1.61</v>
@@ -57194,7 +57221,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57275,7 +57302,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ271">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR271">
         <v>1.71</v>
@@ -57606,7 +57633,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -57684,7 +57711,7 @@
         <v>1.62</v>
       </c>
       <c r="AP273">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ273">
         <v>1.67</v>
@@ -57890,7 +57917,7 @@
         <v>0.54</v>
       </c>
       <c r="AP274">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ274">
         <v>0.53</v>
@@ -58018,7 +58045,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58305,7 +58332,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ276">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR276">
         <v>1.25</v>
@@ -58508,10 +58535,10 @@
         <v>1.69</v>
       </c>
       <c r="AP277">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ277">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR277">
         <v>1.68</v>
@@ -58842,7 +58869,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -58923,7 +58950,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ279">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR279">
         <v>1.32</v>
@@ -59126,7 +59153,7 @@
         <v>0.77</v>
       </c>
       <c r="AP280">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ280">
         <v>0.73</v>
@@ -59254,7 +59281,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -59538,10 +59565,10 @@
         <v>1</v>
       </c>
       <c r="AP282">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ282">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR282">
         <v>1.6</v>
@@ -59744,10 +59771,10 @@
         <v>1.38</v>
       </c>
       <c r="AP283">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AQ283">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR283">
         <v>1.8</v>
@@ -59950,10 +59977,10 @@
         <v>1.07</v>
       </c>
       <c r="AP284">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ284">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR284">
         <v>1.3</v>
@@ -60362,10 +60389,10 @@
         <v>0.85</v>
       </c>
       <c r="AP286">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ286">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AR286">
         <v>1.36</v>
@@ -60568,7 +60595,7 @@
         <v>1.14</v>
       </c>
       <c r="AP287">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ287">
         <v>1.13</v>
@@ -60696,7 +60723,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -60980,10 +61007,10 @@
         <v>1.15</v>
       </c>
       <c r="AP289">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AQ289">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR289">
         <v>1.67</v>
@@ -61108,7 +61135,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61189,7 +61216,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ290">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR290">
         <v>1.93</v>
@@ -61314,7 +61341,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61395,7 +61422,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ291">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR291">
         <v>1.41</v>
@@ -61520,7 +61547,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61804,7 +61831,7 @@
         <v>1.53</v>
       </c>
       <c r="AP293">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ293">
         <v>1.5</v>
@@ -61932,7 +61959,7 @@
         <v>90</v>
       </c>
       <c r="P294" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q294">
         <v>4.5</v>
@@ -62962,7 +62989,7 @@
         <v>265</v>
       </c>
       <c r="P299" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q299">
         <v>3.5</v>
@@ -63168,7 +63195,7 @@
         <v>266</v>
       </c>
       <c r="P300" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q300">
         <v>3</v>
@@ -63580,7 +63607,7 @@
         <v>102</v>
       </c>
       <c r="P302" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q302">
         <v>2.1</v>
@@ -63737,6 +63764,1654 @@
       </c>
       <c r="BP302">
         <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7509889</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F303">
+        <v>31</v>
+      </c>
+      <c r="G303" t="s">
+        <v>79</v>
+      </c>
+      <c r="H303" t="s">
+        <v>73</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>3</v>
+      </c>
+      <c r="K303">
+        <v>3</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+      <c r="M303">
+        <v>3</v>
+      </c>
+      <c r="N303">
+        <v>3</v>
+      </c>
+      <c r="O303" t="s">
+        <v>102</v>
+      </c>
+      <c r="P303" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q303">
+        <v>4.33</v>
+      </c>
+      <c r="R303">
+        <v>2</v>
+      </c>
+      <c r="S303">
+        <v>2.88</v>
+      </c>
+      <c r="T303">
+        <v>1.5</v>
+      </c>
+      <c r="U303">
+        <v>2.5</v>
+      </c>
+      <c r="V303">
+        <v>3.4</v>
+      </c>
+      <c r="W303">
+        <v>1.3</v>
+      </c>
+      <c r="X303">
+        <v>10</v>
+      </c>
+      <c r="Y303">
+        <v>1.06</v>
+      </c>
+      <c r="Z303">
+        <v>3.36</v>
+      </c>
+      <c r="AA303">
+        <v>3.41</v>
+      </c>
+      <c r="AB303">
+        <v>2.25</v>
+      </c>
+      <c r="AC303">
+        <v>0</v>
+      </c>
+      <c r="AD303">
+        <v>0</v>
+      </c>
+      <c r="AE303">
+        <v>1.5</v>
+      </c>
+      <c r="AF303">
+        <v>2.4</v>
+      </c>
+      <c r="AG303">
+        <v>2.15</v>
+      </c>
+      <c r="AH303">
+        <v>1.57</v>
+      </c>
+      <c r="AI303">
+        <v>1.95</v>
+      </c>
+      <c r="AJ303">
+        <v>1.8</v>
+      </c>
+      <c r="AK303">
+        <v>0</v>
+      </c>
+      <c r="AL303">
+        <v>0</v>
+      </c>
+      <c r="AM303">
+        <v>0</v>
+      </c>
+      <c r="AN303">
+        <v>1.2</v>
+      </c>
+      <c r="AO303">
+        <v>1.47</v>
+      </c>
+      <c r="AP303">
+        <v>1.13</v>
+      </c>
+      <c r="AQ303">
+        <v>1.56</v>
+      </c>
+      <c r="AR303">
+        <v>1.57</v>
+      </c>
+      <c r="AS303">
+        <v>1.19</v>
+      </c>
+      <c r="AT303">
+        <v>2.76</v>
+      </c>
+      <c r="AU303">
+        <v>0</v>
+      </c>
+      <c r="AV303">
+        <v>4</v>
+      </c>
+      <c r="AW303">
+        <v>3</v>
+      </c>
+      <c r="AX303">
+        <v>9</v>
+      </c>
+      <c r="AY303">
+        <v>3</v>
+      </c>
+      <c r="AZ303">
+        <v>16</v>
+      </c>
+      <c r="BA303">
+        <v>0</v>
+      </c>
+      <c r="BB303">
+        <v>5</v>
+      </c>
+      <c r="BC303">
+        <v>5</v>
+      </c>
+      <c r="BD303">
+        <v>0</v>
+      </c>
+      <c r="BE303">
+        <v>0</v>
+      </c>
+      <c r="BF303">
+        <v>0</v>
+      </c>
+      <c r="BG303">
+        <v>0</v>
+      </c>
+      <c r="BH303">
+        <v>0</v>
+      </c>
+      <c r="BI303">
+        <v>0</v>
+      </c>
+      <c r="BJ303">
+        <v>0</v>
+      </c>
+      <c r="BK303">
+        <v>0</v>
+      </c>
+      <c r="BL303">
+        <v>0</v>
+      </c>
+      <c r="BM303">
+        <v>0</v>
+      </c>
+      <c r="BN303">
+        <v>0</v>
+      </c>
+      <c r="BO303">
+        <v>0</v>
+      </c>
+      <c r="BP303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7509891</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F304">
+        <v>31</v>
+      </c>
+      <c r="G304" t="s">
+        <v>85</v>
+      </c>
+      <c r="H304" t="s">
+        <v>72</v>
+      </c>
+      <c r="I304">
+        <v>2</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>2</v>
+      </c>
+      <c r="L304">
+        <v>2</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>2</v>
+      </c>
+      <c r="O304" t="s">
+        <v>268</v>
+      </c>
+      <c r="P304" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q304">
+        <v>3.4</v>
+      </c>
+      <c r="R304">
+        <v>2</v>
+      </c>
+      <c r="S304">
+        <v>3.5</v>
+      </c>
+      <c r="T304">
+        <v>1.5</v>
+      </c>
+      <c r="U304">
+        <v>2.5</v>
+      </c>
+      <c r="V304">
+        <v>3.4</v>
+      </c>
+      <c r="W304">
+        <v>1.3</v>
+      </c>
+      <c r="X304">
+        <v>10</v>
+      </c>
+      <c r="Y304">
+        <v>1.06</v>
+      </c>
+      <c r="Z304">
+        <v>2.78</v>
+      </c>
+      <c r="AA304">
+        <v>2.96</v>
+      </c>
+      <c r="AB304">
+        <v>2.96</v>
+      </c>
+      <c r="AC304">
+        <v>0</v>
+      </c>
+      <c r="AD304">
+        <v>0</v>
+      </c>
+      <c r="AE304">
+        <v>0</v>
+      </c>
+      <c r="AF304">
+        <v>0</v>
+      </c>
+      <c r="AG304">
+        <v>2.05</v>
+      </c>
+      <c r="AH304">
+        <v>1.61</v>
+      </c>
+      <c r="AI304">
+        <v>1.95</v>
+      </c>
+      <c r="AJ304">
+        <v>1.8</v>
+      </c>
+      <c r="AK304">
+        <v>0</v>
+      </c>
+      <c r="AL304">
+        <v>0</v>
+      </c>
+      <c r="AM304">
+        <v>0</v>
+      </c>
+      <c r="AN304">
+        <v>1.43</v>
+      </c>
+      <c r="AO304">
+        <v>1.13</v>
+      </c>
+      <c r="AP304">
+        <v>1.53</v>
+      </c>
+      <c r="AQ304">
+        <v>1.06</v>
+      </c>
+      <c r="AR304">
+        <v>1.29</v>
+      </c>
+      <c r="AS304">
+        <v>1.29</v>
+      </c>
+      <c r="AT304">
+        <v>2.58</v>
+      </c>
+      <c r="AU304">
+        <v>6</v>
+      </c>
+      <c r="AV304">
+        <v>3</v>
+      </c>
+      <c r="AW304">
+        <v>8</v>
+      </c>
+      <c r="AX304">
+        <v>15</v>
+      </c>
+      <c r="AY304">
+        <v>16</v>
+      </c>
+      <c r="AZ304">
+        <v>24</v>
+      </c>
+      <c r="BA304">
+        <v>2</v>
+      </c>
+      <c r="BB304">
+        <v>7</v>
+      </c>
+      <c r="BC304">
+        <v>9</v>
+      </c>
+      <c r="BD304">
+        <v>0</v>
+      </c>
+      <c r="BE304">
+        <v>0</v>
+      </c>
+      <c r="BF304">
+        <v>0</v>
+      </c>
+      <c r="BG304">
+        <v>0</v>
+      </c>
+      <c r="BH304">
+        <v>0</v>
+      </c>
+      <c r="BI304">
+        <v>0</v>
+      </c>
+      <c r="BJ304">
+        <v>0</v>
+      </c>
+      <c r="BK304">
+        <v>0</v>
+      </c>
+      <c r="BL304">
+        <v>0</v>
+      </c>
+      <c r="BM304">
+        <v>0</v>
+      </c>
+      <c r="BN304">
+        <v>0</v>
+      </c>
+      <c r="BO304">
+        <v>0</v>
+      </c>
+      <c r="BP304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7509892</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F305">
+        <v>31</v>
+      </c>
+      <c r="G305" t="s">
+        <v>80</v>
+      </c>
+      <c r="H305" t="s">
+        <v>78</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>1</v>
+      </c>
+      <c r="L305">
+        <v>2</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>3</v>
+      </c>
+      <c r="O305" t="s">
+        <v>269</v>
+      </c>
+      <c r="P305" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q305">
+        <v>2.75</v>
+      </c>
+      <c r="R305">
+        <v>2.05</v>
+      </c>
+      <c r="S305">
+        <v>4.33</v>
+      </c>
+      <c r="T305">
+        <v>1.5</v>
+      </c>
+      <c r="U305">
+        <v>2.5</v>
+      </c>
+      <c r="V305">
+        <v>3.4</v>
+      </c>
+      <c r="W305">
+        <v>1.3</v>
+      </c>
+      <c r="X305">
+        <v>10</v>
+      </c>
+      <c r="Y305">
+        <v>1.06</v>
+      </c>
+      <c r="Z305">
+        <v>2.09</v>
+      </c>
+      <c r="AA305">
+        <v>3.3</v>
+      </c>
+      <c r="AB305">
+        <v>3.95</v>
+      </c>
+      <c r="AC305">
+        <v>0</v>
+      </c>
+      <c r="AD305">
+        <v>0</v>
+      </c>
+      <c r="AE305">
+        <v>0</v>
+      </c>
+      <c r="AF305">
+        <v>0</v>
+      </c>
+      <c r="AG305">
+        <v>2.15</v>
+      </c>
+      <c r="AH305">
+        <v>1.6</v>
+      </c>
+      <c r="AI305">
+        <v>1.95</v>
+      </c>
+      <c r="AJ305">
+        <v>1.8</v>
+      </c>
+      <c r="AK305">
+        <v>0</v>
+      </c>
+      <c r="AL305">
+        <v>0</v>
+      </c>
+      <c r="AM305">
+        <v>0</v>
+      </c>
+      <c r="AN305">
+        <v>1.57</v>
+      </c>
+      <c r="AO305">
+        <v>1.29</v>
+      </c>
+      <c r="AP305">
+        <v>1.67</v>
+      </c>
+      <c r="AQ305">
+        <v>1.2</v>
+      </c>
+      <c r="AR305">
+        <v>1.43</v>
+      </c>
+      <c r="AS305">
+        <v>1.2</v>
+      </c>
+      <c r="AT305">
+        <v>2.63</v>
+      </c>
+      <c r="AU305">
+        <v>8</v>
+      </c>
+      <c r="AV305">
+        <v>3</v>
+      </c>
+      <c r="AW305">
+        <v>4</v>
+      </c>
+      <c r="AX305">
+        <v>10</v>
+      </c>
+      <c r="AY305">
+        <v>14</v>
+      </c>
+      <c r="AZ305">
+        <v>17</v>
+      </c>
+      <c r="BA305">
+        <v>6</v>
+      </c>
+      <c r="BB305">
+        <v>4</v>
+      </c>
+      <c r="BC305">
+        <v>10</v>
+      </c>
+      <c r="BD305">
+        <v>0</v>
+      </c>
+      <c r="BE305">
+        <v>0</v>
+      </c>
+      <c r="BF305">
+        <v>0</v>
+      </c>
+      <c r="BG305">
+        <v>0</v>
+      </c>
+      <c r="BH305">
+        <v>0</v>
+      </c>
+      <c r="BI305">
+        <v>0</v>
+      </c>
+      <c r="BJ305">
+        <v>0</v>
+      </c>
+      <c r="BK305">
+        <v>0</v>
+      </c>
+      <c r="BL305">
+        <v>0</v>
+      </c>
+      <c r="BM305">
+        <v>0</v>
+      </c>
+      <c r="BN305">
+        <v>0</v>
+      </c>
+      <c r="BO305">
+        <v>0</v>
+      </c>
+      <c r="BP305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7509894</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45745.45833333334</v>
+      </c>
+      <c r="F306">
+        <v>31</v>
+      </c>
+      <c r="G306" t="s">
+        <v>81</v>
+      </c>
+      <c r="H306" t="s">
+        <v>75</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306">
+        <v>3</v>
+      </c>
+      <c r="N306">
+        <v>3</v>
+      </c>
+      <c r="O306" t="s">
+        <v>102</v>
+      </c>
+      <c r="P306" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q306">
+        <v>2.88</v>
+      </c>
+      <c r="R306">
+        <v>2</v>
+      </c>
+      <c r="S306">
+        <v>4.33</v>
+      </c>
+      <c r="T306">
+        <v>1.5</v>
+      </c>
+      <c r="U306">
+        <v>2.5</v>
+      </c>
+      <c r="V306">
+        <v>3.4</v>
+      </c>
+      <c r="W306">
+        <v>1.3</v>
+      </c>
+      <c r="X306">
+        <v>10</v>
+      </c>
+      <c r="Y306">
+        <v>1.06</v>
+      </c>
+      <c r="Z306">
+        <v>2.1</v>
+      </c>
+      <c r="AA306">
+        <v>3.29</v>
+      </c>
+      <c r="AB306">
+        <v>3.93</v>
+      </c>
+      <c r="AC306">
+        <v>0</v>
+      </c>
+      <c r="AD306">
+        <v>0</v>
+      </c>
+      <c r="AE306">
+        <v>0</v>
+      </c>
+      <c r="AF306">
+        <v>0</v>
+      </c>
+      <c r="AG306">
+        <v>2.15</v>
+      </c>
+      <c r="AH306">
+        <v>1.57</v>
+      </c>
+      <c r="AI306">
+        <v>1.95</v>
+      </c>
+      <c r="AJ306">
+        <v>1.8</v>
+      </c>
+      <c r="AK306">
+        <v>0</v>
+      </c>
+      <c r="AL306">
+        <v>0</v>
+      </c>
+      <c r="AM306">
+        <v>0</v>
+      </c>
+      <c r="AN306">
+        <v>1.2</v>
+      </c>
+      <c r="AO306">
+        <v>1</v>
+      </c>
+      <c r="AP306">
+        <v>1.13</v>
+      </c>
+      <c r="AQ306">
+        <v>1.13</v>
+      </c>
+      <c r="AR306">
+        <v>1.42</v>
+      </c>
+      <c r="AS306">
+        <v>1.23</v>
+      </c>
+      <c r="AT306">
+        <v>2.65</v>
+      </c>
+      <c r="AU306">
+        <v>3</v>
+      </c>
+      <c r="AV306">
+        <v>8</v>
+      </c>
+      <c r="AW306">
+        <v>9</v>
+      </c>
+      <c r="AX306">
+        <v>16</v>
+      </c>
+      <c r="AY306">
+        <v>16</v>
+      </c>
+      <c r="AZ306">
+        <v>32</v>
+      </c>
+      <c r="BA306">
+        <v>5</v>
+      </c>
+      <c r="BB306">
+        <v>6</v>
+      </c>
+      <c r="BC306">
+        <v>11</v>
+      </c>
+      <c r="BD306">
+        <v>0</v>
+      </c>
+      <c r="BE306">
+        <v>0</v>
+      </c>
+      <c r="BF306">
+        <v>0</v>
+      </c>
+      <c r="BG306">
+        <v>0</v>
+      </c>
+      <c r="BH306">
+        <v>0</v>
+      </c>
+      <c r="BI306">
+        <v>0</v>
+      </c>
+      <c r="BJ306">
+        <v>0</v>
+      </c>
+      <c r="BK306">
+        <v>0</v>
+      </c>
+      <c r="BL306">
+        <v>0</v>
+      </c>
+      <c r="BM306">
+        <v>0</v>
+      </c>
+      <c r="BN306">
+        <v>0</v>
+      </c>
+      <c r="BO306">
+        <v>0</v>
+      </c>
+      <c r="BP306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7509890</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45745.55208333334</v>
+      </c>
+      <c r="F307">
+        <v>31</v>
+      </c>
+      <c r="G307" t="s">
+        <v>82</v>
+      </c>
+      <c r="H307" t="s">
+        <v>87</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
+      <c r="K307">
+        <v>1</v>
+      </c>
+      <c r="L307">
+        <v>2</v>
+      </c>
+      <c r="M307">
+        <v>2</v>
+      </c>
+      <c r="N307">
+        <v>4</v>
+      </c>
+      <c r="O307" t="s">
+        <v>270</v>
+      </c>
+      <c r="P307" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q307">
+        <v>2</v>
+      </c>
+      <c r="R307">
+        <v>2.3</v>
+      </c>
+      <c r="S307">
+        <v>7.5</v>
+      </c>
+      <c r="T307">
+        <v>1.4</v>
+      </c>
+      <c r="U307">
+        <v>2.75</v>
+      </c>
+      <c r="V307">
+        <v>2.75</v>
+      </c>
+      <c r="W307">
+        <v>1.4</v>
+      </c>
+      <c r="X307">
+        <v>8</v>
+      </c>
+      <c r="Y307">
+        <v>1.08</v>
+      </c>
+      <c r="Z307">
+        <v>1.47</v>
+      </c>
+      <c r="AA307">
+        <v>4.6</v>
+      </c>
+      <c r="AB307">
+        <v>7.2</v>
+      </c>
+      <c r="AC307">
+        <v>0</v>
+      </c>
+      <c r="AD307">
+        <v>0</v>
+      </c>
+      <c r="AE307">
+        <v>0</v>
+      </c>
+      <c r="AF307">
+        <v>0</v>
+      </c>
+      <c r="AG307">
+        <v>1.97</v>
+      </c>
+      <c r="AH307">
+        <v>1.84</v>
+      </c>
+      <c r="AI307">
+        <v>2.1</v>
+      </c>
+      <c r="AJ307">
+        <v>1.67</v>
+      </c>
+      <c r="AK307">
+        <v>0</v>
+      </c>
+      <c r="AL307">
+        <v>0</v>
+      </c>
+      <c r="AM307">
+        <v>0</v>
+      </c>
+      <c r="AN307">
+        <v>1.53</v>
+      </c>
+      <c r="AO307">
+        <v>1.47</v>
+      </c>
+      <c r="AP307">
+        <v>1.5</v>
+      </c>
+      <c r="AQ307">
+        <v>1.44</v>
+      </c>
+      <c r="AR307">
+        <v>1.85</v>
+      </c>
+      <c r="AS307">
+        <v>1.18</v>
+      </c>
+      <c r="AT307">
+        <v>3.03</v>
+      </c>
+      <c r="AU307">
+        <v>8</v>
+      </c>
+      <c r="AV307">
+        <v>3</v>
+      </c>
+      <c r="AW307">
+        <v>11</v>
+      </c>
+      <c r="AX307">
+        <v>2</v>
+      </c>
+      <c r="AY307">
+        <v>25</v>
+      </c>
+      <c r="AZ307">
+        <v>6</v>
+      </c>
+      <c r="BA307">
+        <v>9</v>
+      </c>
+      <c r="BB307">
+        <v>1</v>
+      </c>
+      <c r="BC307">
+        <v>10</v>
+      </c>
+      <c r="BD307">
+        <v>0</v>
+      </c>
+      <c r="BE307">
+        <v>0</v>
+      </c>
+      <c r="BF307">
+        <v>0</v>
+      </c>
+      <c r="BG307">
+        <v>0</v>
+      </c>
+      <c r="BH307">
+        <v>0</v>
+      </c>
+      <c r="BI307">
+        <v>0</v>
+      </c>
+      <c r="BJ307">
+        <v>0</v>
+      </c>
+      <c r="BK307">
+        <v>0</v>
+      </c>
+      <c r="BL307">
+        <v>0</v>
+      </c>
+      <c r="BM307">
+        <v>0</v>
+      </c>
+      <c r="BN307">
+        <v>0</v>
+      </c>
+      <c r="BO307">
+        <v>0</v>
+      </c>
+      <c r="BP307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7509895</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45745.64583333334</v>
+      </c>
+      <c r="F308">
+        <v>31</v>
+      </c>
+      <c r="G308" t="s">
+        <v>84</v>
+      </c>
+      <c r="H308" t="s">
+        <v>77</v>
+      </c>
+      <c r="I308">
+        <v>4</v>
+      </c>
+      <c r="J308">
+        <v>1</v>
+      </c>
+      <c r="K308">
+        <v>5</v>
+      </c>
+      <c r="L308">
+        <v>5</v>
+      </c>
+      <c r="M308">
+        <v>1</v>
+      </c>
+      <c r="N308">
+        <v>6</v>
+      </c>
+      <c r="O308" t="s">
+        <v>271</v>
+      </c>
+      <c r="P308" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q308">
+        <v>2.25</v>
+      </c>
+      <c r="R308">
+        <v>2.2</v>
+      </c>
+      <c r="S308">
+        <v>5.5</v>
+      </c>
+      <c r="T308">
+        <v>1.4</v>
+      </c>
+      <c r="U308">
+        <v>2.75</v>
+      </c>
+      <c r="V308">
+        <v>3</v>
+      </c>
+      <c r="W308">
+        <v>1.36</v>
+      </c>
+      <c r="X308">
+        <v>8</v>
+      </c>
+      <c r="Y308">
+        <v>1.08</v>
+      </c>
+      <c r="Z308">
+        <v>1.68</v>
+      </c>
+      <c r="AA308">
+        <v>3.95</v>
+      </c>
+      <c r="AB308">
+        <v>5.3</v>
+      </c>
+      <c r="AC308">
+        <v>0</v>
+      </c>
+      <c r="AD308">
+        <v>0</v>
+      </c>
+      <c r="AE308">
+        <v>0</v>
+      </c>
+      <c r="AF308">
+        <v>0</v>
+      </c>
+      <c r="AG308">
+        <v>1.98</v>
+      </c>
+      <c r="AH308">
+        <v>1.83</v>
+      </c>
+      <c r="AI308">
+        <v>1.95</v>
+      </c>
+      <c r="AJ308">
+        <v>1.8</v>
+      </c>
+      <c r="AK308">
+        <v>0</v>
+      </c>
+      <c r="AL308">
+        <v>0</v>
+      </c>
+      <c r="AM308">
+        <v>0</v>
+      </c>
+      <c r="AN308">
+        <v>2.53</v>
+      </c>
+      <c r="AO308">
+        <v>0.93</v>
+      </c>
+      <c r="AP308">
+        <v>2.56</v>
+      </c>
+      <c r="AQ308">
+        <v>0.88</v>
+      </c>
+      <c r="AR308">
+        <v>1.65</v>
+      </c>
+      <c r="AS308">
+        <v>1.32</v>
+      </c>
+      <c r="AT308">
+        <v>2.97</v>
+      </c>
+      <c r="AU308">
+        <v>8</v>
+      </c>
+      <c r="AV308">
+        <v>3</v>
+      </c>
+      <c r="AW308">
+        <v>6</v>
+      </c>
+      <c r="AX308">
+        <v>7</v>
+      </c>
+      <c r="AY308">
+        <v>16</v>
+      </c>
+      <c r="AZ308">
+        <v>11</v>
+      </c>
+      <c r="BA308">
+        <v>3</v>
+      </c>
+      <c r="BB308">
+        <v>2</v>
+      </c>
+      <c r="BC308">
+        <v>5</v>
+      </c>
+      <c r="BD308">
+        <v>0</v>
+      </c>
+      <c r="BE308">
+        <v>0</v>
+      </c>
+      <c r="BF308">
+        <v>0</v>
+      </c>
+      <c r="BG308">
+        <v>0</v>
+      </c>
+      <c r="BH308">
+        <v>0</v>
+      </c>
+      <c r="BI308">
+        <v>0</v>
+      </c>
+      <c r="BJ308">
+        <v>0</v>
+      </c>
+      <c r="BK308">
+        <v>0</v>
+      </c>
+      <c r="BL308">
+        <v>0</v>
+      </c>
+      <c r="BM308">
+        <v>0</v>
+      </c>
+      <c r="BN308">
+        <v>0</v>
+      </c>
+      <c r="BO308">
+        <v>0</v>
+      </c>
+      <c r="BP308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7509888</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F309">
+        <v>31</v>
+      </c>
+      <c r="G309" t="s">
+        <v>76</v>
+      </c>
+      <c r="H309" t="s">
+        <v>88</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>1</v>
+      </c>
+      <c r="K309">
+        <v>1</v>
+      </c>
+      <c r="L309">
+        <v>1</v>
+      </c>
+      <c r="M309">
+        <v>2</v>
+      </c>
+      <c r="N309">
+        <v>3</v>
+      </c>
+      <c r="O309" t="s">
+        <v>200</v>
+      </c>
+      <c r="P309" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q309">
+        <v>3.25</v>
+      </c>
+      <c r="R309">
+        <v>1.95</v>
+      </c>
+      <c r="S309">
+        <v>4</v>
+      </c>
+      <c r="T309">
+        <v>1.57</v>
+      </c>
+      <c r="U309">
+        <v>2.25</v>
+      </c>
+      <c r="V309">
+        <v>3.75</v>
+      </c>
+      <c r="W309">
+        <v>1.25</v>
+      </c>
+      <c r="X309">
+        <v>11</v>
+      </c>
+      <c r="Y309">
+        <v>1.05</v>
+      </c>
+      <c r="Z309">
+        <v>2.44</v>
+      </c>
+      <c r="AA309">
+        <v>3.09</v>
+      </c>
+      <c r="AB309">
+        <v>3.31</v>
+      </c>
+      <c r="AC309">
+        <v>1.11</v>
+      </c>
+      <c r="AD309">
+        <v>6.25</v>
+      </c>
+      <c r="AE309">
+        <v>1.5</v>
+      </c>
+      <c r="AF309">
+        <v>2.55</v>
+      </c>
+      <c r="AG309">
+        <v>2.3</v>
+      </c>
+      <c r="AH309">
+        <v>1.5</v>
+      </c>
+      <c r="AI309">
+        <v>2</v>
+      </c>
+      <c r="AJ309">
+        <v>1.75</v>
+      </c>
+      <c r="AK309">
+        <v>1.33</v>
+      </c>
+      <c r="AL309">
+        <v>1.38</v>
+      </c>
+      <c r="AM309">
+        <v>1.55</v>
+      </c>
+      <c r="AN309">
+        <v>1.8</v>
+      </c>
+      <c r="AO309">
+        <v>1.07</v>
+      </c>
+      <c r="AP309">
+        <v>1.69</v>
+      </c>
+      <c r="AQ309">
+        <v>1.19</v>
+      </c>
+      <c r="AR309">
+        <v>1.44</v>
+      </c>
+      <c r="AS309">
+        <v>1.12</v>
+      </c>
+      <c r="AT309">
+        <v>2.56</v>
+      </c>
+      <c r="AU309">
+        <v>4</v>
+      </c>
+      <c r="AV309">
+        <v>4</v>
+      </c>
+      <c r="AW309">
+        <v>5</v>
+      </c>
+      <c r="AX309">
+        <v>6</v>
+      </c>
+      <c r="AY309">
+        <v>10</v>
+      </c>
+      <c r="AZ309">
+        <v>10</v>
+      </c>
+      <c r="BA309">
+        <v>8</v>
+      </c>
+      <c r="BB309">
+        <v>1</v>
+      </c>
+      <c r="BC309">
+        <v>9</v>
+      </c>
+      <c r="BD309">
+        <v>1.7</v>
+      </c>
+      <c r="BE309">
+        <v>8</v>
+      </c>
+      <c r="BF309">
+        <v>2.45</v>
+      </c>
+      <c r="BG309">
+        <v>1.44</v>
+      </c>
+      <c r="BH309">
+        <v>2.45</v>
+      </c>
+      <c r="BI309">
+        <v>1.82</v>
+      </c>
+      <c r="BJ309">
+        <v>1.83</v>
+      </c>
+      <c r="BK309">
+        <v>2.45</v>
+      </c>
+      <c r="BL309">
+        <v>1.46</v>
+      </c>
+      <c r="BM309">
+        <v>3.4</v>
+      </c>
+      <c r="BN309">
+        <v>1.25</v>
+      </c>
+      <c r="BO309">
+        <v>3.2</v>
+      </c>
+      <c r="BP309">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7509887</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45746.41666666666</v>
+      </c>
+      <c r="F310">
+        <v>31</v>
+      </c>
+      <c r="G310" t="s">
+        <v>86</v>
+      </c>
+      <c r="H310" t="s">
+        <v>71</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+      <c r="J310">
+        <v>1</v>
+      </c>
+      <c r="K310">
+        <v>2</v>
+      </c>
+      <c r="L310">
+        <v>2</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>3</v>
+      </c>
+      <c r="O310" t="s">
+        <v>272</v>
+      </c>
+      <c r="P310" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q310">
+        <v>3.2</v>
+      </c>
+      <c r="R310">
+        <v>2</v>
+      </c>
+      <c r="S310">
+        <v>3.75</v>
+      </c>
+      <c r="T310">
+        <v>1.5</v>
+      </c>
+      <c r="U310">
+        <v>2.5</v>
+      </c>
+      <c r="V310">
+        <v>3.4</v>
+      </c>
+      <c r="W310">
+        <v>1.3</v>
+      </c>
+      <c r="X310">
+        <v>10</v>
+      </c>
+      <c r="Y310">
+        <v>1.06</v>
+      </c>
+      <c r="Z310">
+        <v>2.47</v>
+      </c>
+      <c r="AA310">
+        <v>3.18</v>
+      </c>
+      <c r="AB310">
+        <v>3.16</v>
+      </c>
+      <c r="AC310">
+        <v>1.08</v>
+      </c>
+      <c r="AD310">
+        <v>7.5</v>
+      </c>
+      <c r="AE310">
+        <v>1.42</v>
+      </c>
+      <c r="AF310">
+        <v>2.8</v>
+      </c>
+      <c r="AG310">
+        <v>2.15</v>
+      </c>
+      <c r="AH310">
+        <v>1.57</v>
+      </c>
+      <c r="AI310">
+        <v>1.95</v>
+      </c>
+      <c r="AJ310">
+        <v>1.8</v>
+      </c>
+      <c r="AK310">
+        <v>1.37</v>
+      </c>
+      <c r="AL310">
+        <v>1.34</v>
+      </c>
+      <c r="AM310">
+        <v>1.53</v>
+      </c>
+      <c r="AN310">
+        <v>1.67</v>
+      </c>
+      <c r="AO310">
+        <v>1.14</v>
+      </c>
+      <c r="AP310">
+        <v>1.75</v>
+      </c>
+      <c r="AQ310">
+        <v>1.07</v>
+      </c>
+      <c r="AR310">
+        <v>1.38</v>
+      </c>
+      <c r="AS310">
+        <v>1.32</v>
+      </c>
+      <c r="AT310">
+        <v>2.7</v>
+      </c>
+      <c r="AU310">
+        <v>5</v>
+      </c>
+      <c r="AV310">
+        <v>7</v>
+      </c>
+      <c r="AW310">
+        <v>7</v>
+      </c>
+      <c r="AX310">
+        <v>13</v>
+      </c>
+      <c r="AY310">
+        <v>14</v>
+      </c>
+      <c r="AZ310">
+        <v>25</v>
+      </c>
+      <c r="BA310">
+        <v>7</v>
+      </c>
+      <c r="BB310">
+        <v>7</v>
+      </c>
+      <c r="BC310">
+        <v>14</v>
+      </c>
+      <c r="BD310">
+        <v>1.95</v>
+      </c>
+      <c r="BE310">
+        <v>8</v>
+      </c>
+      <c r="BF310">
+        <v>2.05</v>
+      </c>
+      <c r="BG310">
+        <v>1.27</v>
+      </c>
+      <c r="BH310">
+        <v>3.3</v>
+      </c>
+      <c r="BI310">
+        <v>1.51</v>
+      </c>
+      <c r="BJ310">
+        <v>2.3</v>
+      </c>
+      <c r="BK310">
+        <v>1.9</v>
+      </c>
+      <c r="BL310">
+        <v>1.75</v>
+      </c>
+      <c r="BM310">
+        <v>2.55</v>
+      </c>
+      <c r="BN310">
+        <v>1.43</v>
+      </c>
+      <c r="BO310">
+        <v>3.5</v>
+      </c>
+      <c r="BP310">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="394">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -835,6 +835,9 @@
     <t>['45', '51']</t>
   </si>
   <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1190,6 +1193,9 @@
   </si>
   <si>
     <t>['21', '53']</t>
+  </si>
+  <si>
+    <t>['27', '40']</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP310"/>
+  <dimension ref="A1:BP311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1888,7 +1894,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ2">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2013,7 +2019,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2425,7 +2431,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2709,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ6">
         <v>1.44</v>
@@ -2837,7 +2843,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3249,7 +3255,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3455,7 +3461,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3867,7 +3873,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -4073,7 +4079,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4279,7 +4285,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4897,7 +4903,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5184,7 +5190,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ18">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
         <v>1.49</v>
@@ -5515,7 +5521,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5927,7 +5933,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6339,7 +6345,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6417,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24">
         <v>0.93</v>
@@ -6957,7 +6963,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7038,7 +7044,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR27">
         <v>1.54</v>
@@ -8193,7 +8199,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8605,7 +8611,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8811,7 +8817,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9635,7 +9641,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9841,7 +9847,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -10047,7 +10053,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10871,7 +10877,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10952,7 +10958,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>0.96</v>
@@ -11283,7 +11289,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11489,7 +11495,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11901,7 +11907,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -11979,7 +11985,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ51">
         <v>1.56</v>
@@ -12107,7 +12113,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -13549,7 +13555,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13961,7 +13967,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14167,7 +14173,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14991,7 +14997,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15403,7 +15409,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15687,7 +15693,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69">
         <v>1.2</v>
@@ -15815,7 +15821,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -15896,7 +15902,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ70">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR70">
         <v>1.7</v>
@@ -16021,7 +16027,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16227,7 +16233,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16433,7 +16439,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16639,7 +16645,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17051,7 +17057,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17257,7 +17263,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17463,7 +17469,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17669,7 +17675,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17875,7 +17881,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -18493,7 +18499,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18699,7 +18705,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18777,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ84">
         <v>1.5</v>
@@ -19111,7 +19117,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19192,7 +19198,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR86">
         <v>1.48</v>
@@ -19317,7 +19323,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19523,7 +19529,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -20141,7 +20147,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -22819,7 +22825,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -23025,7 +23031,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23515,7 +23521,7 @@
         <v>0.25</v>
       </c>
       <c r="AP107">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ107">
         <v>1</v>
@@ -24136,7 +24142,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ110">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR110">
         <v>1.32</v>
@@ -24673,7 +24679,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25497,7 +25503,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25703,7 +25709,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26527,7 +26533,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26608,7 +26614,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ122">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR122">
         <v>1.46</v>
@@ -27351,7 +27357,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27763,7 +27769,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27969,7 +27975,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28175,7 +28181,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28381,7 +28387,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28459,7 +28465,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ131">
         <v>1.07</v>
@@ -28587,7 +28593,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29411,7 +29417,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29823,7 +29829,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30441,7 +30447,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30647,7 +30653,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30853,7 +30859,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -31059,7 +31065,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31471,7 +31477,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -32089,7 +32095,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32295,7 +32301,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32579,7 +32585,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ151">
         <v>0.53</v>
@@ -32707,7 +32713,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33200,7 +33206,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ154">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR154">
         <v>1.17</v>
@@ -33325,7 +33331,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33737,7 +33743,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34149,7 +34155,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34561,7 +34567,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34973,7 +34979,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35385,7 +35391,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -36003,7 +36009,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36621,7 +36627,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36699,7 +36705,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ171">
         <v>1.19</v>
@@ -36905,7 +36911,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ172">
         <v>1.06</v>
@@ -37114,7 +37120,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ173">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR173">
         <v>1.69</v>
@@ -38063,7 +38069,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38269,7 +38275,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -39299,7 +39305,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39505,7 +39511,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -40123,7 +40129,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40741,7 +40747,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40947,7 +40953,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41977,7 +41983,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42264,7 +42270,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ198">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR198">
         <v>1.28</v>
@@ -42595,7 +42601,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -43007,7 +43013,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43085,7 +43091,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202">
         <v>2.07</v>
@@ -43419,7 +43425,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -44037,7 +44043,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44243,7 +44249,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -45067,7 +45073,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45273,7 +45279,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45891,7 +45897,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -45969,7 +45975,7 @@
         <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ216">
         <v>0.88</v>
@@ -46097,7 +46103,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46715,7 +46721,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46921,7 +46927,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47127,7 +47133,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47539,7 +47545,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47951,7 +47957,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48157,7 +48163,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48363,7 +48369,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48856,7 +48862,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ230">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR230">
         <v>1.34</v>
@@ -48981,7 +48987,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49187,7 +49193,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49805,7 +49811,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -50011,7 +50017,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50501,7 +50507,7 @@
         <v>1.82</v>
       </c>
       <c r="AP238">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ238">
         <v>1.67</v>
@@ -50629,7 +50635,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -51041,7 +51047,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51659,7 +51665,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -52895,7 +52901,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -52976,7 +52982,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ250">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR250">
         <v>1.79</v>
@@ -53513,7 +53519,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -54955,7 +54961,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55573,7 +55579,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -56191,7 +56197,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56397,7 +56403,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56603,7 +56609,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -56684,7 +56690,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ268">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR268">
         <v>1.56</v>
@@ -57221,7 +57227,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57299,7 +57305,7 @@
         <v>0.83</v>
       </c>
       <c r="AP271">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ271">
         <v>1.13</v>
@@ -57633,7 +57639,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -58045,7 +58051,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58869,7 +58875,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -59281,7 +59287,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60183,7 +60189,7 @@
         <v>0.93</v>
       </c>
       <c r="AP285">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ285">
         <v>0.8100000000000001</v>
@@ -60598,7 +60604,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ287">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AR287">
         <v>1.39</v>
@@ -60723,7 +60729,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -61135,7 +61141,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61341,7 +61347,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61547,7 +61553,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61959,7 +61965,7 @@
         <v>90</v>
       </c>
       <c r="P294" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q294">
         <v>4.5</v>
@@ -62989,7 +62995,7 @@
         <v>265</v>
       </c>
       <c r="P299" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q299">
         <v>3.5</v>
@@ -63195,7 +63201,7 @@
         <v>266</v>
       </c>
       <c r="P300" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q300">
         <v>3</v>
@@ -63607,7 +63613,7 @@
         <v>102</v>
       </c>
       <c r="P302" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q302">
         <v>2.1</v>
@@ -63813,7 +63819,7 @@
         <v>102</v>
       </c>
       <c r="P303" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q303">
         <v>4.33</v>
@@ -64225,7 +64231,7 @@
         <v>269</v>
       </c>
       <c r="P305" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q305">
         <v>2.75</v>
@@ -64431,7 +64437,7 @@
         <v>102</v>
       </c>
       <c r="P306" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q306">
         <v>2.88</v>
@@ -64637,7 +64643,7 @@
         <v>270</v>
       </c>
       <c r="P307" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q307">
         <v>2</v>
@@ -64843,7 +64849,7 @@
         <v>271</v>
       </c>
       <c r="P308" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q308">
         <v>2.25</v>
@@ -65049,7 +65055,7 @@
         <v>200</v>
       </c>
       <c r="P309" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q309">
         <v>3.25</v>
@@ -65412,6 +65418,212 @@
       </c>
       <c r="BP310">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7509893</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45746.51041666666</v>
+      </c>
+      <c r="F311">
+        <v>31</v>
+      </c>
+      <c r="G311" t="s">
+        <v>74</v>
+      </c>
+      <c r="H311" t="s">
+        <v>89</v>
+      </c>
+      <c r="I311">
+        <v>0</v>
+      </c>
+      <c r="J311">
+        <v>2</v>
+      </c>
+      <c r="K311">
+        <v>2</v>
+      </c>
+      <c r="L311">
+        <v>1</v>
+      </c>
+      <c r="M311">
+        <v>2</v>
+      </c>
+      <c r="N311">
+        <v>3</v>
+      </c>
+      <c r="O311" t="s">
+        <v>273</v>
+      </c>
+      <c r="P311" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q311">
+        <v>3.25</v>
+      </c>
+      <c r="R311">
+        <v>2.05</v>
+      </c>
+      <c r="S311">
+        <v>3.5</v>
+      </c>
+      <c r="T311">
+        <v>1.44</v>
+      </c>
+      <c r="U311">
+        <v>2.63</v>
+      </c>
+      <c r="V311">
+        <v>3.25</v>
+      </c>
+      <c r="W311">
+        <v>1.33</v>
+      </c>
+      <c r="X311">
+        <v>10</v>
+      </c>
+      <c r="Y311">
+        <v>1.06</v>
+      </c>
+      <c r="Z311">
+        <v>2.72</v>
+      </c>
+      <c r="AA311">
+        <v>3.19</v>
+      </c>
+      <c r="AB311">
+        <v>2.83</v>
+      </c>
+      <c r="AC311">
+        <v>1.07</v>
+      </c>
+      <c r="AD311">
+        <v>8</v>
+      </c>
+      <c r="AE311">
+        <v>1.36</v>
+      </c>
+      <c r="AF311">
+        <v>3.1</v>
+      </c>
+      <c r="AG311">
+        <v>2.03</v>
+      </c>
+      <c r="AH311">
+        <v>1.79</v>
+      </c>
+      <c r="AI311">
+        <v>1.91</v>
+      </c>
+      <c r="AJ311">
+        <v>1.91</v>
+      </c>
+      <c r="AK311">
+        <v>1.44</v>
+      </c>
+      <c r="AL311">
+        <v>1.34</v>
+      </c>
+      <c r="AM311">
+        <v>1.46</v>
+      </c>
+      <c r="AN311">
+        <v>1.47</v>
+      </c>
+      <c r="AO311">
+        <v>1.13</v>
+      </c>
+      <c r="AP311">
+        <v>1.38</v>
+      </c>
+      <c r="AQ311">
+        <v>1.25</v>
+      </c>
+      <c r="AR311">
+        <v>1.72</v>
+      </c>
+      <c r="AS311">
+        <v>1.35</v>
+      </c>
+      <c r="AT311">
+        <v>3.07</v>
+      </c>
+      <c r="AU311">
+        <v>4</v>
+      </c>
+      <c r="AV311">
+        <v>5</v>
+      </c>
+      <c r="AW311">
+        <v>11</v>
+      </c>
+      <c r="AX311">
+        <v>5</v>
+      </c>
+      <c r="AY311">
+        <v>20</v>
+      </c>
+      <c r="AZ311">
+        <v>11</v>
+      </c>
+      <c r="BA311">
+        <v>3</v>
+      </c>
+      <c r="BB311">
+        <v>2</v>
+      </c>
+      <c r="BC311">
+        <v>5</v>
+      </c>
+      <c r="BD311">
+        <v>1.75</v>
+      </c>
+      <c r="BE311">
+        <v>8.5</v>
+      </c>
+      <c r="BF311">
+        <v>2.3</v>
+      </c>
+      <c r="BG311">
+        <v>1.25</v>
+      </c>
+      <c r="BH311">
+        <v>3.4</v>
+      </c>
+      <c r="BI311">
+        <v>1.47</v>
+      </c>
+      <c r="BJ311">
+        <v>2.4</v>
+      </c>
+      <c r="BK311">
+        <v>1.83</v>
+      </c>
+      <c r="BL311">
+        <v>1.8</v>
+      </c>
+      <c r="BM311">
+        <v>2.4</v>
+      </c>
+      <c r="BN311">
+        <v>1.46</v>
+      </c>
+      <c r="BO311">
+        <v>3.4</v>
+      </c>
+      <c r="BP311">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="399">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -838,6 +838,15 @@
     <t>['90+1']</t>
   </si>
   <si>
+    <t>['38', '90+7']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['7']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -938,9 +947,6 @@
   </si>
   <si>
     <t>['49']</t>
-  </si>
-  <si>
-    <t>['27']</t>
   </si>
   <si>
     <t>['34', '56']</t>
@@ -1196,6 +1202,15 @@
   </si>
   <si>
     <t>['27', '40']</t>
+  </si>
+  <si>
+    <t>['24', '44']</t>
+  </si>
+  <si>
+    <t>['50', '90+5']</t>
+  </si>
+  <si>
+    <t>['27', '50']</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP311"/>
+  <dimension ref="A1:BP318"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1891,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ2">
         <v>1.25</v>
@@ -2019,7 +2034,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2306,7 +2321,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ4">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2431,7 +2446,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2509,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -2843,7 +2858,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2921,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ7">
         <v>0.93</v>
@@ -3130,7 +3145,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ8">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3255,7 +3270,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3333,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3461,7 +3476,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3748,7 +3763,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ11">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3873,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -4079,7 +4094,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4160,7 +4175,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ13">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -4285,7 +4300,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4569,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ15">
         <v>1.44</v>
@@ -4778,7 +4793,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4903,7 +4918,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -5187,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ18">
         <v>1.25</v>
@@ -5521,7 +5536,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5602,7 +5617,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ20">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5933,7 +5948,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6345,7 +6360,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6629,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ25">
         <v>1.56</v>
@@ -6835,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ26">
         <v>1.06</v>
@@ -6963,7 +6978,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -7247,10 +7262,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR28">
         <v>2.15</v>
@@ -7865,10 +7880,10 @@
         <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ31">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR31">
         <v>0</v>
@@ -8199,7 +8214,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8483,7 +8498,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ34">
         <v>0.88</v>
@@ -8611,7 +8626,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8692,7 +8707,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ35">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR35">
         <v>1.36</v>
@@ -8817,7 +8832,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9101,7 +9116,7 @@
         <v>2</v>
       </c>
       <c r="AP37">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ37">
         <v>1.19</v>
@@ -9310,7 +9325,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ38">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>1.18</v>
@@ -9516,7 +9531,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ39">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR39">
         <v>0</v>
@@ -9641,7 +9656,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9847,7 +9862,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9928,7 +9943,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ41">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR41">
         <v>1.16</v>
@@ -10053,7 +10068,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10134,7 +10149,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ42">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -10337,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ43">
         <v>1.2</v>
@@ -10546,7 +10561,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR44">
         <v>1.6</v>
@@ -10749,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ45">
         <v>1.13</v>
@@ -10877,7 +10892,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -10955,7 +10970,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ46">
         <v>1.25</v>
@@ -11289,7 +11304,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11367,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ48">
         <v>1.06</v>
@@ -11495,7 +11510,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11907,7 +11922,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12113,7 +12128,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12194,7 +12209,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ52">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR52">
         <v>1.42</v>
@@ -12809,7 +12824,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ55">
         <v>1.06</v>
@@ -13015,10 +13030,10 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ56">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR56">
         <v>1.46</v>
@@ -13555,7 +13570,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13633,7 +13648,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
         <v>1.07</v>
@@ -13967,7 +13982,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14048,7 +14063,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ61">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR61">
         <v>1.42</v>
@@ -14173,7 +14188,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -14251,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ62">
         <v>1.13</v>
@@ -14666,7 +14681,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.44</v>
@@ -14997,7 +15012,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15078,7 +15093,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ66">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR66">
         <v>1.61</v>
@@ -15281,7 +15296,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ67">
         <v>1.56</v>
@@ -15409,7 +15424,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15821,7 +15836,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -16027,7 +16042,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16105,10 +16120,10 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ71">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR71">
         <v>1.89</v>
@@ -16233,7 +16248,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16439,7 +16454,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16517,10 +16532,10 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16645,7 +16660,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17057,7 +17072,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17135,7 +17150,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17263,7 +17278,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17469,7 +17484,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17675,7 +17690,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17881,7 +17896,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17962,7 +17977,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ80">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR80">
         <v>1.3</v>
@@ -18168,7 +18183,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ81">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
         <v>1.68</v>
@@ -18499,7 +18514,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18705,7 +18720,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -18989,10 +19004,10 @@
         <v>0.67</v>
       </c>
       <c r="AP85">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ85">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR85">
         <v>1.41</v>
@@ -19117,7 +19132,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19323,7 +19338,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19401,7 +19416,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ87">
         <v>2.07</v>
@@ -19529,7 +19544,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -19607,10 +19622,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ88">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR88">
         <v>1.29</v>
@@ -19816,7 +19831,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ89">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR89">
         <v>1.21</v>
@@ -20019,7 +20034,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ90">
         <v>1.13</v>
@@ -20147,7 +20162,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -21052,7 +21067,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ95">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -21464,7 +21479,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ97">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR97">
         <v>1.32</v>
@@ -22079,7 +22094,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ100">
         <v>1.56</v>
@@ -22288,7 +22303,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR101">
         <v>1.13</v>
@@ -22494,7 +22509,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ102">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22697,7 +22712,7 @@
         <v>1.4</v>
       </c>
       <c r="AP103">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ103">
         <v>1.5</v>
@@ -22825,7 +22840,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22903,7 +22918,7 @@
         <v>2.2</v>
       </c>
       <c r="AP104">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ104">
         <v>2.07</v>
@@ -23031,7 +23046,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23112,7 +23127,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR105">
         <v>1.48</v>
@@ -23315,10 +23330,10 @@
         <v>0.75</v>
       </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ106">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR106">
         <v>1.29</v>
@@ -23933,7 +23948,7 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ109">
         <v>0.93</v>
@@ -24345,7 +24360,7 @@
         <v>0.75</v>
       </c>
       <c r="AP111">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ111">
         <v>1.2</v>
@@ -24554,7 +24569,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ112">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR112">
         <v>1.57</v>
@@ -24679,7 +24694,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25503,7 +25518,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25584,7 +25599,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ117">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -25709,7 +25724,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26408,7 +26423,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ121">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26533,7 +26548,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26611,7 +26626,7 @@
         <v>1.57</v>
       </c>
       <c r="AP122">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ122">
         <v>1.25</v>
@@ -27023,7 +27038,7 @@
         <v>1.33</v>
       </c>
       <c r="AP124">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ124">
         <v>0.93</v>
@@ -27232,7 +27247,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ125">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR125">
         <v>1.55</v>
@@ -27357,7 +27372,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27435,10 +27450,10 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ126">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR126">
         <v>1.73</v>
@@ -27644,7 +27659,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ127">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR127">
         <v>1.2</v>
@@ -27769,7 +27784,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27847,7 +27862,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ128">
         <v>1.5</v>
@@ -27975,7 +27990,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28053,7 +28068,7 @@
         <v>0.4</v>
       </c>
       <c r="AP129">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ129">
         <v>1</v>
@@ -28181,7 +28196,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28259,7 +28274,7 @@
         <v>0.8</v>
       </c>
       <c r="AP130">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ130">
         <v>1.2</v>
@@ -28387,7 +28402,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28593,7 +28608,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -28674,7 +28689,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ132">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR132">
         <v>1.56</v>
@@ -28880,7 +28895,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ133">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR133">
         <v>1.46</v>
@@ -29083,7 +29098,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ134">
         <v>1.06</v>
@@ -29417,7 +29432,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29498,7 +29513,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ136">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR136">
         <v>1.26</v>
@@ -29829,7 +29844,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30447,7 +30462,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30653,7 +30668,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30731,7 +30746,7 @@
         <v>2.14</v>
       </c>
       <c r="AP142">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ142">
         <v>2.07</v>
@@ -30859,7 +30874,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -31065,7 +31080,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31146,7 +31161,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR144">
         <v>1.46</v>
@@ -31349,7 +31364,7 @@
         <v>1.5</v>
       </c>
       <c r="AP145">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ145">
         <v>1.07</v>
@@ -31477,7 +31492,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31555,7 +31570,7 @@
         <v>1.43</v>
       </c>
       <c r="AP146">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ146">
         <v>1.19</v>
@@ -31764,7 +31779,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ147">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR147">
         <v>1.21</v>
@@ -32095,7 +32110,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32173,10 +32188,10 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ149">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR149">
         <v>1.34</v>
@@ -32301,7 +32316,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32379,7 +32394,7 @@
         <v>0.83</v>
       </c>
       <c r="AP150">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ150">
         <v>1</v>
@@ -32588,7 +32603,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ151">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR151">
         <v>1.67</v>
@@ -32713,7 +32728,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -32791,7 +32806,7 @@
         <v>0.86</v>
       </c>
       <c r="AP152">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ152">
         <v>1.06</v>
@@ -33331,7 +33346,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33618,7 +33633,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33743,7 +33758,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34155,7 +34170,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34567,7 +34582,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34851,7 +34866,7 @@
         <v>1.43</v>
       </c>
       <c r="AP162">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ162">
         <v>1.07</v>
@@ -34979,7 +34994,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35060,7 +35075,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ163">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR163">
         <v>1.43</v>
@@ -35263,10 +35278,10 @@
         <v>0.63</v>
       </c>
       <c r="AP164">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ164">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR164">
         <v>1.25</v>
@@ -35391,7 +35406,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35469,7 +35484,7 @@
         <v>2.25</v>
       </c>
       <c r="AP165">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ165">
         <v>2.07</v>
@@ -35678,7 +35693,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -36009,7 +36024,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36293,10 +36308,10 @@
         <v>0.5</v>
       </c>
       <c r="AP169">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ169">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36499,10 +36514,10 @@
         <v>1.63</v>
       </c>
       <c r="AP170">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ170">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR170">
         <v>1.38</v>
@@ -36627,7 +36642,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -37532,7 +37547,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ175">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR175">
         <v>1.25</v>
@@ -38069,7 +38084,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38147,7 +38162,7 @@
         <v>1.13</v>
       </c>
       <c r="AP178">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ178">
         <v>0.88</v>
@@ -38275,7 +38290,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38559,7 +38574,7 @@
         <v>0.63</v>
       </c>
       <c r="AP180">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ180">
         <v>1</v>
@@ -38971,7 +38986,7 @@
         <v>2.33</v>
       </c>
       <c r="AP182">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ182">
         <v>2.07</v>
@@ -39177,7 +39192,7 @@
         <v>1.56</v>
       </c>
       <c r="AP183">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ183">
         <v>1.19</v>
@@ -39305,7 +39320,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39386,7 +39401,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ184">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR184">
         <v>1.68</v>
@@ -39511,7 +39526,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -40004,7 +40019,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ187">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR187">
         <v>1.56</v>
@@ -40129,7 +40144,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40207,10 +40222,10 @@
         <v>0.89</v>
       </c>
       <c r="AP188">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ188">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR188">
         <v>1.56</v>
@@ -40413,10 +40428,10 @@
         <v>0.75</v>
       </c>
       <c r="AP189">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ189">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.33</v>
@@ -40747,7 +40762,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40828,7 +40843,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ191">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR191">
         <v>1.37</v>
@@ -40953,7 +40968,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41652,7 +41667,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ195">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR195">
         <v>1.65</v>
@@ -41983,7 +41998,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42267,7 +42282,7 @@
         <v>1.2</v>
       </c>
       <c r="AP198">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ198">
         <v>1.25</v>
@@ -42476,7 +42491,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ199">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR199">
         <v>1.22</v>
@@ -42601,7 +42616,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -42679,7 +42694,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ200">
         <v>1.13</v>
@@ -43013,7 +43028,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43297,7 +43312,7 @@
         <v>1.11</v>
       </c>
       <c r="AP203">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ203">
         <v>1.07</v>
@@ -43425,7 +43440,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43712,7 +43727,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ205">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR205">
         <v>1.88</v>
@@ -44043,7 +44058,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44124,7 +44139,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ207">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR207">
         <v>1.56</v>
@@ -44249,7 +44264,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44327,10 +44342,10 @@
         <v>1.7</v>
       </c>
       <c r="AP208">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ208">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR208">
         <v>1.42</v>
@@ -44739,7 +44754,7 @@
         <v>1</v>
       </c>
       <c r="AP210">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ210">
         <v>0.93</v>
@@ -44945,10 +44960,10 @@
         <v>0.6</v>
       </c>
       <c r="AP211">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ211">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR211">
         <v>1.37</v>
@@ -45073,7 +45088,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45279,7 +45294,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45357,10 +45372,10 @@
         <v>0.55</v>
       </c>
       <c r="AP213">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ213">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR213">
         <v>1.3</v>
@@ -45566,7 +45581,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ214">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR214">
         <v>1.56</v>
@@ -45897,7 +45912,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46103,7 +46118,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46721,7 +46736,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46927,7 +46942,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47133,7 +47148,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47417,10 +47432,10 @@
         <v>0.55</v>
       </c>
       <c r="AP223">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ223">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR223">
         <v>1.25</v>
@@ -47545,7 +47560,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47623,7 +47638,7 @@
         <v>0.91</v>
       </c>
       <c r="AP224">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ224">
         <v>1.06</v>
@@ -47957,7 +47972,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48163,7 +48178,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48369,7 +48384,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -48447,7 +48462,7 @@
         <v>1.1</v>
       </c>
       <c r="AP228">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ228">
         <v>1.2</v>
@@ -48653,10 +48668,10 @@
         <v>0.6</v>
       </c>
       <c r="AP229">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ229">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR229">
         <v>1.45</v>
@@ -48859,7 +48874,7 @@
         <v>1.09</v>
       </c>
       <c r="AP230">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ230">
         <v>1.25</v>
@@ -48987,7 +49002,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49068,7 +49083,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ231">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR231">
         <v>1.71</v>
@@ -49193,7 +49208,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49480,7 +49495,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ233">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR233">
         <v>1.42</v>
@@ -49811,7 +49826,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -49889,7 +49904,7 @@
         <v>1.5</v>
       </c>
       <c r="AP235">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ235">
         <v>1.5</v>
@@ -50017,7 +50032,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50304,7 +50319,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ237">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR237">
         <v>1.46</v>
@@ -50510,7 +50525,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ238">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR238">
         <v>1.73</v>
@@ -50635,7 +50650,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -51047,7 +51062,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51331,10 +51346,10 @@
         <v>0.55</v>
       </c>
       <c r="AP242">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ242">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -51537,7 +51552,7 @@
         <v>1.33</v>
       </c>
       <c r="AP243">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ243">
         <v>1.44</v>
@@ -51665,7 +51680,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51949,7 +51964,7 @@
         <v>1.27</v>
       </c>
       <c r="AP245">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ245">
         <v>1.2</v>
@@ -52158,7 +52173,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ246">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR246">
         <v>1.59</v>
@@ -52364,7 +52379,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ247">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR247">
         <v>1.4</v>
@@ -52773,7 +52788,7 @@
         <v>0.67</v>
       </c>
       <c r="AP249">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ249">
         <v>1</v>
@@ -52901,7 +52916,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -53185,7 +53200,7 @@
         <v>1.09</v>
       </c>
       <c r="AP251">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ251">
         <v>1.07</v>
@@ -53519,7 +53534,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -54218,7 +54233,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ256">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR256">
         <v>1.38</v>
@@ -54424,7 +54439,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ257">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR257">
         <v>1.38</v>
@@ -54627,7 +54642,7 @@
         <v>1</v>
       </c>
       <c r="AP258">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ258">
         <v>0.88</v>
@@ -54833,10 +54848,10 @@
         <v>0.83</v>
       </c>
       <c r="AP259">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ259">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR259">
         <v>1.26</v>
@@ -54961,7 +54976,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55042,7 +55057,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ260">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR260">
         <v>1.76</v>
@@ -55579,7 +55594,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55657,10 +55672,10 @@
         <v>0.77</v>
       </c>
       <c r="AP263">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ263">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR263">
         <v>1.4</v>
@@ -56069,7 +56084,7 @@
         <v>1.15</v>
       </c>
       <c r="AP265">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ265">
         <v>1.19</v>
@@ -56197,7 +56212,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56275,10 +56290,10 @@
         <v>0.46</v>
       </c>
       <c r="AP266">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ266">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR266">
         <v>1.3</v>
@@ -56403,7 +56418,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56609,7 +56624,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -57099,7 +57114,7 @@
         <v>1</v>
       </c>
       <c r="AP270">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ270">
         <v>1.06</v>
@@ -57227,7 +57242,7 @@
         <v>165</v>
       </c>
       <c r="P271" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="Q271">
         <v>2.65</v>
@@ -57639,7 +57654,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -57720,7 +57735,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ273">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR273">
         <v>1.39</v>
@@ -57926,7 +57941,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ274">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR274">
         <v>1.43</v>
@@ -58051,7 +58066,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58129,10 +58144,10 @@
         <v>0.71</v>
       </c>
       <c r="AP275">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ275">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR275">
         <v>1.45</v>
@@ -58335,7 +58350,7 @@
         <v>1.36</v>
       </c>
       <c r="AP276">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ276">
         <v>1.44</v>
@@ -58875,7 +58890,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -59162,7 +59177,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ280">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR280">
         <v>1.4</v>
@@ -59287,7 +59302,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60192,7 +60207,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ285">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR285">
         <v>1.71</v>
@@ -60729,7 +60744,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -60807,7 +60822,7 @@
         <v>1</v>
       </c>
       <c r="AP288">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AQ288">
         <v>1</v>
@@ -61141,7 +61156,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61347,7 +61362,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61425,7 +61440,7 @@
         <v>1</v>
       </c>
       <c r="AP291">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ291">
         <v>1.06</v>
@@ -61553,7 +61568,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61634,7 +61649,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ292">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR292">
         <v>1.84</v>
@@ -61965,7 +61980,7 @@
         <v>90</v>
       </c>
       <c r="P294" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q294">
         <v>4.5</v>
@@ -62043,7 +62058,7 @@
         <v>2</v>
       </c>
       <c r="AP294">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ294">
         <v>2.07</v>
@@ -62249,7 +62264,7 @@
         <v>1</v>
       </c>
       <c r="AP295">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ295">
         <v>1.06</v>
@@ -62455,10 +62470,10 @@
         <v>0.87</v>
       </c>
       <c r="AP296">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AQ296">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR296">
         <v>1.27</v>
@@ -62664,7 +62679,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ297">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR297">
         <v>1.35</v>
@@ -62867,10 +62882,10 @@
         <v>0.67</v>
       </c>
       <c r="AP298">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AQ298">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AR298">
         <v>1.5</v>
@@ -62995,7 +63010,7 @@
         <v>265</v>
       </c>
       <c r="P299" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q299">
         <v>3.5</v>
@@ -63073,7 +63088,7 @@
         <v>0.93</v>
       </c>
       <c r="AP299">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AQ299">
         <v>0.93</v>
@@ -63201,7 +63216,7 @@
         <v>266</v>
       </c>
       <c r="P300" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q300">
         <v>3</v>
@@ -63282,7 +63297,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ300">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR300">
         <v>1.47</v>
@@ -63488,7 +63503,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ301">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR301">
         <v>1.38</v>
@@ -63613,7 +63628,7 @@
         <v>102</v>
       </c>
       <c r="P302" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q302">
         <v>2.1</v>
@@ -63819,7 +63834,7 @@
         <v>102</v>
       </c>
       <c r="P303" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q303">
         <v>4.33</v>
@@ -64231,7 +64246,7 @@
         <v>269</v>
       </c>
       <c r="P305" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q305">
         <v>2.75</v>
@@ -64437,7 +64452,7 @@
         <v>102</v>
       </c>
       <c r="P306" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q306">
         <v>2.88</v>
@@ -64643,7 +64658,7 @@
         <v>270</v>
       </c>
       <c r="P307" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q307">
         <v>2</v>
@@ -64849,7 +64864,7 @@
         <v>271</v>
       </c>
       <c r="P308" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q308">
         <v>2.25</v>
@@ -65055,7 +65070,7 @@
         <v>200</v>
       </c>
       <c r="P309" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q309">
         <v>3.25</v>
@@ -65467,7 +65482,7 @@
         <v>273</v>
       </c>
       <c r="P311" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q311">
         <v>3.25</v>
@@ -65624,6 +65639,1448 @@
       </c>
       <c r="BP311">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="312" spans="1:68">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>7509904</v>
+      </c>
+      <c r="C312" t="s">
+        <v>68</v>
+      </c>
+      <c r="D312" t="s">
+        <v>69</v>
+      </c>
+      <c r="E312" s="2">
+        <v>45751.64583333334</v>
+      </c>
+      <c r="F312">
+        <v>32</v>
+      </c>
+      <c r="G312" t="s">
+        <v>77</v>
+      </c>
+      <c r="H312" t="s">
+        <v>82</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+      <c r="J312">
+        <v>1</v>
+      </c>
+      <c r="K312">
+        <v>2</v>
+      </c>
+      <c r="L312">
+        <v>1</v>
+      </c>
+      <c r="M312">
+        <v>2</v>
+      </c>
+      <c r="N312">
+        <v>3</v>
+      </c>
+      <c r="O312" t="s">
+        <v>141</v>
+      </c>
+      <c r="P312" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q312">
+        <v>4.33</v>
+      </c>
+      <c r="R312">
+        <v>2</v>
+      </c>
+      <c r="S312">
+        <v>2.88</v>
+      </c>
+      <c r="T312">
+        <v>1.5</v>
+      </c>
+      <c r="U312">
+        <v>2.5</v>
+      </c>
+      <c r="V312">
+        <v>3.4</v>
+      </c>
+      <c r="W312">
+        <v>1.3</v>
+      </c>
+      <c r="X312">
+        <v>10</v>
+      </c>
+      <c r="Y312">
+        <v>1.06</v>
+      </c>
+      <c r="Z312">
+        <v>3.63</v>
+      </c>
+      <c r="AA312">
+        <v>3.29</v>
+      </c>
+      <c r="AB312">
+        <v>2.19</v>
+      </c>
+      <c r="AC312">
+        <v>1.08</v>
+      </c>
+      <c r="AD312">
+        <v>7.5</v>
+      </c>
+      <c r="AE312">
+        <v>1.42</v>
+      </c>
+      <c r="AF312">
+        <v>2.85</v>
+      </c>
+      <c r="AG312">
+        <v>2.1</v>
+      </c>
+      <c r="AH312">
+        <v>1.6</v>
+      </c>
+      <c r="AI312">
+        <v>1.95</v>
+      </c>
+      <c r="AJ312">
+        <v>1.8</v>
+      </c>
+      <c r="AK312">
+        <v>1.68</v>
+      </c>
+      <c r="AL312">
+        <v>1.32</v>
+      </c>
+      <c r="AM312">
+        <v>1.29</v>
+      </c>
+      <c r="AN312">
+        <v>1.2</v>
+      </c>
+      <c r="AO312">
+        <v>1.67</v>
+      </c>
+      <c r="AP312">
+        <v>1.13</v>
+      </c>
+      <c r="AQ312">
+        <v>1.75</v>
+      </c>
+      <c r="AR312">
+        <v>1.32</v>
+      </c>
+      <c r="AS312">
+        <v>1.57</v>
+      </c>
+      <c r="AT312">
+        <v>2.89</v>
+      </c>
+      <c r="AU312">
+        <v>3</v>
+      </c>
+      <c r="AV312">
+        <v>7</v>
+      </c>
+      <c r="AW312">
+        <v>11</v>
+      </c>
+      <c r="AX312">
+        <v>11</v>
+      </c>
+      <c r="AY312">
+        <v>19</v>
+      </c>
+      <c r="AZ312">
+        <v>22</v>
+      </c>
+      <c r="BA312">
+        <v>2</v>
+      </c>
+      <c r="BB312">
+        <v>7</v>
+      </c>
+      <c r="BC312">
+        <v>9</v>
+      </c>
+      <c r="BD312">
+        <v>2.55</v>
+      </c>
+      <c r="BE312">
+        <v>6.4</v>
+      </c>
+      <c r="BF312">
+        <v>1.65</v>
+      </c>
+      <c r="BG312">
+        <v>1.4</v>
+      </c>
+      <c r="BH312">
+        <v>2.7</v>
+      </c>
+      <c r="BI312">
+        <v>1.68</v>
+      </c>
+      <c r="BJ312">
+        <v>2.05</v>
+      </c>
+      <c r="BK312">
+        <v>2.07</v>
+      </c>
+      <c r="BL312">
+        <v>1.67</v>
+      </c>
+      <c r="BM312">
+        <v>2.65</v>
+      </c>
+      <c r="BN312">
+        <v>1.41</v>
+      </c>
+      <c r="BO312">
+        <v>3.55</v>
+      </c>
+      <c r="BP312">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="313" spans="1:68">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>7509899</v>
+      </c>
+      <c r="C313" t="s">
+        <v>68</v>
+      </c>
+      <c r="D313" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F313">
+        <v>32</v>
+      </c>
+      <c r="G313" t="s">
+        <v>87</v>
+      </c>
+      <c r="H313" t="s">
+        <v>86</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
+      </c>
+      <c r="N313">
+        <v>0</v>
+      </c>
+      <c r="O313" t="s">
+        <v>102</v>
+      </c>
+      <c r="P313" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q313">
+        <v>3.5</v>
+      </c>
+      <c r="R313">
+        <v>1.95</v>
+      </c>
+      <c r="S313">
+        <v>3.5</v>
+      </c>
+      <c r="T313">
+        <v>1.53</v>
+      </c>
+      <c r="U313">
+        <v>2.38</v>
+      </c>
+      <c r="V313">
+        <v>3.5</v>
+      </c>
+      <c r="W313">
+        <v>1.29</v>
+      </c>
+      <c r="X313">
+        <v>11</v>
+      </c>
+      <c r="Y313">
+        <v>1.05</v>
+      </c>
+      <c r="Z313">
+        <v>2.84</v>
+      </c>
+      <c r="AA313">
+        <v>3.03</v>
+      </c>
+      <c r="AB313">
+        <v>2.84</v>
+      </c>
+      <c r="AC313">
+        <v>1.11</v>
+      </c>
+      <c r="AD313">
+        <v>7.49</v>
+      </c>
+      <c r="AE313">
+        <v>1.38</v>
+      </c>
+      <c r="AF313">
+        <v>3.14</v>
+      </c>
+      <c r="AG313">
+        <v>2.25</v>
+      </c>
+      <c r="AH313">
+        <v>1.53</v>
+      </c>
+      <c r="AI313">
+        <v>2</v>
+      </c>
+      <c r="AJ313">
+        <v>1.75</v>
+      </c>
+      <c r="AK313">
+        <v>1.45</v>
+      </c>
+      <c r="AL313">
+        <v>1.44</v>
+      </c>
+      <c r="AM313">
+        <v>1.46</v>
+      </c>
+      <c r="AN313">
+        <v>0.8</v>
+      </c>
+      <c r="AO313">
+        <v>0.53</v>
+      </c>
+      <c r="AP313">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AQ313">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR313">
+        <v>1.39</v>
+      </c>
+      <c r="AS313">
+        <v>1.18</v>
+      </c>
+      <c r="AT313">
+        <v>2.57</v>
+      </c>
+      <c r="AU313">
+        <v>3</v>
+      </c>
+      <c r="AV313">
+        <v>2</v>
+      </c>
+      <c r="AW313">
+        <v>6</v>
+      </c>
+      <c r="AX313">
+        <v>6</v>
+      </c>
+      <c r="AY313">
+        <v>10</v>
+      </c>
+      <c r="AZ313">
+        <v>9</v>
+      </c>
+      <c r="BA313">
+        <v>3</v>
+      </c>
+      <c r="BB313">
+        <v>5</v>
+      </c>
+      <c r="BC313">
+        <v>8</v>
+      </c>
+      <c r="BD313">
+        <v>2</v>
+      </c>
+      <c r="BE313">
+        <v>6.3</v>
+      </c>
+      <c r="BF313">
+        <v>2.3</v>
+      </c>
+      <c r="BG313">
+        <v>1.31</v>
+      </c>
+      <c r="BH313">
+        <v>2.92</v>
+      </c>
+      <c r="BI313">
+        <v>1.62</v>
+      </c>
+      <c r="BJ313">
+        <v>2.22</v>
+      </c>
+      <c r="BK313">
+        <v>2.03</v>
+      </c>
+      <c r="BL313">
+        <v>1.75</v>
+      </c>
+      <c r="BM313">
+        <v>2.67</v>
+      </c>
+      <c r="BN313">
+        <v>1.39</v>
+      </c>
+      <c r="BO313">
+        <v>3.68</v>
+      </c>
+      <c r="BP313">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:68">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>7509900</v>
+      </c>
+      <c r="C314" t="s">
+        <v>68</v>
+      </c>
+      <c r="D314" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F314">
+        <v>32</v>
+      </c>
+      <c r="G314" t="s">
+        <v>75</v>
+      </c>
+      <c r="H314" t="s">
+        <v>79</v>
+      </c>
+      <c r="I314">
+        <v>1</v>
+      </c>
+      <c r="J314">
+        <v>2</v>
+      </c>
+      <c r="K314">
+        <v>3</v>
+      </c>
+      <c r="L314">
+        <v>2</v>
+      </c>
+      <c r="M314">
+        <v>2</v>
+      </c>
+      <c r="N314">
+        <v>4</v>
+      </c>
+      <c r="O314" t="s">
+        <v>274</v>
+      </c>
+      <c r="P314" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q314">
+        <v>2.63</v>
+      </c>
+      <c r="R314">
+        <v>2</v>
+      </c>
+      <c r="S314">
+        <v>5</v>
+      </c>
+      <c r="T314">
+        <v>1.5</v>
+      </c>
+      <c r="U314">
+        <v>2.5</v>
+      </c>
+      <c r="V314">
+        <v>3.5</v>
+      </c>
+      <c r="W314">
+        <v>1.29</v>
+      </c>
+      <c r="X314">
+        <v>11</v>
+      </c>
+      <c r="Y314">
+        <v>1.05</v>
+      </c>
+      <c r="Z314">
+        <v>2.02</v>
+      </c>
+      <c r="AA314">
+        <v>3.31</v>
+      </c>
+      <c r="AB314">
+        <v>4.2</v>
+      </c>
+      <c r="AC314">
+        <v>1.11</v>
+      </c>
+      <c r="AD314">
+        <v>7.34</v>
+      </c>
+      <c r="AE314">
+        <v>1.48</v>
+      </c>
+      <c r="AF314">
+        <v>2.76</v>
+      </c>
+      <c r="AG314">
+        <v>2.2</v>
+      </c>
+      <c r="AH314">
+        <v>1.55</v>
+      </c>
+      <c r="AI314">
+        <v>2.05</v>
+      </c>
+      <c r="AJ314">
+        <v>1.7</v>
+      </c>
+      <c r="AK314">
+        <v>1.21</v>
+      </c>
+      <c r="AL314">
+        <v>1.34</v>
+      </c>
+      <c r="AM314">
+        <v>2.03</v>
+      </c>
+      <c r="AN314">
+        <v>1.19</v>
+      </c>
+      <c r="AO314">
+        <v>0.73</v>
+      </c>
+      <c r="AP314">
+        <v>1.18</v>
+      </c>
+      <c r="AQ314">
+        <v>0.75</v>
+      </c>
+      <c r="AR314">
+        <v>1.44</v>
+      </c>
+      <c r="AS314">
+        <v>1.39</v>
+      </c>
+      <c r="AT314">
+        <v>2.83</v>
+      </c>
+      <c r="AU314">
+        <v>6</v>
+      </c>
+      <c r="AV314">
+        <v>4</v>
+      </c>
+      <c r="AW314">
+        <v>13</v>
+      </c>
+      <c r="AX314">
+        <v>3</v>
+      </c>
+      <c r="AY314">
+        <v>20</v>
+      </c>
+      <c r="AZ314">
+        <v>7</v>
+      </c>
+      <c r="BA314">
+        <v>6</v>
+      </c>
+      <c r="BB314">
+        <v>0</v>
+      </c>
+      <c r="BC314">
+        <v>6</v>
+      </c>
+      <c r="BD314">
+        <v>1.61</v>
+      </c>
+      <c r="BE314">
+        <v>6.75</v>
+      </c>
+      <c r="BF314">
+        <v>3.08</v>
+      </c>
+      <c r="BG314">
+        <v>1.24</v>
+      </c>
+      <c r="BH314">
+        <v>3.34</v>
+      </c>
+      <c r="BI314">
+        <v>1.52</v>
+      </c>
+      <c r="BJ314">
+        <v>2.4</v>
+      </c>
+      <c r="BK314">
+        <v>1.91</v>
+      </c>
+      <c r="BL314">
+        <v>1.89</v>
+      </c>
+      <c r="BM314">
+        <v>2.38</v>
+      </c>
+      <c r="BN314">
+        <v>1.53</v>
+      </c>
+      <c r="BO314">
+        <v>3.14</v>
+      </c>
+      <c r="BP314">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="315" spans="1:68">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>7509906</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F315">
+        <v>32</v>
+      </c>
+      <c r="G315" t="s">
+        <v>72</v>
+      </c>
+      <c r="H315" t="s">
+        <v>76</v>
+      </c>
+      <c r="I315">
+        <v>1</v>
+      </c>
+      <c r="J315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>1</v>
+      </c>
+      <c r="L315">
+        <v>1</v>
+      </c>
+      <c r="M315">
+        <v>1</v>
+      </c>
+      <c r="N315">
+        <v>2</v>
+      </c>
+      <c r="O315" t="s">
+        <v>275</v>
+      </c>
+      <c r="P315" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q315">
+        <v>3.4</v>
+      </c>
+      <c r="R315">
+        <v>1.95</v>
+      </c>
+      <c r="S315">
+        <v>3.75</v>
+      </c>
+      <c r="T315">
+        <v>1.53</v>
+      </c>
+      <c r="U315">
+        <v>2.38</v>
+      </c>
+      <c r="V315">
+        <v>3.75</v>
+      </c>
+      <c r="W315">
+        <v>1.25</v>
+      </c>
+      <c r="X315">
+        <v>11</v>
+      </c>
+      <c r="Y315">
+        <v>1.05</v>
+      </c>
+      <c r="Z315">
+        <v>2.7</v>
+      </c>
+      <c r="AA315">
+        <v>2.98</v>
+      </c>
+      <c r="AB315">
+        <v>3.03</v>
+      </c>
+      <c r="AC315">
+        <v>1.11</v>
+      </c>
+      <c r="AD315">
+        <v>7.16</v>
+      </c>
+      <c r="AE315">
+        <v>1.49</v>
+      </c>
+      <c r="AF315">
+        <v>2.45</v>
+      </c>
+      <c r="AG315">
+        <v>2.37</v>
+      </c>
+      <c r="AH315">
+        <v>1.48</v>
+      </c>
+      <c r="AI315">
+        <v>2.05</v>
+      </c>
+      <c r="AJ315">
+        <v>1.7</v>
+      </c>
+      <c r="AK315">
+        <v>1.4</v>
+      </c>
+      <c r="AL315">
+        <v>1.43</v>
+      </c>
+      <c r="AM315">
+        <v>1.52</v>
+      </c>
+      <c r="AN315">
+        <v>1.13</v>
+      </c>
+      <c r="AO315">
+        <v>1</v>
+      </c>
+      <c r="AP315">
+        <v>1.13</v>
+      </c>
+      <c r="AQ315">
+        <v>1</v>
+      </c>
+      <c r="AR315">
+        <v>1.47</v>
+      </c>
+      <c r="AS315">
+        <v>1.32</v>
+      </c>
+      <c r="AT315">
+        <v>2.79</v>
+      </c>
+      <c r="AU315">
+        <v>2</v>
+      </c>
+      <c r="AV315">
+        <v>3</v>
+      </c>
+      <c r="AW315">
+        <v>5</v>
+      </c>
+      <c r="AX315">
+        <v>7</v>
+      </c>
+      <c r="AY315">
+        <v>8</v>
+      </c>
+      <c r="AZ315">
+        <v>12</v>
+      </c>
+      <c r="BA315">
+        <v>2</v>
+      </c>
+      <c r="BB315">
+        <v>5</v>
+      </c>
+      <c r="BC315">
+        <v>7</v>
+      </c>
+      <c r="BD315">
+        <v>2.14</v>
+      </c>
+      <c r="BE315">
+        <v>6.2</v>
+      </c>
+      <c r="BF315">
+        <v>2.15</v>
+      </c>
+      <c r="BG315">
+        <v>1.37</v>
+      </c>
+      <c r="BH315">
+        <v>2.75</v>
+      </c>
+      <c r="BI315">
+        <v>1.7</v>
+      </c>
+      <c r="BJ315">
+        <v>2.1</v>
+      </c>
+      <c r="BK315">
+        <v>2.13</v>
+      </c>
+      <c r="BL315">
+        <v>1.68</v>
+      </c>
+      <c r="BM315">
+        <v>2.83</v>
+      </c>
+      <c r="BN315">
+        <v>1.33</v>
+      </c>
+      <c r="BO315">
+        <v>4.05</v>
+      </c>
+      <c r="BP315">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="316" spans="1:68">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>7509897</v>
+      </c>
+      <c r="C316" t="s">
+        <v>68</v>
+      </c>
+      <c r="D316" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="2">
+        <v>45752.41666666666</v>
+      </c>
+      <c r="F316">
+        <v>32</v>
+      </c>
+      <c r="G316" t="s">
+        <v>70</v>
+      </c>
+      <c r="H316" t="s">
+        <v>85</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
+      <c r="M316">
+        <v>2</v>
+      </c>
+      <c r="N316">
+        <v>3</v>
+      </c>
+      <c r="O316" t="s">
+        <v>276</v>
+      </c>
+      <c r="P316" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q316">
+        <v>2.88</v>
+      </c>
+      <c r="R316">
+        <v>2.1</v>
+      </c>
+      <c r="S316">
+        <v>4</v>
+      </c>
+      <c r="T316">
+        <v>1.44</v>
+      </c>
+      <c r="U316">
+        <v>2.63</v>
+      </c>
+      <c r="V316">
+        <v>3.25</v>
+      </c>
+      <c r="W316">
+        <v>1.33</v>
+      </c>
+      <c r="X316">
+        <v>9</v>
+      </c>
+      <c r="Y316">
+        <v>1.07</v>
+      </c>
+      <c r="Z316">
+        <v>2.18</v>
+      </c>
+      <c r="AA316">
+        <v>3.38</v>
+      </c>
+      <c r="AB316">
+        <v>3.58</v>
+      </c>
+      <c r="AC316">
+        <v>1</v>
+      </c>
+      <c r="AD316">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE316">
+        <v>1.28</v>
+      </c>
+      <c r="AF316">
+        <v>3.86</v>
+      </c>
+      <c r="AG316">
+        <v>1.95</v>
+      </c>
+      <c r="AH316">
+        <v>1.7</v>
+      </c>
+      <c r="AI316">
+        <v>1.8</v>
+      </c>
+      <c r="AJ316">
+        <v>1.95</v>
+      </c>
+      <c r="AK316">
+        <v>1.31</v>
+      </c>
+      <c r="AL316">
+        <v>1.36</v>
+      </c>
+      <c r="AM316">
+        <v>1.74</v>
+      </c>
+      <c r="AN316">
+        <v>1.13</v>
+      </c>
+      <c r="AO316">
+        <v>0.63</v>
+      </c>
+      <c r="AP316">
+        <v>1.06</v>
+      </c>
+      <c r="AQ316">
+        <v>0.76</v>
+      </c>
+      <c r="AR316">
+        <v>1.68</v>
+      </c>
+      <c r="AS316">
+        <v>1.28</v>
+      </c>
+      <c r="AT316">
+        <v>2.96</v>
+      </c>
+      <c r="AU316">
+        <v>8</v>
+      </c>
+      <c r="AV316">
+        <v>9</v>
+      </c>
+      <c r="AW316">
+        <v>7</v>
+      </c>
+      <c r="AX316">
+        <v>10</v>
+      </c>
+      <c r="AY316">
+        <v>15</v>
+      </c>
+      <c r="AZ316">
+        <v>20</v>
+      </c>
+      <c r="BA316">
+        <v>1</v>
+      </c>
+      <c r="BB316">
+        <v>3</v>
+      </c>
+      <c r="BC316">
+        <v>4</v>
+      </c>
+      <c r="BD316">
+        <v>1.71</v>
+      </c>
+      <c r="BE316">
+        <v>6.5</v>
+      </c>
+      <c r="BF316">
+        <v>2.82</v>
+      </c>
+      <c r="BG316">
+        <v>1.32</v>
+      </c>
+      <c r="BH316">
+        <v>2.88</v>
+      </c>
+      <c r="BI316">
+        <v>1.67</v>
+      </c>
+      <c r="BJ316">
+        <v>2.14</v>
+      </c>
+      <c r="BK316">
+        <v>2.14</v>
+      </c>
+      <c r="BL316">
+        <v>1.67</v>
+      </c>
+      <c r="BM316">
+        <v>2.52</v>
+      </c>
+      <c r="BN316">
+        <v>1.49</v>
+      </c>
+      <c r="BO316">
+        <v>3.74</v>
+      </c>
+      <c r="BP316">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7509903</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45752.51041666666</v>
+      </c>
+      <c r="F317">
+        <v>32</v>
+      </c>
+      <c r="G317" t="s">
+        <v>73</v>
+      </c>
+      <c r="H317" t="s">
+        <v>80</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>1</v>
+      </c>
+      <c r="M317">
+        <v>2</v>
+      </c>
+      <c r="N317">
+        <v>3</v>
+      </c>
+      <c r="O317" t="s">
+        <v>187</v>
+      </c>
+      <c r="P317" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q317">
+        <v>2.6</v>
+      </c>
+      <c r="R317">
+        <v>2</v>
+      </c>
+      <c r="S317">
+        <v>5</v>
+      </c>
+      <c r="T317">
+        <v>1.5</v>
+      </c>
+      <c r="U317">
+        <v>2.5</v>
+      </c>
+      <c r="V317">
+        <v>3.5</v>
+      </c>
+      <c r="W317">
+        <v>1.29</v>
+      </c>
+      <c r="X317">
+        <v>11</v>
+      </c>
+      <c r="Y317">
+        <v>1.05</v>
+      </c>
+      <c r="Z317">
+        <v>1.93</v>
+      </c>
+      <c r="AA317">
+        <v>3.39</v>
+      </c>
+      <c r="AB317">
+        <v>4.5</v>
+      </c>
+      <c r="AC317">
+        <v>1.11</v>
+      </c>
+      <c r="AD317">
+        <v>7.49</v>
+      </c>
+      <c r="AE317">
+        <v>1.35</v>
+      </c>
+      <c r="AF317">
+        <v>3.3</v>
+      </c>
+      <c r="AG317">
+        <v>2.25</v>
+      </c>
+      <c r="AH317">
+        <v>1.53</v>
+      </c>
+      <c r="AI317">
+        <v>2.05</v>
+      </c>
+      <c r="AJ317">
+        <v>1.7</v>
+      </c>
+      <c r="AK317">
+        <v>1.21</v>
+      </c>
+      <c r="AL317">
+        <v>1.35</v>
+      </c>
+      <c r="AM317">
+        <v>2</v>
+      </c>
+      <c r="AN317">
+        <v>2.4</v>
+      </c>
+      <c r="AO317">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP317">
+        <v>2.25</v>
+      </c>
+      <c r="AQ317">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR317">
+        <v>1.56</v>
+      </c>
+      <c r="AS317">
+        <v>1.25</v>
+      </c>
+      <c r="AT317">
+        <v>2.81</v>
+      </c>
+      <c r="AU317">
+        <v>6</v>
+      </c>
+      <c r="AV317">
+        <v>6</v>
+      </c>
+      <c r="AW317">
+        <v>9</v>
+      </c>
+      <c r="AX317">
+        <v>4</v>
+      </c>
+      <c r="AY317">
+        <v>16</v>
+      </c>
+      <c r="AZ317">
+        <v>11</v>
+      </c>
+      <c r="BA317">
+        <v>4</v>
+      </c>
+      <c r="BB317">
+        <v>1</v>
+      </c>
+      <c r="BC317">
+        <v>5</v>
+      </c>
+      <c r="BD317">
+        <v>1.36</v>
+      </c>
+      <c r="BE317">
+        <v>9.5</v>
+      </c>
+      <c r="BF317">
+        <v>3.95</v>
+      </c>
+      <c r="BG317">
+        <v>1.33</v>
+      </c>
+      <c r="BH317">
+        <v>2.83</v>
+      </c>
+      <c r="BI317">
+        <v>1.69</v>
+      </c>
+      <c r="BJ317">
+        <v>2.12</v>
+      </c>
+      <c r="BK317">
+        <v>2.14</v>
+      </c>
+      <c r="BL317">
+        <v>1.67</v>
+      </c>
+      <c r="BM317">
+        <v>2.75</v>
+      </c>
+      <c r="BN317">
+        <v>1.37</v>
+      </c>
+      <c r="BO317">
+        <v>3.82</v>
+      </c>
+      <c r="BP317">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7509901</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45752.60416666666</v>
+      </c>
+      <c r="F318">
+        <v>32</v>
+      </c>
+      <c r="G318" t="s">
+        <v>88</v>
+      </c>
+      <c r="H318" t="s">
+        <v>74</v>
+      </c>
+      <c r="I318">
+        <v>0</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>0</v>
+      </c>
+      <c r="L318">
+        <v>1</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>1</v>
+      </c>
+      <c r="O318" t="s">
+        <v>98</v>
+      </c>
+      <c r="P318" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q318">
+        <v>3.1</v>
+      </c>
+      <c r="R318">
+        <v>1.95</v>
+      </c>
+      <c r="S318">
+        <v>4</v>
+      </c>
+      <c r="T318">
+        <v>1.53</v>
+      </c>
+      <c r="U318">
+        <v>2.38</v>
+      </c>
+      <c r="V318">
+        <v>3.5</v>
+      </c>
+      <c r="W318">
+        <v>1.29</v>
+      </c>
+      <c r="X318">
+        <v>11</v>
+      </c>
+      <c r="Y318">
+        <v>1.05</v>
+      </c>
+      <c r="Z318">
+        <v>2.36</v>
+      </c>
+      <c r="AA318">
+        <v>3.14</v>
+      </c>
+      <c r="AB318">
+        <v>3.41</v>
+      </c>
+      <c r="AC318">
+        <v>1.11</v>
+      </c>
+      <c r="AD318">
+        <v>7.41</v>
+      </c>
+      <c r="AE318">
+        <v>1.46</v>
+      </c>
+      <c r="AF318">
+        <v>2.85</v>
+      </c>
+      <c r="AG318">
+        <v>2.3</v>
+      </c>
+      <c r="AH318">
+        <v>1.5</v>
+      </c>
+      <c r="AI318">
+        <v>2</v>
+      </c>
+      <c r="AJ318">
+        <v>1.75</v>
+      </c>
+      <c r="AK318">
+        <v>1.25</v>
+      </c>
+      <c r="AL318">
+        <v>1.39</v>
+      </c>
+      <c r="AM318">
+        <v>1.82</v>
+      </c>
+      <c r="AN318">
+        <v>1.8</v>
+      </c>
+      <c r="AO318">
+        <v>0.53</v>
+      </c>
+      <c r="AP318">
+        <v>1.88</v>
+      </c>
+      <c r="AQ318">
+        <v>0.5</v>
+      </c>
+      <c r="AR318">
+        <v>1.29</v>
+      </c>
+      <c r="AS318">
+        <v>1.22</v>
+      </c>
+      <c r="AT318">
+        <v>2.51</v>
+      </c>
+      <c r="AU318">
+        <v>3</v>
+      </c>
+      <c r="AV318">
+        <v>3</v>
+      </c>
+      <c r="AW318">
+        <v>8</v>
+      </c>
+      <c r="AX318">
+        <v>6</v>
+      </c>
+      <c r="AY318">
+        <v>16</v>
+      </c>
+      <c r="AZ318">
+        <v>11</v>
+      </c>
+      <c r="BA318">
+        <v>5</v>
+      </c>
+      <c r="BB318">
+        <v>4</v>
+      </c>
+      <c r="BC318">
+        <v>9</v>
+      </c>
+      <c r="BD318">
+        <v>1.81</v>
+      </c>
+      <c r="BE318">
+        <v>6.4</v>
+      </c>
+      <c r="BF318">
+        <v>2.6</v>
+      </c>
+      <c r="BG318">
+        <v>1.36</v>
+      </c>
+      <c r="BH318">
+        <v>2.79</v>
+      </c>
+      <c r="BI318">
+        <v>1.73</v>
+      </c>
+      <c r="BJ318">
+        <v>2.06</v>
+      </c>
+      <c r="BK318">
+        <v>2.18</v>
+      </c>
+      <c r="BL318">
+        <v>1.65</v>
+      </c>
+      <c r="BM318">
+        <v>2.81</v>
+      </c>
+      <c r="BN318">
+        <v>1.33</v>
+      </c>
+      <c r="BO318">
+        <v>3.96</v>
+      </c>
+      <c r="BP318">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="404">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,15 @@
     <t>['7']</t>
   </si>
   <si>
+    <t>['44', '69', '83']</t>
+  </si>
+  <si>
+    <t>['18', '25', '45+1', '55', '81']</t>
+  </si>
+  <si>
+    <t>['65', '73']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1212,6 +1221,12 @@
   <si>
     <t>['27', '50']</t>
   </si>
+  <si>
+    <t>['27', '78', '90+2']</t>
+  </si>
+  <si>
+    <t>['73', '74', '84']</t>
+  </si>
 </sst>
 </file>
 
@@ -1572,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP318"/>
+  <dimension ref="A1:BP321"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2034,7 +2049,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2446,7 +2461,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -2858,7 +2873,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -2939,7 +2954,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ7">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3270,7 +3285,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3476,7 +3491,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3554,10 +3569,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ10">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3888,7 +3903,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -3969,7 +3984,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4094,7 +4109,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q13">
         <v>3.4</v>
@@ -4300,7 +4315,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4918,7 +4933,7 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q17">
         <v>2.88</v>
@@ -4996,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ17">
         <v>1.13</v>
@@ -5536,7 +5551,7 @@
         <v>107</v>
       </c>
       <c r="P20" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q20">
         <v>2.88</v>
@@ -5820,7 +5835,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
         <v>1.19</v>
@@ -5948,7 +5963,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -6029,7 +6044,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR22">
         <v>1.6</v>
@@ -6360,7 +6375,7 @@
         <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q24">
         <v>2.98</v>
@@ -6441,7 +6456,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ24">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR24">
         <v>1.67</v>
@@ -6978,7 +6993,7 @@
         <v>102</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q27">
         <v>2.74</v>
@@ -8089,7 +8104,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR32">
         <v>0.67</v>
@@ -8214,7 +8229,7 @@
         <v>102</v>
       </c>
       <c r="P33" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
@@ -8626,7 +8641,7 @@
         <v>116</v>
       </c>
       <c r="P35" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8832,7 +8847,7 @@
         <v>117</v>
       </c>
       <c r="P36" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
@@ -9528,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -9656,7 +9671,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -9734,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ40">
         <v>1</v>
@@ -9862,7 +9877,7 @@
         <v>121</v>
       </c>
       <c r="P41" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q41">
         <v>2.63</v>
@@ -9940,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ41">
         <v>0.5600000000000001</v>
@@ -10068,7 +10083,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10892,7 +10907,7 @@
         <v>125</v>
       </c>
       <c r="P46" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q46">
         <v>3.75</v>
@@ -11304,7 +11319,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q48">
         <v>3.4</v>
@@ -11510,7 +11525,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11591,7 +11606,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ49">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR49">
         <v>0.9399999999999999</v>
@@ -11797,7 +11812,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ50">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -11922,7 +11937,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12128,7 +12143,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12206,7 +12221,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ52">
         <v>1.75</v>
@@ -12415,7 +12430,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ53">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR53">
         <v>1.32</v>
@@ -12618,7 +12633,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -13570,7 +13585,7 @@
         <v>102</v>
       </c>
       <c r="P59" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q59">
         <v>3.1</v>
@@ -13651,7 +13666,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR59">
         <v>1.43</v>
@@ -13982,7 +13997,7 @@
         <v>133</v>
       </c>
       <c r="P61" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q61">
         <v>2.38</v>
@@ -14060,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ61">
         <v>0.5600000000000001</v>
@@ -14188,7 +14203,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -15012,7 +15027,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15424,7 +15439,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -15505,7 +15520,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15836,7 +15851,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -16042,7 +16057,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16248,7 +16263,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16454,7 +16469,7 @@
         <v>102</v>
       </c>
       <c r="P73" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q73">
         <v>2.5</v>
@@ -16660,7 +16675,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16944,7 +16959,7 @@
         <v>1.33</v>
       </c>
       <c r="AP75">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ75">
         <v>0.88</v>
@@ -17072,7 +17087,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -17278,7 +17293,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17484,7 +17499,7 @@
         <v>144</v>
       </c>
       <c r="P78" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17771,7 +17786,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR79">
         <v>1.53</v>
@@ -17896,7 +17911,7 @@
         <v>145</v>
       </c>
       <c r="P80" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q80">
         <v>3.4</v>
@@ -17974,7 +17989,7 @@
         <v>0.67</v>
       </c>
       <c r="AP80">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ80">
         <v>0.9399999999999999</v>
@@ -18180,7 +18195,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -18514,7 +18529,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18720,7 +18735,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -19132,7 +19147,7 @@
         <v>147</v>
       </c>
       <c r="P86" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19338,7 +19353,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -19419,7 +19434,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ87">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR87">
         <v>1.8</v>
@@ -19544,7 +19559,7 @@
         <v>149</v>
       </c>
       <c r="P88" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q88">
         <v>3.75</v>
@@ -20162,7 +20177,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -20243,7 +20258,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ91">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR91">
         <v>1.67</v>
@@ -20446,10 +20461,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ92">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR92">
         <v>1.53</v>
@@ -21270,7 +21285,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96">
         <v>0.88</v>
@@ -21888,7 +21903,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>1.06</v>
@@ -22840,7 +22855,7 @@
         <v>160</v>
       </c>
       <c r="P104" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -22921,7 +22936,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ104">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR104">
         <v>1.28</v>
@@ -23046,7 +23061,7 @@
         <v>161</v>
       </c>
       <c r="P105" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -23951,7 +23966,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ109">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR109">
         <v>1.52</v>
@@ -24566,7 +24581,7 @@
         <v>0.6</v>
       </c>
       <c r="AP112">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ112">
         <v>0.9399999999999999</v>
@@ -24694,7 +24709,7 @@
         <v>163</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q113">
         <v>2.75</v>
@@ -25184,7 +25199,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ115">
         <v>1.13</v>
@@ -25518,7 +25533,7 @@
         <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q117">
         <v>3</v>
@@ -25724,7 +25739,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26008,7 +26023,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ119">
         <v>1.44</v>
@@ -26548,7 +26563,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26835,7 +26850,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ123">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR123">
         <v>1.52</v>
@@ -27041,7 +27056,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ124">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR124">
         <v>1.36</v>
@@ -27372,7 +27387,7 @@
         <v>169</v>
       </c>
       <c r="P126" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q126">
         <v>3.1</v>
@@ -27784,7 +27799,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q128">
         <v>3.65</v>
@@ -27990,7 +28005,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q129">
         <v>3.35</v>
@@ -28196,7 +28211,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28402,7 +28417,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28483,7 +28498,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR131">
         <v>1.62</v>
@@ -28608,7 +28623,7 @@
         <v>119</v>
       </c>
       <c r="P132" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29432,7 +29447,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -29510,7 +29525,7 @@
         <v>0.29</v>
       </c>
       <c r="AP136">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
         <v>0.76</v>
@@ -29844,7 +29859,7 @@
         <v>175</v>
       </c>
       <c r="P138" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q138">
         <v>2.6</v>
@@ -30128,7 +30143,7 @@
         <v>1</v>
       </c>
       <c r="AP139">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ139">
         <v>1.06</v>
@@ -30462,7 +30477,7 @@
         <v>178</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30540,10 +30555,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ141">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR141">
         <v>1.62</v>
@@ -30668,7 +30683,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -30749,7 +30764,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ142">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR142">
         <v>1.2</v>
@@ -30874,7 +30889,7 @@
         <v>179</v>
       </c>
       <c r="P143" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q143">
         <v>2.55</v>
@@ -31080,7 +31095,7 @@
         <v>102</v>
       </c>
       <c r="P144" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q144">
         <v>3.95</v>
@@ -31367,7 +31382,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ145">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR145">
         <v>1.73</v>
@@ -31492,7 +31507,7 @@
         <v>181</v>
       </c>
       <c r="P146" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31982,7 +31997,7 @@
         <v>1.57</v>
       </c>
       <c r="AP148">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ148">
         <v>1.5</v>
@@ -32110,7 +32125,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32316,7 +32331,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32728,7 +32743,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33346,7 +33361,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33758,7 +33773,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34042,7 +34057,7 @@
         <v>1.14</v>
       </c>
       <c r="AP158">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ158">
         <v>1.06</v>
@@ -34170,7 +34185,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -34454,7 +34469,7 @@
         <v>1.13</v>
       </c>
       <c r="AP160">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ160">
         <v>1.44</v>
@@ -34582,7 +34597,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q161">
         <v>2.2</v>
@@ -34663,7 +34678,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ161">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR161">
         <v>1.67</v>
@@ -34869,7 +34884,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ162">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR162">
         <v>1.37</v>
@@ -34994,7 +35009,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35406,7 +35421,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -35487,7 +35502,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ165">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR165">
         <v>1.36</v>
@@ -36024,7 +36039,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36102,7 +36117,7 @@
         <v>0.86</v>
       </c>
       <c r="AP168">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ168">
         <v>1.2</v>
@@ -36642,7 +36657,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -38084,7 +38099,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38290,7 +38305,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -38368,7 +38383,7 @@
         <v>1.33</v>
       </c>
       <c r="AP179">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ179">
         <v>1.5</v>
@@ -38783,7 +38798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ181">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR181">
         <v>1.41</v>
@@ -38989,7 +39004,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ182">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR182">
         <v>1.39</v>
@@ -39320,7 +39335,7 @@
         <v>91</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>2.3</v>
@@ -39398,7 +39413,7 @@
         <v>0.44</v>
       </c>
       <c r="AP184">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ184">
         <v>0.76</v>
@@ -39526,7 +39541,7 @@
         <v>204</v>
       </c>
       <c r="P185" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>3.1</v>
@@ -40144,7 +40159,7 @@
         <v>206</v>
       </c>
       <c r="P188" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q188">
         <v>3.25</v>
@@ -40634,10 +40649,10 @@
         <v>1.25</v>
       </c>
       <c r="AP190">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ190">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR190">
         <v>1.89</v>
@@ -40762,7 +40777,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -40968,7 +40983,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41998,7 +42013,7 @@
         <v>102</v>
       </c>
       <c r="P197" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q197">
         <v>2.5</v>
@@ -42488,7 +42503,7 @@
         <v>0.67</v>
       </c>
       <c r="AP199">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ199">
         <v>0.5</v>
@@ -42616,7 +42631,7 @@
         <v>149</v>
       </c>
       <c r="P200" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -43028,7 +43043,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43109,7 +43124,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ202">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR202">
         <v>1.7</v>
@@ -43315,7 +43330,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ203">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR203">
         <v>1.37</v>
@@ -43440,7 +43455,7 @@
         <v>216</v>
       </c>
       <c r="P204" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q204">
         <v>3.4</v>
@@ -43724,7 +43739,7 @@
         <v>0.9</v>
       </c>
       <c r="AP205">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ205">
         <v>0.9399999999999999</v>
@@ -43930,7 +43945,7 @@
         <v>1.4</v>
       </c>
       <c r="AP206">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ206">
         <v>1.19</v>
@@ -44058,7 +44073,7 @@
         <v>218</v>
       </c>
       <c r="P207" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44264,7 +44279,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -44757,7 +44772,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ210">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR210">
         <v>1.56</v>
@@ -45088,7 +45103,7 @@
         <v>216</v>
       </c>
       <c r="P212" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45294,7 +45309,7 @@
         <v>112</v>
       </c>
       <c r="P213" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -45912,7 +45927,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46118,7 +46133,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46402,7 +46417,7 @@
         <v>1.7</v>
       </c>
       <c r="AP218">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ218">
         <v>1.56</v>
@@ -46608,7 +46623,7 @@
         <v>1.36</v>
       </c>
       <c r="AP219">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ219">
         <v>1.19</v>
@@ -46736,7 +46751,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -46942,7 +46957,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47148,7 +47163,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47226,10 +47241,10 @@
         <v>2.18</v>
       </c>
       <c r="AP222">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ222">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR222">
         <v>1.73</v>
@@ -47560,7 +47575,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47847,7 +47862,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ225">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR225">
         <v>1.49</v>
@@ -47972,7 +47987,7 @@
         <v>102</v>
       </c>
       <c r="P226" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q226">
         <v>2.95</v>
@@ -48178,7 +48193,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48259,7 +48274,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ227">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR227">
         <v>1.29</v>
@@ -48384,7 +48399,7 @@
         <v>111</v>
       </c>
       <c r="P228" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q228">
         <v>2.9</v>
@@ -49002,7 +49017,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49208,7 +49223,7 @@
         <v>112</v>
       </c>
       <c r="P232" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49286,7 +49301,7 @@
         <v>1.64</v>
       </c>
       <c r="AP232">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ232">
         <v>1.56</v>
@@ -49826,7 +49841,7 @@
         <v>102</v>
       </c>
       <c r="P235" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q235">
         <v>4.75</v>
@@ -50032,7 +50047,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50110,7 +50125,7 @@
         <v>0.73</v>
       </c>
       <c r="AP236">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ236">
         <v>1</v>
@@ -50650,7 +50665,7 @@
         <v>235</v>
       </c>
       <c r="P239" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q239">
         <v>3</v>
@@ -51062,7 +51077,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51680,7 +51695,7 @@
         <v>102</v>
       </c>
       <c r="P244" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q244">
         <v>4.75</v>
@@ -51761,7 +51776,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ244">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR244">
         <v>1.33</v>
@@ -52916,7 +52931,7 @@
         <v>240</v>
       </c>
       <c r="P250" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q250">
         <v>2.6</v>
@@ -52994,7 +53009,7 @@
         <v>1</v>
       </c>
       <c r="AP250">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ250">
         <v>1.25</v>
@@ -53203,7 +53218,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ251">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR251">
         <v>1.22</v>
@@ -53406,7 +53421,7 @@
         <v>1.46</v>
       </c>
       <c r="AP252">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ252">
         <v>1.44</v>
@@ -53534,7 +53549,7 @@
         <v>242</v>
       </c>
       <c r="P253" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q253">
         <v>3.4</v>
@@ -53615,7 +53630,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ253">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR253">
         <v>1.42</v>
@@ -54976,7 +54991,7 @@
         <v>247</v>
       </c>
       <c r="P260" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q260">
         <v>2.3</v>
@@ -55054,7 +55069,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP260">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ260">
         <v>0.76</v>
@@ -55469,7 +55484,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ262">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR262">
         <v>1.44</v>
@@ -55594,7 +55609,7 @@
         <v>102</v>
       </c>
       <c r="P263" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q263">
         <v>3.5</v>
@@ -55881,7 +55896,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ264">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR264">
         <v>1.31</v>
@@ -56212,7 +56227,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56418,7 +56433,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -56624,7 +56639,7 @@
         <v>102</v>
       </c>
       <c r="P268" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q268">
         <v>3.4</v>
@@ -56908,7 +56923,7 @@
         <v>1.25</v>
       </c>
       <c r="AP269">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ269">
         <v>1.2</v>
@@ -57654,7 +57669,7 @@
         <v>253</v>
       </c>
       <c r="P273" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q273">
         <v>4.2</v>
@@ -58066,7 +58081,7 @@
         <v>255</v>
       </c>
       <c r="P275" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q275">
         <v>2.7</v>
@@ -58762,7 +58777,7 @@
         <v>1.08</v>
       </c>
       <c r="AP278">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ278">
         <v>1.06</v>
@@ -58890,7 +58905,7 @@
         <v>235</v>
       </c>
       <c r="P279" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q279">
         <v>2.8</v>
@@ -58968,7 +58983,7 @@
         <v>1</v>
       </c>
       <c r="AP279">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ279">
         <v>0.88</v>
@@ -59302,7 +59317,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -59383,7 +59398,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ281">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR281">
         <v>1.38</v>
@@ -60744,7 +60759,7 @@
         <v>231</v>
       </c>
       <c r="P288" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -61031,7 +61046,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ289">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR289">
         <v>1.67</v>
@@ -61156,7 +61171,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61234,7 +61249,7 @@
         <v>1.57</v>
       </c>
       <c r="AP290">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ290">
         <v>1.56</v>
@@ -61362,7 +61377,7 @@
         <v>245</v>
       </c>
       <c r="P291" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61568,7 +61583,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61646,7 +61661,7 @@
         <v>1.57</v>
       </c>
       <c r="AP292">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ292">
         <v>1.75</v>
@@ -61980,7 +61995,7 @@
         <v>90</v>
       </c>
       <c r="P294" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q294">
         <v>4.5</v>
@@ -62061,7 +62076,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ294">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AR294">
         <v>1.39</v>
@@ -63010,7 +63025,7 @@
         <v>265</v>
       </c>
       <c r="P299" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q299">
         <v>3.5</v>
@@ -63091,7 +63106,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ299">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR299">
         <v>1.31</v>
@@ -63216,7 +63231,7 @@
         <v>266</v>
       </c>
       <c r="P300" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q300">
         <v>3</v>
@@ -63500,7 +63515,7 @@
         <v>0.79</v>
       </c>
       <c r="AP301">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ301">
         <v>0.75</v>
@@ -63628,7 +63643,7 @@
         <v>102</v>
       </c>
       <c r="P302" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q302">
         <v>2.1</v>
@@ -63706,7 +63721,7 @@
         <v>0.93</v>
       </c>
       <c r="AP302">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ302">
         <v>1.06</v>
@@ -63834,7 +63849,7 @@
         <v>102</v>
       </c>
       <c r="P303" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q303">
         <v>4.33</v>
@@ -64246,7 +64261,7 @@
         <v>269</v>
       </c>
       <c r="P305" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q305">
         <v>2.75</v>
@@ -64452,7 +64467,7 @@
         <v>102</v>
       </c>
       <c r="P306" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q306">
         <v>2.88</v>
@@ -64658,7 +64673,7 @@
         <v>270</v>
       </c>
       <c r="P307" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q307">
         <v>2</v>
@@ -64864,7 +64879,7 @@
         <v>271</v>
       </c>
       <c r="P308" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q308">
         <v>2.25</v>
@@ -65070,7 +65085,7 @@
         <v>200</v>
       </c>
       <c r="P309" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q309">
         <v>3.25</v>
@@ -65357,7 +65372,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ310">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR310">
         <v>1.38</v>
@@ -65482,7 +65497,7 @@
         <v>273</v>
       </c>
       <c r="P311" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q311">
         <v>3.25</v>
@@ -65688,7 +65703,7 @@
         <v>141</v>
       </c>
       <c r="P312" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q312">
         <v>4.33</v>
@@ -66100,7 +66115,7 @@
         <v>274</v>
       </c>
       <c r="P314" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q314">
         <v>2.63</v>
@@ -66199,13 +66214,13 @@
         <v>4</v>
       </c>
       <c r="AW314">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX314">
         <v>3</v>
       </c>
       <c r="AY314">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ314">
         <v>7</v>
@@ -66405,16 +66420,16 @@
         <v>3</v>
       </c>
       <c r="AW315">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX315">
+        <v>2</v>
+      </c>
+      <c r="AY315">
         <v>7</v>
       </c>
-      <c r="AY315">
+      <c r="AZ315">
         <v>8</v>
-      </c>
-      <c r="AZ315">
-        <v>12</v>
       </c>
       <c r="BA315">
         <v>2</v>
@@ -66512,7 +66527,7 @@
         <v>276</v>
       </c>
       <c r="P316" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q316">
         <v>2.88</v>
@@ -66718,7 +66733,7 @@
         <v>187</v>
       </c>
       <c r="P317" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q317">
         <v>2.6</v>
@@ -67081,6 +67096,624 @@
       </c>
       <c r="BP318">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7509898</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F319">
+        <v>32</v>
+      </c>
+      <c r="G319" t="s">
+        <v>78</v>
+      </c>
+      <c r="H319" t="s">
+        <v>71</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>1</v>
+      </c>
+      <c r="K319">
+        <v>2</v>
+      </c>
+      <c r="L319">
+        <v>3</v>
+      </c>
+      <c r="M319">
+        <v>3</v>
+      </c>
+      <c r="N319">
+        <v>6</v>
+      </c>
+      <c r="O319" t="s">
+        <v>277</v>
+      </c>
+      <c r="P319" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q319">
+        <v>3</v>
+      </c>
+      <c r="R319">
+        <v>2.05</v>
+      </c>
+      <c r="S319">
+        <v>4</v>
+      </c>
+      <c r="T319">
+        <v>1.5</v>
+      </c>
+      <c r="U319">
+        <v>2.5</v>
+      </c>
+      <c r="V319">
+        <v>3.4</v>
+      </c>
+      <c r="W319">
+        <v>1.3</v>
+      </c>
+      <c r="X319">
+        <v>10</v>
+      </c>
+      <c r="Y319">
+        <v>1.06</v>
+      </c>
+      <c r="Z319">
+        <v>2.33</v>
+      </c>
+      <c r="AA319">
+        <v>3.26</v>
+      </c>
+      <c r="AB319">
+        <v>3.35</v>
+      </c>
+      <c r="AC319">
+        <v>1.08</v>
+      </c>
+      <c r="AD319">
+        <v>7.5</v>
+      </c>
+      <c r="AE319">
+        <v>1.4</v>
+      </c>
+      <c r="AF319">
+        <v>2.9</v>
+      </c>
+      <c r="AG319">
+        <v>2.1</v>
+      </c>
+      <c r="AH319">
+        <v>1.6</v>
+      </c>
+      <c r="AI319">
+        <v>1.95</v>
+      </c>
+      <c r="AJ319">
+        <v>1.8</v>
+      </c>
+      <c r="AK319">
+        <v>1.33</v>
+      </c>
+      <c r="AL319">
+        <v>1.33</v>
+      </c>
+      <c r="AM319">
+        <v>1.6</v>
+      </c>
+      <c r="AN319">
+        <v>1.75</v>
+      </c>
+      <c r="AO319">
+        <v>1.07</v>
+      </c>
+      <c r="AP319">
+        <v>1.71</v>
+      </c>
+      <c r="AQ319">
+        <v>1.06</v>
+      </c>
+      <c r="AR319">
+        <v>1.37</v>
+      </c>
+      <c r="AS319">
+        <v>1.37</v>
+      </c>
+      <c r="AT319">
+        <v>2.74</v>
+      </c>
+      <c r="AU319">
+        <v>7</v>
+      </c>
+      <c r="AV319">
+        <v>5</v>
+      </c>
+      <c r="AW319">
+        <v>7</v>
+      </c>
+      <c r="AX319">
+        <v>4</v>
+      </c>
+      <c r="AY319">
+        <v>18</v>
+      </c>
+      <c r="AZ319">
+        <v>10</v>
+      </c>
+      <c r="BA319">
+        <v>11</v>
+      </c>
+      <c r="BB319">
+        <v>3</v>
+      </c>
+      <c r="BC319">
+        <v>14</v>
+      </c>
+      <c r="BD319">
+        <v>1.91</v>
+      </c>
+      <c r="BE319">
+        <v>6.1</v>
+      </c>
+      <c r="BF319">
+        <v>2.1</v>
+      </c>
+      <c r="BG319">
+        <v>1.45</v>
+      </c>
+      <c r="BH319">
+        <v>2.55</v>
+      </c>
+      <c r="BI319">
+        <v>1.76</v>
+      </c>
+      <c r="BJ319">
+        <v>1.94</v>
+      </c>
+      <c r="BK319">
+        <v>2.23</v>
+      </c>
+      <c r="BL319">
+        <v>1.57</v>
+      </c>
+      <c r="BM319">
+        <v>2.88</v>
+      </c>
+      <c r="BN319">
+        <v>1.35</v>
+      </c>
+      <c r="BO319">
+        <v>3.8</v>
+      </c>
+      <c r="BP319">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7509902</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45753.41666666666</v>
+      </c>
+      <c r="F320">
+        <v>32</v>
+      </c>
+      <c r="G320" t="s">
+        <v>89</v>
+      </c>
+      <c r="H320" t="s">
+        <v>84</v>
+      </c>
+      <c r="I320">
+        <v>3</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>3</v>
+      </c>
+      <c r="L320">
+        <v>5</v>
+      </c>
+      <c r="M320">
+        <v>3</v>
+      </c>
+      <c r="N320">
+        <v>8</v>
+      </c>
+      <c r="O320" t="s">
+        <v>278</v>
+      </c>
+      <c r="P320" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q320">
+        <v>3.25</v>
+      </c>
+      <c r="R320">
+        <v>2.1</v>
+      </c>
+      <c r="S320">
+        <v>3.2</v>
+      </c>
+      <c r="T320">
+        <v>1.4</v>
+      </c>
+      <c r="U320">
+        <v>2.75</v>
+      </c>
+      <c r="V320">
+        <v>3</v>
+      </c>
+      <c r="W320">
+        <v>1.36</v>
+      </c>
+      <c r="X320">
+        <v>8</v>
+      </c>
+      <c r="Y320">
+        <v>1.08</v>
+      </c>
+      <c r="Z320">
+        <v>2.86</v>
+      </c>
+      <c r="AA320">
+        <v>3.21</v>
+      </c>
+      <c r="AB320">
+        <v>2.68</v>
+      </c>
+      <c r="AC320">
+        <v>1.06</v>
+      </c>
+      <c r="AD320">
+        <v>8.5</v>
+      </c>
+      <c r="AE320">
+        <v>1.3</v>
+      </c>
+      <c r="AF320">
+        <v>3.35</v>
+      </c>
+      <c r="AG320">
+        <v>1.93</v>
+      </c>
+      <c r="AH320">
+        <v>1.88</v>
+      </c>
+      <c r="AI320">
+        <v>1.7</v>
+      </c>
+      <c r="AJ320">
+        <v>2.05</v>
+      </c>
+      <c r="AK320">
+        <v>1.49</v>
+      </c>
+      <c r="AL320">
+        <v>1.3</v>
+      </c>
+      <c r="AM320">
+        <v>1.46</v>
+      </c>
+      <c r="AN320">
+        <v>1.47</v>
+      </c>
+      <c r="AO320">
+        <v>2.07</v>
+      </c>
+      <c r="AP320">
+        <v>1.56</v>
+      </c>
+      <c r="AQ320">
+        <v>1.94</v>
+      </c>
+      <c r="AR320">
+        <v>1.8</v>
+      </c>
+      <c r="AS320">
+        <v>1.43</v>
+      </c>
+      <c r="AT320">
+        <v>3.23</v>
+      </c>
+      <c r="AU320">
+        <v>7</v>
+      </c>
+      <c r="AV320">
+        <v>9</v>
+      </c>
+      <c r="AW320">
+        <v>9</v>
+      </c>
+      <c r="AX320">
+        <v>13</v>
+      </c>
+      <c r="AY320">
+        <v>20</v>
+      </c>
+      <c r="AZ320">
+        <v>24</v>
+      </c>
+      <c r="BA320">
+        <v>9</v>
+      </c>
+      <c r="BB320">
+        <v>4</v>
+      </c>
+      <c r="BC320">
+        <v>13</v>
+      </c>
+      <c r="BD320">
+        <v>2.07</v>
+      </c>
+      <c r="BE320">
+        <v>6.4</v>
+      </c>
+      <c r="BF320">
+        <v>1.94</v>
+      </c>
+      <c r="BG320">
+        <v>1.44</v>
+      </c>
+      <c r="BH320">
+        <v>2.55</v>
+      </c>
+      <c r="BI320">
+        <v>1.73</v>
+      </c>
+      <c r="BJ320">
+        <v>1.98</v>
+      </c>
+      <c r="BK320">
+        <v>2.17</v>
+      </c>
+      <c r="BL320">
+        <v>1.6</v>
+      </c>
+      <c r="BM320">
+        <v>2.8</v>
+      </c>
+      <c r="BN320">
+        <v>1.38</v>
+      </c>
+      <c r="BO320">
+        <v>3.7</v>
+      </c>
+      <c r="BP320">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7509905</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45753.51041666666</v>
+      </c>
+      <c r="F321">
+        <v>32</v>
+      </c>
+      <c r="G321" t="s">
+        <v>83</v>
+      </c>
+      <c r="H321" t="s">
+        <v>81</v>
+      </c>
+      <c r="I321">
+        <v>0</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>0</v>
+      </c>
+      <c r="L321">
+        <v>2</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
+      </c>
+      <c r="N321">
+        <v>2</v>
+      </c>
+      <c r="O321" t="s">
+        <v>279</v>
+      </c>
+      <c r="P321" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q321">
+        <v>2.3</v>
+      </c>
+      <c r="R321">
+        <v>2.2</v>
+      </c>
+      <c r="S321">
+        <v>5.5</v>
+      </c>
+      <c r="T321">
+        <v>1.4</v>
+      </c>
+      <c r="U321">
+        <v>2.75</v>
+      </c>
+      <c r="V321">
+        <v>3</v>
+      </c>
+      <c r="W321">
+        <v>1.36</v>
+      </c>
+      <c r="X321">
+        <v>8</v>
+      </c>
+      <c r="Y321">
+        <v>1.08</v>
+      </c>
+      <c r="Z321">
+        <v>1.72</v>
+      </c>
+      <c r="AA321">
+        <v>3.91</v>
+      </c>
+      <c r="AB321">
+        <v>5.1</v>
+      </c>
+      <c r="AC321">
+        <v>1.05</v>
+      </c>
+      <c r="AD321">
+        <v>9.5</v>
+      </c>
+      <c r="AE321">
+        <v>1.3</v>
+      </c>
+      <c r="AF321">
+        <v>3.4</v>
+      </c>
+      <c r="AG321">
+        <v>1.97</v>
+      </c>
+      <c r="AH321">
+        <v>1.84</v>
+      </c>
+      <c r="AI321">
+        <v>1.95</v>
+      </c>
+      <c r="AJ321">
+        <v>1.8</v>
+      </c>
+      <c r="AK321">
+        <v>1.18</v>
+      </c>
+      <c r="AL321">
+        <v>1.25</v>
+      </c>
+      <c r="AM321">
+        <v>2.1</v>
+      </c>
+      <c r="AN321">
+        <v>2.07</v>
+      </c>
+      <c r="AO321">
+        <v>0.93</v>
+      </c>
+      <c r="AP321">
+        <v>2.13</v>
+      </c>
+      <c r="AQ321">
+        <v>0.88</v>
+      </c>
+      <c r="AR321">
+        <v>1.92</v>
+      </c>
+      <c r="AS321">
+        <v>1.31</v>
+      </c>
+      <c r="AT321">
+        <v>3.23</v>
+      </c>
+      <c r="AU321">
+        <v>6</v>
+      </c>
+      <c r="AV321">
+        <v>4</v>
+      </c>
+      <c r="AW321">
+        <v>6</v>
+      </c>
+      <c r="AX321">
+        <v>3</v>
+      </c>
+      <c r="AY321">
+        <v>16</v>
+      </c>
+      <c r="AZ321">
+        <v>11</v>
+      </c>
+      <c r="BA321">
+        <v>3</v>
+      </c>
+      <c r="BB321">
+        <v>3</v>
+      </c>
+      <c r="BC321">
+        <v>6</v>
+      </c>
+      <c r="BD321">
+        <v>1.43</v>
+      </c>
+      <c r="BE321">
+        <v>7</v>
+      </c>
+      <c r="BF321">
+        <v>3.15</v>
+      </c>
+      <c r="BG321">
+        <v>1.3</v>
+      </c>
+      <c r="BH321">
+        <v>3.05</v>
+      </c>
+      <c r="BI321">
+        <v>1.53</v>
+      </c>
+      <c r="BJ321">
+        <v>2.32</v>
+      </c>
+      <c r="BK321">
+        <v>1.86</v>
+      </c>
+      <c r="BL321">
+        <v>1.82</v>
+      </c>
+      <c r="BM321">
+        <v>2.33</v>
+      </c>
+      <c r="BN321">
+        <v>1.52</v>
+      </c>
+      <c r="BO321">
+        <v>2.95</v>
+      </c>
+      <c r="BP321">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -910,9 +910,6 @@
     <t>['42', '88']</t>
   </si>
   <si>
-    <t>['9']</t>
-  </si>
-  <si>
     <t>['37', '46']</t>
   </si>
   <si>
@@ -920,6 +917,9 @@
   </si>
   <si>
     <t>['45', '47']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
   <si>
     <t>['45+1', '90+4']</t>
@@ -934,10 +934,10 @@
     <t>['44', '83']</t>
   </si>
   <si>
-    <t>['28', '67']</t>
+    <t>['47', '66', '81']</t>
   </si>
   <si>
-    <t>['47', '66', '81']</t>
+    <t>['28', '67']</t>
   </si>
   <si>
     <t>['30', '48']</t>
@@ -955,10 +955,10 @@
     <t>['25', '81']</t>
   </si>
   <si>
-    <t>['86']</t>
+    <t>['14', '29', '45+3']</t>
   </si>
   <si>
-    <t>['14', '29', '45+3']</t>
+    <t>['86']</t>
   </si>
   <si>
     <t>['54']</t>
@@ -1351,10 +1351,10 @@
     <t>['15', '75']</t>
   </si>
   <si>
-    <t>['8', '18']</t>
+    <t>['12', '79']</t>
   </si>
   <si>
-    <t>['12', '79']</t>
+    <t>['8', '18']</t>
   </si>
   <si>
     <t>['4', '77']</t>
@@ -70776,7 +70776,7 @@
         <v>335</v>
       </c>
       <c r="B336">
-        <v>7509927</v>
+        <v>7509928</v>
       </c>
       <c r="C336" t="s">
         <v>68</v>
@@ -70791,19 +70791,19 @@
         <v>35</v>
       </c>
       <c r="G336" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H336" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I336">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J336">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K336">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L336">
         <v>1</v>
@@ -70815,46 +70815,46 @@
         <v>3</v>
       </c>
       <c r="O336" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="P336" t="s">
         <v>445</v>
       </c>
       <c r="Q336">
+        <v>4.33</v>
+      </c>
+      <c r="R336">
+        <v>2.05</v>
+      </c>
+      <c r="S336">
+        <v>2.75</v>
+      </c>
+      <c r="T336">
+        <v>1.44</v>
+      </c>
+      <c r="U336">
+        <v>2.63</v>
+      </c>
+      <c r="V336">
         <v>3.25</v>
       </c>
-      <c r="R336">
-        <v>2</v>
-      </c>
-      <c r="S336">
-        <v>3.75</v>
-      </c>
-      <c r="T336">
-        <v>1.5</v>
-      </c>
-      <c r="U336">
-        <v>2.5</v>
-      </c>
-      <c r="V336">
-        <v>3.5</v>
-      </c>
       <c r="W336">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X336">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y336">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z336">
-        <v>2.38</v>
+        <v>3.19</v>
       </c>
       <c r="AA336">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="AB336">
-        <v>2.99</v>
+        <v>2.27</v>
       </c>
       <c r="AC336">
         <v>0</v>
@@ -70863,16 +70863,16 @@
         <v>0</v>
       </c>
       <c r="AE336">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF336">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG336">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH336">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AI336">
         <v>1.95</v>
@@ -70890,52 +70890,52 @@
         <v>0</v>
       </c>
       <c r="AN336">
-        <v>1.59</v>
+        <v>1.06</v>
       </c>
       <c r="AO336">
-        <v>0.9399999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="AP336">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AQ336">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AR336">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="AS336">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AT336">
-        <v>2.61</v>
+        <v>2.91</v>
       </c>
       <c r="AU336">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV336">
         <v>5</v>
       </c>
       <c r="AW336">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX336">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AY336">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AZ336">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BA336">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB336">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC336">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD336">
         <v>0</v>
@@ -70982,7 +70982,7 @@
         <v>336</v>
       </c>
       <c r="B337">
-        <v>7509928</v>
+        <v>7509927</v>
       </c>
       <c r="C337" t="s">
         <v>68</v>
@@ -70997,19 +70997,19 @@
         <v>35</v>
       </c>
       <c r="G337" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H337" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K337">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L337">
         <v>1</v>
@@ -71021,46 +71021,46 @@
         <v>3</v>
       </c>
       <c r="O337" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="P337" t="s">
         <v>446</v>
       </c>
       <c r="Q337">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R337">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S337">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T337">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U337">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V337">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="W337">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X337">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y337">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z337">
-        <v>3.19</v>
+        <v>2.38</v>
       </c>
       <c r="AA337">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="AB337">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="AC337">
         <v>0</v>
@@ -71069,16 +71069,16 @@
         <v>0</v>
       </c>
       <c r="AE337">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF337">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG337">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH337">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AI337">
         <v>1.95</v>
@@ -71096,52 +71096,52 @@
         <v>0</v>
       </c>
       <c r="AN337">
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="AO337">
-        <v>1.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP337">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="AQ337">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AR337">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AS337">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AT337">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="AU337">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV337">
         <v>5</v>
       </c>
       <c r="AW337">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX337">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AY337">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AZ337">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA337">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB337">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC337">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD337">
         <v>0</v>
@@ -74278,7 +74278,7 @@
         <v>352</v>
       </c>
       <c r="B353">
-        <v>7509947</v>
+        <v>7509948</v>
       </c>
       <c r="C353" t="s">
         <v>68</v>
@@ -74293,55 +74293,55 @@
         <v>37</v>
       </c>
       <c r="G353" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H353" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J353">
         <v>0</v>
       </c>
       <c r="K353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M353">
         <v>0</v>
       </c>
       <c r="N353">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O353" t="s">
-        <v>298</v>
+        <v>102</v>
       </c>
       <c r="P353" t="s">
         <v>102</v>
       </c>
       <c r="Q353">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R353">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S353">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T353">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U353">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V353">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W353">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X353">
         <v>10</v>
@@ -74350,25 +74350,25 @@
         <v>1.06</v>
       </c>
       <c r="Z353">
-        <v>3.06</v>
+        <v>2.33</v>
       </c>
       <c r="AA353">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AB353">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="AC353">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD353">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE353">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AF353">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG353">
         <v>2.1</v>
@@ -74392,52 +74392,52 @@
         <v>0</v>
       </c>
       <c r="AN353">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO353">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="AP353">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="AQ353">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="AR353">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AS353">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AT353">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="AU353">
+        <v>6</v>
+      </c>
+      <c r="AV353">
         <v>3</v>
       </c>
-      <c r="AV353">
-        <v>6</v>
-      </c>
       <c r="AW353">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX353">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY353">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AZ353">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BA353">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB353">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC353">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BD353">
         <v>0</v>
@@ -74523,7 +74523,7 @@
         <v>3</v>
       </c>
       <c r="O354" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P354" t="s">
         <v>452</v>
@@ -74935,7 +74935,7 @@
         <v>3</v>
       </c>
       <c r="O356" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P356" t="s">
         <v>421</v>
@@ -75141,7 +75141,7 @@
         <v>4</v>
       </c>
       <c r="O357" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P357" t="s">
         <v>453</v>
@@ -75308,7 +75308,7 @@
         <v>357</v>
       </c>
       <c r="B358">
-        <v>7509948</v>
+        <v>7509947</v>
       </c>
       <c r="C358" t="s">
         <v>68</v>
@@ -75323,55 +75323,55 @@
         <v>37</v>
       </c>
       <c r="G358" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H358" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J358">
         <v>0</v>
       </c>
       <c r="K358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358">
         <v>0</v>
       </c>
       <c r="N358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O358" t="s">
-        <v>102</v>
+        <v>301</v>
       </c>
       <c r="P358" t="s">
         <v>102</v>
       </c>
       <c r="Q358">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R358">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S358">
+        <v>2.88</v>
+      </c>
+      <c r="T358">
+        <v>1.44</v>
+      </c>
+      <c r="U358">
+        <v>2.63</v>
+      </c>
+      <c r="V358">
         <v>3.25</v>
       </c>
-      <c r="T358">
-        <v>1.5</v>
-      </c>
-      <c r="U358">
-        <v>2.5</v>
-      </c>
-      <c r="V358">
-        <v>3.4</v>
-      </c>
       <c r="W358">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X358">
         <v>10</v>
@@ -75380,25 +75380,25 @@
         <v>1.06</v>
       </c>
       <c r="Z358">
-        <v>2.33</v>
+        <v>3.06</v>
       </c>
       <c r="AA358">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AB358">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
       <c r="AC358">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD358">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE358">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF358">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG358">
         <v>2.1</v>
@@ -75422,52 +75422,52 @@
         <v>0</v>
       </c>
       <c r="AN358">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AO358">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AP358">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="AQ358">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="AR358">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AS358">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AT358">
-        <v>2.78</v>
+        <v>2.61</v>
       </c>
       <c r="AU358">
+        <v>3</v>
+      </c>
+      <c r="AV358">
         <v>6</v>
       </c>
-      <c r="AV358">
-        <v>3</v>
-      </c>
       <c r="AW358">
+        <v>6</v>
+      </c>
+      <c r="AX358">
         <v>11</v>
       </c>
-      <c r="AX358">
+      <c r="AY358">
+        <v>9</v>
+      </c>
+      <c r="AZ358">
+        <v>17</v>
+      </c>
+      <c r="BA358">
         <v>5</v>
       </c>
-      <c r="AY358">
-        <v>17</v>
-      </c>
-      <c r="AZ358">
-        <v>8</v>
-      </c>
-      <c r="BA358">
-        <v>3</v>
-      </c>
       <c r="BB358">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC358">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BD358">
         <v>0</v>
@@ -76750,7 +76750,7 @@
         <v>364</v>
       </c>
       <c r="B365">
-        <v>7509961</v>
+        <v>7509957</v>
       </c>
       <c r="C365" t="s">
         <v>68</v>
@@ -76765,25 +76765,25 @@
         <v>38</v>
       </c>
       <c r="G365" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H365" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I365">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J365">
         <v>1</v>
       </c>
       <c r="K365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L365">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N365">
         <v>4</v>
@@ -76792,55 +76792,55 @@
         <v>306</v>
       </c>
       <c r="P365" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="Q365">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R365">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S365">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T365">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U365">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V365">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="W365">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X365">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y365">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z365">
-        <v>2.11</v>
+        <v>3.03</v>
       </c>
       <c r="AA365">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AB365">
-        <v>3.81</v>
+        <v>2.4</v>
       </c>
       <c r="AC365">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD365">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AE365">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF365">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AG365">
         <v>2.13</v>
@@ -76849,106 +76849,106 @@
         <v>1.65</v>
       </c>
       <c r="AI365">
+        <v>1.8</v>
+      </c>
+      <c r="AJ365">
         <v>1.95</v>
       </c>
-      <c r="AJ365">
-        <v>1.8</v>
-      </c>
       <c r="AK365">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AL365">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AM365">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AN365">
-        <v>1.47</v>
+        <v>0.76</v>
       </c>
       <c r="AO365">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP365">
-        <v>1.37</v>
+        <v>0.84</v>
       </c>
       <c r="AQ365">
-        <v>1.16</v>
+        <v>0.95</v>
       </c>
       <c r="AR365">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS365">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AT365">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AU365">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AV365">
         <v>5</v>
       </c>
       <c r="AW365">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX365">
+        <v>8</v>
+      </c>
+      <c r="AY365">
+        <v>19</v>
+      </c>
+      <c r="AZ365">
         <v>13</v>
       </c>
-      <c r="AY365">
-        <v>13</v>
-      </c>
-      <c r="AZ365">
-        <v>18</v>
-      </c>
       <c r="BA365">
         <v>2</v>
       </c>
       <c r="BB365">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC365">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD365">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="BE365">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BF365">
-        <v>2.54</v>
+        <v>1.98</v>
       </c>
       <c r="BG365">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="BH365">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="BI365">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BJ365">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="BK365">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="BL365">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="BM365">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="BN365">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO365">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="BP365">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="366" spans="1:68">
@@ -76956,7 +76956,7 @@
         <v>365</v>
       </c>
       <c r="B366">
-        <v>7509957</v>
+        <v>7509961</v>
       </c>
       <c r="C366" t="s">
         <v>68</v>
@@ -76971,25 +76971,25 @@
         <v>38</v>
       </c>
       <c r="G366" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H366" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I366">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J366">
         <v>1</v>
       </c>
       <c r="K366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L366">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N366">
         <v>4</v>
@@ -76998,55 +76998,55 @@
         <v>307</v>
       </c>
       <c r="P366" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="Q366">
+        <v>3.2</v>
+      </c>
+      <c r="R366">
+        <v>2</v>
+      </c>
+      <c r="S366">
+        <v>3.75</v>
+      </c>
+      <c r="T366">
+        <v>1.5</v>
+      </c>
+      <c r="U366">
+        <v>2.5</v>
+      </c>
+      <c r="V366">
         <v>3.4</v>
       </c>
-      <c r="R366">
-        <v>2.1</v>
-      </c>
-      <c r="S366">
-        <v>3.25</v>
-      </c>
-      <c r="T366">
-        <v>1.44</v>
-      </c>
-      <c r="U366">
+      <c r="W366">
+        <v>1.3</v>
+      </c>
+      <c r="X366">
+        <v>10</v>
+      </c>
+      <c r="Y366">
+        <v>1.06</v>
+      </c>
+      <c r="Z366">
+        <v>2.11</v>
+      </c>
+      <c r="AA366">
+        <v>2.99</v>
+      </c>
+      <c r="AB366">
+        <v>3.81</v>
+      </c>
+      <c r="AC366">
+        <v>1.05</v>
+      </c>
+      <c r="AD366">
+        <v>6.6</v>
+      </c>
+      <c r="AE366">
+        <v>1.4</v>
+      </c>
+      <c r="AF366">
         <v>2.63</v>
-      </c>
-      <c r="V366">
-        <v>3.25</v>
-      </c>
-      <c r="W366">
-        <v>1.33</v>
-      </c>
-      <c r="X366">
-        <v>9</v>
-      </c>
-      <c r="Y366">
-        <v>1.07</v>
-      </c>
-      <c r="Z366">
-        <v>3.03</v>
-      </c>
-      <c r="AA366">
-        <v>3.08</v>
-      </c>
-      <c r="AB366">
-        <v>2.4</v>
-      </c>
-      <c r="AC366">
-        <v>1.03</v>
-      </c>
-      <c r="AD366">
-        <v>7.5</v>
-      </c>
-      <c r="AE366">
-        <v>1.33</v>
-      </c>
-      <c r="AF366">
-        <v>2.9</v>
       </c>
       <c r="AG366">
         <v>2.13</v>
@@ -77055,106 +77055,106 @@
         <v>1.65</v>
       </c>
       <c r="AI366">
+        <v>1.95</v>
+      </c>
+      <c r="AJ366">
         <v>1.8</v>
       </c>
-      <c r="AJ366">
-        <v>1.95</v>
-      </c>
       <c r="AK366">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AL366">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AM366">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AN366">
-        <v>0.76</v>
+        <v>1.47</v>
       </c>
       <c r="AO366">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP366">
-        <v>0.84</v>
+        <v>1.37</v>
       </c>
       <c r="AQ366">
-        <v>0.95</v>
+        <v>1.16</v>
       </c>
       <c r="AR366">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS366">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AT366">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AU366">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV366">
         <v>5</v>
       </c>
       <c r="AW366">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX366">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AY366">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ366">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA366">
         <v>2</v>
       </c>
       <c r="BB366">
+        <v>1</v>
+      </c>
+      <c r="BC366">
         <v>3</v>
       </c>
-      <c r="BC366">
-        <v>5</v>
-      </c>
       <c r="BD366">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="BE366">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF366">
+        <v>2.54</v>
+      </c>
+      <c r="BG366">
+        <v>1.29</v>
+      </c>
+      <c r="BH366">
+        <v>3.04</v>
+      </c>
+      <c r="BI366">
+        <v>1.56</v>
+      </c>
+      <c r="BJ366">
+        <v>2.21</v>
+      </c>
+      <c r="BK366">
         <v>1.98</v>
       </c>
-      <c r="BG366">
-        <v>1.34</v>
-      </c>
-      <c r="BH366">
-        <v>2.78</v>
-      </c>
-      <c r="BI366">
-        <v>1.65</v>
-      </c>
-      <c r="BJ366">
-        <v>2.05</v>
-      </c>
-      <c r="BK366">
-        <v>2.12</v>
-      </c>
       <c r="BL366">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="BM366">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="BN366">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="BO366">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="BP366">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="367" spans="1:68">
@@ -78604,7 +78604,7 @@
         <v>373</v>
       </c>
       <c r="B374">
-        <v>7509922</v>
+        <v>7509918</v>
       </c>
       <c r="C374" t="s">
         <v>68</v>
@@ -78619,10 +78619,10 @@
         <v>34</v>
       </c>
       <c r="G374" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H374" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I374">
         <v>0</v>
@@ -78634,175 +78634,175 @@
         <v>1</v>
       </c>
       <c r="L374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N374">
         <v>2</v>
       </c>
       <c r="O374" t="s">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="P374" t="s">
-        <v>166</v>
+        <v>458</v>
       </c>
       <c r="Q374">
+        <v>3.6</v>
+      </c>
+      <c r="R374">
+        <v>2</v>
+      </c>
+      <c r="S374">
+        <v>3.25</v>
+      </c>
+      <c r="T374">
+        <v>1.5</v>
+      </c>
+      <c r="U374">
+        <v>2.5</v>
+      </c>
+      <c r="V374">
+        <v>3.4</v>
+      </c>
+      <c r="W374">
+        <v>1.3</v>
+      </c>
+      <c r="X374">
+        <v>10</v>
+      </c>
+      <c r="Y374">
+        <v>1.06</v>
+      </c>
+      <c r="Z374">
+        <v>3.09</v>
+      </c>
+      <c r="AA374">
+        <v>3.17</v>
+      </c>
+      <c r="AB374">
+        <v>2.32</v>
+      </c>
+      <c r="AC374">
+        <v>1.09</v>
+      </c>
+      <c r="AD374">
+        <v>7</v>
+      </c>
+      <c r="AE374">
+        <v>1.42</v>
+      </c>
+      <c r="AF374">
+        <v>2.8</v>
+      </c>
+      <c r="AG374">
+        <v>1.94</v>
+      </c>
+      <c r="AH374">
+        <v>1.8</v>
+      </c>
+      <c r="AI374">
+        <v>1.91</v>
+      </c>
+      <c r="AJ374">
+        <v>1.91</v>
+      </c>
+      <c r="AK374">
+        <v>1.48</v>
+      </c>
+      <c r="AL374">
+        <v>1.33</v>
+      </c>
+      <c r="AM374">
+        <v>1.38</v>
+      </c>
+      <c r="AN374">
+        <v>0.89</v>
+      </c>
+      <c r="AO374">
+        <v>0.44</v>
+      </c>
+      <c r="AP374">
+        <v>0.84</v>
+      </c>
+      <c r="AQ374">
+        <v>0.58</v>
+      </c>
+      <c r="AR374">
+        <v>1.43</v>
+      </c>
+      <c r="AS374">
+        <v>1.19</v>
+      </c>
+      <c r="AT374">
+        <v>2.62</v>
+      </c>
+      <c r="AU374">
+        <v>2</v>
+      </c>
+      <c r="AV374">
+        <v>4</v>
+      </c>
+      <c r="AW374">
+        <v>15</v>
+      </c>
+      <c r="AX374">
+        <v>11</v>
+      </c>
+      <c r="AY374">
+        <v>17</v>
+      </c>
+      <c r="AZ374">
+        <v>15</v>
+      </c>
+      <c r="BA374">
+        <v>5</v>
+      </c>
+      <c r="BB374">
+        <v>2</v>
+      </c>
+      <c r="BC374">
+        <v>7</v>
+      </c>
+      <c r="BD374">
+        <v>1.95</v>
+      </c>
+      <c r="BE374">
+        <v>8</v>
+      </c>
+      <c r="BF374">
+        <v>2.05</v>
+      </c>
+      <c r="BG374">
+        <v>1.43</v>
+      </c>
+      <c r="BH374">
+        <v>2.54</v>
+      </c>
+      <c r="BI374">
+        <v>1.77</v>
+      </c>
+      <c r="BJ374">
+        <v>1.95</v>
+      </c>
+      <c r="BK374">
         <v>2.3</v>
       </c>
-      <c r="R374">
-        <v>2.25</v>
-      </c>
-      <c r="S374">
-        <v>5</v>
-      </c>
-      <c r="T374">
-        <v>1.36</v>
-      </c>
-      <c r="U374">
-        <v>3</v>
-      </c>
-      <c r="V374">
-        <v>2.63</v>
-      </c>
-      <c r="W374">
-        <v>1.44</v>
-      </c>
-      <c r="X374">
-        <v>7</v>
-      </c>
-      <c r="Y374">
-        <v>1.1</v>
-      </c>
-      <c r="Z374">
-        <v>1.81</v>
-      </c>
-      <c r="AA374">
-        <v>3.64</v>
-      </c>
-      <c r="AB374">
-        <v>4.1</v>
-      </c>
-      <c r="AC374">
-        <v>1.05</v>
-      </c>
-      <c r="AD374">
-        <v>9.5</v>
-      </c>
-      <c r="AE374">
-        <v>1.25</v>
-      </c>
-      <c r="AF374">
-        <v>3.7</v>
-      </c>
-      <c r="AG374">
-        <v>1.8</v>
-      </c>
-      <c r="AH374">
-        <v>1.94</v>
-      </c>
-      <c r="AI374">
-        <v>1.75</v>
-      </c>
-      <c r="AJ374">
-        <v>2</v>
-      </c>
-      <c r="AK374">
-        <v>1.18</v>
-      </c>
-      <c r="AL374">
-        <v>1.22</v>
-      </c>
-      <c r="AM374">
-        <v>2.1</v>
-      </c>
-      <c r="AN374">
-        <v>1.56</v>
-      </c>
-      <c r="AO374">
-        <v>0.5</v>
-      </c>
-      <c r="AP374">
-        <v>1.53</v>
-      </c>
-      <c r="AQ374">
-        <v>0.53</v>
-      </c>
-      <c r="AR374">
-        <v>1.75</v>
-      </c>
-      <c r="AS374">
-        <v>1.18</v>
-      </c>
-      <c r="AT374">
-        <v>2.93</v>
-      </c>
-      <c r="AU374">
-        <v>10</v>
-      </c>
-      <c r="AV374">
-        <v>5</v>
-      </c>
-      <c r="AW374">
-        <v>21</v>
-      </c>
-      <c r="AX374">
-        <v>8</v>
-      </c>
-      <c r="AY374">
-        <v>31</v>
-      </c>
-      <c r="AZ374">
-        <v>13</v>
-      </c>
-      <c r="BA374">
-        <v>10</v>
-      </c>
-      <c r="BB374">
-        <v>3</v>
-      </c>
-      <c r="BC374">
-        <v>13</v>
-      </c>
-      <c r="BD374">
-        <v>1.62</v>
-      </c>
-      <c r="BE374">
-        <v>8.5</v>
-      </c>
-      <c r="BF374">
-        <v>2.6</v>
-      </c>
-      <c r="BG374">
-        <v>1.22</v>
-      </c>
-      <c r="BH374">
-        <v>3.5</v>
-      </c>
-      <c r="BI374">
-        <v>1.44</v>
-      </c>
-      <c r="BJ374">
-        <v>2.51</v>
-      </c>
-      <c r="BK374">
-        <v>1.77</v>
-      </c>
       <c r="BL374">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="BM374">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="BN374">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="BO374">
-        <v>2.97</v>
+        <v>4.45</v>
       </c>
       <c r="BP374">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="375" spans="1:68">
@@ -78810,7 +78810,7 @@
         <v>374</v>
       </c>
       <c r="B375">
-        <v>7509925</v>
+        <v>7509919</v>
       </c>
       <c r="C375" t="s">
         <v>68</v>
@@ -78825,190 +78825,190 @@
         <v>34</v>
       </c>
       <c r="G375" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H375" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I375">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J375">
         <v>0</v>
       </c>
       <c r="K375">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L375">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N375">
+        <v>0</v>
+      </c>
+      <c r="O375" t="s">
+        <v>102</v>
+      </c>
+      <c r="P375" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q375">
+        <v>3.1</v>
+      </c>
+      <c r="R375">
+        <v>1.95</v>
+      </c>
+      <c r="S375">
         <v>4</v>
       </c>
-      <c r="O375" t="s">
-        <v>314</v>
-      </c>
-      <c r="P375" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q375">
-        <v>1.91</v>
-      </c>
-      <c r="R375">
+      <c r="T375">
+        <v>1.53</v>
+      </c>
+      <c r="U375">
         <v>2.38</v>
       </c>
-      <c r="S375">
-        <v>7.5</v>
-      </c>
-      <c r="T375">
-        <v>1.36</v>
-      </c>
-      <c r="U375">
-        <v>3</v>
-      </c>
       <c r="V375">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="W375">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="X375">
+        <v>11</v>
+      </c>
+      <c r="Y375">
+        <v>1.05</v>
+      </c>
+      <c r="Z375">
+        <v>2.61</v>
+      </c>
+      <c r="AA375">
+        <v>3.06</v>
+      </c>
+      <c r="AB375">
+        <v>2.78</v>
+      </c>
+      <c r="AC375">
+        <v>1.1</v>
+      </c>
+      <c r="AD375">
+        <v>6.5</v>
+      </c>
+      <c r="AE375">
+        <v>1.45</v>
+      </c>
+      <c r="AF375">
+        <v>2.7</v>
+      </c>
+      <c r="AG375">
+        <v>2.1</v>
+      </c>
+      <c r="AH375">
+        <v>1.6</v>
+      </c>
+      <c r="AI375">
+        <v>2</v>
+      </c>
+      <c r="AJ375">
+        <v>1.75</v>
+      </c>
+      <c r="AK375">
+        <v>1.3</v>
+      </c>
+      <c r="AL375">
+        <v>1.33</v>
+      </c>
+      <c r="AM375">
+        <v>1.57</v>
+      </c>
+      <c r="AN375">
+        <v>1.83</v>
+      </c>
+      <c r="AO375">
+        <v>0.83</v>
+      </c>
+      <c r="AP375">
+        <v>1.9</v>
+      </c>
+      <c r="AQ375">
+        <v>0.84</v>
+      </c>
+      <c r="AR375">
+        <v>1.4</v>
+      </c>
+      <c r="AS375">
+        <v>1.3</v>
+      </c>
+      <c r="AT375">
+        <v>2.7</v>
+      </c>
+      <c r="AU375">
+        <v>0</v>
+      </c>
+      <c r="AV375">
+        <v>8</v>
+      </c>
+      <c r="AW375">
+        <v>13</v>
+      </c>
+      <c r="AX375">
         <v>7</v>
-      </c>
-      <c r="Y375">
-        <v>1.1</v>
-      </c>
-      <c r="Z375">
-        <v>1.47</v>
-      </c>
-      <c r="AA375">
-        <v>4.4</v>
-      </c>
-      <c r="AB375">
-        <v>6.2</v>
-      </c>
-      <c r="AC375">
-        <v>1.04</v>
-      </c>
-      <c r="AD375">
-        <v>10</v>
-      </c>
-      <c r="AE375">
-        <v>1.25</v>
-      </c>
-      <c r="AF375">
-        <v>3.9</v>
-      </c>
-      <c r="AG375">
-        <v>1.79</v>
-      </c>
-      <c r="AH375">
-        <v>1.95</v>
-      </c>
-      <c r="AI375">
-        <v>2.05</v>
-      </c>
-      <c r="AJ375">
-        <v>1.7</v>
-      </c>
-      <c r="AK375">
-        <v>1.08</v>
-      </c>
-      <c r="AL375">
-        <v>1.14</v>
-      </c>
-      <c r="AM375">
-        <v>2.9</v>
-      </c>
-      <c r="AN375">
-        <v>2.06</v>
-      </c>
-      <c r="AO375">
-        <v>0.67</v>
-      </c>
-      <c r="AP375">
-        <v>2.05</v>
-      </c>
-      <c r="AQ375">
-        <v>0.63</v>
-      </c>
-      <c r="AR375">
-        <v>1.9</v>
-      </c>
-      <c r="AS375">
-        <v>1.36</v>
-      </c>
-      <c r="AT375">
-        <v>3.26</v>
-      </c>
-      <c r="AU375">
-        <v>7</v>
-      </c>
-      <c r="AV375">
-        <v>6</v>
-      </c>
-      <c r="AW375">
-        <v>6</v>
-      </c>
-      <c r="AX375">
-        <v>16</v>
       </c>
       <c r="AY375">
         <v>13</v>
       </c>
       <c r="AZ375">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA375">
+        <v>7</v>
+      </c>
+      <c r="BB375">
         <v>4</v>
       </c>
-      <c r="BB375">
+      <c r="BC375">
+        <v>11</v>
+      </c>
+      <c r="BD375">
+        <v>1.85</v>
+      </c>
+      <c r="BE375">
         <v>8</v>
       </c>
-      <c r="BC375">
-        <v>12</v>
-      </c>
-      <c r="BD375">
-        <v>1.25</v>
-      </c>
-      <c r="BE375">
-        <v>11</v>
-      </c>
       <c r="BF375">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="BG375">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BH375">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="BI375">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="BJ375">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="BK375">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="BL375">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="BM375">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="BN375">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="BO375">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="BP375">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="376" spans="1:68">
@@ -79016,7 +79016,7 @@
         <v>375</v>
       </c>
       <c r="B376">
-        <v>7509926</v>
+        <v>7509920</v>
       </c>
       <c r="C376" t="s">
         <v>68</v>
@@ -79031,10 +79031,10 @@
         <v>34</v>
       </c>
       <c r="G376" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H376" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I376">
         <v>0</v>
@@ -79061,160 +79061,160 @@
         <v>102</v>
       </c>
       <c r="Q376">
+        <v>3</v>
+      </c>
+      <c r="R376">
+        <v>2.1</v>
+      </c>
+      <c r="S376">
+        <v>3.5</v>
+      </c>
+      <c r="T376">
+        <v>1.4</v>
+      </c>
+      <c r="U376">
+        <v>2.75</v>
+      </c>
+      <c r="V376">
+        <v>3</v>
+      </c>
+      <c r="W376">
+        <v>1.36</v>
+      </c>
+      <c r="X376">
+        <v>8</v>
+      </c>
+      <c r="Y376">
+        <v>1.08</v>
+      </c>
+      <c r="Z376">
+        <v>2.58</v>
+      </c>
+      <c r="AA376">
+        <v>3.28</v>
+      </c>
+      <c r="AB376">
+        <v>2.65</v>
+      </c>
+      <c r="AC376">
+        <v>1.06</v>
+      </c>
+      <c r="AD376">
+        <v>8.5</v>
+      </c>
+      <c r="AE376">
+        <v>1.33</v>
+      </c>
+      <c r="AF376">
         <v>3.25</v>
       </c>
-      <c r="R376">
-        <v>2</v>
-      </c>
-      <c r="S376">
-        <v>3.6</v>
-      </c>
-      <c r="T376">
-        <v>1.5</v>
-      </c>
-      <c r="U376">
-        <v>2.5</v>
-      </c>
-      <c r="V376">
-        <v>3.5</v>
-      </c>
-      <c r="W376">
-        <v>1.29</v>
-      </c>
-      <c r="X376">
-        <v>10</v>
-      </c>
-      <c r="Y376">
-        <v>1.06</v>
-      </c>
-      <c r="Z376">
-        <v>2.57</v>
-      </c>
-      <c r="AA376">
-        <v>2.97</v>
-      </c>
-      <c r="AB376">
-        <v>2.9</v>
-      </c>
-      <c r="AC376">
-        <v>1.1</v>
-      </c>
-      <c r="AD376">
-        <v>6.5</v>
-      </c>
-      <c r="AE376">
-        <v>1.44</v>
-      </c>
-      <c r="AF376">
-        <v>2.75</v>
-      </c>
       <c r="AG376">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH376">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AI376">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AJ376">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AK376">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL376">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM376">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AN376">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AO376">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="AP376">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="AQ376">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="AR376">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AS376">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AT376">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AU376">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV376">
+        <v>2</v>
+      </c>
+      <c r="AW376">
+        <v>16</v>
+      </c>
+      <c r="AX376">
+        <v>6</v>
+      </c>
+      <c r="AY376">
+        <v>21</v>
+      </c>
+      <c r="AZ376">
         <v>8</v>
       </c>
-      <c r="AW376">
-        <v>11</v>
-      </c>
-      <c r="AX376">
-        <v>26</v>
-      </c>
-      <c r="AY376">
-        <v>15</v>
-      </c>
-      <c r="AZ376">
-        <v>34</v>
-      </c>
       <c r="BA376">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB376">
+        <v>3</v>
+      </c>
+      <c r="BC376">
         <v>8</v>
       </c>
-      <c r="BC376">
-        <v>14</v>
-      </c>
       <c r="BD376">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="BE376">
         <v>8</v>
       </c>
       <c r="BF376">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BG376">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="BH376">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="BI376">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="BJ376">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="BK376">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="BL376">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BM376">
-        <v>2.51</v>
+        <v>2.93</v>
       </c>
       <c r="BN376">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BO376">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="BP376">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="377" spans="1:68">
@@ -79428,7 +79428,7 @@
         <v>377</v>
       </c>
       <c r="B378">
-        <v>7509924</v>
+        <v>7509926</v>
       </c>
       <c r="C378" t="s">
         <v>68</v>
@@ -79443,190 +79443,190 @@
         <v>34</v>
       </c>
       <c r="G378" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H378" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I378">
         <v>0</v>
       </c>
       <c r="J378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L378">
         <v>0</v>
       </c>
       <c r="M378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O378" t="s">
         <v>102</v>
       </c>
       <c r="P378" t="s">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="Q378">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="R378">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S378">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T378">
+        <v>1.5</v>
+      </c>
+      <c r="U378">
+        <v>2.5</v>
+      </c>
+      <c r="V378">
+        <v>3.5</v>
+      </c>
+      <c r="W378">
+        <v>1.29</v>
+      </c>
+      <c r="X378">
+        <v>10</v>
+      </c>
+      <c r="Y378">
+        <v>1.06</v>
+      </c>
+      <c r="Z378">
+        <v>2.57</v>
+      </c>
+      <c r="AA378">
+        <v>2.97</v>
+      </c>
+      <c r="AB378">
+        <v>2.9</v>
+      </c>
+      <c r="AC378">
+        <v>1.1</v>
+      </c>
+      <c r="AD378">
+        <v>6.5</v>
+      </c>
+      <c r="AE378">
+        <v>1.44</v>
+      </c>
+      <c r="AF378">
+        <v>2.75</v>
+      </c>
+      <c r="AG378">
+        <v>1.98</v>
+      </c>
+      <c r="AH378">
+        <v>1.77</v>
+      </c>
+      <c r="AI378">
+        <v>1.91</v>
+      </c>
+      <c r="AJ378">
+        <v>1.91</v>
+      </c>
+      <c r="AK378">
+        <v>1.38</v>
+      </c>
+      <c r="AL378">
         <v>1.33</v>
       </c>
-      <c r="U378">
-        <v>3.25</v>
-      </c>
-      <c r="V378">
-        <v>2.63</v>
-      </c>
-      <c r="W378">
+      <c r="AM378">
+        <v>1.48</v>
+      </c>
+      <c r="AN378">
+        <v>1.33</v>
+      </c>
+      <c r="AO378">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AP378">
+        <v>1.32</v>
+      </c>
+      <c r="AQ378">
+        <v>0.95</v>
+      </c>
+      <c r="AR378">
         <v>1.44</v>
       </c>
-      <c r="X378">
-        <v>6.5</v>
-      </c>
-      <c r="Y378">
-        <v>1.11</v>
-      </c>
-      <c r="Z378">
-        <v>1.65</v>
-      </c>
-      <c r="AA378">
-        <v>3.96</v>
-      </c>
-      <c r="AB378">
-        <v>4.7</v>
-      </c>
-      <c r="AC378">
-        <v>1.05</v>
-      </c>
-      <c r="AD378">
-        <v>9.5</v>
-      </c>
-      <c r="AE378">
-        <v>1.25</v>
-      </c>
-      <c r="AF378">
-        <v>3.8</v>
-      </c>
-      <c r="AG378">
-        <v>1.79</v>
-      </c>
-      <c r="AH378">
-        <v>1.95</v>
-      </c>
-      <c r="AI378">
-        <v>1.7</v>
-      </c>
-      <c r="AJ378">
-        <v>2.05</v>
-      </c>
-      <c r="AK378">
-        <v>1.17</v>
-      </c>
-      <c r="AL378">
-        <v>1.22</v>
-      </c>
-      <c r="AM378">
+      <c r="AS378">
+        <v>1.37</v>
+      </c>
+      <c r="AT378">
+        <v>2.81</v>
+      </c>
+      <c r="AU378">
+        <v>4</v>
+      </c>
+      <c r="AV378">
+        <v>8</v>
+      </c>
+      <c r="AW378">
+        <v>11</v>
+      </c>
+      <c r="AX378">
+        <v>26</v>
+      </c>
+      <c r="AY378">
+        <v>15</v>
+      </c>
+      <c r="AZ378">
+        <v>34</v>
+      </c>
+      <c r="BA378">
+        <v>6</v>
+      </c>
+      <c r="BB378">
+        <v>8</v>
+      </c>
+      <c r="BC378">
+        <v>14</v>
+      </c>
+      <c r="BD378">
         <v>2.1</v>
       </c>
-      <c r="AN378">
-        <v>2.44</v>
-      </c>
-      <c r="AO378">
-        <v>1</v>
-      </c>
-      <c r="AP378">
-        <v>2.32</v>
-      </c>
-      <c r="AQ378">
-        <v>1.11</v>
-      </c>
-      <c r="AR378">
-        <v>1.7</v>
-      </c>
-      <c r="AS378">
+      <c r="BE378">
+        <v>8</v>
+      </c>
+      <c r="BF378">
+        <v>1.91</v>
+      </c>
+      <c r="BG378">
         <v>1.27</v>
       </c>
-      <c r="AT378">
-        <v>2.97</v>
-      </c>
-      <c r="AU378">
-        <v>6</v>
-      </c>
-      <c r="AV378">
-        <v>7</v>
-      </c>
-      <c r="AW378">
-        <v>10</v>
-      </c>
-      <c r="AX378">
-        <v>10</v>
-      </c>
-      <c r="AY378">
-        <v>16</v>
-      </c>
-      <c r="AZ378">
-        <v>17</v>
-      </c>
-      <c r="BA378">
-        <v>7</v>
-      </c>
-      <c r="BB378">
-        <v>4</v>
-      </c>
-      <c r="BC378">
-        <v>11</v>
-      </c>
-      <c r="BD378">
-        <v>1.5</v>
-      </c>
-      <c r="BE378">
-        <v>9</v>
-      </c>
-      <c r="BF378">
-        <v>2.88</v>
-      </c>
-      <c r="BG378">
-        <v>1.33</v>
-      </c>
       <c r="BH378">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BI378">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BJ378">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="BK378">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BL378">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BM378">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="BN378">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="BO378">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="BP378">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="379" spans="1:68">
@@ -79634,7 +79634,7 @@
         <v>378</v>
       </c>
       <c r="B379">
-        <v>7509920</v>
+        <v>7509925</v>
       </c>
       <c r="C379" t="s">
         <v>68</v>
@@ -79649,190 +79649,190 @@
         <v>34</v>
       </c>
       <c r="G379" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H379" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I379">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J379">
         <v>0</v>
       </c>
       <c r="K379">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L379">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M379">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N379">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O379" t="s">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="P379" t="s">
-        <v>102</v>
+        <v>258</v>
       </c>
       <c r="Q379">
+        <v>1.91</v>
+      </c>
+      <c r="R379">
+        <v>2.38</v>
+      </c>
+      <c r="S379">
+        <v>7.5</v>
+      </c>
+      <c r="T379">
+        <v>1.36</v>
+      </c>
+      <c r="U379">
         <v>3</v>
       </c>
-      <c r="R379">
-        <v>2.1</v>
-      </c>
-      <c r="S379">
-        <v>3.5</v>
-      </c>
-      <c r="T379">
-        <v>1.4</v>
-      </c>
-      <c r="U379">
-        <v>2.75</v>
-      </c>
       <c r="V379">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W379">
+        <v>1.44</v>
+      </c>
+      <c r="X379">
+        <v>7</v>
+      </c>
+      <c r="Y379">
+        <v>1.1</v>
+      </c>
+      <c r="Z379">
+        <v>1.47</v>
+      </c>
+      <c r="AA379">
+        <v>4.4</v>
+      </c>
+      <c r="AB379">
+        <v>6.2</v>
+      </c>
+      <c r="AC379">
+        <v>1.04</v>
+      </c>
+      <c r="AD379">
+        <v>10</v>
+      </c>
+      <c r="AE379">
+        <v>1.25</v>
+      </c>
+      <c r="AF379">
+        <v>3.9</v>
+      </c>
+      <c r="AG379">
+        <v>1.79</v>
+      </c>
+      <c r="AH379">
+        <v>1.95</v>
+      </c>
+      <c r="AI379">
+        <v>2.05</v>
+      </c>
+      <c r="AJ379">
+        <v>1.7</v>
+      </c>
+      <c r="AK379">
+        <v>1.08</v>
+      </c>
+      <c r="AL379">
+        <v>1.14</v>
+      </c>
+      <c r="AM379">
+        <v>2.9</v>
+      </c>
+      <c r="AN379">
+        <v>2.06</v>
+      </c>
+      <c r="AO379">
+        <v>0.67</v>
+      </c>
+      <c r="AP379">
+        <v>2.05</v>
+      </c>
+      <c r="AQ379">
+        <v>0.63</v>
+      </c>
+      <c r="AR379">
+        <v>1.9</v>
+      </c>
+      <c r="AS379">
         <v>1.36</v>
       </c>
-      <c r="X379">
+      <c r="AT379">
+        <v>3.26</v>
+      </c>
+      <c r="AU379">
+        <v>7</v>
+      </c>
+      <c r="AV379">
+        <v>6</v>
+      </c>
+      <c r="AW379">
+        <v>6</v>
+      </c>
+      <c r="AX379">
+        <v>16</v>
+      </c>
+      <c r="AY379">
+        <v>13</v>
+      </c>
+      <c r="AZ379">
+        <v>22</v>
+      </c>
+      <c r="BA379">
+        <v>4</v>
+      </c>
+      <c r="BB379">
         <v>8</v>
       </c>
-      <c r="Y379">
-        <v>1.08</v>
-      </c>
-      <c r="Z379">
-        <v>2.58</v>
-      </c>
-      <c r="AA379">
-        <v>3.28</v>
-      </c>
-      <c r="AB379">
-        <v>2.65</v>
-      </c>
-      <c r="AC379">
-        <v>1.06</v>
-      </c>
-      <c r="AD379">
-        <v>8.5</v>
-      </c>
-      <c r="AE379">
-        <v>1.33</v>
-      </c>
-      <c r="AF379">
-        <v>3.25</v>
-      </c>
-      <c r="AG379">
-        <v>1.8</v>
-      </c>
-      <c r="AH379">
-        <v>1.94</v>
-      </c>
-      <c r="AI379">
-        <v>1.7</v>
-      </c>
-      <c r="AJ379">
-        <v>2.05</v>
-      </c>
-      <c r="AK379">
-        <v>1.4</v>
-      </c>
-      <c r="AL379">
+      <c r="BC379">
+        <v>12</v>
+      </c>
+      <c r="BD379">
+        <v>1.25</v>
+      </c>
+      <c r="BE379">
+        <v>11</v>
+      </c>
+      <c r="BF379">
+        <v>4.2</v>
+      </c>
+      <c r="BG379">
+        <v>1.23</v>
+      </c>
+      <c r="BH379">
+        <v>3.42</v>
+      </c>
+      <c r="BI379">
+        <v>1.46</v>
+      </c>
+      <c r="BJ379">
+        <v>2.45</v>
+      </c>
+      <c r="BK379">
+        <v>1.85</v>
+      </c>
+      <c r="BL379">
+        <v>1.85</v>
+      </c>
+      <c r="BM379">
+        <v>2.3</v>
+      </c>
+      <c r="BN379">
+        <v>1.52</v>
+      </c>
+      <c r="BO379">
+        <v>3.05</v>
+      </c>
+      <c r="BP379">
         <v>1.28</v>
-      </c>
-      <c r="AM379">
-        <v>1.53</v>
-      </c>
-      <c r="AN379">
-        <v>1.67</v>
-      </c>
-      <c r="AO379">
-        <v>1.22</v>
-      </c>
-      <c r="AP379">
-        <v>1.63</v>
-      </c>
-      <c r="AQ379">
-        <v>1.15</v>
-      </c>
-      <c r="AR379">
-        <v>1.51</v>
-      </c>
-      <c r="AS379">
-        <v>1.22</v>
-      </c>
-      <c r="AT379">
-        <v>2.73</v>
-      </c>
-      <c r="AU379">
-        <v>5</v>
-      </c>
-      <c r="AV379">
-        <v>2</v>
-      </c>
-      <c r="AW379">
-        <v>16</v>
-      </c>
-      <c r="AX379">
-        <v>6</v>
-      </c>
-      <c r="AY379">
-        <v>21</v>
-      </c>
-      <c r="AZ379">
-        <v>8</v>
-      </c>
-      <c r="BA379">
-        <v>5</v>
-      </c>
-      <c r="BB379">
-        <v>3</v>
-      </c>
-      <c r="BC379">
-        <v>8</v>
-      </c>
-      <c r="BD379">
-        <v>1.75</v>
-      </c>
-      <c r="BE379">
-        <v>8</v>
-      </c>
-      <c r="BF379">
-        <v>2.38</v>
-      </c>
-      <c r="BG379">
-        <v>1.36</v>
-      </c>
-      <c r="BH379">
-        <v>2.69</v>
-      </c>
-      <c r="BI379">
-        <v>1.8</v>
-      </c>
-      <c r="BJ379">
-        <v>1.9</v>
-      </c>
-      <c r="BK379">
-        <v>2.19</v>
-      </c>
-      <c r="BL379">
-        <v>1.6</v>
-      </c>
-      <c r="BM379">
-        <v>2.93</v>
-      </c>
-      <c r="BN379">
-        <v>1.33</v>
-      </c>
-      <c r="BO379">
-        <v>4.1</v>
-      </c>
-      <c r="BP379">
-        <v>1.16</v>
       </c>
     </row>
     <row r="380" spans="1:68">
@@ -79840,7 +79840,7 @@
         <v>379</v>
       </c>
       <c r="B380">
-        <v>7509919</v>
+        <v>7509924</v>
       </c>
       <c r="C380" t="s">
         <v>68</v>
@@ -79855,142 +79855,142 @@
         <v>34</v>
       </c>
       <c r="G380" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H380" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I380">
         <v>0</v>
       </c>
       <c r="J380">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K380">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L380">
         <v>0</v>
       </c>
       <c r="M380">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N380">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O380" t="s">
         <v>102</v>
       </c>
       <c r="P380" t="s">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="Q380">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R380">
+        <v>2.3</v>
+      </c>
+      <c r="S380">
+        <v>5</v>
+      </c>
+      <c r="T380">
+        <v>1.33</v>
+      </c>
+      <c r="U380">
+        <v>3.25</v>
+      </c>
+      <c r="V380">
+        <v>2.63</v>
+      </c>
+      <c r="W380">
+        <v>1.44</v>
+      </c>
+      <c r="X380">
+        <v>6.5</v>
+      </c>
+      <c r="Y380">
+        <v>1.11</v>
+      </c>
+      <c r="Z380">
+        <v>1.65</v>
+      </c>
+      <c r="AA380">
+        <v>3.96</v>
+      </c>
+      <c r="AB380">
+        <v>4.7</v>
+      </c>
+      <c r="AC380">
+        <v>1.05</v>
+      </c>
+      <c r="AD380">
+        <v>9.5</v>
+      </c>
+      <c r="AE380">
+        <v>1.25</v>
+      </c>
+      <c r="AF380">
+        <v>3.8</v>
+      </c>
+      <c r="AG380">
+        <v>1.79</v>
+      </c>
+      <c r="AH380">
         <v>1.95</v>
       </c>
-      <c r="S380">
-        <v>4</v>
-      </c>
-      <c r="T380">
-        <v>1.53</v>
-      </c>
-      <c r="U380">
-        <v>2.38</v>
-      </c>
-      <c r="V380">
-        <v>3.5</v>
-      </c>
-      <c r="W380">
-        <v>1.29</v>
-      </c>
-      <c r="X380">
-        <v>11</v>
-      </c>
-      <c r="Y380">
-        <v>1.05</v>
-      </c>
-      <c r="Z380">
-        <v>2.61</v>
-      </c>
-      <c r="AA380">
-        <v>3.06</v>
-      </c>
-      <c r="AB380">
-        <v>2.78</v>
-      </c>
-      <c r="AC380">
-        <v>1.1</v>
-      </c>
-      <c r="AD380">
-        <v>6.5</v>
-      </c>
-      <c r="AE380">
-        <v>1.45</v>
-      </c>
-      <c r="AF380">
-        <v>2.7</v>
-      </c>
-      <c r="AG380">
+      <c r="AI380">
+        <v>1.7</v>
+      </c>
+      <c r="AJ380">
+        <v>2.05</v>
+      </c>
+      <c r="AK380">
+        <v>1.17</v>
+      </c>
+      <c r="AL380">
+        <v>1.22</v>
+      </c>
+      <c r="AM380">
         <v>2.1</v>
       </c>
-      <c r="AH380">
-        <v>1.6</v>
-      </c>
-      <c r="AI380">
-        <v>2</v>
-      </c>
-      <c r="AJ380">
-        <v>1.75</v>
-      </c>
-      <c r="AK380">
-        <v>1.3</v>
-      </c>
-      <c r="AL380">
-        <v>1.33</v>
-      </c>
-      <c r="AM380">
-        <v>1.57</v>
-      </c>
       <c r="AN380">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AO380">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP380">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AQ380">
-        <v>0.84</v>
+        <v>1.11</v>
       </c>
       <c r="AR380">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AS380">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT380">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AU380">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV380">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW380">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX380">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY380">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ380">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA380">
         <v>7</v>
@@ -80002,43 +80002,43 @@
         <v>11</v>
       </c>
       <c r="BD380">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="BE380">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF380">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="BG380">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BH380">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="BI380">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BJ380">
+        <v>2.1</v>
+      </c>
+      <c r="BK380">
         <v>2.05</v>
-      </c>
-      <c r="BK380">
-        <v>2.03</v>
       </c>
       <c r="BL380">
         <v>1.7</v>
       </c>
       <c r="BM380">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BN380">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BO380">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="BP380">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="381" spans="1:68">
@@ -80046,7 +80046,7 @@
         <v>380</v>
       </c>
       <c r="B381">
-        <v>7509918</v>
+        <v>7509922</v>
       </c>
       <c r="C381" t="s">
         <v>68</v>
@@ -80061,10 +80061,10 @@
         <v>34</v>
       </c>
       <c r="G381" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H381" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I381">
         <v>0</v>
@@ -80076,175 +80076,175 @@
         <v>1</v>
       </c>
       <c r="L381">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M381">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N381">
         <v>2</v>
       </c>
       <c r="O381" t="s">
-        <v>102</v>
+        <v>314</v>
       </c>
       <c r="P381" t="s">
-        <v>458</v>
+        <v>166</v>
       </c>
       <c r="Q381">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R381">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S381">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="T381">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="U381">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V381">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="W381">
+        <v>1.44</v>
+      </c>
+      <c r="X381">
+        <v>7</v>
+      </c>
+      <c r="Y381">
+        <v>1.1</v>
+      </c>
+      <c r="Z381">
+        <v>1.81</v>
+      </c>
+      <c r="AA381">
+        <v>3.64</v>
+      </c>
+      <c r="AB381">
+        <v>4.1</v>
+      </c>
+      <c r="AC381">
+        <v>1.05</v>
+      </c>
+      <c r="AD381">
+        <v>9.5</v>
+      </c>
+      <c r="AE381">
+        <v>1.25</v>
+      </c>
+      <c r="AF381">
+        <v>3.7</v>
+      </c>
+      <c r="AG381">
+        <v>1.8</v>
+      </c>
+      <c r="AH381">
+        <v>1.94</v>
+      </c>
+      <c r="AI381">
+        <v>1.75</v>
+      </c>
+      <c r="AJ381">
+        <v>2</v>
+      </c>
+      <c r="AK381">
+        <v>1.18</v>
+      </c>
+      <c r="AL381">
+        <v>1.22</v>
+      </c>
+      <c r="AM381">
+        <v>2.1</v>
+      </c>
+      <c r="AN381">
+        <v>1.56</v>
+      </c>
+      <c r="AO381">
+        <v>0.5</v>
+      </c>
+      <c r="AP381">
+        <v>1.53</v>
+      </c>
+      <c r="AQ381">
+        <v>0.53</v>
+      </c>
+      <c r="AR381">
+        <v>1.75</v>
+      </c>
+      <c r="AS381">
+        <v>1.18</v>
+      </c>
+      <c r="AT381">
+        <v>2.93</v>
+      </c>
+      <c r="AU381">
+        <v>10</v>
+      </c>
+      <c r="AV381">
+        <v>5</v>
+      </c>
+      <c r="AW381">
+        <v>21</v>
+      </c>
+      <c r="AX381">
+        <v>8</v>
+      </c>
+      <c r="AY381">
+        <v>31</v>
+      </c>
+      <c r="AZ381">
+        <v>13</v>
+      </c>
+      <c r="BA381">
+        <v>10</v>
+      </c>
+      <c r="BB381">
+        <v>3</v>
+      </c>
+      <c r="BC381">
+        <v>13</v>
+      </c>
+      <c r="BD381">
+        <v>1.62</v>
+      </c>
+      <c r="BE381">
+        <v>8.5</v>
+      </c>
+      <c r="BF381">
+        <v>2.6</v>
+      </c>
+      <c r="BG381">
+        <v>1.22</v>
+      </c>
+      <c r="BH381">
+        <v>3.5</v>
+      </c>
+      <c r="BI381">
+        <v>1.44</v>
+      </c>
+      <c r="BJ381">
+        <v>2.51</v>
+      </c>
+      <c r="BK381">
+        <v>1.77</v>
+      </c>
+      <c r="BL381">
+        <v>1.95</v>
+      </c>
+      <c r="BM381">
+        <v>2.25</v>
+      </c>
+      <c r="BN381">
+        <v>1.54</v>
+      </c>
+      <c r="BO381">
+        <v>2.97</v>
+      </c>
+      <c r="BP381">
         <v>1.3</v>
-      </c>
-      <c r="X381">
-        <v>10</v>
-      </c>
-      <c r="Y381">
-        <v>1.06</v>
-      </c>
-      <c r="Z381">
-        <v>3.09</v>
-      </c>
-      <c r="AA381">
-        <v>3.17</v>
-      </c>
-      <c r="AB381">
-        <v>2.32</v>
-      </c>
-      <c r="AC381">
-        <v>1.09</v>
-      </c>
-      <c r="AD381">
-        <v>7</v>
-      </c>
-      <c r="AE381">
-        <v>1.42</v>
-      </c>
-      <c r="AF381">
-        <v>2.8</v>
-      </c>
-      <c r="AG381">
-        <v>1.94</v>
-      </c>
-      <c r="AH381">
-        <v>1.8</v>
-      </c>
-      <c r="AI381">
-        <v>1.91</v>
-      </c>
-      <c r="AJ381">
-        <v>1.91</v>
-      </c>
-      <c r="AK381">
-        <v>1.48</v>
-      </c>
-      <c r="AL381">
-        <v>1.33</v>
-      </c>
-      <c r="AM381">
-        <v>1.38</v>
-      </c>
-      <c r="AN381">
-        <v>0.89</v>
-      </c>
-      <c r="AO381">
-        <v>0.44</v>
-      </c>
-      <c r="AP381">
-        <v>0.84</v>
-      </c>
-      <c r="AQ381">
-        <v>0.58</v>
-      </c>
-      <c r="AR381">
-        <v>1.43</v>
-      </c>
-      <c r="AS381">
-        <v>1.19</v>
-      </c>
-      <c r="AT381">
-        <v>2.62</v>
-      </c>
-      <c r="AU381">
-        <v>2</v>
-      </c>
-      <c r="AV381">
-        <v>4</v>
-      </c>
-      <c r="AW381">
-        <v>15</v>
-      </c>
-      <c r="AX381">
-        <v>11</v>
-      </c>
-      <c r="AY381">
-        <v>17</v>
-      </c>
-      <c r="AZ381">
-        <v>15</v>
-      </c>
-      <c r="BA381">
-        <v>5</v>
-      </c>
-      <c r="BB381">
-        <v>2</v>
-      </c>
-      <c r="BC381">
-        <v>7</v>
-      </c>
-      <c r="BD381">
-        <v>1.95</v>
-      </c>
-      <c r="BE381">
-        <v>8</v>
-      </c>
-      <c r="BF381">
-        <v>2.05</v>
-      </c>
-      <c r="BG381">
-        <v>1.43</v>
-      </c>
-      <c r="BH381">
-        <v>2.54</v>
-      </c>
-      <c r="BI381">
-        <v>1.77</v>
-      </c>
-      <c r="BJ381">
-        <v>1.95</v>
-      </c>
-      <c r="BK381">
-        <v>2.3</v>
-      </c>
-      <c r="BL381">
-        <v>1.52</v>
-      </c>
-      <c r="BM381">
-        <v>3.08</v>
-      </c>
-      <c r="BN381">
-        <v>1.28</v>
-      </c>
-      <c r="BO381">
-        <v>4.45</v>
-      </c>
-      <c r="BP381">
-        <v>1.14</v>
       </c>
     </row>
     <row r="382" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="462">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -976,6 +976,9 @@
     <t>['83', '85']</t>
   </si>
   <si>
+    <t>['39', '86']</t>
+  </si>
+  <si>
     <t>['24', '45+2', '80']</t>
   </si>
   <si>
@@ -1758,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP389"/>
+  <dimension ref="A1:BP390"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2220,7 +2223,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
@@ -2632,7 +2635,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q5">
         <v>3.2</v>
@@ -3044,7 +3047,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
@@ -3456,7 +3459,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -4074,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -4361,7 +4364,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ13">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR13">
         <v>1.31</v>
@@ -4486,7 +4489,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q14">
         <v>2.3</v>
@@ -4564,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
         <v>1.05</v>
@@ -5928,7 +5931,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -6340,7 +6343,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q23">
         <v>2.98</v>
@@ -6752,7 +6755,7 @@
         <v>102</v>
       </c>
       <c r="P25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q25">
         <v>2.74</v>
@@ -7370,7 +7373,7 @@
         <v>91</v>
       </c>
       <c r="P28" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -8272,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ32">
         <v>0.95</v>
@@ -8400,7 +8403,7 @@
         <v>115</v>
       </c>
       <c r="P33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q33">
         <v>2.9</v>
@@ -8606,7 +8609,7 @@
         <v>116</v>
       </c>
       <c r="P34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -9018,7 +9021,7 @@
         <v>102</v>
       </c>
       <c r="P36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q36">
         <v>2.8</v>
@@ -9305,7 +9308,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ37">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9636,7 +9639,7 @@
         <v>119</v>
       </c>
       <c r="P39" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -9842,7 +9845,7 @@
         <v>120</v>
       </c>
       <c r="P40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
@@ -10254,7 +10257,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q42">
         <v>2.88</v>
@@ -10666,7 +10669,7 @@
         <v>123</v>
       </c>
       <c r="P44" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -11696,7 +11699,7 @@
         <v>102</v>
       </c>
       <c r="P49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q49">
         <v>3.75</v>
@@ -11902,7 +11905,7 @@
         <v>116</v>
       </c>
       <c r="P50" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -12108,7 +12111,7 @@
         <v>128</v>
       </c>
       <c r="P51" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12314,7 +12317,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q52">
         <v>3.79</v>
@@ -12804,7 +12807,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ54">
         <v>1.11</v>
@@ -13425,7 +13428,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ57">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR57">
         <v>1.46</v>
@@ -13756,7 +13759,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13962,7 +13965,7 @@
         <v>102</v>
       </c>
       <c r="P60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -14374,7 +14377,7 @@
         <v>134</v>
       </c>
       <c r="P62" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -15198,7 +15201,7 @@
         <v>136</v>
       </c>
       <c r="P66" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q66">
         <v>2.4</v>
@@ -15610,7 +15613,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q68">
         <v>3.1</v>
@@ -16022,7 +16025,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q70">
         <v>3.5</v>
@@ -16228,7 +16231,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q71">
         <v>3.5</v>
@@ -16434,7 +16437,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q72">
         <v>2.4</v>
@@ -16512,7 +16515,7 @@
         <v>1.25</v>
       </c>
       <c r="AP72">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ72">
         <v>1.05</v>
@@ -16846,7 +16849,7 @@
         <v>142</v>
       </c>
       <c r="P74" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q74">
         <v>2.95</v>
@@ -17052,7 +17055,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -17464,7 +17467,7 @@
         <v>102</v>
       </c>
       <c r="P77" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q77">
         <v>3.2</v>
@@ -17876,7 +17879,7 @@
         <v>144</v>
       </c>
       <c r="P79" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q79">
         <v>3.1</v>
@@ -18163,7 +18166,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ80">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -18288,7 +18291,7 @@
         <v>145</v>
       </c>
       <c r="P81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q81">
         <v>3.4</v>
@@ -18700,7 +18703,7 @@
         <v>146</v>
       </c>
       <c r="P83" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q83">
         <v>3.6</v>
@@ -18906,7 +18909,7 @@
         <v>102</v>
       </c>
       <c r="P84" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q84">
         <v>3.4</v>
@@ -19112,7 +19115,7 @@
         <v>147</v>
       </c>
       <c r="P85" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q85">
         <v>3.2</v>
@@ -19524,7 +19527,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q87">
         <v>3.2</v>
@@ -20142,7 +20145,7 @@
         <v>151</v>
       </c>
       <c r="P90" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q90">
         <v>3.75</v>
@@ -20348,7 +20351,7 @@
         <v>152</v>
       </c>
       <c r="P91" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q91">
         <v>3.1</v>
@@ -21253,7 +21256,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ95">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR95">
         <v>1.55</v>
@@ -22486,7 +22489,7 @@
         <v>0.4</v>
       </c>
       <c r="AP101">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ101">
         <v>0.68</v>
@@ -23026,7 +23029,7 @@
         <v>159</v>
       </c>
       <c r="P104" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q104">
         <v>3.9</v>
@@ -23232,7 +23235,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q105">
         <v>3.25</v>
@@ -24674,7 +24677,7 @@
         <v>163</v>
       </c>
       <c r="P112" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q112">
         <v>2.75</v>
@@ -25785,7 +25788,7 @@
         <v>1.16</v>
       </c>
       <c r="AQ117">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR117">
         <v>1.61</v>
@@ -25910,7 +25913,7 @@
         <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q118">
         <v>2.88</v>
@@ -26606,7 +26609,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ121">
         <v>1.16</v>
@@ -26734,7 +26737,7 @@
         <v>166</v>
       </c>
       <c r="P122" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q122">
         <v>3.45</v>
@@ -26940,7 +26943,7 @@
         <v>167</v>
       </c>
       <c r="P123" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -27970,7 +27973,7 @@
         <v>102</v>
       </c>
       <c r="P128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q128">
         <v>3.35</v>
@@ -28176,7 +28179,7 @@
         <v>102</v>
       </c>
       <c r="P129" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q129">
         <v>3.65</v>
@@ -28382,7 +28385,7 @@
         <v>170</v>
       </c>
       <c r="P130" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28588,7 +28591,7 @@
         <v>102</v>
       </c>
       <c r="P131" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28794,7 +28797,7 @@
         <v>121</v>
       </c>
       <c r="P132" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q132">
         <v>3.4</v>
@@ -29287,7 +29290,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ134">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29618,7 +29621,7 @@
         <v>173</v>
       </c>
       <c r="P136" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q136">
         <v>2.5</v>
@@ -30236,7 +30239,7 @@
         <v>176</v>
       </c>
       <c r="P139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q139">
         <v>2.6</v>
@@ -30854,7 +30857,7 @@
         <v>102</v>
       </c>
       <c r="P142" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q142">
         <v>4.2</v>
@@ -31060,7 +31063,7 @@
         <v>102</v>
       </c>
       <c r="P143" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q143">
         <v>3.95</v>
@@ -31266,7 +31269,7 @@
         <v>179</v>
       </c>
       <c r="P144" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q144">
         <v>2.55</v>
@@ -31344,7 +31347,7 @@
         <v>0.83</v>
       </c>
       <c r="AP144">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ144">
         <v>1.15</v>
@@ -31472,7 +31475,7 @@
         <v>180</v>
       </c>
       <c r="P145" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q145">
         <v>3.1</v>
@@ -32296,7 +32299,7 @@
         <v>183</v>
       </c>
       <c r="P149" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q149">
         <v>2.63</v>
@@ -32502,7 +32505,7 @@
         <v>184</v>
       </c>
       <c r="P150" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q150">
         <v>3.6</v>
@@ -32914,7 +32917,7 @@
         <v>186</v>
       </c>
       <c r="P152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q152">
         <v>2.95</v>
@@ -33532,7 +33535,7 @@
         <v>188</v>
       </c>
       <c r="P155" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q155">
         <v>3.7</v>
@@ -33819,7 +33822,7 @@
         <v>1.37</v>
       </c>
       <c r="AQ156">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR156">
         <v>1.49</v>
@@ -33944,7 +33947,7 @@
         <v>102</v>
       </c>
       <c r="P157" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q157">
         <v>2.9</v>
@@ -34356,7 +34359,7 @@
         <v>102</v>
       </c>
       <c r="P159" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q159">
         <v>2.2</v>
@@ -35180,7 +35183,7 @@
         <v>193</v>
       </c>
       <c r="P163" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -35592,7 +35595,7 @@
         <v>194</v>
       </c>
       <c r="P165" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q165">
         <v>4.33</v>
@@ -36082,7 +36085,7 @@
         <v>1.38</v>
       </c>
       <c r="AP167">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ167">
         <v>1.43</v>
@@ -36210,7 +36213,7 @@
         <v>196</v>
       </c>
       <c r="P168" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q168">
         <v>2.4</v>
@@ -36828,7 +36831,7 @@
         <v>197</v>
       </c>
       <c r="P171" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -38270,7 +38273,7 @@
         <v>201</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q178">
         <v>3.1</v>
@@ -38476,7 +38479,7 @@
         <v>102</v>
       </c>
       <c r="P179" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q179">
         <v>3.55</v>
@@ -39587,7 +39590,7 @@
         <v>1.16</v>
       </c>
       <c r="AQ184">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR184">
         <v>1.33</v>
@@ -39712,7 +39715,7 @@
         <v>91</v>
       </c>
       <c r="P185" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q185">
         <v>2.3</v>
@@ -40124,7 +40127,7 @@
         <v>205</v>
       </c>
       <c r="P187" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q187">
         <v>3.25</v>
@@ -40536,7 +40539,7 @@
         <v>207</v>
       </c>
       <c r="P189" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q189">
         <v>3.1</v>
@@ -40948,7 +40951,7 @@
         <v>209</v>
       </c>
       <c r="P191" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q191">
         <v>2.75</v>
@@ -41026,7 +41029,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP191">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ191">
         <v>0.53</v>
@@ -41154,7 +41157,7 @@
         <v>210</v>
       </c>
       <c r="P192" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q192">
         <v>2.4</v>
@@ -41772,7 +41775,7 @@
         <v>102</v>
       </c>
       <c r="P195" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q195">
         <v>2.5</v>
@@ -42471,7 +42474,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ198">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR198">
         <v>1.22</v>
@@ -42802,7 +42805,7 @@
         <v>151</v>
       </c>
       <c r="P200" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q200">
         <v>2.63</v>
@@ -43086,7 +43089,7 @@
         <v>1.56</v>
       </c>
       <c r="AP201">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ201">
         <v>1.63</v>
@@ -43214,7 +43217,7 @@
         <v>215</v>
       </c>
       <c r="P202" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q202">
         <v>4.33</v>
@@ -43832,7 +43835,7 @@
         <v>217</v>
       </c>
       <c r="P205" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q205">
         <v>3.4</v>
@@ -44038,7 +44041,7 @@
         <v>218</v>
       </c>
       <c r="P206" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q206">
         <v>2.75</v>
@@ -44450,7 +44453,7 @@
         <v>102</v>
       </c>
       <c r="P208" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -45274,7 +45277,7 @@
         <v>217</v>
       </c>
       <c r="P212" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q212">
         <v>3</v>
@@ -45352,7 +45355,7 @@
         <v>0.5</v>
       </c>
       <c r="AP212">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ212">
         <v>1.1</v>
@@ -45480,7 +45483,7 @@
         <v>108</v>
       </c>
       <c r="P213" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q213">
         <v>2.7</v>
@@ -46098,7 +46101,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q216">
         <v>2.87</v>
@@ -46304,7 +46307,7 @@
         <v>223</v>
       </c>
       <c r="P217" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q217">
         <v>2.65</v>
@@ -46922,7 +46925,7 @@
         <v>224</v>
       </c>
       <c r="P220" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q220">
         <v>2.05</v>
@@ -47128,7 +47131,7 @@
         <v>102</v>
       </c>
       <c r="P221" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q221">
         <v>3.75</v>
@@ -47334,7 +47337,7 @@
         <v>225</v>
       </c>
       <c r="P222" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q222">
         <v>3.1</v>
@@ -47746,7 +47749,7 @@
         <v>102</v>
       </c>
       <c r="P224" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q224">
         <v>2.95</v>
@@ -47952,7 +47955,7 @@
         <v>102</v>
       </c>
       <c r="P225" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q225">
         <v>3</v>
@@ -48364,7 +48367,7 @@
         <v>227</v>
       </c>
       <c r="P227" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q227">
         <v>3.3</v>
@@ -48651,7 +48654,7 @@
         <v>2.26</v>
       </c>
       <c r="AQ228">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR228">
         <v>1.45</v>
@@ -48982,7 +48985,7 @@
         <v>110</v>
       </c>
       <c r="P230" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q230">
         <v>2.9</v>
@@ -49188,7 +49191,7 @@
         <v>230</v>
       </c>
       <c r="P231" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q231">
         <v>2.6</v>
@@ -49394,7 +49397,7 @@
         <v>108</v>
       </c>
       <c r="P232" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q232">
         <v>3.1</v>
@@ -49806,7 +49809,7 @@
         <v>102</v>
       </c>
       <c r="P234" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q234">
         <v>4.75</v>
@@ -50090,7 +50093,7 @@
         <v>0.91</v>
       </c>
       <c r="AP235">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ235">
         <v>0.63</v>
@@ -50218,7 +50221,7 @@
         <v>233</v>
       </c>
       <c r="P236" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q236">
         <v>3.4</v>
@@ -50630,7 +50633,7 @@
         <v>235</v>
       </c>
       <c r="P238" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q238">
         <v>3</v>
@@ -51248,7 +51251,7 @@
         <v>237</v>
       </c>
       <c r="P241" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q241">
         <v>2.75</v>
@@ -51535,7 +51538,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ242">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -51660,7 +51663,7 @@
         <v>102</v>
       </c>
       <c r="P243" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q243">
         <v>4.75</v>
@@ -52562,7 +52565,7 @@
         <v>0.83</v>
       </c>
       <c r="AP247">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ247">
         <v>1</v>
@@ -52690,7 +52693,7 @@
         <v>239</v>
       </c>
       <c r="P248" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q248">
         <v>2.6</v>
@@ -53801,7 +53804,7 @@
         <v>1.84</v>
       </c>
       <c r="AQ253">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR253">
         <v>1.38</v>
@@ -53926,7 +53929,7 @@
         <v>243</v>
       </c>
       <c r="P254" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q254">
         <v>3.4</v>
@@ -54750,7 +54753,7 @@
         <v>245</v>
       </c>
       <c r="P258" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -55652,7 +55655,7 @@
         <v>2.08</v>
       </c>
       <c r="AP262">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ262">
         <v>2</v>
@@ -55986,7 +55989,7 @@
         <v>102</v>
       </c>
       <c r="P264" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q264">
         <v>3.5</v>
@@ -56398,7 +56401,7 @@
         <v>250</v>
       </c>
       <c r="P266" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q266">
         <v>2.85</v>
@@ -56604,7 +56607,7 @@
         <v>251</v>
       </c>
       <c r="P267" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q267">
         <v>2.4</v>
@@ -57222,7 +57225,7 @@
         <v>102</v>
       </c>
       <c r="P270" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q270">
         <v>3.4</v>
@@ -58046,7 +58049,7 @@
         <v>253</v>
       </c>
       <c r="P274" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q274">
         <v>2.7</v>
@@ -58252,7 +58255,7 @@
         <v>254</v>
       </c>
       <c r="P275" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q275">
         <v>4.2</v>
@@ -58539,7 +58542,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ276">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR276">
         <v>1.43</v>
@@ -58870,7 +58873,7 @@
         <v>235</v>
       </c>
       <c r="P278" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q278">
         <v>2.8</v>
@@ -59488,7 +59491,7 @@
         <v>258</v>
       </c>
       <c r="P281" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q281">
         <v>3</v>
@@ -60802,7 +60805,7 @@
         <v>1.14</v>
       </c>
       <c r="AP287">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ287">
         <v>1.15</v>
@@ -60930,7 +60933,7 @@
         <v>232</v>
       </c>
       <c r="P288" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q288">
         <v>3.25</v>
@@ -61342,7 +61345,7 @@
         <v>260</v>
       </c>
       <c r="P290" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61548,7 +61551,7 @@
         <v>246</v>
       </c>
       <c r="P291" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q291">
         <v>3.5</v>
@@ -61754,7 +61757,7 @@
         <v>261</v>
       </c>
       <c r="P292" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q292">
         <v>3.1</v>
@@ -61960,7 +61963,7 @@
         <v>90</v>
       </c>
       <c r="P293" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q293">
         <v>4.5</v>
@@ -62865,7 +62868,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ297">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR297">
         <v>1.35</v>
@@ -63196,7 +63199,7 @@
         <v>265</v>
       </c>
       <c r="P299" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q299">
         <v>3.5</v>
@@ -63402,7 +63405,7 @@
         <v>266</v>
       </c>
       <c r="P300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q300">
         <v>3</v>
@@ -63814,7 +63817,7 @@
         <v>102</v>
       </c>
       <c r="P302" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q302">
         <v>2.1</v>
@@ -64020,7 +64023,7 @@
         <v>102</v>
       </c>
       <c r="P303" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q303">
         <v>4.33</v>
@@ -64432,7 +64435,7 @@
         <v>269</v>
       </c>
       <c r="P305" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q305">
         <v>2.75</v>
@@ -64638,7 +64641,7 @@
         <v>102</v>
       </c>
       <c r="P306" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q306">
         <v>2.88</v>
@@ -64716,7 +64719,7 @@
         <v>1</v>
       </c>
       <c r="AP306">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ306">
         <v>1.11</v>
@@ -64844,7 +64847,7 @@
         <v>270</v>
       </c>
       <c r="P307" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q307">
         <v>2</v>
@@ -65050,7 +65053,7 @@
         <v>271</v>
       </c>
       <c r="P308" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q308">
         <v>2.25</v>
@@ -65462,7 +65465,7 @@
         <v>200</v>
       </c>
       <c r="P310" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q310">
         <v>3.25</v>
@@ -65668,7 +65671,7 @@
         <v>273</v>
       </c>
       <c r="P311" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q311">
         <v>3.25</v>
@@ -65874,7 +65877,7 @@
         <v>141</v>
       </c>
       <c r="P312" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q312">
         <v>4.33</v>
@@ -66286,7 +66289,7 @@
         <v>274</v>
       </c>
       <c r="P314" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q314">
         <v>2.63</v>
@@ -66492,7 +66495,7 @@
         <v>275</v>
       </c>
       <c r="P315" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q315">
         <v>2.88</v>
@@ -66904,7 +66907,7 @@
         <v>187</v>
       </c>
       <c r="P317" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q317">
         <v>2.6</v>
@@ -67191,7 +67194,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ318">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR318">
         <v>1.29</v>
@@ -67316,7 +67319,7 @@
         <v>277</v>
       </c>
       <c r="P319" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q319">
         <v>3.25</v>
@@ -67522,7 +67525,7 @@
         <v>278</v>
       </c>
       <c r="P320" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q320">
         <v>3</v>
@@ -67934,7 +67937,7 @@
         <v>280</v>
       </c>
       <c r="P322" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q322">
         <v>3.5</v>
@@ -68140,7 +68143,7 @@
         <v>281</v>
       </c>
       <c r="P323" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q323">
         <v>3.1</v>
@@ -68552,7 +68555,7 @@
         <v>102</v>
       </c>
       <c r="P325" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q325">
         <v>4.33</v>
@@ -69042,7 +69045,7 @@
         <v>1.44</v>
       </c>
       <c r="AP327">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ327">
         <v>1.26</v>
@@ -69170,7 +69173,7 @@
         <v>210</v>
       </c>
       <c r="P328" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q328">
         <v>3.6</v>
@@ -69582,7 +69585,7 @@
         <v>144</v>
       </c>
       <c r="P330" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q330">
         <v>2.38</v>
@@ -69788,7 +69791,7 @@
         <v>284</v>
       </c>
       <c r="P331" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q331">
         <v>4.33</v>
@@ -69994,7 +69997,7 @@
         <v>285</v>
       </c>
       <c r="P332" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q332">
         <v>4.33</v>
@@ -70612,7 +70615,7 @@
         <v>287</v>
       </c>
       <c r="P335" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q335">
         <v>2.75</v>
@@ -70818,7 +70821,7 @@
         <v>288</v>
       </c>
       <c r="P336" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q336">
         <v>4.33</v>
@@ -71024,7 +71027,7 @@
         <v>221</v>
       </c>
       <c r="P337" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q337">
         <v>3.25</v>
@@ -71230,7 +71233,7 @@
         <v>289</v>
       </c>
       <c r="P338" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q338">
         <v>2.1</v>
@@ -71436,7 +71439,7 @@
         <v>102</v>
       </c>
       <c r="P339" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q339">
         <v>3.75</v>
@@ -71848,7 +71851,7 @@
         <v>228</v>
       </c>
       <c r="P341" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q341">
         <v>3.25</v>
@@ -72260,7 +72263,7 @@
         <v>292</v>
       </c>
       <c r="P343" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q343">
         <v>2.75</v>
@@ -72547,7 +72550,7 @@
         <v>2.05</v>
       </c>
       <c r="AQ344">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR344">
         <v>1.9</v>
@@ -72750,7 +72753,7 @@
         <v>1.75</v>
       </c>
       <c r="AP345">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ345">
         <v>1.67</v>
@@ -73496,7 +73499,7 @@
         <v>276</v>
       </c>
       <c r="P349" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q349">
         <v>2.5</v>
@@ -74526,7 +74529,7 @@
         <v>298</v>
       </c>
       <c r="P354" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q354">
         <v>2.88</v>
@@ -74732,7 +74735,7 @@
         <v>164</v>
       </c>
       <c r="P355" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q355">
         <v>3.1</v>
@@ -74938,7 +74941,7 @@
         <v>299</v>
       </c>
       <c r="P356" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q356">
         <v>4</v>
@@ -75144,7 +75147,7 @@
         <v>300</v>
       </c>
       <c r="P357" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q357">
         <v>2.88</v>
@@ -75762,7 +75765,7 @@
         <v>303</v>
       </c>
       <c r="P360" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q360">
         <v>2.38</v>
@@ -76174,7 +76177,7 @@
         <v>102</v>
       </c>
       <c r="P362" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q362">
         <v>5</v>
@@ -76380,7 +76383,7 @@
         <v>115</v>
       </c>
       <c r="P363" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q363">
         <v>3</v>
@@ -77410,7 +77413,7 @@
         <v>309</v>
       </c>
       <c r="P368" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q368">
         <v>2.75</v>
@@ -77694,10 +77697,10 @@
         <v>0.47</v>
       </c>
       <c r="AP369">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AQ369">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR369">
         <v>1.4</v>
@@ -77822,7 +77825,7 @@
         <v>102</v>
       </c>
       <c r="P370" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q370">
         <v>2.3</v>
@@ -78028,7 +78031,7 @@
         <v>310</v>
       </c>
       <c r="P371" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q371">
         <v>2.88</v>
@@ -78646,7 +78649,7 @@
         <v>102</v>
       </c>
       <c r="P374" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q374">
         <v>3.6</v>
@@ -78727,7 +78730,7 @@
         <v>0.84</v>
       </c>
       <c r="AQ374">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="AR374">
         <v>1.43</v>
@@ -80706,7 +80709,7 @@
         <v>102</v>
       </c>
       <c r="P384" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q384">
         <v>3.55</v>
@@ -81736,7 +81739,7 @@
         <v>319</v>
       </c>
       <c r="P389" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q389">
         <v>3.04</v>
@@ -81893,6 +81896,212 @@
       </c>
       <c r="BP389">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="390" spans="1:68">
+      <c r="A390" s="1">
+        <v>389</v>
+      </c>
+      <c r="B390">
+        <v>7899322</v>
+      </c>
+      <c r="C390" t="s">
+        <v>68</v>
+      </c>
+      <c r="D390" t="s">
+        <v>69</v>
+      </c>
+      <c r="E390" s="2">
+        <v>45823.64583333334</v>
+      </c>
+      <c r="F390">
+        <v>0</v>
+      </c>
+      <c r="G390" t="s">
+        <v>81</v>
+      </c>
+      <c r="H390" t="s">
+        <v>74</v>
+      </c>
+      <c r="I390">
+        <v>1</v>
+      </c>
+      <c r="J390">
+        <v>0</v>
+      </c>
+      <c r="K390">
+        <v>1</v>
+      </c>
+      <c r="L390">
+        <v>2</v>
+      </c>
+      <c r="M390">
+        <v>0</v>
+      </c>
+      <c r="N390">
+        <v>2</v>
+      </c>
+      <c r="O390" t="s">
+        <v>320</v>
+      </c>
+      <c r="P390" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q390">
+        <v>2.8</v>
+      </c>
+      <c r="R390">
+        <v>2</v>
+      </c>
+      <c r="S390">
+        <v>3.7</v>
+      </c>
+      <c r="T390">
+        <v>1.44</v>
+      </c>
+      <c r="U390">
+        <v>2.55</v>
+      </c>
+      <c r="V390">
+        <v>3.1</v>
+      </c>
+      <c r="W390">
+        <v>1.33</v>
+      </c>
+      <c r="X390">
+        <v>8.25</v>
+      </c>
+      <c r="Y390">
+        <v>1.06</v>
+      </c>
+      <c r="Z390">
+        <v>2.22</v>
+      </c>
+      <c r="AA390">
+        <v>3.13</v>
+      </c>
+      <c r="AB390">
+        <v>3.33</v>
+      </c>
+      <c r="AC390">
+        <v>1.07</v>
+      </c>
+      <c r="AD390">
+        <v>7.5</v>
+      </c>
+      <c r="AE390">
+        <v>1.38</v>
+      </c>
+      <c r="AF390">
+        <v>2.8</v>
+      </c>
+      <c r="AG390">
+        <v>2.1</v>
+      </c>
+      <c r="AH390">
+        <v>1.6</v>
+      </c>
+      <c r="AI390">
+        <v>1.9</v>
+      </c>
+      <c r="AJ390">
+        <v>1.77</v>
+      </c>
+      <c r="AK390">
+        <v>1.33</v>
+      </c>
+      <c r="AL390">
+        <v>1.32</v>
+      </c>
+      <c r="AM390">
+        <v>1.62</v>
+      </c>
+      <c r="AN390">
+        <v>1.08</v>
+      </c>
+      <c r="AO390">
+        <v>1.11</v>
+      </c>
+      <c r="AP390">
+        <v>1.13</v>
+      </c>
+      <c r="AQ390">
+        <v>1.08</v>
+      </c>
+      <c r="AR390">
+        <v>1.36</v>
+      </c>
+      <c r="AS390">
+        <v>1.46</v>
+      </c>
+      <c r="AT390">
+        <v>2.82</v>
+      </c>
+      <c r="AU390">
+        <v>5</v>
+      </c>
+      <c r="AV390">
+        <v>3</v>
+      </c>
+      <c r="AW390">
+        <v>5</v>
+      </c>
+      <c r="AX390">
+        <v>2</v>
+      </c>
+      <c r="AY390">
+        <v>10</v>
+      </c>
+      <c r="AZ390">
+        <v>5</v>
+      </c>
+      <c r="BA390">
+        <v>7</v>
+      </c>
+      <c r="BB390">
+        <v>1</v>
+      </c>
+      <c r="BC390">
+        <v>8</v>
+      </c>
+      <c r="BD390">
+        <v>1.5</v>
+      </c>
+      <c r="BE390">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF390">
+        <v>3.2</v>
+      </c>
+      <c r="BG390">
+        <v>1.3</v>
+      </c>
+      <c r="BH390">
+        <v>2.97</v>
+      </c>
+      <c r="BI390">
+        <v>1.58</v>
+      </c>
+      <c r="BJ390">
+        <v>2.17</v>
+      </c>
+      <c r="BK390">
+        <v>2.02</v>
+      </c>
+      <c r="BL390">
+        <v>1.71</v>
+      </c>
+      <c r="BM390">
+        <v>2.64</v>
+      </c>
+      <c r="BN390">
+        <v>1.4</v>
+      </c>
+      <c r="BO390">
+        <v>3.58</v>
+      </c>
+      <c r="BP390">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Italy Serie B_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="463">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1401,6 +1401,9 @@
   <si>
     <t>['25', '62', '79']</t>
   </si>
+  <si>
+    <t>['38', '49']</t>
+  </si>
 </sst>
 </file>
 
@@ -1761,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP390"/>
+  <dimension ref="A1:BP391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2919,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ6">
         <v>1.26</v>
@@ -3128,7 +3131,7 @@
         <v>1.16</v>
       </c>
       <c r="AQ7">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -6421,10 +6424,10 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ23">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR23">
         <v>1.67</v>
@@ -11574,7 +11577,7 @@
         <v>1.16</v>
       </c>
       <c r="AQ48">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR48">
         <v>1.3</v>
@@ -12189,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ51">
         <v>1.63</v>
@@ -15694,7 +15697,7 @@
         <v>1.37</v>
       </c>
       <c r="AQ68">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR68">
         <v>1.55</v>
@@ -15897,7 +15900,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ69">
         <v>1.15</v>
@@ -18987,7 +18990,7 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ84">
         <v>1.43</v>
@@ -20432,7 +20435,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ91">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR91">
         <v>1.67</v>
@@ -22695,7 +22698,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ102">
         <v>1.1</v>
@@ -24552,7 +24555,7 @@
         <v>0.84</v>
       </c>
       <c r="AQ111">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR111">
         <v>1.52</v>
@@ -27436,7 +27439,7 @@
         <v>2.26</v>
       </c>
       <c r="AQ125">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR125">
         <v>1.36</v>
@@ -28669,7 +28672,7 @@
         <v>1.2</v>
       </c>
       <c r="AP131">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ131">
         <v>0.95</v>
@@ -30732,7 +30735,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ141">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR141">
         <v>1.62</v>
@@ -32789,7 +32792,7 @@
         <v>0.57</v>
       </c>
       <c r="AP151">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ151">
         <v>0.53</v>
@@ -34852,7 +34855,7 @@
         <v>2.32</v>
       </c>
       <c r="AQ161">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR161">
         <v>1.67</v>
@@ -36909,7 +36912,7 @@
         <v>1.38</v>
       </c>
       <c r="AP171">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ171">
         <v>1.05</v>
@@ -37115,7 +37118,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ172">
         <v>1.16</v>
@@ -38972,7 +38975,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ181">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR181">
         <v>1.41</v>
@@ -43295,7 +43298,7 @@
         <v>2.1</v>
       </c>
       <c r="AP202">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ202">
         <v>2</v>
@@ -44946,7 +44949,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ210">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR210">
         <v>1.56</v>
@@ -46179,7 +46182,7 @@
         <v>1.2</v>
       </c>
       <c r="AP216">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ216">
         <v>1.05</v>
@@ -48448,7 +48451,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ227">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR227">
         <v>1.29</v>
@@ -50917,7 +50920,7 @@
         <v>1.82</v>
       </c>
       <c r="AP239">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ239">
         <v>1.67</v>
@@ -54010,7 +54013,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ254">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR254">
         <v>1.42</v>
@@ -57509,7 +57512,7 @@
         <v>0.83</v>
       </c>
       <c r="AP271">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ271">
         <v>1.11</v>
@@ -59572,7 +59575,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ281">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR281">
         <v>1.38</v>
@@ -59981,7 +59984,7 @@
         <v>0.93</v>
       </c>
       <c r="AP283">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ283">
         <v>1</v>
@@ -63280,7 +63283,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ299">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR299">
         <v>1.31</v>
@@ -65749,7 +65752,7 @@
         <v>1.13</v>
       </c>
       <c r="AP311">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ311">
         <v>1.15</v>
@@ -67812,7 +67815,7 @@
         <v>2.05</v>
       </c>
       <c r="AQ321">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR321">
         <v>1.92</v>
@@ -68839,7 +68842,7 @@
         <v>1.06</v>
       </c>
       <c r="AP326">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ326">
         <v>1.11</v>
@@ -70284,7 +70287,7 @@
         <v>1.84</v>
       </c>
       <c r="AQ333">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR333">
         <v>1.37</v>
@@ -70487,7 +70490,7 @@
         <v>0.75</v>
       </c>
       <c r="AP334">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ334">
         <v>0.63</v>
@@ -75228,7 +75231,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ357">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR357">
         <v>1.41</v>
@@ -75637,7 +75640,7 @@
         <v>0.72</v>
       </c>
       <c r="AP359">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AQ359">
         <v>0.68</v>
@@ -78936,7 +78939,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ375">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="AR375">
         <v>1.4</v>
@@ -82023,10 +82026,10 @@
         <v>1.11</v>
       </c>
       <c r="AP390">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AQ390">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AR390">
         <v>1.36</v>
@@ -82102,6 +82105,212 @@
       </c>
       <c r="BP390">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="391" spans="1:68">
+      <c r="A391" s="1">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>7899321</v>
+      </c>
+      <c r="C391" t="s">
+        <v>68</v>
+      </c>
+      <c r="D391" t="s">
+        <v>69</v>
+      </c>
+      <c r="E391" s="2">
+        <v>45830.64583333334</v>
+      </c>
+      <c r="F391">
+        <v>0</v>
+      </c>
+      <c r="G391" t="s">
+        <v>74</v>
+      </c>
+      <c r="H391" t="s">
+        <v>81</v>
+      </c>
+      <c r="I391">
+        <v>0</v>
+      </c>
+      <c r="J391">
+        <v>1</v>
+      </c>
+      <c r="K391">
+        <v>1</v>
+      </c>
+      <c r="L391">
+        <v>0</v>
+      </c>
+      <c r="M391">
+        <v>2</v>
+      </c>
+      <c r="N391">
+        <v>2</v>
+      </c>
+      <c r="O391" t="s">
+        <v>102</v>
+      </c>
+      <c r="P391" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q391">
+        <v>2.65</v>
+      </c>
+      <c r="R391">
+        <v>2.1</v>
+      </c>
+      <c r="S391">
+        <v>3.9</v>
+      </c>
+      <c r="T391">
+        <v>1.42</v>
+      </c>
+      <c r="U391">
+        <v>2.7</v>
+      </c>
+      <c r="V391">
+        <v>2.9</v>
+      </c>
+      <c r="W391">
+        <v>1.36</v>
+      </c>
+      <c r="X391">
+        <v>7</v>
+      </c>
+      <c r="Y391">
+        <v>1.06</v>
+      </c>
+      <c r="Z391">
+        <v>2.34</v>
+      </c>
+      <c r="AA391">
+        <v>3.23</v>
+      </c>
+      <c r="AB391">
+        <v>2.99</v>
+      </c>
+      <c r="AC391">
+        <v>1.05</v>
+      </c>
+      <c r="AD391">
+        <v>8</v>
+      </c>
+      <c r="AE391">
+        <v>1.37</v>
+      </c>
+      <c r="AF391">
+        <v>2.8</v>
+      </c>
+      <c r="AG391">
+        <v>2.15</v>
+      </c>
+      <c r="AH391">
+        <v>1.6</v>
+      </c>
+      <c r="AI391">
+        <v>1.79</v>
+      </c>
+      <c r="AJ391">
+        <v>1.89</v>
+      </c>
+      <c r="AK391">
+        <v>1.27</v>
+      </c>
+      <c r="AL391">
+        <v>1.32</v>
+      </c>
+      <c r="AM391">
+        <v>1.74</v>
+      </c>
+      <c r="AN391">
+        <v>1.08</v>
+      </c>
+      <c r="AO391">
+        <v>1.13</v>
+      </c>
+      <c r="AP391">
+        <v>1.05</v>
+      </c>
+      <c r="AQ391">
+        <v>1.18</v>
+      </c>
+      <c r="AR391">
+        <v>1.46</v>
+      </c>
+      <c r="AS391">
+        <v>1.36</v>
+      </c>
+      <c r="AT391">
+        <v>2.82</v>
+      </c>
+      <c r="AU391">
+        <v>3</v>
+      </c>
+      <c r="AV391">
+        <v>8</v>
+      </c>
+      <c r="AW391">
+        <v>2</v>
+      </c>
+      <c r="AX391">
+        <v>0</v>
+      </c>
+      <c r="AY391">
+        <v>5</v>
+      </c>
+      <c r="AZ391">
+        <v>8</v>
+      </c>
+      <c r="BA391">
+        <v>3</v>
+      </c>
+      <c r="BB391">
+        <v>5</v>
+      </c>
+      <c r="BC391">
+        <v>8</v>
+      </c>
+      <c r="BD391">
+        <v>1.61</v>
+      </c>
+      <c r="BE391">
+        <v>6.4</v>
+      </c>
+      <c r="BF391">
+        <v>2.55</v>
+      </c>
+      <c r="BG391">
+        <v>1.42</v>
+      </c>
+      <c r="BH391">
+        <v>2.65</v>
+      </c>
+      <c r="BI391">
+        <v>1.71</v>
+      </c>
+      <c r="BJ391">
+        <v>2</v>
+      </c>
+      <c r="BK391">
+        <v>2.12</v>
+      </c>
+      <c r="BL391">
+        <v>1.63</v>
+      </c>
+      <c r="BM391">
+        <v>2.7</v>
+      </c>
+      <c r="BN391">
+        <v>1.38</v>
+      </c>
+      <c r="BO391">
+        <v>3.65</v>
+      </c>
+      <c r="BP391">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
